--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$105</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$78</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,11 +36,11 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Inicial: 01/08/2025, Data Final: 25/05/2026</t>
+      <t>Data Inicial: 01/08/2025, Data Final: 25/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
     </r>
   </si>
   <si>
-    <t>Relatório exportado em segunda-feira, 18 de maio de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em quinta-feira, 21 de maio de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -109,24 +109,24 @@
     <t>VENCIDO ENTRE 31 A 90 DIAS</t>
   </si>
   <si>
+    <t>FA-11069</t>
+  </si>
+  <si>
+    <t>ALBERTO MANOEL DOS REIS</t>
+  </si>
+  <si>
+    <t>VENCIDO</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>ATIVUZ VEÍCULOS</t>
+  </si>
+  <si>
     <t>VENCIDO ATÉ 30 DIAS</t>
   </si>
   <si>
-    <t>FA-11069</t>
-  </si>
-  <si>
-    <t>ALBERTO MANOEL DOS REIS</t>
-  </si>
-  <si>
-    <t>VENCIDO</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>ATIVUZ VEÍCULOS</t>
-  </si>
-  <si>
     <t>ND-11305</t>
   </si>
   <si>
@@ -151,12 +151,6 @@
     <t>NOTA DE DÉBITO</t>
   </si>
   <si>
-    <t>1.3 UBER SUPPLIER</t>
-  </si>
-  <si>
-    <t>FA-11183</t>
-  </si>
-  <si>
     <t>FA-11446</t>
   </si>
   <si>
@@ -169,187 +163,277 @@
     <t>JOÃO PAULO CONSÓRCIOS</t>
   </si>
   <si>
-    <t>FA-11452</t>
+    <t>FA-11410</t>
+  </si>
+  <si>
+    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11356</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11553</t>
+  </si>
+  <si>
+    <t>YURI BATISTA DA COSTA</t>
+  </si>
+  <si>
+    <t>FA-11424</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11351</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11587</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11114</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11355</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11618</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>VENCIDO ACIMA DE 90 DIAS</t>
+  </si>
+  <si>
+    <t>ND-10427</t>
+  </si>
+  <si>
+    <t>FA-11557</t>
+  </si>
+  <si>
+    <t>FA-11471</t>
   </si>
   <si>
     <t>YAGO ELIAS COSTA BATISTA</t>
   </si>
   <si>
-    <t>FA-11410</t>
-  </si>
-  <si>
-    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+    <t>FA-11399</t>
+  </si>
+  <si>
+    <t>FA-11473</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11478</t>
+  </si>
+  <si>
+    <t>FA-11496</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>FA-11614</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11453</t>
+  </si>
+  <si>
+    <t>FA-11390</t>
+  </si>
+  <si>
+    <t>FA-11458</t>
+  </si>
+  <si>
+    <t>FA-11615</t>
+  </si>
+  <si>
+    <t>FA-11396</t>
+  </si>
+  <si>
+    <t>FA-11525</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
+    <t>FA-11497</t>
+  </si>
+  <si>
+    <t>FA-11466</t>
+  </si>
+  <si>
+    <t>FA-11474</t>
+  </si>
+  <si>
+    <t>FA-11560</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11481</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11402</t>
+  </si>
+  <si>
+    <t>FA-11616</t>
+  </si>
+  <si>
+    <t>FA-11667</t>
+  </si>
+  <si>
+    <t>FA-11620</t>
+  </si>
+  <si>
+    <t>FA-11482</t>
+  </si>
+  <si>
+    <t>FA-11483</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11484</t>
+  </si>
+  <si>
+    <t>FA-11561</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11479</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
   </si>
   <si>
     <t>FA-11461</t>
   </si>
   <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11356</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
+    <t>FA-11279</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11476</t>
+  </si>
+  <si>
+    <t>FA-11611</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
   </si>
   <si>
     <t>FA-11464</t>
   </si>
   <si>
-    <t>FA-11553</t>
-  </si>
-  <si>
-    <t>YURI BATISTA DA COSTA</t>
-  </si>
-  <si>
-    <t>FA-11424</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-11468</t>
-  </si>
-  <si>
-    <t>FA-11351</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11587</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11114</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11355</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11618</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>VENCIDO ACIMA DE 90 DIAS</t>
-  </si>
-  <si>
-    <t>ND-10427</t>
-  </si>
-  <si>
-    <t>FA-11497</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>FA-11522</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11471</t>
-  </si>
-  <si>
-    <t>FA-11557</t>
-  </si>
-  <si>
-    <t>FA-11556</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11476</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11399</t>
-  </si>
-  <si>
-    <t>FA-11473</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11278</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11475</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11558</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11478</t>
-  </si>
-  <si>
-    <t>FA-11472</t>
-  </si>
-  <si>
-    <t>FA-11496</t>
-  </si>
-  <si>
-    <t>FA-11614</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11453</t>
-  </si>
-  <si>
-    <t>FA-11390</t>
-  </si>
-  <si>
-    <t>FA-11458</t>
-  </si>
-  <si>
-    <t>FA-11615</t>
-  </si>
-  <si>
-    <t>FA-11396</t>
-  </si>
-  <si>
-    <t>HOJE</t>
-  </si>
-  <si>
-    <t>FA-11654</t>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-11480</t>
+  </si>
+  <si>
+    <t>FA-11562</t>
+  </si>
+  <si>
+    <t>FA-11563</t>
+  </si>
+  <si>
+    <t>FA-11487</t>
+  </si>
+  <si>
+    <t>FA-11494</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11617</t>
+  </si>
+  <si>
+    <t>FA-11668</t>
+  </si>
+  <si>
+    <t>FA-11621</t>
+  </si>
+  <si>
+    <t>FA-11656</t>
   </si>
   <si>
     <t>LUCA ZOLI</t>
   </si>
   <si>
-    <t>Z. FROTA INVESTIDORES - LUZ DIVINA</t>
-  </si>
-  <si>
-    <t>FA-11642</t>
+    <t>FA-11504</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11488</t>
+  </si>
+  <si>
+    <t>FA-11280</t>
+  </si>
+  <si>
+    <t>FA-11434</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11412</t>
+  </si>
+  <si>
+    <t>FA-11489</t>
+  </si>
+  <si>
+    <t>FA-11491</t>
+  </si>
+  <si>
+    <t>FA-11564</t>
+  </si>
+  <si>
+    <t>FA-11329</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-11644</t>
   </si>
   <si>
     <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
@@ -358,208 +442,10 @@
     <t>PÚBLICO</t>
   </si>
   <si>
-    <t>FA-11466</t>
-  </si>
-  <si>
-    <t>FA-11400</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11525</t>
-  </si>
-  <si>
-    <t>FA-11474</t>
-  </si>
-  <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
-    <t>FA-11481</t>
-  </si>
-  <si>
-    <t>FA-11560</t>
-  </si>
-  <si>
-    <t>FA-11402</t>
-  </si>
-  <si>
-    <t>FA-11401</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11526</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11616</t>
-  </si>
-  <si>
-    <t>FA-11493</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11279</t>
-  </si>
-  <si>
-    <t>FA-11482</t>
-  </si>
-  <si>
-    <t>FA-11620</t>
-  </si>
-  <si>
-    <t>FA-11503</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11433</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11411</t>
-  </si>
-  <si>
-    <t>FA-11484</t>
-  </si>
-  <si>
-    <t>FA-11561</t>
-  </si>
-  <si>
-    <t>FA-11483</t>
-  </si>
-  <si>
-    <t>FA-11268</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11479</t>
-  </si>
-  <si>
-    <t>FA-11328</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>FA-11535</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t>FA-11600</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>FA-11630</t>
+    <t>FA-11632</t>
   </si>
   <si>
     <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11590</t>
-  </si>
-  <si>
-    <t>FA-11577</t>
-  </si>
-  <si>
-    <t>ADRIANO TEOTONIO DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11611</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>FA-11480</t>
-  </si>
-  <si>
-    <t>FA-11562</t>
-  </si>
-  <si>
-    <t>FA-11487</t>
-  </si>
-  <si>
-    <t>FA-11563</t>
-  </si>
-  <si>
-    <t>FA-11494</t>
-  </si>
-  <si>
-    <t>FA-11617</t>
-  </si>
-  <si>
-    <t>FA-11280</t>
-  </si>
-  <si>
-    <t>FA-11488</t>
-  </si>
-  <si>
-    <t>FA-11656</t>
-  </si>
-  <si>
-    <t>FA-11504</t>
-  </si>
-  <si>
-    <t>FA-11621</t>
-  </si>
-  <si>
-    <t>FA-11434</t>
-  </si>
-  <si>
-    <t>FA-11412</t>
-  </si>
-  <si>
-    <t>FA-11491</t>
-  </si>
-  <si>
-    <t>FA-11564</t>
-  </si>
-  <si>
-    <t>FA-11489</t>
-  </si>
-  <si>
-    <t>FA-11329</t>
-  </si>
-  <si>
-    <t>FA-11536</t>
-  </si>
-  <si>
-    <t>FA-11601</t>
-  </si>
-  <si>
-    <t>FA-11578</t>
-  </si>
-  <si>
-    <t>FA-11644</t>
-  </si>
-  <si>
-    <t>FA-11591</t>
-  </si>
-  <si>
-    <t>FA-11632</t>
   </si>
   <si>
     <t>FA-11613</t>
@@ -711,7 +597,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S111"/>
+  <dimension ref="A1:S84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -828,43 +714,43 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-42</v>
+        <v>-45</v>
       </c>
       <c r="G6" s="8">
-        <v>-28</v>
+        <v>-31</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
       </c>
       <c r="I6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="K6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="M6" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="O6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="P6" s="6" t="s">
+      <c r="Q6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R6" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="Q6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R6" s="6" t="s">
-        <v>30</v>
       </c>
       <c r="S6" s="9">
         <v>91.54</v>
@@ -887,16 +773,16 @@
         <v>23</v>
       </c>
       <c r="F7" s="8">
-        <v>-35</v>
+        <v>-38</v>
       </c>
       <c r="G7" s="8">
-        <v>-26</v>
+        <v>-29</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>24</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>31</v>
@@ -911,10 +797,10 @@
         <v>23</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P7" s="6" t="s">
         <v>23</v>
@@ -946,16 +832,16 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-35</v>
+        <v>-38</v>
       </c>
       <c r="G8" s="8">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J8" s="6" t="s">
         <v>34</v>
@@ -970,10 +856,10 @@
         <v>23</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P8" s="6" t="s">
         <v>23</v>
@@ -982,7 +868,7 @@
         <v>23</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S8" s="9">
         <v>302.72</v>
@@ -1005,16 +891,16 @@
         <v>46127</v>
       </c>
       <c r="F9" s="8">
-        <v>-21</v>
+        <v>-24</v>
       </c>
       <c r="G9" s="8">
-        <v>-21</v>
+        <v>-24</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>36</v>
@@ -1023,25 +909,25 @@
         <v>23</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P9" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="P9" s="6" t="s">
-        <v>29</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S9" s="9">
         <v>97.15</v>
@@ -1064,16 +950,16 @@
         <v>46097</v>
       </c>
       <c r="F10" s="8">
-        <v>-21</v>
+        <v>-24</v>
       </c>
       <c r="G10" s="8">
-        <v>-21</v>
+        <v>-24</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>31</v>
@@ -1088,10 +974,10 @@
         <v>23</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>23</v>
@@ -1123,16 +1009,16 @@
         <v>23</v>
       </c>
       <c r="F11" s="8">
-        <v>-28</v>
+        <v>-31</v>
       </c>
       <c r="G11" s="8">
-        <v>-20</v>
+        <v>-23</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>31</v>
@@ -1147,10 +1033,10 @@
         <v>23</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>23</v>
@@ -1167,34 +1053,34 @@
     </row>
     <row r="12" ht="23" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B12" s="7">
         <v>46140</v>
       </c>
       <c r="C12" s="7">
-        <v>46118</v>
+        <v>46125</v>
       </c>
       <c r="D12" s="7">
-        <v>46111</v>
+        <v>46125</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F12" s="8">
-        <v>-49</v>
+        <v>-38</v>
       </c>
       <c r="G12" s="8">
-        <v>-20</v>
+        <v>-23</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>24</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>23</v>
@@ -1206,10 +1092,10 @@
         <v>23</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>23</v>
@@ -1221,7 +1107,7 @@
         <v>33</v>
       </c>
       <c r="S12" s="9">
-        <v>275.41</v>
+        <v>408.24</v>
       </c>
     </row>
     <row r="13" ht="23" customHeight="1">
@@ -1229,58 +1115,58 @@
         <v>22</v>
       </c>
       <c r="B13" s="7">
-        <v>46140</v>
+        <v>46146</v>
       </c>
       <c r="C13" s="7">
-        <v>46125</v>
+        <v>46113</v>
       </c>
       <c r="D13" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>23</v>
+        <v>46150</v>
+      </c>
+      <c r="E13" s="7">
+        <v>46141</v>
       </c>
       <c r="F13" s="8">
-        <v>-35</v>
+        <v>-13</v>
       </c>
       <c r="G13" s="8">
-        <v>-20</v>
+        <v>-17</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>32</v>
-      </c>
       <c r="M13" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P13" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="S13" s="9">
-        <v>408.24</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="14" ht="23" customHeight="1">
@@ -1291,55 +1177,55 @@
         <v>46146</v>
       </c>
       <c r="C14" s="7">
-        <v>46113</v>
+        <v>46153</v>
       </c>
       <c r="D14" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E14" s="7">
-        <v>46141</v>
+        <v>46153</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F14" s="8">
         <v>-10</v>
       </c>
       <c r="G14" s="8">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="S14" s="9">
-        <v>12.9</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="15" ht="23" customHeight="1">
@@ -1350,43 +1236,43 @@
         <v>46146</v>
       </c>
       <c r="C15" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="D15" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="8">
-        <v>-28</v>
+        <v>-17</v>
       </c>
       <c r="G15" s="8">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>23</v>
@@ -1395,10 +1281,10 @@
         <v>23</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="S15" s="9">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" ht="23" customHeight="1">
@@ -1409,55 +1295,55 @@
         <v>46146</v>
       </c>
       <c r="C16" s="7">
-        <v>46153</v>
+        <v>46082</v>
       </c>
       <c r="D16" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>23</v>
+        <v>46146</v>
+      </c>
+      <c r="E16" s="7">
+        <v>46097</v>
       </c>
       <c r="F16" s="8">
-        <v>-7</v>
+        <v>-17</v>
       </c>
       <c r="G16" s="8">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S16" s="9">
-        <v>61.21</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="17" ht="23" customHeight="1">
@@ -1477,34 +1363,34 @@
         <v>23</v>
       </c>
       <c r="F17" s="8">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="G17" s="8">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P17" s="6" t="s">
         <v>23</v>
@@ -1513,10 +1399,10 @@
         <v>23</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S17" s="9">
-        <v>120</v>
+        <v>205.82</v>
       </c>
     </row>
     <row r="18" ht="23" customHeight="1">
@@ -1527,55 +1413,55 @@
         <v>46146</v>
       </c>
       <c r="C18" s="7">
-        <v>46082</v>
+        <v>46146</v>
       </c>
       <c r="D18" s="7">
         <v>46146</v>
       </c>
       <c r="E18" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F18" s="8">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="G18" s="8">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S18" s="9">
-        <v>146.55</v>
+        <v>620</v>
       </c>
     </row>
     <row r="19" ht="23" customHeight="1">
@@ -1586,25 +1472,25 @@
         <v>46146</v>
       </c>
       <c r="C19" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="D19" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>-21</v>
+        <v>-31</v>
       </c>
       <c r="G19" s="8">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>49</v>
@@ -1619,22 +1505,22 @@
         <v>23</v>
       </c>
       <c r="N19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="Q19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R19" s="6" t="s">
-        <v>30</v>
-      </c>
       <c r="S19" s="9">
-        <v>150</v>
+        <v>655.21</v>
       </c>
     </row>
     <row r="20" ht="23" customHeight="1">
@@ -1642,28 +1528,28 @@
         <v>22</v>
       </c>
       <c r="B20" s="7">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="C20" s="7">
-        <v>46146</v>
+        <v>46139</v>
       </c>
       <c r="D20" s="7">
-        <v>46146</v>
+        <v>46139</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F20" s="8">
-        <v>-14</v>
+        <v>-24</v>
       </c>
       <c r="G20" s="8">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>51</v>
@@ -1678,10 +1564,10 @@
         <v>23</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>23</v>
@@ -1690,10 +1576,10 @@
         <v>23</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S20" s="9">
-        <v>205.82</v>
+        <v>103.36</v>
       </c>
     </row>
     <row r="21" ht="23" customHeight="1">
@@ -1701,28 +1587,28 @@
         <v>22</v>
       </c>
       <c r="B21" s="7">
-        <v>46146</v>
+        <v>46149</v>
       </c>
       <c r="C21" s="7">
-        <v>46146</v>
+        <v>46142</v>
       </c>
       <c r="D21" s="7">
-        <v>46146</v>
+        <v>46142</v>
       </c>
       <c r="E21" s="7">
-        <v>46119</v>
+        <v>46148</v>
       </c>
       <c r="F21" s="8">
-        <v>-14</v>
+        <v>-21</v>
       </c>
       <c r="G21" s="8">
         <v>-14</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>53</v>
@@ -1731,16 +1617,16 @@
         <v>23</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="N21" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>23</v>
@@ -1749,10 +1635,10 @@
         <v>37</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="S21" s="9">
-        <v>600</v>
+        <v>685.71</v>
       </c>
     </row>
     <row r="22" ht="23" customHeight="1">
@@ -1760,58 +1646,58 @@
         <v>22</v>
       </c>
       <c r="B22" s="7">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="C22" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="D22" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E22" s="7">
-        <v>46141</v>
+        <v>46125</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F22" s="8">
-        <v>-14</v>
+        <v>-38</v>
       </c>
       <c r="G22" s="8">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S22" s="9">
-        <v>620</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
@@ -1819,46 +1705,46 @@
         <v>22</v>
       </c>
       <c r="B23" s="7">
+        <v>46150</v>
+      </c>
+      <c r="C23" s="7">
         <v>46146</v>
       </c>
-      <c r="C23" s="7">
-        <v>46132</v>
-      </c>
       <c r="D23" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F23" s="8">
-        <v>-28</v>
+        <v>-17</v>
       </c>
       <c r="G23" s="8">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N23" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P23" s="6" t="s">
         <v>23</v>
@@ -1867,10 +1753,10 @@
         <v>23</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S23" s="9">
-        <v>655.21</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
@@ -1878,58 +1764,58 @@
         <v>22</v>
       </c>
       <c r="B24" s="7">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="C24" s="7">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D24" s="7">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="E24" s="7">
-        <v>46119</v>
+        <v>46153</v>
       </c>
       <c r="F24" s="8">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="G24" s="8">
-        <v>-14</v>
+        <v>-13</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q24" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S24" s="9">
-        <v>700</v>
+        <v>278.57</v>
       </c>
     </row>
     <row r="25" ht="23" customHeight="1">
@@ -1937,46 +1823,46 @@
         <v>22</v>
       </c>
       <c r="B25" s="7">
-        <v>46147</v>
+        <v>46153</v>
       </c>
       <c r="C25" s="7">
-        <v>46139</v>
+        <v>45901</v>
       </c>
       <c r="D25" s="7">
-        <v>46139</v>
+        <v>45938</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F25" s="8">
-        <v>-21</v>
+        <v>-225</v>
       </c>
       <c r="G25" s="8">
-        <v>-13</v>
+        <v>-10</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J25" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K25" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="M25" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P25" s="6" t="s">
         <v>23</v>
@@ -1985,10 +1871,10 @@
         <v>23</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S25" s="9">
-        <v>103.36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" ht="23" customHeight="1">
@@ -1996,58 +1882,58 @@
         <v>22</v>
       </c>
       <c r="B26" s="7">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="C26" s="7">
-        <v>46142</v>
+        <v>46082</v>
       </c>
       <c r="D26" s="7">
-        <v>46142</v>
+        <v>46153</v>
       </c>
       <c r="E26" s="7">
-        <v>46148</v>
+        <v>46097</v>
       </c>
       <c r="F26" s="8">
-        <v>-18</v>
+        <v>-10</v>
       </c>
       <c r="G26" s="8">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="S26" s="9">
-        <v>685.71</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
@@ -2055,28 +1941,28 @@
         <v>22</v>
       </c>
       <c r="B27" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C27" s="7">
-        <v>46125</v>
+        <v>46153</v>
       </c>
       <c r="D27" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E27" s="7">
+        <v>46141</v>
       </c>
       <c r="F27" s="8">
-        <v>-35</v>
+        <v>-10</v>
       </c>
       <c r="G27" s="8">
         <v>-10</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>64</v>
@@ -2085,28 +1971,28 @@
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S27" s="9">
-        <v>53.82</v>
+        <v>310</v>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
@@ -2114,58 +2000,58 @@
         <v>22</v>
       </c>
       <c r="B28" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C28" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D28" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E28" s="7">
+        <v>46119</v>
       </c>
       <c r="F28" s="8">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="G28" s="8">
         <v>-10</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J28" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="K28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>67</v>
-      </c>
       <c r="M28" s="6" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S28" s="9">
-        <v>170</v>
+        <v>600</v>
       </c>
     </row>
     <row r="29" ht="23" customHeight="1">
@@ -2173,16 +2059,16 @@
         <v>22</v>
       </c>
       <c r="B29" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="C29" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="D29" s="7">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="E29" s="7">
-        <v>46153</v>
+        <v>46112</v>
       </c>
       <c r="F29" s="8">
         <v>-10</v>
@@ -2191,28 +2077,28 @@
         <v>-10</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>23</v>
@@ -2221,10 +2107,10 @@
         <v>37</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S29" s="9">
-        <v>278.57</v>
+        <v>630</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -2235,55 +2121,55 @@
         <v>46153</v>
       </c>
       <c r="C30" s="7">
-        <v>45901</v>
+        <v>46153</v>
       </c>
       <c r="D30" s="7">
-        <v>45938</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E30" s="7">
+        <v>46119</v>
       </c>
       <c r="F30" s="8">
-        <v>-222</v>
+        <v>-10</v>
       </c>
       <c r="G30" s="8">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S30" s="9">
-        <v>30</v>
+        <v>650</v>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1">
@@ -2294,28 +2180,28 @@
         <v>46153</v>
       </c>
       <c r="C31" s="7">
-        <v>46082</v>
+        <v>46153</v>
       </c>
       <c r="D31" s="7">
         <v>46153</v>
       </c>
       <c r="E31" s="7">
-        <v>46097</v>
+        <v>46119</v>
       </c>
       <c r="F31" s="8">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="G31" s="8">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>23</v>
@@ -2327,22 +2213,22 @@
         <v>23</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P31" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>33</v>
       </c>
       <c r="S31" s="9">
-        <v>146.55</v>
+        <v>680</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
@@ -2350,46 +2236,46 @@
         <v>22</v>
       </c>
       <c r="B32" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C32" s="7">
-        <v>46139</v>
+        <v>46125</v>
       </c>
       <c r="D32" s="7">
-        <v>46132</v>
+        <v>46125</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F32" s="8">
-        <v>-28</v>
+        <v>-38</v>
       </c>
       <c r="G32" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J32" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="K32" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="M32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>23</v>
@@ -2401,7 +2287,7 @@
         <v>33</v>
       </c>
       <c r="S32" s="9">
-        <v>450</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
@@ -2409,58 +2295,58 @@
         <v>22</v>
       </c>
       <c r="B33" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C33" s="7">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D33" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E33" s="7">
-        <v>46127</v>
+        <v>46146</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F33" s="8">
-        <v>-7</v>
+        <v>-17</v>
       </c>
       <c r="G33" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J33" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="K33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>75</v>
-      </c>
       <c r="M33" s="6" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S33" s="9">
-        <v>600</v>
+        <v>280</v>
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
@@ -2468,58 +2354,58 @@
         <v>22</v>
       </c>
       <c r="B34" s="7">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="C34" s="7">
-        <v>46153</v>
+        <v>46132</v>
       </c>
       <c r="D34" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E34" s="7">
-        <v>46119</v>
+        <v>46132</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F34" s="8">
-        <v>-7</v>
+        <v>-31</v>
       </c>
       <c r="G34" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S34" s="9">
-        <v>600</v>
+        <v>317.54</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2527,58 +2413,58 @@
         <v>22</v>
       </c>
       <c r="B35" s="7">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="C35" s="7">
-        <v>46153</v>
+        <v>46132</v>
       </c>
       <c r="D35" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E35" s="7">
-        <v>46141</v>
+        <v>46132</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F35" s="8">
-        <v>-7</v>
+        <v>-31</v>
       </c>
       <c r="G35" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S35" s="9">
-        <v>620</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2586,58 +2472,58 @@
         <v>22</v>
       </c>
       <c r="B36" s="7">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="C36" s="7">
-        <v>46153</v>
+        <v>46139</v>
       </c>
       <c r="D36" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E36" s="7">
-        <v>46141</v>
+        <v>46139</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-7</v>
+        <v>-24</v>
       </c>
       <c r="G36" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S36" s="9">
-        <v>620</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2645,7 +2531,7 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="C37" s="7">
         <v>46153</v>
@@ -2653,50 +2539,50 @@
       <c r="D37" s="7">
         <v>46153</v>
       </c>
-      <c r="E37" s="7">
-        <v>46119</v>
+      <c r="E37" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F37" s="8">
-        <v>-7</v>
+        <v>-10</v>
       </c>
       <c r="G37" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S37" s="9">
-        <v>620</v>
+        <v>530</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2704,31 +2590,31 @@
         <v>22</v>
       </c>
       <c r="B38" s="7">
-        <v>46153</v>
+        <v>46156</v>
       </c>
       <c r="C38" s="7">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D38" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E38" s="7">
-        <v>46112</v>
+        <v>46146</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-7</v>
+        <v>-17</v>
       </c>
       <c r="G38" s="8">
         <v>-7</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
@@ -2740,22 +2626,22 @@
         <v>23</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S38" s="9">
-        <v>630</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2763,58 +2649,58 @@
         <v>22</v>
       </c>
       <c r="B39" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C39" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D39" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E39" s="7">
-        <v>46119</v>
+        <v>46160</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F39" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="G39" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S39" s="9">
-        <v>650</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
@@ -2822,58 +2708,58 @@
         <v>22</v>
       </c>
       <c r="B40" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C40" s="7">
-        <v>46153</v>
+        <v>46082</v>
       </c>
       <c r="D40" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E40" s="7">
-        <v>46092</v>
+        <v>46097</v>
       </c>
       <c r="F40" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="G40" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S40" s="9">
-        <v>650</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
@@ -2881,46 +2767,46 @@
         <v>22</v>
       </c>
       <c r="B41" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C41" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D41" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E41" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F41" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="G41" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>23</v>
@@ -2929,10 +2815,10 @@
         <v>37</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S41" s="9">
-        <v>680</v>
+        <v>172</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
@@ -2940,46 +2826,46 @@
         <v>22</v>
       </c>
       <c r="B42" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C42" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D42" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E42" s="7">
         <v>46141</v>
       </c>
       <c r="F42" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="G42" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>23</v>
@@ -2988,10 +2874,10 @@
         <v>37</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S42" s="9">
-        <v>680</v>
+        <v>310</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
@@ -2999,58 +2885,58 @@
         <v>22</v>
       </c>
       <c r="B43" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C43" s="7">
-        <v>46153</v>
+        <v>46139</v>
       </c>
       <c r="D43" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E43" s="7">
-        <v>46119</v>
+        <v>46132</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F43" s="8">
-        <v>-7</v>
+        <v>-31</v>
       </c>
       <c r="G43" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>33</v>
       </c>
       <c r="S43" s="9">
-        <v>680</v>
+        <v>350</v>
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
@@ -3058,58 +2944,58 @@
         <v>22</v>
       </c>
       <c r="B44" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C44" s="7">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D44" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E44" s="7">
-        <v>46119</v>
+        <v>46146</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F44" s="8">
-        <v>-7</v>
+        <v>-17</v>
       </c>
       <c r="G44" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R44" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="Q44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R44" s="6" t="s">
-        <v>30</v>
-      </c>
       <c r="S44" s="9">
-        <v>700</v>
+        <v>450</v>
       </c>
     </row>
     <row r="45" ht="23" customHeight="1">
@@ -3117,58 +3003,58 @@
         <v>22</v>
       </c>
       <c r="B45" s="7">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="C45" s="7">
-        <v>46125</v>
+        <v>46160</v>
       </c>
       <c r="D45" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E45" s="7">
+        <v>46119</v>
       </c>
       <c r="F45" s="8">
-        <v>-35</v>
+        <v>-3</v>
       </c>
       <c r="G45" s="8">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S45" s="9">
-        <v>150</v>
+        <v>600</v>
       </c>
     </row>
     <row r="46" ht="23" customHeight="1">
@@ -3176,58 +3062,58 @@
         <v>22</v>
       </c>
       <c r="B46" s="7">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="C46" s="7">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="D46" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E46" s="7">
+        <v>46141</v>
       </c>
       <c r="F46" s="8">
-        <v>-14</v>
+        <v>-3</v>
       </c>
       <c r="G46" s="8">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S46" s="9">
-        <v>280</v>
+        <v>620</v>
       </c>
     </row>
     <row r="47" ht="23" customHeight="1">
@@ -3235,58 +3121,58 @@
         <v>22</v>
       </c>
       <c r="B47" s="7">
-        <v>46154</v>
+        <v>46160</v>
       </c>
       <c r="C47" s="7">
-        <v>46132</v>
+        <v>46160</v>
       </c>
       <c r="D47" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E47" s="7">
+        <v>46119</v>
       </c>
       <c r="F47" s="8">
-        <v>-28</v>
+        <v>-3</v>
       </c>
       <c r="G47" s="8">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S47" s="9">
-        <v>317.54</v>
+        <v>620</v>
       </c>
     </row>
     <row r="48" ht="23" customHeight="1">
@@ -3294,31 +3180,31 @@
         <v>22</v>
       </c>
       <c r="B48" s="7">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="C48" s="7">
-        <v>46132</v>
+        <v>46160</v>
       </c>
       <c r="D48" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E48" s="7">
+        <v>46112</v>
       </c>
       <c r="F48" s="8">
-        <v>-28</v>
+        <v>-3</v>
       </c>
       <c r="G48" s="8">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
@@ -3330,22 +3216,22 @@
         <v>23</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S48" s="9">
-        <v>140</v>
+        <v>630</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
@@ -3353,58 +3239,58 @@
         <v>22</v>
       </c>
       <c r="B49" s="7">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="C49" s="7">
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="D49" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E49" s="7">
+        <v>46150</v>
       </c>
       <c r="F49" s="8">
-        <v>-21</v>
+        <v>-3</v>
       </c>
       <c r="G49" s="8">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S49" s="9">
-        <v>250</v>
+        <v>630</v>
       </c>
     </row>
     <row r="50" ht="23" customHeight="1">
@@ -3412,58 +3298,58 @@
         <v>22</v>
       </c>
       <c r="B50" s="7">
-        <v>46155</v>
+        <v>46160</v>
       </c>
       <c r="C50" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D50" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E50" s="7">
+        <v>46163</v>
       </c>
       <c r="F50" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="G50" s="8">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S50" s="9">
-        <v>530</v>
+        <v>630</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
@@ -3471,58 +3357,58 @@
         <v>22</v>
       </c>
       <c r="B51" s="7">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="C51" s="7">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="D51" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E51" s="7">
+        <v>46153</v>
       </c>
       <c r="F51" s="8">
-        <v>-14</v>
+        <v>-3</v>
       </c>
       <c r="G51" s="8">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S51" s="9">
-        <v>130</v>
+        <v>650</v>
       </c>
     </row>
     <row r="52" ht="23" customHeight="1">
@@ -3538,50 +3424,50 @@
       <c r="D52" s="7">
         <v>46160</v>
       </c>
-      <c r="E52" s="7" t="s">
-        <v>23</v>
+      <c r="E52" s="7">
+        <v>46119</v>
       </c>
       <c r="F52" s="8">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G52" s="8">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>23</v>
+        <v>94</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S52" s="9">
-        <v>97.5</v>
+        <v>650</v>
       </c>
     </row>
     <row r="53" ht="23" customHeight="1">
@@ -3592,55 +3478,55 @@
         <v>46160</v>
       </c>
       <c r="C53" s="7">
-        <v>46082</v>
+        <v>46160</v>
       </c>
       <c r="D53" s="7">
         <v>46160</v>
       </c>
       <c r="E53" s="7">
-        <v>46097</v>
+        <v>46119</v>
       </c>
       <c r="F53" s="8">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G53" s="8">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S53" s="9">
-        <v>146.55</v>
+        <v>680</v>
       </c>
     </row>
     <row r="54" ht="23" customHeight="1">
@@ -3651,43 +3537,43 @@
         <v>46160</v>
       </c>
       <c r="C54" s="7">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="D54" s="7">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="E54" s="7">
-        <v>46160</v>
+        <v>46119</v>
       </c>
       <c r="F54" s="8">
         <v>-3</v>
       </c>
       <c r="G54" s="8">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>23</v>
@@ -3696,69 +3582,69 @@
         <v>37</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S54" s="9">
-        <v>278.57</v>
+        <v>680</v>
       </c>
     </row>
     <row r="55" ht="23" customHeight="1">
       <c r="A55" s="6" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="B55" s="7">
         <v>46160</v>
       </c>
       <c r="C55" s="7">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="D55" s="7">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="E55" s="7">
-        <v>46160</v>
+        <v>46141</v>
       </c>
       <c r="F55" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G55" s="8">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="S55" s="9">
-        <v>342.86</v>
+        <v>680</v>
       </c>
     </row>
     <row r="56" ht="23" customHeight="1">
@@ -3769,55 +3655,55 @@
         <v>46160</v>
       </c>
       <c r="C56" s="7">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="D56" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E56" s="7">
+        <v>46119</v>
       </c>
       <c r="F56" s="8">
-        <v>-14</v>
+        <v>-3</v>
       </c>
       <c r="G56" s="8">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="N56" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O56" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P56" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="O56" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="Q56" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S56" s="9">
-        <v>450</v>
+        <v>700</v>
       </c>
     </row>
     <row r="57" ht="23" customHeight="1">
@@ -3825,58 +3711,58 @@
         <v>22</v>
       </c>
       <c r="B57" s="7">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C57" s="7">
-        <v>46160</v>
+        <v>46139</v>
       </c>
       <c r="D57" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E57" s="7">
-        <v>46112</v>
+        <v>46139</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F57" s="8">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="G57" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S57" s="9">
-        <v>600</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" ht="23" customHeight="1">
@@ -3884,7 +3770,7 @@
         <v>22</v>
       </c>
       <c r="B58" s="7">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C58" s="7">
         <v>46160</v>
@@ -3892,50 +3778,50 @@
       <c r="D58" s="7">
         <v>46160</v>
       </c>
-      <c r="E58" s="7">
-        <v>46127</v>
+      <c r="E58" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F58" s="8">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G58" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S58" s="9">
-        <v>600</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" ht="23" customHeight="1">
@@ -3943,58 +3829,58 @@
         <v>22</v>
       </c>
       <c r="B59" s="7">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C59" s="7">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="D59" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E59" s="7">
-        <v>46119</v>
+        <v>46153</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F59" s="8">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="G59" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S59" s="9">
-        <v>600</v>
+        <v>277.36</v>
       </c>
     </row>
     <row r="60" ht="23" customHeight="1">
@@ -4002,46 +3888,46 @@
         <v>22</v>
       </c>
       <c r="B60" s="7">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="C60" s="7">
-        <v>46160</v>
+        <v>46113</v>
       </c>
       <c r="D60" s="7">
-        <v>46160</v>
+        <v>46150</v>
       </c>
       <c r="E60" s="7">
-        <v>46141</v>
+        <v>46149</v>
       </c>
       <c r="F60" s="8">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="G60" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>23</v>
@@ -4050,10 +3936,10 @@
         <v>37</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S60" s="9">
-        <v>620</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="61" ht="23" customHeight="1">
@@ -4061,58 +3947,58 @@
         <v>22</v>
       </c>
       <c r="B61" s="7">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="C61" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D61" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E61" s="7">
-        <v>46119</v>
+        <v>46146</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F61" s="8">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="G61" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q61" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S61" s="9">
-        <v>620</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" ht="23" customHeight="1">
@@ -4120,22 +4006,22 @@
         <v>22</v>
       </c>
       <c r="B62" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C62" s="7">
-        <v>46160</v>
+        <v>46082</v>
       </c>
       <c r="D62" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E62" s="7">
-        <v>46141</v>
+        <v>46097</v>
       </c>
       <c r="F62" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G62" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>23</v>
@@ -4144,34 +4030,34 @@
         <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S62" s="9">
-        <v>620</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="63" ht="23" customHeight="1">
@@ -4179,22 +4065,22 @@
         <v>22</v>
       </c>
       <c r="B63" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C63" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D63" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E63" s="7">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="F63" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G63" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>23</v>
@@ -4203,22 +4089,22 @@
         <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
@@ -4227,10 +4113,10 @@
         <v>37</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S63" s="9">
-        <v>630</v>
+        <v>600</v>
       </c>
     </row>
     <row r="64" ht="23" customHeight="1">
@@ -4238,22 +4124,22 @@
         <v>22</v>
       </c>
       <c r="B64" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C64" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D64" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E64" s="7">
-        <v>46112</v>
+        <v>46141</v>
       </c>
       <c r="F64" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G64" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>23</v>
@@ -4262,22 +4148,22 @@
         <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
@@ -4286,10 +4172,10 @@
         <v>37</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S64" s="9">
-        <v>630</v>
+        <v>620</v>
       </c>
     </row>
     <row r="65" ht="23" customHeight="1">
@@ -4297,22 +4183,22 @@
         <v>22</v>
       </c>
       <c r="B65" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C65" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D65" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E65" s="7">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="F65" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G65" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>23</v>
@@ -4321,22 +4207,22 @@
         <v>23</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
@@ -4345,10 +4231,10 @@
         <v>37</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S65" s="9">
-        <v>630</v>
+        <v>620</v>
       </c>
     </row>
     <row r="66" ht="23" customHeight="1">
@@ -4356,22 +4242,22 @@
         <v>22</v>
       </c>
       <c r="B66" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C66" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D66" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E66" s="7">
-        <v>46150</v>
+        <v>46119</v>
       </c>
       <c r="F66" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G66" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>23</v>
@@ -4380,22 +4266,22 @@
         <v>23</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
@@ -4404,10 +4290,10 @@
         <v>37</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S66" s="9">
-        <v>630</v>
+        <v>620</v>
       </c>
     </row>
     <row r="67" ht="23" customHeight="1">
@@ -4415,22 +4301,22 @@
         <v>22</v>
       </c>
       <c r="B67" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C67" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D67" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E67" s="7">
         <v>46119</v>
       </c>
       <c r="F67" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G67" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>23</v>
@@ -4439,31 +4325,31 @@
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="M67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Q67" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S67" s="9">
         <v>630</v>
@@ -4474,22 +4360,22 @@
         <v>22</v>
       </c>
       <c r="B68" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C68" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D68" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E68" s="7">
-        <v>46092</v>
+        <v>46150</v>
       </c>
       <c r="F68" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G68" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>23</v>
@@ -4498,22 +4384,22 @@
         <v>23</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="M68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
@@ -4522,10 +4408,10 @@
         <v>37</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S68" s="9">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="69" ht="23" customHeight="1">
@@ -4533,22 +4419,22 @@
         <v>22</v>
       </c>
       <c r="B69" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C69" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D69" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E69" s="7">
-        <v>46119</v>
+        <v>46163</v>
       </c>
       <c r="F69" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G69" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>23</v>
@@ -4557,22 +4443,22 @@
         <v>23</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
@@ -4581,10 +4467,10 @@
         <v>37</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S69" s="9">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="70" ht="23" customHeight="1">
@@ -4592,22 +4478,22 @@
         <v>22</v>
       </c>
       <c r="B70" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C70" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D70" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E70" s="7">
         <v>46153</v>
       </c>
       <c r="F70" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G70" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>23</v>
@@ -4616,22 +4502,22 @@
         <v>23</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4640,7 +4526,7 @@
         <v>37</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S70" s="9">
         <v>650</v>
@@ -4651,22 +4537,22 @@
         <v>22</v>
       </c>
       <c r="B71" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C71" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D71" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E71" s="7">
         <v>46160</v>
       </c>
-      <c r="C71" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D71" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E71" s="7">
-        <v>46127</v>
-      </c>
       <c r="F71" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G71" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4675,22 +4561,22 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
@@ -4699,7 +4585,7 @@
         <v>37</v>
       </c>
       <c r="R71" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S71" s="9">
         <v>650</v>
@@ -4710,22 +4596,22 @@
         <v>22</v>
       </c>
       <c r="B72" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C72" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D72" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E72" s="7">
-        <v>46119</v>
+        <v>46127</v>
       </c>
       <c r="F72" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G72" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4734,22 +4620,22 @@
         <v>23</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>23</v>
@@ -4758,10 +4644,10 @@
         <v>37</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S72" s="9">
-        <v>670</v>
+        <v>650</v>
       </c>
     </row>
     <row r="73" ht="23" customHeight="1">
@@ -4769,22 +4655,22 @@
         <v>22</v>
       </c>
       <c r="B73" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C73" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D73" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E73" s="7">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="F73" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G73" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4793,22 +4679,22 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4817,10 +4703,10 @@
         <v>37</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S73" s="9">
-        <v>680</v>
+        <v>650</v>
       </c>
     </row>
     <row r="74" ht="23" customHeight="1">
@@ -4828,22 +4714,22 @@
         <v>22</v>
       </c>
       <c r="B74" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C74" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D74" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E74" s="7">
-        <v>46119</v>
+        <v>46092</v>
       </c>
       <c r="F74" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G74" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4852,22 +4738,22 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4876,10 +4762,10 @@
         <v>37</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S74" s="9">
-        <v>680</v>
+        <v>650</v>
       </c>
     </row>
     <row r="75" ht="23" customHeight="1">
@@ -4887,22 +4773,22 @@
         <v>22</v>
       </c>
       <c r="B75" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C75" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D75" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E75" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F75" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G75" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>23</v>
@@ -4911,22 +4797,22 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>23</v>
@@ -4935,10 +4821,10 @@
         <v>37</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S75" s="9">
-        <v>680</v>
+        <v>670</v>
       </c>
     </row>
     <row r="76" ht="23" customHeight="1">
@@ -4946,22 +4832,22 @@
         <v>22</v>
       </c>
       <c r="B76" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C76" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D76" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E76" s="7">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="F76" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G76" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -4970,22 +4856,22 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -4994,7 +4880,7 @@
         <v>37</v>
       </c>
       <c r="R76" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S76" s="9">
         <v>680</v>
@@ -5005,22 +4891,22 @@
         <v>22</v>
       </c>
       <c r="B77" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C77" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D77" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E77" s="7">
-        <v>46092</v>
+        <v>46119</v>
       </c>
       <c r="F77" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G77" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -5029,22 +4915,22 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -5053,10 +4939,10 @@
         <v>37</v>
       </c>
       <c r="R77" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S77" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="78" ht="23" customHeight="1">
@@ -5064,22 +4950,22 @@
         <v>22</v>
       </c>
       <c r="B78" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C78" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D78" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E78" s="7">
         <v>46119</v>
       </c>
       <c r="F78" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G78" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -5088,34 +4974,34 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="M78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="Q78" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R78" s="6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="S78" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="79" ht="23" customHeight="1">
@@ -5123,22 +5009,22 @@
         <v>22</v>
       </c>
       <c r="B79" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C79" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D79" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E79" s="7">
-        <v>46099</v>
+        <v>46141</v>
       </c>
       <c r="F79" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G79" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>23</v>
@@ -5147,22 +5033,22 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
@@ -5174,30 +5060,30 @@
         <v>33</v>
       </c>
       <c r="S79" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="80" ht="23" customHeight="1">
       <c r="A80" s="6" t="s">
-        <v>140</v>
+        <v>22</v>
       </c>
       <c r="B80" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C80" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D80" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E80" s="7">
-        <v>46129</v>
+        <v>46099</v>
       </c>
       <c r="F80" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G80" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>23</v>
@@ -5206,22 +5092,22 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
@@ -5230,33 +5116,33 @@
         <v>37</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="S80" s="9">
-        <v>800</v>
+        <v>700</v>
       </c>
     </row>
     <row r="81" ht="23" customHeight="1">
       <c r="A81" s="6" t="s">
-        <v>140</v>
+        <v>22</v>
       </c>
       <c r="B81" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C81" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D81" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E81" s="7">
         <v>46160</v>
       </c>
-      <c r="C81" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D81" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E81" s="7">
-        <v>46148</v>
-      </c>
       <c r="F81" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G81" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>23</v>
@@ -5265,34 +5151,34 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="Q81" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R81" s="6" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="S81" s="9">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="82" ht="23" customHeight="1">
@@ -5300,105 +5186,105 @@
         <v>22</v>
       </c>
       <c r="B82" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C82" s="7">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="D82" s="7">
-        <v>46154</v>
+        <v>46167</v>
       </c>
       <c r="E82" s="7">
         <v>46160</v>
       </c>
       <c r="F82" s="8">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="G82" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="Q82" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R82" s="6" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="S82" s="9">
-        <v>1028.57</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="83" ht="23" customHeight="1">
       <c r="A83" s="6" t="s">
-        <v>104</v>
+        <v>22</v>
       </c>
       <c r="B83" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C83" s="7">
-        <v>46160</v>
+        <v>46113</v>
       </c>
       <c r="D83" s="7">
-        <v>46160</v>
+        <v>46150</v>
       </c>
       <c r="E83" s="7">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="F83" s="8">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="G83" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>23</v>
@@ -5407,1662 +5293,69 @@
         <v>37</v>
       </c>
       <c r="R83" s="6" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="S83" s="9">
-        <v>1200</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="84" ht="23" customHeight="1">
-      <c r="A84" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B84" s="7">
-        <v>46160</v>
-      </c>
-      <c r="C84" s="7">
-        <v>46160</v>
-      </c>
-      <c r="D84" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E84" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F84" s="8">
-        <v>0</v>
-      </c>
-      <c r="G84" s="8">
-        <v>0</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J84" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L84" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="M84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N84" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q84" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R84" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="S84" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="85" ht="23" customHeight="1">
-      <c r="A85" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B85" s="7">
-        <v>46161</v>
-      </c>
-      <c r="C85" s="7">
-        <v>46113</v>
-      </c>
-      <c r="D85" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E85" s="7">
-        <v>46149</v>
-      </c>
-      <c r="F85" s="8">
-        <v>-10</v>
-      </c>
-      <c r="G85" s="8">
-        <v>1</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J85" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="K85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L85" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="M85" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="N85" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O85" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q85" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R85" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S85" s="9">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="86" ht="23" customHeight="1">
-      <c r="A86" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B86" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C86" s="7">
-        <v>46082</v>
-      </c>
-      <c r="D86" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E86" s="7">
-        <v>46097</v>
-      </c>
-      <c r="F86" s="8">
-        <v>7</v>
-      </c>
-      <c r="G86" s="8">
-        <v>7</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J86" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L86" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N86" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q86" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="R86" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S86" s="9">
-        <v>146.55</v>
-      </c>
-    </row>
-    <row r="87" ht="23" customHeight="1">
-      <c r="A87" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B87" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C87" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D87" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E87" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F87" s="8">
-        <v>7</v>
-      </c>
-      <c r="G87" s="8">
-        <v>7</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J87" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="K87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L87" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="M87" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="N87" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O87" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q87" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R87" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S87" s="9">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="88" ht="23" customHeight="1">
-      <c r="A88" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B88" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C88" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D88" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E88" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F88" s="8">
-        <v>7</v>
-      </c>
-      <c r="G88" s="8">
-        <v>7</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J88" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="K88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="M88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N88" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q88" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R88" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S88" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="89" ht="23" customHeight="1">
-      <c r="A89" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B89" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C89" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D89" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E89" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F89" s="8">
-        <v>7</v>
-      </c>
-      <c r="G89" s="8">
-        <v>7</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J89" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="K89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L89" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="M89" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="N89" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O89" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q89" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R89" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S89" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="90" ht="23" customHeight="1">
-      <c r="A90" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B90" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C90" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D90" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E90" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F90" s="8">
-        <v>7</v>
-      </c>
-      <c r="G90" s="8">
-        <v>7</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="K90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L90" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="M90" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="N90" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q90" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R90" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S90" s="9">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="91" ht="23" customHeight="1">
-      <c r="A91" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B91" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C91" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D91" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E91" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F91" s="8">
-        <v>7</v>
-      </c>
-      <c r="G91" s="8">
-        <v>7</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J91" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="K91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L91" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="M91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N91" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O91" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P91" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q91" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R91" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S91" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="92" ht="23" customHeight="1">
-      <c r="A92" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B92" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C92" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D92" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E92" s="7">
-        <v>46150</v>
-      </c>
-      <c r="F92" s="8">
-        <v>7</v>
-      </c>
-      <c r="G92" s="8">
-        <v>7</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J92" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="K92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L92" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="M92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N92" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O92" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q92" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R92" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S92" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="93" ht="23" customHeight="1">
-      <c r="A93" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B93" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C93" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D93" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E93" s="7">
-        <v>46092</v>
-      </c>
-      <c r="F93" s="8">
-        <v>7</v>
-      </c>
-      <c r="G93" s="8">
-        <v>7</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J93" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="K93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L93" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="M93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N93" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O93" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q93" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R93" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S93" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="94" ht="23" customHeight="1">
-      <c r="A94" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B94" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C94" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D94" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E94" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F94" s="8">
-        <v>7</v>
-      </c>
-      <c r="G94" s="8">
-        <v>7</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J94" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="K94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L94" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="M94" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="N94" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q94" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R94" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S94" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="95" ht="23" customHeight="1">
-      <c r="A95" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B95" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C95" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D95" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E95" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F95" s="8">
-        <v>7</v>
-      </c>
-      <c r="G95" s="8">
-        <v>7</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J95" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="K95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L95" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="M95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N95" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O95" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q95" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R95" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S95" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="96" ht="23" customHeight="1">
-      <c r="A96" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B96" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C96" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D96" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E96" s="7">
-        <v>46127</v>
-      </c>
-      <c r="F96" s="8">
-        <v>7</v>
-      </c>
-      <c r="G96" s="8">
-        <v>7</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J96" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="K96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L96" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="M96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N96" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O96" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q96" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R96" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S96" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="97" ht="23" customHeight="1">
-      <c r="A97" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B97" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C97" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D97" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E97" s="7">
-        <v>46153</v>
-      </c>
-      <c r="F97" s="8">
-        <v>7</v>
-      </c>
-      <c r="G97" s="8">
-        <v>7</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J97" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="K97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L97" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="M97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N97" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O97" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q97" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R97" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S97" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="98" ht="23" customHeight="1">
-      <c r="A98" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B98" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C98" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D98" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E98" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F98" s="8">
-        <v>7</v>
-      </c>
-      <c r="G98" s="8">
-        <v>7</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J98" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="K98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L98" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="M98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N98" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O98" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q98" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R98" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S98" s="9">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="99" ht="23" customHeight="1">
-      <c r="A99" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B99" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C99" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D99" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E99" s="7">
-        <v>46113</v>
-      </c>
-      <c r="F99" s="8">
-        <v>7</v>
-      </c>
-      <c r="G99" s="8">
-        <v>7</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J99" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="K99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L99" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M99" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N99" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O99" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q99" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R99" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S99" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="100" ht="23" customHeight="1">
-      <c r="A100" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B100" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C100" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D100" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E100" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F100" s="8">
-        <v>7</v>
-      </c>
-      <c r="G100" s="8">
-        <v>7</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J100" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="K100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L100" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N100" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O100" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q100" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R100" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S100" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="101" ht="23" customHeight="1">
-      <c r="A101" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B101" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C101" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D101" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E101" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F101" s="8">
-        <v>7</v>
-      </c>
-      <c r="G101" s="8">
-        <v>7</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J101" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="K101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L101" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="M101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N101" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O101" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q101" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R101" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S101" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="102" ht="23" customHeight="1">
-      <c r="A102" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B102" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C102" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D102" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E102" s="7">
-        <v>46119</v>
-      </c>
-      <c r="F102" s="8">
-        <v>7</v>
-      </c>
-      <c r="G102" s="8">
-        <v>7</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J102" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="K102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L102" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="M102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N102" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O102" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q102" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R102" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S102" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="103" ht="23" customHeight="1">
-      <c r="A103" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B103" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C103" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D103" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E103" s="7">
-        <v>46099</v>
-      </c>
-      <c r="F103" s="8">
-        <v>7</v>
-      </c>
-      <c r="G103" s="8">
-        <v>7</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I103" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J103" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="K103" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L103" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="M103" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N103" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O103" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P103" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q103" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R103" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S103" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="104" ht="23" customHeight="1">
-      <c r="A104" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B104" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C104" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D104" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E104" s="7">
-        <v>46129</v>
-      </c>
-      <c r="F104" s="8">
-        <v>7</v>
-      </c>
-      <c r="G104" s="8">
-        <v>7</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J104" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="K104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L104" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="M104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N104" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O104" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q104" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R104" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="S104" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="105" ht="23" customHeight="1">
-      <c r="A105" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="B105" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C105" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D105" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E105" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F105" s="8">
-        <v>7</v>
-      </c>
-      <c r="G105" s="8">
-        <v>7</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J105" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="K105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L105" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="M105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N105" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O105" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q105" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R105" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="S105" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="106" ht="23" customHeight="1">
-      <c r="A106" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B106" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C106" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D106" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E106" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F106" s="8">
-        <v>7</v>
-      </c>
-      <c r="G106" s="8">
-        <v>7</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I106" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J106" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="K106" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L106" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="M106" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N106" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O106" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P106" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q106" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R106" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="S106" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="107" ht="23" customHeight="1">
-      <c r="A107" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B107" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C107" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D107" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E107" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F107" s="8">
-        <v>7</v>
-      </c>
-      <c r="G107" s="8">
-        <v>7</v>
-      </c>
-      <c r="H107" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I107" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J107" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K107" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L107" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="M107" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N107" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O107" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P107" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q107" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R107" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="S107" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="108" ht="23" customHeight="1">
-      <c r="A108" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B108" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C108" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D108" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E108" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F108" s="8">
-        <v>7</v>
-      </c>
-      <c r="G108" s="8">
-        <v>7</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I108" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J108" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="K108" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L108" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="M108" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N108" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O108" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q108" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R108" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="S108" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="109" ht="23" customHeight="1">
-      <c r="A109" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B109" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C109" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D109" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E109" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F109" s="8">
-        <v>7</v>
-      </c>
-      <c r="G109" s="8">
-        <v>7</v>
-      </c>
-      <c r="H109" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I109" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J109" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="K109" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L109" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="M109" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N109" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="O109" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P109" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q109" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R109" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="S109" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="110" ht="23" customHeight="1">
-      <c r="A110" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B110" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C110" s="7">
-        <v>46113</v>
-      </c>
-      <c r="D110" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E110" s="7">
-        <v>46149</v>
-      </c>
-      <c r="F110" s="8">
-        <v>-10</v>
-      </c>
-      <c r="G110" s="8">
-        <v>7</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I110" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J110" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="K110" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L110" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="M110" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="N110" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O110" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="P110" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q110" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="R110" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="S110" s="9">
-        <v>4400</v>
-      </c>
-    </row>
-    <row r="111" ht="23" customHeight="1">
-      <c r="A111" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B111" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C111" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D111" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E111" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F111" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G111" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H111" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I111" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J111" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K111" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L111" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M111" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N111" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O111" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P111" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q111" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R111" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S111" s="13">
-        <f>SUM(S6:S110)</f>
+      <c r="A84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F84" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G84" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R84" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S84" s="13">
+        <f>SUM(S6:S83)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$82</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$89</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,11 +36,11 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Inicial: 01/08/2025, Data Final: 25/05/2026, Conta de Recebimento: 1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
+      <t>Data Inicial: 01/08/2025, Data Final: 25/05/2026</t>
     </r>
   </si>
   <si>
-    <t>Relatório exportado em sexta-feira, 22 de maio de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em segunda-feira, 25 de maio de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -124,24 +124,24 @@
     <t>ATIVUZ VEÍCULOS</t>
   </si>
   <si>
+    <t>ND-11305</t>
+  </si>
+  <si>
+    <t>MARCELO BENTO DE ARAUJO</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>FA-11387</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
     <t>VENCIDO ATÉ 30 DIAS</t>
   </si>
   <si>
-    <t>ND-11305</t>
-  </si>
-  <si>
-    <t>MARCELO BENTO DE ARAUJO</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
-    <t>FA-11387</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
     <t>FA-11518</t>
   </si>
   <si>
@@ -151,6 +151,12 @@
     <t>NOTA DE DÉBITO</t>
   </si>
   <si>
+    <t>1.3 UBER SUPPLIER</t>
+  </si>
+  <si>
+    <t>FA-11183</t>
+  </si>
+  <si>
     <t>FA-11446</t>
   </si>
   <si>
@@ -304,10 +310,19 @@
     <t>FA-11616</t>
   </si>
   <si>
+    <t>FA-11482</t>
+  </si>
+  <si>
     <t>FA-11620</t>
   </si>
   <si>
-    <t>FA-11482</t>
+    <t>FA-11484</t>
+  </si>
+  <si>
+    <t>FA-11675</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
   </si>
   <si>
     <t>FA-11483</t>
@@ -316,21 +331,12 @@
     <t>LUCAS NAJA MOURA RODRIGUES</t>
   </si>
   <si>
-    <t>FA-11484</t>
-  </si>
-  <si>
     <t>FA-11561</t>
   </si>
   <si>
     <t>ELSON VIEIRA DA SILVA</t>
   </si>
   <si>
-    <t>FA-11675</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
     <t>FA-11479</t>
   </si>
   <si>
@@ -364,28 +370,31 @@
     <t>FA-11464</t>
   </si>
   <si>
+    <t>FA-11690</t>
+  </si>
+  <si>
     <t>FA-11667</t>
   </si>
   <si>
+    <t>FA-11399</t>
+  </si>
+  <si>
     <t>HOJE</t>
   </si>
   <si>
-    <t>FA-11399</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
     <t>FA-11480</t>
   </si>
   <si>
     <t>FA-11562</t>
   </si>
   <si>
+    <t>FA-11487</t>
+  </si>
+  <si>
     <t>FA-11563</t>
   </si>
   <si>
-    <t>FA-11487</t>
+    <t>FA-11668</t>
   </si>
   <si>
     <t>FA-11494</t>
@@ -397,36 +406,33 @@
     <t>FA-11617</t>
   </si>
   <si>
-    <t>FA-11668</t>
-  </si>
-  <si>
     <t>FA-11683</t>
   </si>
   <si>
     <t>GILVAN RODRIGUES MACHADO</t>
   </si>
   <si>
+    <t>FA-11280</t>
+  </si>
+  <si>
+    <t>FA-11488</t>
+  </si>
+  <si>
+    <t>FA-11504</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11621</t>
+  </si>
+  <si>
     <t>FA-11656</t>
   </si>
   <si>
     <t>LUCA ZOLI</t>
   </si>
   <si>
-    <t>FA-11621</t>
-  </si>
-  <si>
-    <t>FA-11504</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11488</t>
-  </si>
-  <si>
-    <t>FA-11280</t>
-  </si>
-  <si>
     <t>FA-11434</t>
   </si>
   <si>
@@ -436,15 +442,18 @@
     <t>FA-11412</t>
   </si>
   <si>
+    <t>FA-11491</t>
+  </si>
+  <si>
+    <t>FA-11691</t>
+  </si>
+  <si>
+    <t>FA-11564</t>
+  </si>
+  <si>
     <t>FA-11489</t>
   </si>
   <si>
-    <t>FA-11491</t>
-  </si>
-  <si>
-    <t>FA-11564</t>
-  </si>
-  <si>
     <t>FA-11676</t>
   </si>
   <si>
@@ -452,6 +461,33 @@
   </si>
   <si>
     <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>FA-11601</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>FA-11536</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - LUZ DIVINA</t>
+  </si>
+  <si>
+    <t>FA-11578</t>
+  </si>
+  <si>
+    <t>ADRIANO TEOTONIO DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11591</t>
   </si>
   <si>
     <t>FA-11632</t>
@@ -618,7 +654,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S88"/>
+  <dimension ref="A1:S95"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -735,10 +771,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-46</v>
+        <v>-49</v>
       </c>
       <c r="G6" s="8">
-        <v>-32</v>
+        <v>-35</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -794,43 +830,43 @@
         <v>23</v>
       </c>
       <c r="F7" s="8">
-        <v>-39</v>
+        <v>-42</v>
       </c>
       <c r="G7" s="8">
-        <v>-30</v>
+        <v>-33</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>24</v>
       </c>
       <c r="I7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="K7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="K7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L7" s="6" t="s">
+      <c r="M7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R7" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q7" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="S7" s="9">
         <v>79.05</v>
@@ -853,25 +889,25 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-39</v>
+        <v>-42</v>
       </c>
       <c r="G8" s="8">
-        <v>-28</v>
+        <v>-31</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>23</v>
@@ -912,16 +948,16 @@
         <v>46127</v>
       </c>
       <c r="F9" s="8">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="G9" s="8">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>36</v>
@@ -971,25 +1007,25 @@
         <v>46097</v>
       </c>
       <c r="F10" s="8">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="G10" s="8">
-        <v>-25</v>
+        <v>-28</v>
       </c>
       <c r="H10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I10" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" s="6" t="s">
+      <c r="K10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>23</v>
@@ -1007,7 +1043,7 @@
         <v>38</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S10" s="9">
         <v>146.55</v>
@@ -1030,43 +1066,43 @@
         <v>23</v>
       </c>
       <c r="F11" s="8">
-        <v>-32</v>
+        <v>-35</v>
       </c>
       <c r="G11" s="8">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>24</v>
       </c>
       <c r="I11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="K11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="K11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L11" s="6" t="s">
+      <c r="M11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R11" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="S11" s="9">
         <v>104.04</v>
@@ -1074,61 +1110,61 @@
     </row>
     <row r="12" ht="23" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B12" s="7">
         <v>46140</v>
       </c>
       <c r="C12" s="7">
-        <v>46125</v>
+        <v>46118</v>
       </c>
       <c r="D12" s="7">
-        <v>46125</v>
+        <v>46111</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F12" s="8">
-        <v>-39</v>
+        <v>-56</v>
       </c>
       <c r="G12" s="8">
-        <v>-24</v>
+        <v>-27</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>24</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="M12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O12" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R12" s="6" t="s">
-        <v>33</v>
-      </c>
       <c r="S12" s="9">
-        <v>408.24</v>
+        <v>275.41</v>
       </c>
     </row>
     <row r="13" ht="23" customHeight="1">
@@ -1136,37 +1172,37 @@
         <v>22</v>
       </c>
       <c r="B13" s="7">
-        <v>46146</v>
+        <v>46140</v>
       </c>
       <c r="C13" s="7">
-        <v>46113</v>
+        <v>46125</v>
       </c>
       <c r="D13" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E13" s="7">
-        <v>46141</v>
+        <v>46125</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F13" s="8">
-        <v>-14</v>
+        <v>-42</v>
       </c>
       <c r="G13" s="8">
-        <v>-18</v>
+        <v>-27</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>23</v>
@@ -1181,13 +1217,13 @@
         <v>23</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="S13" s="9">
-        <v>12.9</v>
+        <v>408.24</v>
       </c>
     </row>
     <row r="14" ht="23" customHeight="1">
@@ -1198,55 +1234,55 @@
         <v>46146</v>
       </c>
       <c r="C14" s="7">
-        <v>46153</v>
+        <v>46113</v>
       </c>
       <c r="D14" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>23</v>
+        <v>46150</v>
+      </c>
+      <c r="E14" s="7">
+        <v>46141</v>
       </c>
       <c r="F14" s="8">
-        <v>-11</v>
+        <v>-17</v>
       </c>
       <c r="G14" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L14" s="6" t="s">
+      <c r="M14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="R14" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="M14" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R14" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="S14" s="9">
-        <v>61.21</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="15" ht="23" customHeight="1">
@@ -1257,37 +1293,37 @@
         <v>46146</v>
       </c>
       <c r="C15" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D15" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="8">
-        <v>-18</v>
+        <v>-14</v>
       </c>
       <c r="G15" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="N15" s="6" t="s">
         <v>27</v>
@@ -1302,10 +1338,10 @@
         <v>23</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S15" s="9">
-        <v>120</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="16" ht="23" customHeight="1">
@@ -1316,34 +1352,34 @@
         <v>46146</v>
       </c>
       <c r="C16" s="7">
-        <v>46082</v>
+        <v>46146</v>
       </c>
       <c r="D16" s="7">
         <v>46146</v>
       </c>
-      <c r="E16" s="7">
-        <v>46097</v>
+      <c r="E16" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F16" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="G16" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>23</v>
@@ -1358,13 +1394,13 @@
         <v>23</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="S16" s="9">
-        <v>146.55</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" ht="23" customHeight="1">
@@ -1375,34 +1411,34 @@
         <v>46146</v>
       </c>
       <c r="C17" s="7">
-        <v>46146</v>
+        <v>46082</v>
       </c>
       <c r="D17" s="7">
         <v>46146</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>23</v>
+      <c r="E17" s="7">
+        <v>46097</v>
       </c>
       <c r="F17" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="G17" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="H17" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>45</v>
-      </c>
       <c r="K17" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>23</v>
@@ -1417,13 +1453,13 @@
         <v>23</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S17" s="9">
-        <v>205.82</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="18" ht="23" customHeight="1">
@@ -1439,20 +1475,20 @@
       <c r="D18" s="7">
         <v>46146</v>
       </c>
-      <c r="E18" s="7">
-        <v>46141</v>
+      <c r="E18" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F18" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="G18" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>47</v>
@@ -1476,13 +1512,13 @@
         <v>23</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S18" s="9">
-        <v>620</v>
+        <v>205.82</v>
       </c>
     </row>
     <row r="19" ht="23" customHeight="1">
@@ -1493,25 +1529,25 @@
         <v>46146</v>
       </c>
       <c r="C19" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="D19" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>23</v>
+        <v>46146</v>
+      </c>
+      <c r="E19" s="7">
+        <v>46141</v>
       </c>
       <c r="F19" s="8">
-        <v>-32</v>
+        <v>-21</v>
       </c>
       <c r="G19" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>49</v>
@@ -1535,13 +1571,13 @@
         <v>23</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S19" s="9">
-        <v>655.21</v>
+        <v>620</v>
       </c>
     </row>
     <row r="20" ht="23" customHeight="1">
@@ -1549,28 +1585,28 @@
         <v>22</v>
       </c>
       <c r="B20" s="7">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="C20" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="D20" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F20" s="8">
-        <v>-25</v>
+        <v>-35</v>
       </c>
       <c r="G20" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>51</v>
@@ -1600,7 +1636,7 @@
         <v>29</v>
       </c>
       <c r="S20" s="9">
-        <v>103.36</v>
+        <v>655.21</v>
       </c>
     </row>
     <row r="21" ht="23" customHeight="1">
@@ -1608,28 +1644,28 @@
         <v>22</v>
       </c>
       <c r="B21" s="7">
-        <v>46149</v>
+        <v>46147</v>
       </c>
       <c r="C21" s="7">
-        <v>46142</v>
+        <v>46139</v>
       </c>
       <c r="D21" s="7">
-        <v>46142</v>
-      </c>
-      <c r="E21" s="7">
-        <v>46148</v>
+        <v>46139</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F21" s="8">
-        <v>-22</v>
+        <v>-28</v>
       </c>
       <c r="G21" s="8">
-        <v>-15</v>
+        <v>-20</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>53</v>
@@ -1653,13 +1689,13 @@
         <v>23</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="S21" s="9">
-        <v>685.71</v>
+        <v>103.36</v>
       </c>
     </row>
     <row r="22" ht="23" customHeight="1">
@@ -1667,58 +1703,58 @@
         <v>22</v>
       </c>
       <c r="B22" s="7">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="C22" s="7">
-        <v>46125</v>
+        <v>46142</v>
       </c>
       <c r="D22" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>23</v>
+        <v>46142</v>
+      </c>
+      <c r="E22" s="7">
+        <v>46148</v>
       </c>
       <c r="F22" s="8">
-        <v>-39</v>
+        <v>-25</v>
       </c>
       <c r="G22" s="8">
-        <v>-14</v>
+        <v>-18</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J22" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="K22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L22" s="6" t="s">
+      <c r="M22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R22" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="M22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O22" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R22" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="S22" s="9">
-        <v>53.82</v>
+        <v>685.71</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
@@ -1729,25 +1765,25 @@
         <v>46150</v>
       </c>
       <c r="C23" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="D23" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F23" s="8">
-        <v>-18</v>
+        <v>-42</v>
       </c>
       <c r="G23" s="8">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>58</v>
@@ -1777,7 +1813,7 @@
         <v>29</v>
       </c>
       <c r="S23" s="9">
-        <v>170</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
@@ -1788,25 +1824,25 @@
         <v>46150</v>
       </c>
       <c r="C24" s="7">
-        <v>46150</v>
+        <v>46146</v>
       </c>
       <c r="D24" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E24" s="7">
-        <v>46153</v>
+        <v>46146</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F24" s="8">
-        <v>-14</v>
+        <v>-21</v>
       </c>
       <c r="G24" s="8">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>60</v>
@@ -1830,13 +1866,13 @@
         <v>23</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S24" s="9">
-        <v>278.57</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" ht="23" customHeight="1">
@@ -1844,38 +1880,38 @@
         <v>22</v>
       </c>
       <c r="B25" s="7">
+        <v>46150</v>
+      </c>
+      <c r="C25" s="7">
+        <v>46150</v>
+      </c>
+      <c r="D25" s="7">
+        <v>46150</v>
+      </c>
+      <c r="E25" s="7">
         <v>46153</v>
       </c>
-      <c r="C25" s="7">
-        <v>45901</v>
-      </c>
-      <c r="D25" s="7">
-        <v>45938</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="F25" s="8">
-        <v>-226</v>
+        <v>-17</v>
       </c>
       <c r="G25" s="8">
-        <v>-11</v>
+        <v>-17</v>
       </c>
       <c r="H25" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="I25" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J25" s="6" t="s">
+      <c r="K25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="K25" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>59</v>
-      </c>
       <c r="M25" s="6" t="s">
         <v>23</v>
       </c>
@@ -1889,13 +1925,13 @@
         <v>23</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S25" s="9">
-        <v>30</v>
+        <v>278.57</v>
       </c>
     </row>
     <row r="26" ht="23" customHeight="1">
@@ -1906,55 +1942,55 @@
         <v>46153</v>
       </c>
       <c r="C26" s="7">
-        <v>46082</v>
+        <v>45901</v>
       </c>
       <c r="D26" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E26" s="7">
-        <v>46097</v>
+        <v>45938</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F26" s="8">
-        <v>-11</v>
+        <v>-229</v>
       </c>
       <c r="G26" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="H26" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R26" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S26" s="9">
         <v>30</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q26" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="R26" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="S26" s="9">
-        <v>146.55</v>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
@@ -1965,34 +2001,34 @@
         <v>46153</v>
       </c>
       <c r="C27" s="7">
-        <v>46153</v>
+        <v>46082</v>
       </c>
       <c r="D27" s="7">
         <v>46153</v>
       </c>
       <c r="E27" s="7">
-        <v>46141</v>
+        <v>46097</v>
       </c>
       <c r="F27" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="G27" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="H27" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J27" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>64</v>
-      </c>
       <c r="K27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -2007,13 +2043,13 @@
         <v>23</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S27" s="9">
-        <v>310</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
@@ -2030,31 +2066,31 @@
         <v>46153</v>
       </c>
       <c r="E28" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F28" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="G28" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>27</v>
@@ -2072,7 +2108,7 @@
         <v>29</v>
       </c>
       <c r="S28" s="9">
-        <v>600</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29" ht="23" customHeight="1">
@@ -2092,16 +2128,16 @@
         <v>46119</v>
       </c>
       <c r="F29" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="G29" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>67</v>
@@ -2131,7 +2167,7 @@
         <v>29</v>
       </c>
       <c r="S29" s="9">
-        <v>650</v>
+        <v>600</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -2151,16 +2187,16 @@
         <v>46119</v>
       </c>
       <c r="F30" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="G30" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>69</v>
@@ -2169,10 +2205,10 @@
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -2187,10 +2223,10 @@
         <v>37</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S30" s="9">
-        <v>680</v>
+        <v>650</v>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1">
@@ -2198,37 +2234,37 @@
         <v>22</v>
       </c>
       <c r="B31" s="7">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="C31" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D31" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E31" s="7">
+        <v>46119</v>
       </c>
       <c r="F31" s="8">
-        <v>-18</v>
+        <v>-14</v>
       </c>
       <c r="G31" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>23</v>
@@ -2243,13 +2279,13 @@
         <v>23</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S31" s="9">
-        <v>280</v>
+        <v>680</v>
       </c>
     </row>
     <row r="32" ht="23" customHeight="1">
@@ -2260,25 +2296,25 @@
         <v>46154</v>
       </c>
       <c r="C32" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="D32" s="7">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F32" s="8">
-        <v>-32</v>
+        <v>-21</v>
       </c>
       <c r="G32" s="8">
-        <v>-10</v>
+        <v>-13</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>72</v>
@@ -2287,10 +2323,10 @@
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>27</v>
@@ -2308,7 +2344,7 @@
         <v>29</v>
       </c>
       <c r="S32" s="9">
-        <v>317.54</v>
+        <v>280</v>
       </c>
     </row>
     <row r="33" ht="23" customHeight="1">
@@ -2316,7 +2352,7 @@
         <v>22</v>
       </c>
       <c r="B33" s="7">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="C33" s="7">
         <v>46132</v>
@@ -2328,28 +2364,28 @@
         <v>23</v>
       </c>
       <c r="F33" s="8">
-        <v>-32</v>
+        <v>-35</v>
       </c>
       <c r="G33" s="8">
-        <v>-9</v>
+        <v>-13</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>24</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>27</v>
@@ -2367,7 +2403,7 @@
         <v>29</v>
       </c>
       <c r="S33" s="9">
-        <v>140</v>
+        <v>317.54</v>
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
@@ -2378,37 +2414,37 @@
         <v>46155</v>
       </c>
       <c r="C34" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="D34" s="7">
-        <v>46139</v>
+        <v>46132</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F34" s="8">
-        <v>-25</v>
+        <v>-35</v>
       </c>
       <c r="G34" s="8">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>27</v>
@@ -2426,7 +2462,7 @@
         <v>29</v>
       </c>
       <c r="S34" s="9">
-        <v>250</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" ht="23" customHeight="1">
@@ -2437,37 +2473,37 @@
         <v>46155</v>
       </c>
       <c r="C35" s="7">
-        <v>46153</v>
+        <v>46139</v>
       </c>
       <c r="D35" s="7">
-        <v>46153</v>
+        <v>46139</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F35" s="8">
-        <v>-11</v>
+        <v>-28</v>
       </c>
       <c r="G35" s="8">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="N35" s="6" t="s">
         <v>27</v>
@@ -2485,7 +2521,7 @@
         <v>29</v>
       </c>
       <c r="S35" s="9">
-        <v>530</v>
+        <v>250</v>
       </c>
     </row>
     <row r="36" ht="23" customHeight="1">
@@ -2493,37 +2529,37 @@
         <v>22</v>
       </c>
       <c r="B36" s="7">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="C36" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D36" s="7">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-18</v>
+        <v>-14</v>
       </c>
       <c r="G36" s="8">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>23</v>
@@ -2544,7 +2580,7 @@
         <v>29</v>
       </c>
       <c r="S36" s="9">
-        <v>130</v>
+        <v>530</v>
       </c>
     </row>
     <row r="37" ht="23" customHeight="1">
@@ -2552,37 +2588,37 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="C37" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D37" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F37" s="8">
-        <v>-4</v>
+        <v>-21</v>
       </c>
       <c r="G37" s="8">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>23</v>
@@ -2603,7 +2639,7 @@
         <v>29</v>
       </c>
       <c r="S37" s="9">
-        <v>97.5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" ht="23" customHeight="1">
@@ -2614,34 +2650,34 @@
         <v>46160</v>
       </c>
       <c r="C38" s="7">
-        <v>46082</v>
+        <v>46160</v>
       </c>
       <c r="D38" s="7">
         <v>46160</v>
       </c>
-      <c r="E38" s="7">
-        <v>46097</v>
+      <c r="E38" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G38" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>23</v>
@@ -2656,13 +2692,13 @@
         <v>23</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S38" s="9">
-        <v>146.55</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="39" ht="23" customHeight="1">
@@ -2673,37 +2709,37 @@
         <v>46160</v>
       </c>
       <c r="C39" s="7">
-        <v>46160</v>
+        <v>46082</v>
       </c>
       <c r="D39" s="7">
         <v>46160</v>
       </c>
       <c r="E39" s="7">
-        <v>46127</v>
+        <v>46097</v>
       </c>
       <c r="F39" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G39" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H39" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J39" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I39" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J39" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>27</v>
@@ -2715,13 +2751,13 @@
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S39" s="9">
-        <v>172</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="40" ht="23" customHeight="1">
@@ -2738,19 +2774,19 @@
         <v>46160</v>
       </c>
       <c r="E40" s="7">
-        <v>46141</v>
+        <v>46127</v>
       </c>
       <c r="F40" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G40" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J40" s="6" t="s">
         <v>79</v>
@@ -2759,10 +2795,10 @@
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>27</v>
@@ -2780,7 +2816,7 @@
         <v>29</v>
       </c>
       <c r="S40" s="9">
-        <v>310</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" ht="23" customHeight="1">
@@ -2791,34 +2827,34 @@
         <v>46160</v>
       </c>
       <c r="C41" s="7">
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="D41" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E41" s="7">
+        <v>46141</v>
       </c>
       <c r="F41" s="8">
-        <v>-32</v>
+        <v>-7</v>
       </c>
       <c r="G41" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>23</v>
@@ -2833,13 +2869,13 @@
         <v>23</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S41" s="9">
-        <v>350</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" ht="23" customHeight="1">
@@ -2850,25 +2886,25 @@
         <v>46160</v>
       </c>
       <c r="C42" s="7">
-        <v>46146</v>
+        <v>46139</v>
       </c>
       <c r="D42" s="7">
-        <v>46146</v>
+        <v>46132</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F42" s="8">
-        <v>-18</v>
+        <v>-35</v>
       </c>
       <c r="G42" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>82</v>
@@ -2877,10 +2913,10 @@
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="N42" s="6" t="s">
         <v>27</v>
@@ -2895,10 +2931,10 @@
         <v>23</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S42" s="9">
-        <v>450</v>
+        <v>350</v>
       </c>
     </row>
     <row r="43" ht="23" customHeight="1">
@@ -2909,37 +2945,37 @@
         <v>46160</v>
       </c>
       <c r="C43" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D43" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E43" s="7">
-        <v>46119</v>
+        <v>46146</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F43" s="8">
-        <v>-4</v>
+        <v>-21</v>
       </c>
       <c r="G43" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>27</v>
@@ -2951,13 +2987,13 @@
         <v>23</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S43" s="9">
-        <v>600</v>
+        <v>450</v>
       </c>
     </row>
     <row r="44" ht="23" customHeight="1">
@@ -2974,31 +3010,31 @@
         <v>46160</v>
       </c>
       <c r="E44" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F44" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G44" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>27</v>
@@ -3016,7 +3052,7 @@
         <v>29</v>
       </c>
       <c r="S44" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="45" ht="23" customHeight="1">
@@ -3033,19 +3069,19 @@
         <v>46160</v>
       </c>
       <c r="E45" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F45" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G45" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J45" s="6" t="s">
         <v>86</v>
@@ -3072,7 +3108,7 @@
         <v>37</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S45" s="9">
         <v>620</v>
@@ -3092,19 +3128,19 @@
         <v>46160</v>
       </c>
       <c r="E46" s="7">
-        <v>46112</v>
+        <v>46119</v>
       </c>
       <c r="F46" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G46" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>88</v>
@@ -3113,10 +3149,10 @@
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>27</v>
@@ -3131,10 +3167,10 @@
         <v>37</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S46" s="9">
-        <v>630</v>
+        <v>620</v>
       </c>
     </row>
     <row r="47" ht="23" customHeight="1">
@@ -3151,28 +3187,28 @@
         <v>46160</v>
       </c>
       <c r="E47" s="7">
-        <v>46150</v>
+        <v>46112</v>
       </c>
       <c r="F47" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G47" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>23</v>
@@ -3210,28 +3246,28 @@
         <v>46160</v>
       </c>
       <c r="E48" s="7">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="F48" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G48" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>23</v>
@@ -3252,7 +3288,7 @@
         <v>29</v>
       </c>
       <c r="S48" s="9">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="49" ht="23" customHeight="1">
@@ -3272,28 +3308,28 @@
         <v>46119</v>
       </c>
       <c r="F49" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G49" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N49" s="6" t="s">
         <v>27</v>
@@ -3328,28 +3364,28 @@
         <v>46160</v>
       </c>
       <c r="E50" s="7">
-        <v>46119</v>
+        <v>46153</v>
       </c>
       <c r="F50" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G50" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>23</v>
@@ -3370,7 +3406,7 @@
         <v>29</v>
       </c>
       <c r="S50" s="9">
-        <v>680</v>
+        <v>650</v>
       </c>
     </row>
     <row r="51" ht="23" customHeight="1">
@@ -3390,16 +3426,16 @@
         <v>46119</v>
       </c>
       <c r="F51" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G51" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J51" s="6" t="s">
         <v>94</v>
@@ -3408,7 +3444,7 @@
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>23</v>
@@ -3426,7 +3462,7 @@
         <v>37</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S51" s="9">
         <v>680</v>
@@ -3446,19 +3482,19 @@
         <v>46160</v>
       </c>
       <c r="E52" s="7">
-        <v>46141</v>
+        <v>46164</v>
       </c>
       <c r="F52" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G52" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>95</v>
@@ -3485,7 +3521,7 @@
         <v>37</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S52" s="9">
         <v>680</v>
@@ -3505,19 +3541,19 @@
         <v>46160</v>
       </c>
       <c r="E53" s="7">
-        <v>46164</v>
+        <v>46119</v>
       </c>
       <c r="F53" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G53" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J53" s="6" t="s">
         <v>97</v>
@@ -3544,7 +3580,7 @@
         <v>37</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S53" s="9">
         <v>680</v>
@@ -3564,19 +3600,19 @@
         <v>46160</v>
       </c>
       <c r="E54" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F54" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G54" s="8">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J54" s="6" t="s">
         <v>99</v>
@@ -3597,16 +3633,16 @@
         <v>27</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q54" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S54" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="55" ht="23" customHeight="1">
@@ -3614,28 +3650,28 @@
         <v>22</v>
       </c>
       <c r="B55" s="7">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="C55" s="7">
-        <v>46139</v>
+        <v>46160</v>
       </c>
       <c r="D55" s="7">
-        <v>46139</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E55" s="7">
+        <v>46119</v>
       </c>
       <c r="F55" s="8">
-        <v>-25</v>
+        <v>-7</v>
       </c>
       <c r="G55" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J55" s="6" t="s">
         <v>101</v>
@@ -3644,7 +3680,7 @@
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
@@ -3659,13 +3695,13 @@
         <v>28</v>
       </c>
       <c r="Q55" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S55" s="9">
-        <v>50</v>
+        <v>700</v>
       </c>
     </row>
     <row r="56" ht="23" customHeight="1">
@@ -3676,35 +3712,35 @@
         <v>46161</v>
       </c>
       <c r="C56" s="7">
-        <v>46160</v>
+        <v>46139</v>
       </c>
       <c r="D56" s="7">
-        <v>46160</v>
+        <v>46139</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F56" s="8">
-        <v>-4</v>
+        <v>-28</v>
       </c>
       <c r="G56" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J56" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="K56" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L56" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
       </c>
@@ -3715,7 +3751,7 @@
         <v>27</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q56" s="6" t="s">
         <v>23</v>
@@ -3724,7 +3760,7 @@
         <v>29</v>
       </c>
       <c r="S56" s="9">
-        <v>130</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" ht="23" customHeight="1">
@@ -3735,25 +3771,25 @@
         <v>46161</v>
       </c>
       <c r="C57" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D57" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F57" s="8">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="G57" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J57" s="6" t="s">
         <v>104</v>
@@ -3762,10 +3798,10 @@
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="N57" s="6" t="s">
         <v>27</v>
@@ -3780,10 +3816,10 @@
         <v>23</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S57" s="9">
-        <v>277.36</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58" ht="23" customHeight="1">
@@ -3803,28 +3839,28 @@
         <v>23</v>
       </c>
       <c r="F58" s="8">
-        <v>-11</v>
+        <v>-14</v>
       </c>
       <c r="G58" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="N58" s="6" t="s">
         <v>27</v>
@@ -3839,10 +3875,10 @@
         <v>23</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S58" s="9">
-        <v>280</v>
+        <v>277.36</v>
       </c>
     </row>
     <row r="59" ht="23" customHeight="1">
@@ -3853,37 +3889,37 @@
         <v>46161</v>
       </c>
       <c r="C59" s="7">
-        <v>46113</v>
+        <v>46153</v>
       </c>
       <c r="D59" s="7">
-        <v>46150</v>
-      </c>
-      <c r="E59" s="7">
-        <v>46149</v>
+        <v>46153</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F59" s="8">
         <v>-14</v>
       </c>
       <c r="G59" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="N59" s="6" t="s">
         <v>27</v>
@@ -3895,13 +3931,13 @@
         <v>23</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S59" s="9">
-        <v>2100</v>
+        <v>280</v>
       </c>
     </row>
     <row r="60" ht="23" customHeight="1">
@@ -3909,28 +3945,28 @@
         <v>22</v>
       </c>
       <c r="B60" s="7">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="C60" s="7">
-        <v>46125</v>
+        <v>46113</v>
       </c>
       <c r="D60" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>23</v>
+        <v>46150</v>
+      </c>
+      <c r="E60" s="7">
+        <v>46149</v>
       </c>
       <c r="F60" s="8">
-        <v>-39</v>
+        <v>-17</v>
       </c>
       <c r="G60" s="8">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J60" s="6" t="s">
         <v>108</v>
@@ -3939,10 +3975,10 @@
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="N60" s="6" t="s">
         <v>27</v>
@@ -3954,13 +3990,13 @@
         <v>23</v>
       </c>
       <c r="Q60" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S60" s="9">
-        <v>50</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="61" ht="23" customHeight="1">
@@ -3971,37 +4007,37 @@
         <v>46162</v>
       </c>
       <c r="C61" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="D61" s="7">
-        <v>46146</v>
+        <v>46125</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F61" s="8">
-        <v>-18</v>
+        <v>-42</v>
       </c>
       <c r="G61" s="8">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N61" s="6" t="s">
         <v>27</v>
@@ -4016,10 +4052,10 @@
         <v>23</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S61" s="9">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" ht="23" customHeight="1">
@@ -4027,46 +4063,46 @@
         <v>22</v>
       </c>
       <c r="B62" s="7">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="C62" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D62" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F62" s="8">
-        <v>-4</v>
+        <v>-21</v>
       </c>
       <c r="G62" s="8">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="N62" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>111</v>
+        <v>27</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>23</v>
@@ -4078,7 +4114,7 @@
         <v>29</v>
       </c>
       <c r="S62" s="9">
-        <v>290</v>
+        <v>200</v>
       </c>
     </row>
     <row r="63" ht="23" customHeight="1">
@@ -4086,28 +4122,28 @@
         <v>22</v>
       </c>
       <c r="B63" s="7">
-        <v>46167</v>
+        <v>46162</v>
       </c>
       <c r="C63" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="D63" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F63" s="8">
-        <v>-11</v>
+        <v>-7</v>
       </c>
       <c r="G63" s="8">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J63" s="6" t="s">
         <v>112</v>
@@ -4116,7 +4152,7 @@
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>23</v>
@@ -4125,7 +4161,7 @@
         <v>27</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
@@ -4137,7 +4173,7 @@
         <v>29</v>
       </c>
       <c r="S63" s="9">
-        <v>130</v>
+        <v>380</v>
       </c>
     </row>
     <row r="64" ht="23" customHeight="1">
@@ -4145,58 +4181,58 @@
         <v>22</v>
       </c>
       <c r="B64" s="7">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="C64" s="7">
-        <v>46082</v>
+        <v>46160</v>
       </c>
       <c r="D64" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E64" s="7">
-        <v>46097</v>
+        <v>46160</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F64" s="8">
-        <v>3</v>
+        <v>-7</v>
       </c>
       <c r="G64" s="8">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q64" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S64" s="9">
-        <v>146.55</v>
+        <v>290</v>
       </c>
     </row>
     <row r="65" ht="23" customHeight="1">
@@ -4207,22 +4243,22 @@
         <v>46167</v>
       </c>
       <c r="C65" s="7">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="D65" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E65" s="7">
-        <v>46119</v>
+        <v>46153</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F65" s="8">
-        <v>3</v>
+        <v>-14</v>
       </c>
       <c r="G65" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="I65" s="6" t="s">
         <v>23</v>
@@ -4234,28 +4270,28 @@
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>113</v>
+        <v>27</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q65" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="R65" s="6" t="s">
         <v>29</v>
       </c>
       <c r="S65" s="9">
-        <v>600</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" ht="23" customHeight="1">
@@ -4266,19 +4302,19 @@
         <v>46167</v>
       </c>
       <c r="C66" s="7">
-        <v>46167</v>
+        <v>46082</v>
       </c>
       <c r="D66" s="7">
         <v>46167</v>
       </c>
       <c r="E66" s="7">
-        <v>46141</v>
+        <v>46097</v>
       </c>
       <c r="F66" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G66" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>23</v>
@@ -4287,34 +4323,34 @@
         <v>23</v>
       </c>
       <c r="J66" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N66" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="K66" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L66" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M66" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N66" s="6" t="s">
-        <v>113</v>
-      </c>
       <c r="O66" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q66" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S66" s="9">
-        <v>620</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="67" ht="23" customHeight="1">
@@ -4331,13 +4367,13 @@
         <v>46167</v>
       </c>
       <c r="E67" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F67" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G67" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>23</v>
@@ -4352,16 +4388,16 @@
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>23</v>
@@ -4373,7 +4409,7 @@
         <v>29</v>
       </c>
       <c r="S67" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="68" ht="23" customHeight="1">
@@ -4390,13 +4426,13 @@
         <v>46167</v>
       </c>
       <c r="E68" s="7">
-        <v>46119</v>
+        <v>46141</v>
       </c>
       <c r="F68" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G68" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>23</v>
@@ -4411,16 +4447,16 @@
         <v>23</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
@@ -4429,7 +4465,7 @@
         <v>37</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S68" s="9">
         <v>620</v>
@@ -4452,10 +4488,10 @@
         <v>46119</v>
       </c>
       <c r="F69" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G69" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>23</v>
@@ -4470,28 +4506,28 @@
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q69" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="S69" s="9">
-        <v>630</v>
+        <v>620</v>
       </c>
     </row>
     <row r="70" ht="23" customHeight="1">
@@ -4508,13 +4544,13 @@
         <v>46167</v>
       </c>
       <c r="E70" s="7">
-        <v>46150</v>
+        <v>46141</v>
       </c>
       <c r="F70" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G70" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>23</v>
@@ -4523,22 +4559,22 @@
         <v>23</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4550,7 +4586,7 @@
         <v>29</v>
       </c>
       <c r="S70" s="9">
-        <v>630</v>
+        <v>620</v>
       </c>
     </row>
     <row r="71" ht="23" customHeight="1">
@@ -4570,10 +4606,10 @@
         <v>46163</v>
       </c>
       <c r="F71" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G71" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4582,22 +4618,22 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
@@ -4626,13 +4662,13 @@
         <v>46167</v>
       </c>
       <c r="E72" s="7">
-        <v>46164</v>
+        <v>46119</v>
       </c>
       <c r="F72" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G72" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4641,25 +4677,25 @@
         <v>23</v>
       </c>
       <c r="J72" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="K72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="K72" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L72" s="6" t="s">
-        <v>123</v>
-      </c>
       <c r="M72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="Q72" s="6" t="s">
         <v>37</v>
@@ -4685,13 +4721,13 @@
         <v>46167</v>
       </c>
       <c r="E73" s="7">
-        <v>46160</v>
+        <v>46150</v>
       </c>
       <c r="F73" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G73" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4700,22 +4736,22 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>125</v>
+        <v>73</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4727,7 +4763,7 @@
         <v>29</v>
       </c>
       <c r="S73" s="9">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="74" ht="23" customHeight="1">
@@ -4744,13 +4780,13 @@
         <v>46167</v>
       </c>
       <c r="E74" s="7">
-        <v>46153</v>
+        <v>46164</v>
       </c>
       <c r="F74" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G74" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4759,22 +4795,22 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4786,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="S74" s="9">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="75" ht="23" customHeight="1">
@@ -4803,13 +4839,13 @@
         <v>46167</v>
       </c>
       <c r="E75" s="7">
-        <v>46127</v>
+        <v>46092</v>
       </c>
       <c r="F75" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G75" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>23</v>
@@ -4818,22 +4854,22 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>23</v>
@@ -4865,10 +4901,10 @@
         <v>46119</v>
       </c>
       <c r="F76" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G76" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -4877,22 +4913,22 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -4921,13 +4957,13 @@
         <v>46167</v>
       </c>
       <c r="E77" s="7">
-        <v>46092</v>
+        <v>46127</v>
       </c>
       <c r="F77" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G77" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -4936,22 +4972,22 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -4980,13 +5016,13 @@
         <v>46167</v>
       </c>
       <c r="E78" s="7">
-        <v>46119</v>
+        <v>46153</v>
       </c>
       <c r="F78" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G78" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -4995,22 +5031,22 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="M78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>23</v>
@@ -5022,7 +5058,7 @@
         <v>29</v>
       </c>
       <c r="S78" s="9">
-        <v>670</v>
+        <v>650</v>
       </c>
     </row>
     <row r="79" ht="23" customHeight="1">
@@ -5039,13 +5075,13 @@
         <v>46167</v>
       </c>
       <c r="E79" s="7">
-        <v>46113</v>
+        <v>46160</v>
       </c>
       <c r="F79" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G79" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>23</v>
@@ -5054,22 +5090,22 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
@@ -5081,7 +5117,7 @@
         <v>29</v>
       </c>
       <c r="S79" s="9">
-        <v>680</v>
+        <v>650</v>
       </c>
     </row>
     <row r="80" ht="23" customHeight="1">
@@ -5101,10 +5137,10 @@
         <v>46119</v>
       </c>
       <c r="F80" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G80" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>23</v>
@@ -5113,22 +5149,22 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="K80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="K80" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>93</v>
-      </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
@@ -5140,7 +5176,7 @@
         <v>29</v>
       </c>
       <c r="S80" s="9">
-        <v>680</v>
+        <v>670</v>
       </c>
     </row>
     <row r="81" ht="23" customHeight="1">
@@ -5157,13 +5193,13 @@
         <v>46167</v>
       </c>
       <c r="E81" s="7">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="F81" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G81" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>23</v>
@@ -5178,16 +5214,16 @@
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>23</v>
@@ -5196,7 +5232,7 @@
         <v>37</v>
       </c>
       <c r="R81" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S81" s="9">
         <v>680</v>
@@ -5216,13 +5252,13 @@
         <v>46167</v>
       </c>
       <c r="E82" s="7">
-        <v>46141</v>
+        <v>46119</v>
       </c>
       <c r="F82" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G82" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>23</v>
@@ -5237,16 +5273,16 @@
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>23</v>
@@ -5255,7 +5291,7 @@
         <v>37</v>
       </c>
       <c r="R82" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S82" s="9">
         <v>680</v>
@@ -5275,13 +5311,13 @@
         <v>46167</v>
       </c>
       <c r="E83" s="7">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F83" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G83" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>23</v>
@@ -5296,16 +5332,16 @@
         <v>23</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>23</v>
@@ -5314,7 +5350,7 @@
         <v>37</v>
       </c>
       <c r="R83" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S83" s="9">
         <v>680</v>
@@ -5334,13 +5370,13 @@
         <v>46167</v>
       </c>
       <c r="E84" s="7">
-        <v>46099</v>
+        <v>46141</v>
       </c>
       <c r="F84" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G84" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>23</v>
@@ -5355,16 +5391,16 @@
         <v>23</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="M84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>23</v>
@@ -5373,10 +5409,10 @@
         <v>37</v>
       </c>
       <c r="R84" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S84" s="9">
-        <v>700</v>
+        <v>680</v>
       </c>
     </row>
     <row r="85" ht="23" customHeight="1">
@@ -5393,13 +5429,13 @@
         <v>46167</v>
       </c>
       <c r="E85" s="7">
-        <v>46160</v>
+        <v>46119</v>
       </c>
       <c r="F85" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G85" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>23</v>
@@ -5408,34 +5444,34 @@
         <v>23</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>141</v>
+        <v>98</v>
       </c>
       <c r="M85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>142</v>
+        <v>23</v>
       </c>
       <c r="Q85" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R85" s="6" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="S85" s="9">
-        <v>1200</v>
+        <v>680</v>
       </c>
     </row>
     <row r="86" ht="23" customHeight="1">
@@ -5452,13 +5488,13 @@
         <v>46167</v>
       </c>
       <c r="E86" s="7">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="F86" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G86" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>23</v>
@@ -5467,34 +5503,34 @@
         <v>23</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>142</v>
+        <v>23</v>
       </c>
       <c r="Q86" s="6" t="s">
         <v>37</v>
       </c>
       <c r="R86" s="6" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="S86" s="9">
-        <v>1200</v>
+        <v>680</v>
       </c>
     </row>
     <row r="87" ht="23" customHeight="1">
@@ -5505,43 +5541,43 @@
         <v>46167</v>
       </c>
       <c r="C87" s="7">
-        <v>46113</v>
+        <v>46167</v>
       </c>
       <c r="D87" s="7">
-        <v>46150</v>
+        <v>46167</v>
       </c>
       <c r="E87" s="7">
-        <v>46149</v>
+        <v>46099</v>
       </c>
       <c r="F87" s="8">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="G87" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="N87" s="6" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P87" s="6" t="s">
         <v>23</v>
@@ -5550,69 +5586,482 @@
         <v>37</v>
       </c>
       <c r="R87" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="S87" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="88" ht="23" customHeight="1">
+      <c r="A88" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B88" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C88" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D88" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E88" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F88" s="8">
+        <v>0</v>
+      </c>
+      <c r="G88" s="8">
+        <v>0</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J88" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="P88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q88" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R88" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="S88" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="89" ht="23" customHeight="1">
+      <c r="A89" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B89" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C89" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D89" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E89" s="7">
+        <v>46129</v>
+      </c>
+      <c r="F89" s="8">
+        <v>0</v>
+      </c>
+      <c r="G89" s="8">
+        <v>0</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="M89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N89" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O89" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="P89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q89" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R89" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="S89" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="90" ht="23" customHeight="1">
+      <c r="A90" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B90" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C90" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D90" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E90" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F90" s="8">
+        <v>0</v>
+      </c>
+      <c r="G90" s="8">
+        <v>0</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="K90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O90" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="P90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q90" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R90" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="S90" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="91" ht="23" customHeight="1">
+      <c r="A91" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B91" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C91" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D91" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E91" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F91" s="8">
+        <v>0</v>
+      </c>
+      <c r="G91" s="8">
+        <v>0</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="K91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N91" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O91" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="P91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q91" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R91" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="S91" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="92" ht="23" customHeight="1">
+      <c r="A92" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B92" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C92" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D92" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E92" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F92" s="8">
+        <v>0</v>
+      </c>
+      <c r="G92" s="8">
+        <v>0</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J92" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="K92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N92" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O92" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="P92" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q92" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R92" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="S92" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="93" ht="23" customHeight="1">
+      <c r="A93" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B93" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C93" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D93" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E93" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F93" s="8">
+        <v>0</v>
+      </c>
+      <c r="G93" s="8">
+        <v>0</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J93" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="K93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N93" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="O93" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="P93" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="Q93" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R93" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="S93" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="94" ht="23" customHeight="1">
+      <c r="A94" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C94" s="7">
+        <v>46113</v>
+      </c>
+      <c r="D94" s="7">
+        <v>46150</v>
+      </c>
+      <c r="E94" s="7">
+        <v>46149</v>
+      </c>
+      <c r="F94" s="8">
+        <v>-17</v>
+      </c>
+      <c r="G94" s="8">
+        <v>0</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J94" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="K94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="P94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q94" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="R94" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="S87" s="9">
+      <c r="S94" s="9">
         <v>4400</v>
       </c>
     </row>
-    <row r="88" ht="23" customHeight="1">
-      <c r="A88" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B88" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C88" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D88" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E88" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F88" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G88" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H88" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I88" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J88" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K88" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L88" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M88" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N88" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O88" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P88" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q88" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R88" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S88" s="13">
-        <f>SUM(S6:S87)</f>
+    <row r="95" ht="23" customHeight="1">
+      <c r="A95" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D95" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E95" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F95" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G95" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I95" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J95" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K95" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M95" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N95" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O95" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P95" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q95" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R95" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S95" s="13">
+        <f>SUM(S6:S94)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$28</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -151,15 +151,6 @@
     <t>FA-11559</t>
   </si>
   <si>
-    <t>FA-11479</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
     <t>FA-11464</t>
   </si>
   <si>
@@ -167,9 +158,6 @@
   </si>
   <si>
     <t>FA-11553</t>
-  </si>
-  <si>
-    <t>FA-11472</t>
   </si>
   <si>
     <t>FA-11411</t>
@@ -378,7 +366,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.13657760620117" customWidth="1" style="1"/>
@@ -1191,22 +1179,22 @@
         <v>22</v>
       </c>
       <c r="B18" s="7">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="C18" s="7">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D18" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E18" s="7">
-        <v>46119</v>
+        <v>46146</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F18" s="8">
-        <v>-10</v>
+        <v>-24</v>
       </c>
       <c r="G18" s="8">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>30</v>
@@ -1224,7 +1212,7 @@
         <v>40</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N18" s="6" t="s">
         <v>27</v>
@@ -1233,16 +1221,16 @@
         <v>27</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S18" s="9">
-        <v>700</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" ht="23" customHeight="1">
@@ -1250,7 +1238,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="7">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="C19" s="7">
         <v>46146</v>
@@ -1265,7 +1253,7 @@
         <v>-24</v>
       </c>
       <c r="G19" s="8">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>30</v>
@@ -1274,16 +1262,16 @@
         <v>30</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="N19" s="6" t="s">
         <v>27</v>
@@ -1301,7 +1289,7 @@
         <v>37</v>
       </c>
       <c r="S19" s="9">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" ht="23" customHeight="1">
@@ -1309,22 +1297,22 @@
         <v>22</v>
       </c>
       <c r="B20" s="7">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="C20" s="7">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="D20" s="7">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F20" s="8">
-        <v>-24</v>
+        <v>-10</v>
       </c>
       <c r="G20" s="8">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>30</v>
@@ -1333,16 +1321,16 @@
         <v>30</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="N20" s="6" t="s">
         <v>27</v>
@@ -1360,7 +1348,7 @@
         <v>37</v>
       </c>
       <c r="S20" s="9">
-        <v>210</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="21" ht="23" customHeight="1">
@@ -1371,16 +1359,16 @@
         <v>46167</v>
       </c>
       <c r="C21" s="7">
-        <v>46153</v>
+        <v>46082</v>
       </c>
       <c r="D21" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E21" s="7">
+        <v>46097</v>
       </c>
       <c r="F21" s="8">
-        <v>-17</v>
+        <v>-3</v>
       </c>
       <c r="G21" s="8">
         <v>-3</v>
@@ -1392,13 +1380,13 @@
         <v>30</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>23</v>
@@ -1410,16 +1398,16 @@
         <v>27</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S21" s="9">
-        <v>50</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="22" ht="23" customHeight="1">
@@ -1430,16 +1418,16 @@
         <v>46167</v>
       </c>
       <c r="C22" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D22" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E22" s="7">
+        <v>46141</v>
       </c>
       <c r="F22" s="8">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="G22" s="8">
         <v>-3</v>
@@ -1451,16 +1439,16 @@
         <v>30</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="N22" s="6" t="s">
         <v>27</v>
@@ -1472,13 +1460,13 @@
         <v>23</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S22" s="9">
-        <v>61.21</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23" ht="23" customHeight="1">
@@ -1489,16 +1477,16 @@
         <v>46167</v>
       </c>
       <c r="C23" s="7">
-        <v>46082</v>
+        <v>46153</v>
       </c>
       <c r="D23" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E23" s="7">
-        <v>46097</v>
+        <v>46153</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F23" s="8">
-        <v>-3</v>
+        <v>-17</v>
       </c>
       <c r="G23" s="8">
         <v>-3</v>
@@ -1510,16 +1498,16 @@
         <v>30</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="N23" s="6" t="s">
         <v>27</v>
@@ -1531,13 +1519,13 @@
         <v>23</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S23" s="9">
-        <v>146.55</v>
+        <v>400</v>
       </c>
     </row>
     <row r="24" ht="23" customHeight="1">
@@ -1548,16 +1536,16 @@
         <v>46167</v>
       </c>
       <c r="C24" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="D24" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E24" s="7">
-        <v>46141</v>
+        <v>46160</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F24" s="8">
-        <v>-3</v>
+        <v>-10</v>
       </c>
       <c r="G24" s="8">
         <v>-3</v>
@@ -1569,14 +1557,14 @@
         <v>30</v>
       </c>
       <c r="J24" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>35</v>
-      </c>
       <c r="M24" s="6" t="s">
         <v>23</v>
       </c>
@@ -1590,13 +1578,13 @@
         <v>23</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S24" s="9">
-        <v>310</v>
+        <v>572.72</v>
       </c>
     </row>
     <row r="25" ht="23" customHeight="1">
@@ -1607,16 +1595,16 @@
         <v>46167</v>
       </c>
       <c r="C25" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="D25" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F25" s="8">
-        <v>-17</v>
+        <v>-3</v>
       </c>
       <c r="G25" s="8">
         <v>-3</v>
@@ -1637,7 +1625,7 @@
         <v>50</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>27</v>
@@ -1652,10 +1640,10 @@
         <v>23</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S25" s="9">
-        <v>400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="26" ht="23" customHeight="1">
@@ -1666,16 +1654,16 @@
         <v>46167</v>
       </c>
       <c r="C26" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D26" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E26" s="7">
+        <v>46119</v>
       </c>
       <c r="F26" s="8">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="G26" s="8">
         <v>-3</v>
@@ -1693,10 +1681,10 @@
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>27</v>
@@ -1708,13 +1696,13 @@
         <v>23</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S26" s="9">
-        <v>572.72</v>
+        <v>600</v>
       </c>
     </row>
     <row r="27" ht="23" customHeight="1">
@@ -1730,8 +1718,8 @@
       <c r="D27" s="7">
         <v>46167</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>23</v>
+      <c r="E27" s="7">
+        <v>46150</v>
       </c>
       <c r="F27" s="8">
         <v>-3</v>
@@ -1746,14 +1734,14 @@
         <v>30</v>
       </c>
       <c r="J27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="K27" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
       </c>
@@ -1767,13 +1755,13 @@
         <v>23</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S27" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="28" ht="23" customHeight="1">
@@ -1790,7 +1778,7 @@
         <v>46167</v>
       </c>
       <c r="E28" s="7">
-        <v>46119</v>
+        <v>46170</v>
       </c>
       <c r="F28" s="8">
         <v>-3</v>
@@ -1805,16 +1793,16 @@
         <v>30</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>27</v>
@@ -1832,7 +1820,7 @@
         <v>37</v>
       </c>
       <c r="S28" s="9">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row r="29" ht="23" customHeight="1">
@@ -1849,7 +1837,7 @@
         <v>46167</v>
       </c>
       <c r="E29" s="7">
-        <v>46150</v>
+        <v>46113</v>
       </c>
       <c r="F29" s="8">
         <v>-3</v>
@@ -1864,16 +1852,16 @@
         <v>30</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>27</v>
@@ -1891,7 +1879,7 @@
         <v>37</v>
       </c>
       <c r="S29" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="30" ht="23" customHeight="1">
@@ -1908,7 +1896,7 @@
         <v>46167</v>
       </c>
       <c r="E30" s="7">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="F30" s="8">
         <v>-3</v>
@@ -1923,16 +1911,16 @@
         <v>30</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -1947,10 +1935,10 @@
         <v>36</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S30" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="31" ht="23" customHeight="1">
@@ -1967,7 +1955,7 @@
         <v>46167</v>
       </c>
       <c r="E31" s="7">
-        <v>46113</v>
+        <v>46168</v>
       </c>
       <c r="F31" s="8">
         <v>-3</v>
@@ -1982,16 +1970,16 @@
         <v>30</v>
       </c>
       <c r="J31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K31" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>47</v>
-      </c>
       <c r="M31" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>27</v>
@@ -2026,7 +2014,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="7">
-        <v>46164</v>
+        <v>46141</v>
       </c>
       <c r="F32" s="8">
         <v>-3</v>
@@ -2085,7 +2073,7 @@
         <v>46167</v>
       </c>
       <c r="E33" s="7">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="F33" s="8">
         <v>-3</v>
@@ -2131,180 +2119,62 @@
       </c>
     </row>
     <row r="34" ht="23" customHeight="1">
-      <c r="A34" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C34" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D34" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E34" s="7">
-        <v>46141</v>
-      </c>
-      <c r="F34" s="8">
-        <v>-3</v>
-      </c>
-      <c r="G34" s="8">
-        <v>-3</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="M34" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N34" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O34" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P34" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q34" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R34" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S34" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="35" ht="23" customHeight="1">
-      <c r="A35" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C35" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D35" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E35" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F35" s="8">
-        <v>-3</v>
-      </c>
-      <c r="G35" s="8">
-        <v>-3</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M35" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N35" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O35" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P35" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q35" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R35" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="S35" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="36" ht="23" customHeight="1">
-      <c r="A36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G36" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="K36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="L36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="M36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="N36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="P36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R36" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="S36" s="13">
-        <f>SUM(S6:S35)</f>
+      <c r="A34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="O34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="P34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="R34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="S34" s="13">
+        <f>SUM(S6:S33)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$79</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$99</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="156">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,11 +36,11 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Inicial: 01/08/2025, Data Final: 01/06/2026</t>
+      <t>Data Inicial: 01/05/2026, Data Final: 08/06/2026</t>
     </r>
   </si>
   <si>
-    <t>Relatório exportado em Monday, June 1, 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em Tuesday, June 2, 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -103,39 +103,27 @@
     <t>1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
   </si>
   <si>
+    <t>VENCIDO ATÉ 30 DIAS</t>
+  </si>
+  <si>
+    <t>ND-11305</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>VENCIDO ENTRE 31 A 90 DIAS</t>
-  </si>
-  <si>
-    <t>ND-11305</t>
-  </si>
-  <si>
     <t>MARCELO BENTO DE ARAUJO</t>
   </si>
   <si>
     <t>VENCIDO</t>
   </si>
   <si>
+    <t>NOTA DE DÉBITO</t>
+  </si>
+  <si>
     <t>AZ EMPREENDIMENTOS</t>
   </si>
   <si>
-    <t>NOTA DE DÉBITO</t>
-  </si>
-  <si>
-    <t>1.3 UBER SUPPLIER</t>
-  </si>
-  <si>
-    <t>FA-11183</t>
-  </si>
-  <si>
-    <t>FA-11446</t>
-  </si>
-  <si>
-    <t>VENCIDO ATÉ 30 DIAS</t>
-  </si>
-  <si>
     <t>FA-11557</t>
   </si>
   <si>
@@ -154,307 +142,364 @@
     <t>FA-11553</t>
   </si>
   <si>
-    <t>FA-11411</t>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11562</t>
+  </si>
+  <si>
+    <t>FA-11773</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11676</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11691</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11280</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11759</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11487</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11486</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>FA-11690</t>
+  </si>
+  <si>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>FA-11668</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11330</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>ND-11700</t>
+  </si>
+  <si>
+    <t>FA-11473</t>
+  </si>
+  <si>
+    <t>FA-11402</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>ADRIANO TEOTONIO DA SILVA</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11480</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11617</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11709</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>FA-11746</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11780</t>
+  </si>
+  <si>
+    <t>FA-11565</t>
+  </si>
+  <si>
+    <t>FA-11566</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11717</t>
+  </si>
+  <si>
+    <t>FA-11669</t>
+  </si>
+  <si>
+    <t>FA-11794</t>
+  </si>
+  <si>
+    <t>FA-11754</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11684</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
+    <t>FA-11711</t>
+  </si>
+  <si>
+    <t>FA-11774</t>
+  </si>
+  <si>
+    <t>FA-11657</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>FA-11622</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11760</t>
+  </si>
+  <si>
+    <t>FA-11772</t>
+  </si>
+  <si>
+    <t>FA-11677</t>
+  </si>
+  <si>
+    <t>FA-11692</t>
+  </si>
+  <si>
+    <t>FA-11712</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11567</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11762</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11778</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>FA-11602</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11537</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - LUZ DIVINA</t>
+  </si>
+  <si>
+    <t>FA-11633</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11645</t>
+  </si>
+  <si>
+    <t>FA-11592</t>
+  </si>
+  <si>
+    <t>FA-11579</t>
+  </si>
+  <si>
+    <t>ND-11699</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-11747</t>
+  </si>
+  <si>
+    <t>FA-11784</t>
+  </si>
+  <si>
+    <t>FA-11722</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11569</t>
+  </si>
+  <si>
+    <t>FA-11568</t>
+  </si>
+  <si>
+    <t>FA-11670</t>
+  </si>
+  <si>
+    <t>FA-11725</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11720</t>
+  </si>
+  <si>
+    <t>FA-11723</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11796</t>
+  </si>
+  <si>
+    <t>FA-11781</t>
+  </si>
+  <si>
+    <t>FA-11685</t>
+  </si>
+  <si>
+    <t>FA-11755</t>
+  </si>
+  <si>
+    <t>FA-11795</t>
+  </si>
+  <si>
+    <t>FA-11775</t>
+  </si>
+  <si>
+    <t>FA-11506</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11658</t>
+  </si>
+  <si>
+    <t>FA-11623</t>
+  </si>
+  <si>
+    <t>FA-11436</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11414</t>
   </si>
   <si>
     <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
   </si>
   <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-11562</t>
-  </si>
-  <si>
-    <t>FA-11710</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11402</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11480</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11773</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11412</t>
-  </si>
-  <si>
-    <t>FA-11676</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11691</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11489</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11280</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11759</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11487</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11486</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>FA-11690</t>
-  </si>
-  <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>ND-11699</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>HOJE</t>
-  </si>
-  <si>
-    <t>FA-11668</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>ND-11700</t>
-  </si>
-  <si>
-    <t>FA-11473</t>
-  </si>
-  <si>
-    <t>FA-11617</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11709</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>FA-11718</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11780</t>
-  </si>
-  <si>
-    <t>FA-11746</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11565</t>
-  </si>
-  <si>
-    <t>FA-11566</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11721</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11717</t>
-  </si>
-  <si>
-    <t>FA-11719</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11669</t>
-  </si>
-  <si>
-    <t>FA-11777</t>
-  </si>
-  <si>
-    <t>FA-11794</t>
-  </si>
-  <si>
-    <t>FA-11684</t>
-  </si>
-  <si>
-    <t>GILVAN RODRIGUES MACHADO</t>
-  </si>
-  <si>
-    <t>FA-11754</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11505</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11622</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>FA-11657</t>
-  </si>
-  <si>
-    <t>LUCA ZOLI</t>
-  </si>
-  <si>
-    <t>FA-11711</t>
-  </si>
-  <si>
-    <t>FA-11774</t>
-  </si>
-  <si>
-    <t>FA-11435</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11760</t>
-  </si>
-  <si>
-    <t>FA-11772</t>
-  </si>
-  <si>
-    <t>FA-11567</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11692</t>
-  </si>
-  <si>
-    <t>FA-11677</t>
-  </si>
-  <si>
-    <t>FA-11712</t>
-  </si>
-  <si>
-    <t>FA-11413</t>
-  </si>
-  <si>
-    <t>FA-11778</t>
-  </si>
-  <si>
-    <t>FA-11330</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-11762</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>FA-11537</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11602</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>Z. FROTA INVESTIDORES - LUZ DIVINA</t>
-  </si>
-  <si>
-    <t>FA-11645</t>
-  </si>
-  <si>
-    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11633</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11579</t>
-  </si>
-  <si>
-    <t>ADRIANO TEOTONIO DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11592</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
+    <t>FA-11570</t>
+  </si>
+  <si>
+    <t>FA-11693</t>
+  </si>
+  <si>
+    <t>FA-11678</t>
+  </si>
+  <si>
+    <t>FA-11763</t>
+  </si>
+  <si>
+    <t>FA-11782</t>
+  </si>
+  <si>
+    <t>FA-11603</t>
+  </si>
+  <si>
+    <t>FA-11580</t>
+  </si>
+  <si>
+    <t>FA-11593</t>
+  </si>
+  <si>
+    <t>FA-11634</t>
+  </si>
+  <si>
+    <t>FA-11646</t>
+  </si>
+  <si>
+    <t>ND-11801</t>
   </si>
 </sst>
 </file>
@@ -597,7 +642,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S79"/>
+  <dimension ref="A1:S99"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -702,40 +747,40 @@
         <v>22</v>
       </c>
       <c r="B6" s="7">
-        <v>46134</v>
+        <v>46146</v>
       </c>
       <c r="C6" s="7">
         <v>46082</v>
       </c>
       <c r="D6" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>23</v>
+        <v>46146</v>
+      </c>
+      <c r="E6" s="7">
+        <v>46097</v>
       </c>
       <c r="F6" s="8">
-        <v>-49</v>
+        <v>-29</v>
       </c>
       <c r="G6" s="8">
-        <v>-40</v>
+        <v>-29</v>
       </c>
       <c r="H6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="K6" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>26</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N6" s="6" t="s">
         <v>27</v>
@@ -744,16 +789,16 @@
         <v>27</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S6" s="9">
-        <v>79.05</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="7">
@@ -761,40 +806,40 @@
         <v>22</v>
       </c>
       <c r="B7" s="7">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="C7" s="7">
         <v>46082</v>
       </c>
       <c r="D7" s="7">
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="E7" s="7">
         <v>46097</v>
       </c>
       <c r="F7" s="8">
-        <v>-35</v>
+        <v>-22</v>
       </c>
       <c r="G7" s="8">
-        <v>-35</v>
+        <v>-22</v>
       </c>
       <c r="H7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="K7" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L7" s="6" t="s">
         <v>26</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N7" s="6" t="s">
         <v>27</v>
@@ -803,13 +848,13 @@
         <v>27</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R7" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="R7" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="S7" s="9">
         <v>146.55</v>
@@ -820,40 +865,40 @@
         <v>22</v>
       </c>
       <c r="B8" s="7">
-        <v>46140</v>
+        <v>46153</v>
       </c>
       <c r="C8" s="7">
-        <v>46082</v>
+        <v>46153</v>
       </c>
       <c r="D8" s="7">
-        <v>46132</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>23</v>
+        <v>46153</v>
+      </c>
+      <c r="E8" s="7">
+        <v>46141</v>
       </c>
       <c r="F8" s="8">
-        <v>-42</v>
+        <v>-22</v>
       </c>
       <c r="G8" s="8">
-        <v>-34</v>
+        <v>-22</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N8" s="6" t="s">
         <v>27</v>
@@ -862,57 +907,57 @@
         <v>27</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="S8" s="9">
-        <v>104.04</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B9" s="7">
-        <v>46140</v>
+        <v>46160</v>
       </c>
       <c r="C9" s="7">
-        <v>46118</v>
+        <v>46082</v>
       </c>
       <c r="D9" s="7">
-        <v>46111</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E9" s="7">
+        <v>46097</v>
       </c>
       <c r="F9" s="8">
-        <v>-63</v>
+        <v>-15</v>
       </c>
       <c r="G9" s="8">
-        <v>-34</v>
+        <v>-15</v>
       </c>
       <c r="H9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>31</v>
-      </c>
       <c r="K9" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>26</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N9" s="6" t="s">
         <v>27</v>
@@ -921,16 +966,16 @@
         <v>27</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S9" s="9">
-        <v>275.41</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="10">
@@ -938,58 +983,58 @@
         <v>22</v>
       </c>
       <c r="B10" s="7">
-        <v>46140</v>
+        <v>46160</v>
       </c>
       <c r="C10" s="7">
-        <v>46125</v>
+        <v>46160</v>
       </c>
       <c r="D10" s="7">
-        <v>46125</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>23</v>
+        <v>46160</v>
+      </c>
+      <c r="E10" s="7">
+        <v>46141</v>
       </c>
       <c r="F10" s="8">
-        <v>-49</v>
+        <v>-15</v>
       </c>
       <c r="G10" s="8">
-        <v>-34</v>
+        <v>-15</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q10" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="K10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q10" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="R10" s="6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="S10" s="9">
-        <v>408.24</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -997,58 +1042,58 @@
         <v>22</v>
       </c>
       <c r="B11" s="7">
+        <v>46164</v>
+      </c>
+      <c r="C11" s="7">
         <v>46146</v>
-      </c>
-      <c r="C11" s="7">
-        <v>46082</v>
       </c>
       <c r="D11" s="7">
         <v>46146</v>
       </c>
-      <c r="E11" s="7">
-        <v>46097</v>
+      <c r="E11" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F11" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G11" s="8">
-        <v>-28</v>
+        <v>-11</v>
       </c>
       <c r="H11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R11" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I11" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="R11" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="S11" s="9">
-        <v>146.55</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12">
@@ -1056,40 +1101,40 @@
         <v>22</v>
       </c>
       <c r="B12" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="C12" s="7">
         <v>46082</v>
       </c>
       <c r="D12" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="E12" s="7">
         <v>46097</v>
       </c>
       <c r="F12" s="8">
-        <v>-21</v>
+        <v>-8</v>
       </c>
       <c r="G12" s="8">
-        <v>-21</v>
+        <v>-8</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N12" s="6" t="s">
         <v>27</v>
@@ -1098,13 +1143,13 @@
         <v>27</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q12" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R12" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="R12" s="6" t="s">
-        <v>28</v>
       </c>
       <c r="S12" s="9">
         <v>146.55</v>
@@ -1115,58 +1160,58 @@
         <v>22</v>
       </c>
       <c r="B13" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="C13" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="D13" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E13" s="7">
-        <v>46141</v>
+        <v>46167</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F13" s="8">
-        <v>-21</v>
+        <v>-8</v>
       </c>
       <c r="G13" s="8">
-        <v>-21</v>
+        <v>-8</v>
       </c>
       <c r="H13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R13" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q13" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S13" s="9">
-        <v>310</v>
+        <v>249.21</v>
       </c>
     </row>
     <row r="14">
@@ -1174,58 +1219,58 @@
         <v>22</v>
       </c>
       <c r="B14" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C14" s="7">
-        <v>46082</v>
+        <v>46167</v>
       </c>
       <c r="D14" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E14" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F14" s="8">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="G14" s="8">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="H14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q14" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="R14" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="S14" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15">
@@ -1233,40 +1278,40 @@
         <v>22</v>
       </c>
       <c r="B15" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="C15" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D15" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E15" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="F15" s="8">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="G15" s="8">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>38</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="N15" s="6" t="s">
         <v>27</v>
@@ -1275,16 +1320,16 @@
         <v>27</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S15" s="9">
-        <v>310</v>
+        <v>650</v>
       </c>
     </row>
     <row r="16">
@@ -1292,40 +1337,40 @@
         <v>22</v>
       </c>
       <c r="B16" s="7">
+        <v>46167</v>
+      </c>
+      <c r="C16" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D16" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E16" s="7">
         <v>46164</v>
       </c>
-      <c r="C16" s="7">
-        <v>46146</v>
-      </c>
-      <c r="D16" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>23</v>
-      </c>
       <c r="F16" s="8">
-        <v>-28</v>
+        <v>-8</v>
       </c>
       <c r="G16" s="8">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N16" s="6" t="s">
         <v>27</v>
@@ -1334,16 +1379,16 @@
         <v>27</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="S16" s="9">
-        <v>210</v>
+        <v>680</v>
       </c>
     </row>
     <row r="17">
@@ -1354,55 +1399,55 @@
         <v>46167</v>
       </c>
       <c r="C17" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D17" s="7">
-        <v>46160</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E17" s="7">
+        <v>46167</v>
       </c>
       <c r="F17" s="8">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="G17" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R17" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M17" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="N17" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O17" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P17" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q17" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R17" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S17" s="9">
-        <v>61.21</v>
+        <v>680</v>
       </c>
     </row>
     <row r="18">
@@ -1410,7 +1455,7 @@
         <v>22</v>
       </c>
       <c r="B18" s="7">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="C18" s="7">
         <v>46167</v>
@@ -1419,49 +1464,49 @@
         <v>46167</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F18" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G18" s="8">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="H18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R18" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R18" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="S18" s="9">
-        <v>120</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19">
@@ -1469,58 +1514,58 @@
         <v>22</v>
       </c>
       <c r="B19" s="7">
+        <v>46169</v>
+      </c>
+      <c r="C19" s="7">
         <v>46167</v>
-      </c>
-      <c r="C19" s="7">
-        <v>46082</v>
       </c>
       <c r="D19" s="7">
         <v>46167</v>
       </c>
-      <c r="E19" s="7">
-        <v>46097</v>
+      <c r="E19" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F19" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G19" s="8">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="H19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R19" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O19" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q19" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="R19" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="S19" s="9">
-        <v>146.55</v>
+        <v>301.57</v>
       </c>
     </row>
     <row r="20">
@@ -1528,7 +1573,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="7">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="C20" s="7">
         <v>46167</v>
@@ -1537,31 +1582,31 @@
         <v>46167</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F20" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G20" s="8">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N20" s="6" t="s">
         <v>27</v>
@@ -1570,16 +1615,16 @@
         <v>27</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="S20" s="9">
-        <v>249.21</v>
+        <v>306.75</v>
       </c>
     </row>
     <row r="21">
@@ -1587,7 +1632,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="7">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="C21" s="7">
         <v>46167</v>
@@ -1595,50 +1640,50 @@
       <c r="D21" s="7">
         <v>46167</v>
       </c>
-      <c r="E21" s="7">
-        <v>46141</v>
+      <c r="E21" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F21" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G21" s="8">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="H21" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N21" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O21" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P21" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q21" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R21" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I21" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="M21" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N21" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O21" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P21" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q21" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R21" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S21" s="9">
-        <v>310</v>
+        <v>220</v>
       </c>
     </row>
     <row r="22">
@@ -1646,58 +1691,58 @@
         <v>22</v>
       </c>
       <c r="B22" s="7">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="C22" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="D22" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F22" s="8">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="G22" s="8">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="H22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R22" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I22" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="M22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O22" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R22" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S22" s="9">
-        <v>380</v>
+        <v>233.82</v>
       </c>
     </row>
     <row r="23">
@@ -1705,40 +1750,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="7">
-        <v>46167</v>
+        <v>46172</v>
       </c>
       <c r="C23" s="7">
-        <v>46160</v>
+        <v>45930</v>
       </c>
       <c r="D23" s="7">
-        <v>46160</v>
+        <v>46172</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F23" s="8">
-        <v>-14</v>
+        <v>-3</v>
       </c>
       <c r="G23" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N23" s="6" t="s">
         <v>27</v>
@@ -1747,16 +1792,16 @@
         <v>27</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="S23" s="9">
-        <v>572.72</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="24">
@@ -1764,7 +1809,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="C24" s="7">
         <v>46167</v>
@@ -1772,50 +1817,50 @@
       <c r="D24" s="7">
         <v>46167</v>
       </c>
-      <c r="E24" s="7">
-        <v>46119</v>
+      <c r="E24" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F24" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G24" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="H24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P24" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q24" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R24" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I24" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="M24" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="N24" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O24" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q24" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R24" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S24" s="9">
-        <v>600</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25">
@@ -1823,40 +1868,40 @@
         <v>22</v>
       </c>
       <c r="B25" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="C25" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="D25" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E25" s="7">
-        <v>46170</v>
+        <v>46174</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F25" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="G25" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>27</v>
@@ -1865,16 +1910,16 @@
         <v>27</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="S25" s="9">
-        <v>650</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26">
@@ -1882,58 +1927,58 @@
         <v>22</v>
       </c>
       <c r="B26" s="7">
+        <v>46174</v>
+      </c>
+      <c r="C26" s="7">
+        <v>46143</v>
+      </c>
+      <c r="D26" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E26" s="7">
         <v>46167</v>
       </c>
-      <c r="C26" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D26" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E26" s="7">
-        <v>46113</v>
-      </c>
       <c r="F26" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="G26" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="H26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R26" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I26" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q26" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R26" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S26" s="9">
-        <v>680</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -1941,40 +1986,40 @@
         <v>22</v>
       </c>
       <c r="B27" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="C27" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="D27" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E27" s="7">
-        <v>46164</v>
+        <v>46174</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F27" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="G27" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N27" s="6" t="s">
         <v>27</v>
@@ -1983,16 +2028,16 @@
         <v>27</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S27" s="9">
-        <v>680</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28">
@@ -2000,58 +2045,58 @@
         <v>22</v>
       </c>
       <c r="B28" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="C28" s="7">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="D28" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E28" s="7">
-        <v>46167</v>
+        <v>46153</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F28" s="8">
-        <v>-7</v>
+        <v>-22</v>
       </c>
       <c r="G28" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="H28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O28" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P28" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R28" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I28" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="M28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O28" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q28" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R28" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S28" s="9">
-        <v>680</v>
+        <v>129.12</v>
       </c>
     </row>
     <row r="29">
@@ -2059,40 +2104,40 @@
         <v>22</v>
       </c>
       <c r="B29" s="7">
-        <v>46168</v>
+        <v>46174</v>
       </c>
       <c r="C29" s="7">
-        <v>46167</v>
+        <v>46082</v>
       </c>
       <c r="D29" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>23</v>
+        <v>46174</v>
+      </c>
+      <c r="E29" s="7">
+        <v>46097</v>
       </c>
       <c r="F29" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="G29" s="8">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>27</v>
@@ -2101,16 +2146,16 @@
         <v>27</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="S29" s="9">
-        <v>262.56</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="30">
@@ -2118,58 +2163,58 @@
         <v>22</v>
       </c>
       <c r="B30" s="7">
-        <v>46169</v>
+        <v>46174</v>
       </c>
       <c r="C30" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="D30" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F30" s="8">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="G30" s="8">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="H30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P30" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q30" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R30" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I30" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="M30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N30" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R30" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S30" s="9">
-        <v>220</v>
+        <v>172.72</v>
       </c>
     </row>
     <row r="31">
@@ -2177,40 +2222,40 @@
         <v>22</v>
       </c>
       <c r="B31" s="7">
-        <v>46169</v>
+        <v>46174</v>
       </c>
       <c r="C31" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="D31" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F31" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="G31" s="8">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>27</v>
@@ -2219,16 +2264,16 @@
         <v>27</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="S31" s="9">
-        <v>301.57</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32">
@@ -2236,40 +2281,40 @@
         <v>22</v>
       </c>
       <c r="B32" s="7">
-        <v>46169</v>
+        <v>46174</v>
       </c>
       <c r="C32" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="D32" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F32" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="G32" s="8">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L32" s="6" t="s">
         <v>64</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>27</v>
@@ -2278,16 +2323,16 @@
         <v>27</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="S32" s="9">
-        <v>306.75</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33">
@@ -2295,58 +2340,58 @@
         <v>22</v>
       </c>
       <c r="B33" s="7">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="C33" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="D33" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F33" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="G33" s="8">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J33" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L33" s="6" t="s">
+      <c r="M33" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N33" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P33" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="M33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N33" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O33" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P33" s="6" t="s">
-        <v>67</v>
-      </c>
       <c r="Q33" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="S33" s="9">
-        <v>220</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34">
@@ -2354,40 +2399,40 @@
         <v>22</v>
       </c>
       <c r="B34" s="7">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="C34" s="7">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="D34" s="7">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F34" s="8">
-        <v>-14</v>
+        <v>-1</v>
       </c>
       <c r="G34" s="8">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>27</v>
@@ -2396,16 +2441,16 @@
         <v>27</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="S34" s="9">
-        <v>233.82</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35">
@@ -2413,40 +2458,40 @@
         <v>22</v>
       </c>
       <c r="B35" s="7">
-        <v>46172</v>
+        <v>46174</v>
       </c>
       <c r="C35" s="7">
-        <v>45930</v>
+        <v>46167</v>
       </c>
       <c r="D35" s="7">
-        <v>46172</v>
+        <v>46167</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F35" s="8">
-        <v>-2</v>
+        <v>-8</v>
       </c>
       <c r="G35" s="8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L35" s="6" t="s">
         <v>69</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="N35" s="6" t="s">
         <v>27</v>
@@ -2455,16 +2500,16 @@
         <v>27</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="S35" s="9">
-        <v>185.5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="36">
@@ -2475,19 +2520,19 @@
         <v>46174</v>
       </c>
       <c r="C36" s="7">
-        <v>46143</v>
+        <v>46167</v>
       </c>
       <c r="D36" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E36" s="7">
-        <v>46153</v>
+        <v>46167</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F36" s="8">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="G36" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>23</v>
@@ -2499,31 +2544,31 @@
         <v>70</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L36" s="6" t="s">
         <v>71</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S36" s="9">
-        <v>50</v>
+        <v>393.43</v>
       </c>
     </row>
     <row r="37">
@@ -2540,49 +2585,49 @@
         <v>46167</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F37" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G37" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J37" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L37" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="K37" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>74</v>
-      </c>
       <c r="M37" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="S37" s="9">
-        <v>80</v>
+        <v>400</v>
       </c>
     </row>
     <row r="38">
@@ -2593,19 +2638,19 @@
         <v>46174</v>
       </c>
       <c r="C38" s="7">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="D38" s="7">
         <v>46174</v>
       </c>
       <c r="E38" s="7">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="F38" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G38" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>23</v>
@@ -2614,34 +2659,34 @@
         <v>23</v>
       </c>
       <c r="J38" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L38" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K38" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L38" s="6" t="s">
-        <v>42</v>
-      </c>
       <c r="M38" s="6" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S38" s="9">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="39">
@@ -2657,14 +2702,14 @@
       <c r="D39" s="7">
         <v>46174</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>23</v>
+      <c r="E39" s="7">
+        <v>46170</v>
       </c>
       <c r="F39" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G39" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>23</v>
@@ -2673,34 +2718,34 @@
         <v>23</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="S39" s="9">
-        <v>120</v>
+        <v>600</v>
       </c>
     </row>
     <row r="40">
@@ -2711,55 +2756,55 @@
         <v>46174</v>
       </c>
       <c r="C40" s="7">
-        <v>46153</v>
+        <v>46174</v>
       </c>
       <c r="D40" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>23</v>
+        <v>46174</v>
+      </c>
+      <c r="E40" s="7">
+        <v>46141</v>
       </c>
       <c r="F40" s="8">
-        <v>-21</v>
+        <v>-1</v>
       </c>
       <c r="G40" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q40" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R40" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I40" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="K40" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L40" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="M40" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="N40" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O40" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="P40" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q40" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R40" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S40" s="9">
-        <v>129.12</v>
+        <v>620</v>
       </c>
     </row>
     <row r="41">
@@ -2770,19 +2815,19 @@
         <v>46174</v>
       </c>
       <c r="C41" s="7">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="D41" s="7">
         <v>46174</v>
       </c>
       <c r="E41" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F41" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G41" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>23</v>
@@ -2791,34 +2836,34 @@
         <v>23</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P41" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="S41" s="9">
-        <v>146.55</v>
+        <v>620</v>
       </c>
     </row>
     <row r="42">
@@ -2829,55 +2874,55 @@
         <v>46174</v>
       </c>
       <c r="C42" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="D42" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>23</v>
+        <v>46174</v>
+      </c>
+      <c r="E42" s="7">
+        <v>46169</v>
       </c>
       <c r="F42" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="G42" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P42" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q42" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R42" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I42" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J42" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="M42" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N42" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O42" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q42" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R42" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S42" s="9">
-        <v>393.43</v>
+        <v>630</v>
       </c>
     </row>
     <row r="43">
@@ -2888,55 +2933,55 @@
         <v>46174</v>
       </c>
       <c r="C43" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="D43" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>23</v>
+        <v>46174</v>
+      </c>
+      <c r="E43" s="7">
+        <v>46163</v>
       </c>
       <c r="F43" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="G43" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N43" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q43" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R43" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I43" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J43" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="M43" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N43" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O43" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="P43" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q43" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R43" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="S43" s="9">
-        <v>400</v>
+        <v>630</v>
       </c>
     </row>
     <row r="44">
@@ -2953,13 +2998,13 @@
         <v>46174</v>
       </c>
       <c r="E44" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F44" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G44" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>23</v>
@@ -2968,34 +3013,34 @@
         <v>23</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S44" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="45">
@@ -3012,13 +3057,13 @@
         <v>46174</v>
       </c>
       <c r="E45" s="7">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="F45" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G45" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>23</v>
@@ -3030,31 +3075,31 @@
         <v>83</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S45" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="46">
@@ -3071,13 +3116,13 @@
         <v>46174</v>
       </c>
       <c r="E46" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F46" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G46" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>23</v>
@@ -3086,34 +3131,34 @@
         <v>23</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K46" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S46" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="47">
@@ -3130,13 +3175,13 @@
         <v>46174</v>
       </c>
       <c r="E47" s="7">
-        <v>46141</v>
+        <v>46168</v>
       </c>
       <c r="F47" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G47" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>23</v>
@@ -3145,34 +3190,34 @@
         <v>23</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K47" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P47" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="S47" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="48">
@@ -3189,13 +3234,13 @@
         <v>46174</v>
       </c>
       <c r="E48" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="F48" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G48" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>23</v>
@@ -3204,34 +3249,34 @@
         <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K48" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S48" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="49">
@@ -3248,13 +3293,13 @@
         <v>46174</v>
       </c>
       <c r="E49" s="7">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="F49" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G49" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>23</v>
@@ -3266,31 +3311,31 @@
         <v>89</v>
       </c>
       <c r="K49" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L49" s="6" t="s">
         <v>90</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S49" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="50">
@@ -3307,13 +3352,13 @@
         <v>46174</v>
       </c>
       <c r="E50" s="7">
-        <v>46169</v>
+        <v>46153</v>
       </c>
       <c r="F50" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G50" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>23</v>
@@ -3325,31 +3370,31 @@
         <v>91</v>
       </c>
       <c r="K50" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S50" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="51">
@@ -3365,14 +3410,14 @@
       <c r="D51" s="7">
         <v>46174</v>
       </c>
-      <c r="E51" s="7">
-        <v>46169</v>
+      <c r="E51" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F51" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G51" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>23</v>
@@ -3381,34 +3426,34 @@
         <v>23</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K51" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S51" s="9">
-        <v>630</v>
+        <v>676.84</v>
       </c>
     </row>
     <row r="52">
@@ -3425,13 +3470,13 @@
         <v>46174</v>
       </c>
       <c r="E52" s="7">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="F52" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G52" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>23</v>
@@ -3443,31 +3488,31 @@
         <v>94</v>
       </c>
       <c r="K52" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S52" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="53">
@@ -3484,13 +3529,13 @@
         <v>46174</v>
       </c>
       <c r="E53" s="7">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="F53" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G53" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>23</v>
@@ -3502,31 +3547,31 @@
         <v>95</v>
       </c>
       <c r="K53" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P53" s="6" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="S53" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="54">
@@ -3543,13 +3588,13 @@
         <v>46174</v>
       </c>
       <c r="E54" s="7">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="F54" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G54" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>23</v>
@@ -3561,31 +3606,31 @@
         <v>96</v>
       </c>
       <c r="K54" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q54" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S54" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="55">
@@ -3602,13 +3647,13 @@
         <v>46174</v>
       </c>
       <c r="E55" s="7">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="F55" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G55" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>23</v>
@@ -3620,31 +3665,31 @@
         <v>97</v>
       </c>
       <c r="K55" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L55" s="6" t="s">
         <v>98</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q55" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S55" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="56">
@@ -3661,13 +3706,13 @@
         <v>46174</v>
       </c>
       <c r="E56" s="7">
-        <v>46169</v>
+        <v>46141</v>
       </c>
       <c r="F56" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G56" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>23</v>
@@ -3679,31 +3724,31 @@
         <v>99</v>
       </c>
       <c r="K56" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L56" s="6" t="s">
         <v>100</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="S56" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="57">
@@ -3720,13 +3765,13 @@
         <v>46174</v>
       </c>
       <c r="E57" s="7">
-        <v>46127</v>
+        <v>46170</v>
       </c>
       <c r="F57" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G57" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>23</v>
@@ -3738,31 +3783,31 @@
         <v>101</v>
       </c>
       <c r="K57" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L57" s="6" t="s">
         <v>102</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S57" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="58">
@@ -3779,13 +3824,13 @@
         <v>46174</v>
       </c>
       <c r="E58" s="7">
-        <v>46153</v>
+        <v>46170</v>
       </c>
       <c r="F58" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G58" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>23</v>
@@ -3797,36 +3842,36 @@
         <v>103</v>
       </c>
       <c r="K58" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S58" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="B59" s="7">
         <v>46174</v>
@@ -3838,13 +3883,13 @@
         <v>46174</v>
       </c>
       <c r="E59" s="7">
-        <v>46160</v>
+        <v>46148</v>
       </c>
       <c r="F59" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G59" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>23</v>
@@ -3856,36 +3901,36 @@
         <v>105</v>
       </c>
       <c r="K59" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L59" s="6" t="s">
         <v>106</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="S59" s="9">
-        <v>650</v>
+        <v>800</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="s">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="B60" s="7">
         <v>46174</v>
@@ -3897,13 +3942,13 @@
         <v>46174</v>
       </c>
       <c r="E60" s="7">
-        <v>46168</v>
+        <v>46129</v>
       </c>
       <c r="F60" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G60" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>23</v>
@@ -3912,39 +3957,39 @@
         <v>23</v>
       </c>
       <c r="J60" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O60" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P60" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q60" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R60" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="K60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L60" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="M60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N60" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="O60" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q60" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R60" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="S60" s="9">
-        <v>650</v>
+        <v>800</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="B61" s="7">
         <v>46174</v>
@@ -3956,13 +4001,13 @@
         <v>46174</v>
       </c>
       <c r="E61" s="7">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="F61" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G61" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>23</v>
@@ -3971,39 +4016,39 @@
         <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="Q61" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="S61" s="9">
-        <v>650</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="B62" s="7">
         <v>46174</v>
@@ -4015,13 +4060,13 @@
         <v>46174</v>
       </c>
       <c r="E62" s="7">
-        <v>46119</v>
+        <v>46160</v>
       </c>
       <c r="F62" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G62" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>23</v>
@@ -4030,39 +4075,39 @@
         <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="K62" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="S62" s="9">
-        <v>670</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="B63" s="7">
         <v>46174</v>
@@ -4073,14 +4118,14 @@
       <c r="D63" s="7">
         <v>46174</v>
       </c>
-      <c r="E63" s="7" t="s">
-        <v>23</v>
+      <c r="E63" s="7">
+        <v>46148</v>
       </c>
       <c r="F63" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G63" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>23</v>
@@ -4089,39 +4134,39 @@
         <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="K63" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q63" s="6" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>37</v>
+        <v>112</v>
       </c>
       <c r="S63" s="9">
-        <v>676.84</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="s">
-        <v>22</v>
+        <v>110</v>
       </c>
       <c r="B64" s="7">
         <v>46174</v>
@@ -4133,13 +4178,13 @@
         <v>46174</v>
       </c>
       <c r="E64" s="7">
-        <v>46170</v>
+        <v>46148</v>
       </c>
       <c r="F64" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G64" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>23</v>
@@ -4148,34 +4193,34 @@
         <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O64" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P64" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q64" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R64" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="K64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N64" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="O64" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q64" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R64" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S64" s="9">
-        <v>680</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="65">
@@ -4183,58 +4228,58 @@
         <v>22</v>
       </c>
       <c r="B65" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C65" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D65" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E65" s="7">
-        <v>46141</v>
+        <v>46153</v>
       </c>
       <c r="F65" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G65" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K65" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="Q65" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="S65" s="9">
-        <v>680</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66">
@@ -4242,58 +4287,58 @@
         <v>22</v>
       </c>
       <c r="B66" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C66" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D66" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E66" s="7">
         <v>46167</v>
       </c>
       <c r="F66" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G66" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="K66" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q66" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S66" s="9">
-        <v>680</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67">
@@ -4301,58 +4346,58 @@
         <v>22</v>
       </c>
       <c r="B67" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C67" s="7">
-        <v>46174</v>
+        <v>46082</v>
       </c>
       <c r="D67" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E67" s="7">
-        <v>46164</v>
+        <v>46097</v>
       </c>
       <c r="F67" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G67" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="K67" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q67" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S67" s="9">
-        <v>680</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="68">
@@ -4360,58 +4405,58 @@
         <v>22</v>
       </c>
       <c r="B68" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C68" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D68" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E68" s="7">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F68" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G68" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="K68" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q68" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S68" s="9">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="69">
@@ -4419,58 +4464,58 @@
         <v>22</v>
       </c>
       <c r="B69" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C69" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D69" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E69" s="7">
-        <v>46113</v>
+        <v>46170</v>
       </c>
       <c r="F69" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G69" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K69" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q69" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S69" s="9">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="70">
@@ -4478,58 +4523,58 @@
         <v>22</v>
       </c>
       <c r="B70" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C70" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D70" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E70" s="7">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="F70" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G70" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K70" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>66</v>
+        <v>122</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>23</v>
+        <v>122</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="Q70" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S70" s="9">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="71">
@@ -4537,58 +4582,58 @@
         <v>22</v>
       </c>
       <c r="B71" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C71" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D71" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E71" s="7">
-        <v>46099</v>
+        <v>46141</v>
       </c>
       <c r="F71" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G71" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I71" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K71" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q71" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R71" s="6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="S71" s="9">
-        <v>700</v>
+        <v>620</v>
       </c>
     </row>
     <row r="72">
@@ -4596,435 +4641,1615 @@
         <v>22</v>
       </c>
       <c r="B72" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C72" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D72" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E72" s="7">
-        <v>46170</v>
+        <v>46141</v>
       </c>
       <c r="F72" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G72" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K72" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>123</v>
+        <v>31</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q72" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="S72" s="9">
-        <v>700</v>
+        <v>620</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="s">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="B73" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C73" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D73" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E73" s="7">
-        <v>46129</v>
+        <v>46163</v>
       </c>
       <c r="F73" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G73" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I73" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J73" s="6" t="s">
         <v>125</v>
       </c>
       <c r="K73" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>126</v>
+        <v>56</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q73" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>127</v>
+        <v>33</v>
       </c>
       <c r="S73" s="9">
-        <v>800</v>
+        <v>630</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="B74" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C74" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D74" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E74" s="7">
-        <v>46148</v>
+        <v>46169</v>
       </c>
       <c r="F74" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G74" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K74" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q74" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>127</v>
+        <v>33</v>
       </c>
       <c r="S74" s="9">
-        <v>800</v>
+        <v>630</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="B75" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C75" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D75" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E75" s="7">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="F75" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G75" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K75" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>132</v>
+        <v>62</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
       <c r="Q75" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="S75" s="9">
-        <v>1200</v>
+        <v>630</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B76" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C76" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D76" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E76" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F76" s="8">
+        <v>6</v>
+      </c>
+      <c r="G76" s="8">
+        <v>6</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J76" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="K76" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L76" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B76" s="7">
-        <v>46174</v>
-      </c>
-      <c r="C76" s="7">
-        <v>46174</v>
-      </c>
-      <c r="D76" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E76" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F76" s="8">
-        <v>0</v>
-      </c>
-      <c r="G76" s="8">
-        <v>0</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I76" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J76" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="K76" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L76" s="6" t="s">
-        <v>136</v>
-      </c>
       <c r="M76" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
       <c r="Q76" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R76" s="6" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="S76" s="9">
-        <v>1200</v>
+        <v>630</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="B77" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C77" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D77" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E77" s="7">
-        <v>46148</v>
+        <v>46170</v>
       </c>
       <c r="F77" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G77" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I77" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="K77" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q77" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R77" s="6" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="S77" s="9">
-        <v>1200</v>
+        <v>630</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
-        <v>130</v>
+        <v>22</v>
       </c>
       <c r="B78" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C78" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D78" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E78" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F78" s="8">
+        <v>6</v>
+      </c>
+      <c r="G78" s="8">
+        <v>6</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N78" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O78" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P78" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q78" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R78" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S78" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C79" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D79" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E79" s="7">
+        <v>46164</v>
+      </c>
+      <c r="F79" s="8">
+        <v>6</v>
+      </c>
+      <c r="G79" s="8">
+        <v>6</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="K79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L79" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="M79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N79" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O79" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q79" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R79" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S79" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C80" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D80" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E80" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F80" s="8">
+        <v>6</v>
+      </c>
+      <c r="G80" s="8">
+        <v>6</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J80" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O80" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q80" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R80" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S80" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C81" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D81" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E81" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F81" s="8">
+        <v>6</v>
+      </c>
+      <c r="G81" s="8">
+        <v>6</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J81" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="K81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L81" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N81" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O81" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q81" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R81" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S81" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C82" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D82" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E82" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F82" s="8">
+        <v>6</v>
+      </c>
+      <c r="G82" s="8">
+        <v>6</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q82" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R82" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S82" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C83" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D83" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E83" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F83" s="8">
+        <v>6</v>
+      </c>
+      <c r="G83" s="8">
+        <v>6</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="K83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L83" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="M83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N83" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O83" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q83" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R83" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S83" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C84" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D84" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E84" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F84" s="8">
+        <v>6</v>
+      </c>
+      <c r="G84" s="8">
+        <v>6</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J84" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q84" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R84" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S84" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C85" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D85" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E85" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F85" s="8">
+        <v>6</v>
+      </c>
+      <c r="G85" s="8">
+        <v>6</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J85" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="K85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L85" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="M85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N85" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O85" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q85" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R85" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S85" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C86" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D86" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E86" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F86" s="8">
+        <v>6</v>
+      </c>
+      <c r="G86" s="8">
+        <v>6</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J86" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q86" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R86" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S86" s="9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B87" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C87" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D87" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E87" s="7">
+        <v>46113</v>
+      </c>
+      <c r="F87" s="8">
+        <v>6</v>
+      </c>
+      <c r="G87" s="8">
+        <v>6</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J87" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="K87" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="M87" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="N87" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O87" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P87" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q87" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R87" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S87" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B88" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C88" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D88" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E88" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F88" s="8">
+        <v>6</v>
+      </c>
+      <c r="G88" s="8">
+        <v>6</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J88" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q88" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R88" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S88" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B89" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C89" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D89" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E89" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F89" s="8">
+        <v>6</v>
+      </c>
+      <c r="G89" s="8">
+        <v>6</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L89" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N89" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O89" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q89" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R89" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S89" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B90" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C90" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D90" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E90" s="7">
+        <v>46164</v>
+      </c>
+      <c r="F90" s="8">
+        <v>6</v>
+      </c>
+      <c r="G90" s="8">
+        <v>6</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O90" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q90" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R90" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S90" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C91" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D91" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E91" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F91" s="8">
+        <v>6</v>
+      </c>
+      <c r="G91" s="8">
+        <v>6</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="K91" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L91" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M91" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N91" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O91" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P91" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q91" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R91" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S91" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B92" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C92" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D92" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E92" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F92" s="8">
+        <v>6</v>
+      </c>
+      <c r="G92" s="8">
+        <v>6</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J92" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="K92" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N92" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O92" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P92" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q92" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R92" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="S92" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B93" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C93" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D93" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E93" s="7">
         <v>46148</v>
       </c>
-      <c r="F78" s="8">
-        <v>0</v>
-      </c>
-      <c r="G78" s="8">
-        <v>0</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I78" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J78" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="K78" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L78" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="M78" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N78" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="O78" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q78" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R78" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="S78" s="9">
+      <c r="F93" s="8">
+        <v>6</v>
+      </c>
+      <c r="G93" s="8">
+        <v>6</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J93" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="K93" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L93" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M93" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N93" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O93" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P93" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q93" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R93" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="S93" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C94" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D94" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E94" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F94" s="8">
+        <v>6</v>
+      </c>
+      <c r="G94" s="8">
+        <v>6</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J94" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="K94" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P94" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q94" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R94" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="S94" s="9">
         <v>1200</v>
       </c>
     </row>
-    <row r="79" ht="23" customHeight="1">
-      <c r="A79" s="10"/>
-      <c r="B79" s="11"/>
-      <c r="C79" s="11"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="12"/>
-      <c r="G79" s="12"/>
-      <c r="H79" s="10"/>
-      <c r="I79" s="10"/>
-      <c r="J79" s="10"/>
-      <c r="K79" s="10"/>
-      <c r="L79" s="10"/>
-      <c r="M79" s="10"/>
-      <c r="N79" s="10"/>
-      <c r="O79" s="10"/>
-      <c r="P79" s="10"/>
-      <c r="Q79" s="10"/>
-      <c r="R79" s="10"/>
-      <c r="S79" s="13">
-        <f>SUM(S6:S78)</f>
+    <row r="95">
+      <c r="A95" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B95" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C95" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D95" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E95" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F95" s="8">
+        <v>6</v>
+      </c>
+      <c r="G95" s="8">
+        <v>6</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J95" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="K95" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L95" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="M95" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N95" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O95" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P95" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q95" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R95" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="S95" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C96" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D96" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E96" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F96" s="8">
+        <v>6</v>
+      </c>
+      <c r="G96" s="8">
+        <v>6</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J96" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K96" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N96" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O96" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P96" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q96" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R96" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="S96" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C97" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D97" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E97" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F97" s="8">
+        <v>6</v>
+      </c>
+      <c r="G97" s="8">
+        <v>6</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J97" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K97" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L97" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="M97" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N97" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O97" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P97" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q97" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R97" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="S97" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B98" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C98" s="7">
+        <v>46143</v>
+      </c>
+      <c r="D98" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E98" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F98" s="8">
+        <v>6</v>
+      </c>
+      <c r="G98" s="8">
+        <v>6</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J98" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="K98" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L98" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M98" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N98" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="O98" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="P98" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q98" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R98" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S98" s="9">
+        <v>2969.17</v>
+      </c>
+    </row>
+    <row r="99" ht="23" customHeight="1">
+      <c r="A99" s="10"/>
+      <c r="B99" s="11"/>
+      <c r="C99" s="11"/>
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="12"/>
+      <c r="H99" s="10"/>
+      <c r="I99" s="10"/>
+      <c r="J99" s="10"/>
+      <c r="K99" s="10"/>
+      <c r="L99" s="10"/>
+      <c r="M99" s="10"/>
+      <c r="N99" s="10"/>
+      <c r="O99" s="10"/>
+      <c r="P99" s="10"/>
+      <c r="Q99" s="10"/>
+      <c r="R99" s="10"/>
+      <c r="S99" s="13">
+        <f>SUM(S6:S98)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$93</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,11 +36,11 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Inicial: 01/05/2026, Data Final: 07/06/2026</t>
+      <t>Data Inicial: 01/05/2026, Data Final: 08/06/2026</t>
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quarta-feira, 3 de junho de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em sexta-feira, 5 de junho de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -103,27 +103,30 @@
     <t>1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
   </si>
   <si>
+    <t>VENCIDO ENTRE 31 A 90 DIAS</t>
+  </si>
+  <si>
+    <t>ND-11305</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>MARCELO BENTO DE ARAUJO</t>
+  </si>
+  <si>
+    <t>VENCIDO</t>
+  </si>
+  <si>
+    <t>NOTA DE DÉBITO</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
     <t>VENCIDO ATÉ 30 DIAS</t>
   </si>
   <si>
-    <t>ND-11305</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>MARCELO BENTO DE ARAUJO</t>
-  </si>
-  <si>
-    <t>VENCIDO</t>
-  </si>
-  <si>
-    <t>NOTA DE DÉBITO</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
     <t>FA-11557</t>
   </si>
   <si>
@@ -220,115 +223,271 @@
     <t>ANDRE CAVALCANTI DA FE</t>
   </si>
   <si>
-    <t>FA-11746</t>
+    <t>FA-11780</t>
+  </si>
+  <si>
+    <t>FA-11565</t>
+  </si>
+  <si>
+    <t>FA-11566</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11717</t>
+  </si>
+  <si>
+    <t>FA-11669</t>
+  </si>
+  <si>
+    <t>FA-11794</t>
+  </si>
+  <si>
+    <t>FA-11684</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
+    <t>FA-11622</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11711</t>
+  </si>
+  <si>
+    <t>FA-11774</t>
+  </si>
+  <si>
+    <t>FA-11567</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11692</t>
+  </si>
+  <si>
+    <t>FA-11712</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11677</t>
+  </si>
+  <si>
+    <t>FA-11772</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>FA-11537</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11602</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>1.3 UBER SUPPLIER</t>
+  </si>
+  <si>
+    <t>FA-11808</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11804</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11760</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>ND-11699</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LOCACAO DE ATIVOS</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA EMPREENDIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>FA-11722</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11784</t>
+  </si>
+  <si>
+    <t>FA-11747</t>
   </si>
   <si>
     <t>ROBERTO MURATORI</t>
   </si>
   <si>
-    <t>FA-11780</t>
-  </si>
-  <si>
-    <t>FA-11566</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11565</t>
-  </si>
-  <si>
-    <t>FA-11794</t>
-  </si>
-  <si>
-    <t>FA-11684</t>
-  </si>
-  <si>
-    <t>GILVAN RODRIGUES MACHADO</t>
-  </si>
-  <si>
-    <t>FA-11717</t>
-  </si>
-  <si>
-    <t>FA-11669</t>
-  </si>
-  <si>
-    <t>FA-11711</t>
-  </si>
-  <si>
-    <t>FA-11774</t>
-  </si>
-  <si>
-    <t>FA-11622</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>FA-11657</t>
+    <t>FA-11568</t>
+  </si>
+  <si>
+    <t>FA-11569</t>
+  </si>
+  <si>
+    <t>FA-11805</t>
+  </si>
+  <si>
+    <t>FA-11725</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11720</t>
+  </si>
+  <si>
+    <t>FA-11723</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11670</t>
+  </si>
+  <si>
+    <t>FA-11755</t>
+  </si>
+  <si>
+    <t>FA-11781</t>
+  </si>
+  <si>
+    <t>FA-11796</t>
+  </si>
+  <si>
+    <t>FA-11685</t>
+  </si>
+  <si>
+    <t>FA-11795</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11623</t>
+  </si>
+  <si>
+    <t>FA-11506</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11775</t>
+  </si>
+  <si>
+    <t>FA-11658</t>
   </si>
   <si>
     <t>LUCA ZOLI</t>
   </si>
   <si>
-    <t>FA-11692</t>
-  </si>
-  <si>
-    <t>FA-11567</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11772</t>
-  </si>
-  <si>
-    <t>FA-11677</t>
-  </si>
-  <si>
-    <t>FA-11712</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>FA-11537</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11602</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>1.3 UBER SUPPLIER</t>
-  </si>
-  <si>
-    <t>FA-11808</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11804</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11760</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
+    <t>FA-11436</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11570</t>
+  </si>
+  <si>
+    <t>FA-11693</t>
+  </si>
+  <si>
+    <t>FA-11678</t>
+  </si>
+  <si>
+    <t>FA-11809</t>
+  </si>
+  <si>
+    <t>FA-11414</t>
+  </si>
+  <si>
+    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11782</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11763</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11603</t>
+  </si>
+  <si>
+    <t>FA-11580</t>
+  </si>
+  <si>
+    <t>ADRIANO TEOTONIO DA SILVA</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11593</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>FA-11634</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>FA-11646</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>ND-11801</t>
   </si>
 </sst>
 </file>
@@ -471,7 +630,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S93"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -588,10 +747,10 @@
         <v>46097</v>
       </c>
       <c r="F6" s="8">
-        <v>-30</v>
+        <v>-32</v>
       </c>
       <c r="G6" s="8">
-        <v>-30</v>
+        <v>-32</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>23</v>
@@ -647,16 +806,16 @@
         <v>46097</v>
       </c>
       <c r="F7" s="8">
-        <v>-23</v>
+        <v>-25</v>
       </c>
       <c r="G7" s="8">
-        <v>-23</v>
+        <v>-25</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>24</v>
@@ -706,25 +865,25 @@
         <v>46141</v>
       </c>
       <c r="F8" s="8">
-        <v>-23</v>
+        <v>-25</v>
       </c>
       <c r="G8" s="8">
-        <v>-23</v>
+        <v>-25</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>25</v>
@@ -739,10 +898,10 @@
         <v>25</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S8" s="9">
         <v>310</v>
@@ -765,16 +924,16 @@
         <v>46097</v>
       </c>
       <c r="F9" s="8">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="G9" s="8">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>24</v>
@@ -824,43 +983,43 @@
         <v>46141</v>
       </c>
       <c r="F10" s="8">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="G10" s="8">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R10" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O10" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="R10" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="S10" s="9">
         <v>310</v>
@@ -883,25 +1042,25 @@
         <v>25</v>
       </c>
       <c r="F11" s="8">
-        <v>-30</v>
+        <v>-32</v>
       </c>
       <c r="G11" s="8">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>25</v>
@@ -919,7 +1078,7 @@
         <v>25</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S11" s="9">
         <v>210</v>
@@ -942,16 +1101,16 @@
         <v>46097</v>
       </c>
       <c r="F12" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="G12" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>24</v>
@@ -1001,16 +1160,16 @@
         <v>25</v>
       </c>
       <c r="F13" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="G13" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>25</v>
@@ -1019,7 +1178,7 @@
         <v>25</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>25</v>
@@ -1037,7 +1196,7 @@
         <v>25</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S13" s="9">
         <v>249.21</v>
@@ -1060,25 +1219,25 @@
         <v>46141</v>
       </c>
       <c r="F14" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="G14" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>25</v>
@@ -1093,10 +1252,10 @@
         <v>25</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S14" s="9">
         <v>310</v>
@@ -1119,28 +1278,28 @@
         <v>46170</v>
       </c>
       <c r="F15" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="G15" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N15" s="6" t="s">
         <v>27</v>
@@ -1152,10 +1311,10 @@
         <v>25</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S15" s="9">
         <v>650</v>
@@ -1178,25 +1337,25 @@
         <v>46164</v>
       </c>
       <c r="F16" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="G16" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>25</v>
@@ -1211,7 +1370,7 @@
         <v>25</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>29</v>
@@ -1237,25 +1396,25 @@
         <v>46167</v>
       </c>
       <c r="F17" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="G17" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>25</v>
@@ -1270,10 +1429,10 @@
         <v>25</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S17" s="9">
         <v>680</v>
@@ -1296,26 +1455,26 @@
         <v>25</v>
       </c>
       <c r="F18" s="8">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="G18" s="8">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J18" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="K18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="M18" s="6" t="s">
         <v>25</v>
       </c>
@@ -1332,7 +1491,7 @@
         <v>25</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S18" s="9">
         <v>233.82</v>
@@ -1355,16 +1514,16 @@
         <v>25</v>
       </c>
       <c r="F19" s="8">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="G19" s="8">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>25</v>
@@ -1373,7 +1532,7 @@
         <v>25</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>25</v>
@@ -1414,25 +1573,25 @@
         <v>25</v>
       </c>
       <c r="F20" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="G20" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>25</v>
@@ -1450,7 +1609,7 @@
         <v>25</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S20" s="9">
         <v>80</v>
@@ -1473,25 +1632,25 @@
         <v>46167</v>
       </c>
       <c r="F21" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G21" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>25</v>
@@ -1509,7 +1668,7 @@
         <v>28</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S21" s="9">
         <v>100</v>
@@ -1532,16 +1691,16 @@
         <v>25</v>
       </c>
       <c r="F22" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G22" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>25</v>
@@ -1550,10 +1709,10 @@
         <v>25</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N22" s="6" t="s">
         <v>27</v>
@@ -1591,16 +1750,16 @@
         <v>25</v>
       </c>
       <c r="F23" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G23" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>25</v>
@@ -1609,10 +1768,10 @@
         <v>25</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N23" s="6" t="s">
         <v>27</v>
@@ -1650,28 +1809,28 @@
         <v>25</v>
       </c>
       <c r="F24" s="8">
-        <v>-23</v>
+        <v>-25</v>
       </c>
       <c r="G24" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>27</v>
@@ -1686,7 +1845,7 @@
         <v>25</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S24" s="9">
         <v>129.12</v>
@@ -1709,16 +1868,16 @@
         <v>46097</v>
       </c>
       <c r="F25" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G25" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>24</v>
@@ -1768,25 +1927,25 @@
         <v>25</v>
       </c>
       <c r="F26" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G26" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>25</v>
@@ -1804,7 +1963,7 @@
         <v>25</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S26" s="9">
         <v>164.07</v>
@@ -1827,25 +1986,25 @@
         <v>25</v>
       </c>
       <c r="F27" s="8">
-        <v>-16</v>
+        <v>-18</v>
       </c>
       <c r="G27" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>25</v>
@@ -1863,7 +2022,7 @@
         <v>25</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S27" s="9">
         <v>172.72</v>
@@ -1886,28 +2045,28 @@
         <v>25</v>
       </c>
       <c r="F28" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="G28" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>27</v>
@@ -1922,7 +2081,7 @@
         <v>25</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S28" s="9">
         <v>350</v>
@@ -1945,25 +2104,25 @@
         <v>25</v>
       </c>
       <c r="F29" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="G29" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>25</v>
@@ -1981,7 +2140,7 @@
         <v>25</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S29" s="9">
         <v>393.43</v>
@@ -2004,25 +2163,25 @@
         <v>25</v>
       </c>
       <c r="F30" s="8">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="G30" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>25</v>
@@ -2060,31 +2219,31 @@
         <v>46174</v>
       </c>
       <c r="E31" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F31" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G31" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>27</v>
@@ -2096,10 +2255,10 @@
         <v>25</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S31" s="9">
         <v>600</v>
@@ -2119,19 +2278,19 @@
         <v>46174</v>
       </c>
       <c r="E32" s="7">
-        <v>46170</v>
+        <v>46141</v>
       </c>
       <c r="F32" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G32" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>64</v>
@@ -2140,10 +2299,10 @@
         <v>25</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>27</v>
@@ -2155,13 +2314,13 @@
         <v>25</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S32" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="33">
@@ -2181,16 +2340,16 @@
         <v>46141</v>
       </c>
       <c r="F33" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G33" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J33" s="6" t="s">
         <v>65</v>
@@ -2214,10 +2373,10 @@
         <v>25</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S33" s="9">
         <v>620</v>
@@ -2237,19 +2396,19 @@
         <v>46174</v>
       </c>
       <c r="E34" s="7">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="F34" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G34" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>67</v>
@@ -2258,7 +2417,7 @@
         <v>25</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>25</v>
@@ -2273,13 +2432,13 @@
         <v>25</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S34" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="35">
@@ -2296,19 +2455,19 @@
         <v>46174</v>
       </c>
       <c r="E35" s="7">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="F35" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G35" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J35" s="6" t="s">
         <v>68</v>
@@ -2317,7 +2476,7 @@
         <v>25</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>25</v>
@@ -2332,10 +2491,10 @@
         <v>25</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S35" s="9">
         <v>630</v>
@@ -2355,19 +2514,19 @@
         <v>46174</v>
       </c>
       <c r="E36" s="7">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="F36" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G36" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>69</v>
@@ -2376,7 +2535,7 @@
         <v>25</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>25</v>
@@ -2391,10 +2550,10 @@
         <v>25</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S36" s="9">
         <v>630</v>
@@ -2414,29 +2573,29 @@
         <v>46174</v>
       </c>
       <c r="E37" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F37" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G37" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J37" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L37" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="K37" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>55</v>
-      </c>
       <c r="M37" s="6" t="s">
         <v>25</v>
       </c>
@@ -2450,10 +2609,10 @@
         <v>25</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S37" s="9">
         <v>630</v>
@@ -2473,19 +2632,19 @@
         <v>46174</v>
       </c>
       <c r="E38" s="7">
-        <v>46163</v>
+        <v>46153</v>
       </c>
       <c r="F38" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G38" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J38" s="6" t="s">
         <v>72</v>
@@ -2494,7 +2653,7 @@
         <v>25</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>25</v>
@@ -2509,13 +2668,13 @@
         <v>25</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S38" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="39">
@@ -2535,25 +2694,25 @@
         <v>46168</v>
       </c>
       <c r="F39" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G39" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>25</v>
@@ -2568,7 +2727,7 @@
         <v>25</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>29</v>
@@ -2594,28 +2753,28 @@
         <v>46170</v>
       </c>
       <c r="F40" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G40" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>27</v>
@@ -2627,10 +2786,10 @@
         <v>25</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S40" s="9">
         <v>650</v>
@@ -2650,28 +2809,28 @@
         <v>46174</v>
       </c>
       <c r="E41" s="7">
-        <v>46153</v>
+        <v>46141</v>
       </c>
       <c r="F41" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G41" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>25</v>
@@ -2686,13 +2845,13 @@
         <v>25</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S41" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="42">
@@ -2709,28 +2868,28 @@
         <v>46174</v>
       </c>
       <c r="E42" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="F42" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G42" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>25</v>
@@ -2745,13 +2904,13 @@
         <v>25</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S42" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="43">
@@ -2768,19 +2927,19 @@
         <v>46174</v>
       </c>
       <c r="E43" s="7">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F43" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G43" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J43" s="6" t="s">
         <v>79</v>
@@ -2789,7 +2948,7 @@
         <v>25</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>25</v>
@@ -2804,10 +2963,10 @@
         <v>25</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S43" s="9">
         <v>680</v>
@@ -2827,28 +2986,28 @@
         <v>46174</v>
       </c>
       <c r="E44" s="7">
-        <v>46141</v>
+        <v>46164</v>
       </c>
       <c r="F44" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G44" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>25</v>
@@ -2863,7 +3022,7 @@
         <v>25</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>29</v>
@@ -2889,16 +3048,16 @@
         <v>46170</v>
       </c>
       <c r="F45" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G45" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J45" s="6" t="s">
         <v>82</v>
@@ -2907,7 +3066,7 @@
         <v>25</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>25</v>
@@ -2922,10 +3081,10 @@
         <v>25</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S45" s="9">
         <v>680</v>
@@ -2933,7 +3092,7 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="B46" s="7">
         <v>46174</v>
@@ -2945,28 +3104,28 @@
         <v>46174</v>
       </c>
       <c r="E46" s="7">
-        <v>46164</v>
+        <v>46129</v>
       </c>
       <c r="F46" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G46" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>25</v>
@@ -2981,18 +3140,18 @@
         <v>25</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="S46" s="9">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="B47" s="7">
         <v>46174</v>
@@ -3004,28 +3163,28 @@
         <v>46174</v>
       </c>
       <c r="E47" s="7">
-        <v>46168</v>
+        <v>46148</v>
       </c>
       <c r="F47" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G47" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>25</v>
@@ -3040,21 +3199,21 @@
         <v>25</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="S47" s="9">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B48" s="7">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C48" s="7">
         <v>46174</v>
@@ -3062,29 +3221,29 @@
       <c r="D48" s="7">
         <v>46174</v>
       </c>
-      <c r="E48" s="7">
-        <v>46129</v>
+      <c r="E48" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F48" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G48" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>25</v>
@@ -3099,21 +3258,21 @@
         <v>25</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="S48" s="9">
-        <v>800</v>
+        <v>117.45</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="B49" s="7">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C49" s="7">
         <v>46174</v>
@@ -3121,32 +3280,32 @@
       <c r="D49" s="7">
         <v>46174</v>
       </c>
-      <c r="E49" s="7">
-        <v>46148</v>
+      <c r="E49" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F49" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G49" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="N49" s="6" t="s">
         <v>27</v>
@@ -3158,18 +3317,18 @@
         <v>25</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>89</v>
+        <v>29</v>
       </c>
       <c r="S49" s="9">
-        <v>800</v>
+        <v>228.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="B50" s="7">
         <v>46175</v>
@@ -3184,25 +3343,25 @@
         <v>25</v>
       </c>
       <c r="F50" s="8">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="G50" s="8">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>25</v>
@@ -3220,10 +3379,10 @@
         <v>25</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S50" s="9">
-        <v>117.45</v>
+        <v>301.57</v>
       </c>
     </row>
     <row r="51">
@@ -3231,58 +3390,58 @@
         <v>22</v>
       </c>
       <c r="B51" s="7">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="C51" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D51" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>25</v>
+        <v>46181</v>
+      </c>
+      <c r="E51" s="7">
+        <v>46153</v>
       </c>
       <c r="F51" s="8">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="G51" s="8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S51" s="9">
-        <v>228.2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52">
@@ -3290,81 +3449,2441 @@
         <v>22</v>
       </c>
       <c r="B52" s="7">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="C52" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D52" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>25</v>
+        <v>46181</v>
+      </c>
+      <c r="E52" s="7">
+        <v>46167</v>
       </c>
       <c r="F52" s="8">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="G52" s="8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J52" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O52" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P52" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q52" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R52" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S52" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C53" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D53" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="8">
+        <v>3</v>
+      </c>
+      <c r="G53" s="8">
+        <v>3</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O53" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P53" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q53" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R53" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S53" s="9">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C54" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D54" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="8">
+        <v>3</v>
+      </c>
+      <c r="G54" s="8">
+        <v>3</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O54" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P54" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q54" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R54" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S54" s="9">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B55" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C55" s="7">
+        <v>46082</v>
+      </c>
+      <c r="D55" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E55" s="7">
+        <v>46097</v>
+      </c>
+      <c r="F55" s="8">
+        <v>3</v>
+      </c>
+      <c r="G55" s="8">
+        <v>3</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N55" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O55" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P55" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q55" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R55" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S55" s="9">
+        <v>146.55</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C56" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D56" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="8">
+        <v>3</v>
+      </c>
+      <c r="G56" s="8">
+        <v>3</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O56" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P56" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q56" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R56" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S56" s="9">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C57" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D57" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="8">
+        <v>3</v>
+      </c>
+      <c r="G57" s="8">
+        <v>3</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J57" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M57" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="N57" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O57" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P57" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q57" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R57" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S57" s="9">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C58" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D58" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="8">
+        <v>3</v>
+      </c>
+      <c r="G58" s="8">
+        <v>3</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O58" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P58" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q58" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R58" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S58" s="9">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C59" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D59" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="8">
+        <v>3</v>
+      </c>
+      <c r="G59" s="8">
+        <v>3</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L59" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M59" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="N59" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O59" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P59" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q59" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="R59" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="S59" s="9">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C60" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D60" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E60" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F60" s="8">
+        <v>3</v>
+      </c>
+      <c r="G60" s="8">
+        <v>3</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O60" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P60" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q60" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R60" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S60" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C61" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D61" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E61" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F61" s="8">
+        <v>3</v>
+      </c>
+      <c r="G61" s="8">
+        <v>3</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L61" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M61" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="N61" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O61" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q61" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R61" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S61" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B62" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C62" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D62" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E62" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F62" s="8">
+        <v>3</v>
+      </c>
+      <c r="G62" s="8">
+        <v>3</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O62" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P62" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q62" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R62" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S62" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C63" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D63" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E63" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F63" s="8">
+        <v>3</v>
+      </c>
+      <c r="G63" s="8">
+        <v>3</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L63" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M63" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N63" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O63" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P63" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q63" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R63" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S63" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B64" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C64" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D64" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E64" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F64" s="8">
+        <v>3</v>
+      </c>
+      <c r="G64" s="8">
+        <v>3</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O64" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P64" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q64" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R64" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S64" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C65" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D65" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E65" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F65" s="8">
+        <v>3</v>
+      </c>
+      <c r="G65" s="8">
+        <v>3</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="N65" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O65" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P65" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q65" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R65" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S65" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B66" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C66" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D66" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E66" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F66" s="8">
+        <v>3</v>
+      </c>
+      <c r="G66" s="8">
+        <v>3</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O66" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P66" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q66" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R66" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S66" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C67" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D67" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E67" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F67" s="8">
+        <v>3</v>
+      </c>
+      <c r="G67" s="8">
+        <v>3</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M67" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N67" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O67" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P67" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q67" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R67" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S67" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C68" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D68" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E68" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F68" s="8">
+        <v>3</v>
+      </c>
+      <c r="G68" s="8">
+        <v>3</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O68" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P68" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q68" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R68" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S68" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C69" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D69" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E69" s="7">
+        <v>46163</v>
+      </c>
+      <c r="F69" s="8">
+        <v>3</v>
+      </c>
+      <c r="G69" s="8">
+        <v>3</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J69" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K69" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L69" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M69" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N69" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O69" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P69" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q69" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R69" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S69" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C70" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D70" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E70" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F70" s="8">
+        <v>3</v>
+      </c>
+      <c r="G70" s="8">
+        <v>3</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O70" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P70" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q70" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R70" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S70" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B71" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C71" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D71" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E71" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F71" s="8">
+        <v>3</v>
+      </c>
+      <c r="G71" s="8">
+        <v>3</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="K71" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L71" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="K52" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="M52" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N52" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O52" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q52" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="R52" s="6" t="s">
+      <c r="M71" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N71" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O71" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P71" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q71" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="S52" s="9">
-        <v>301.57</v>
-      </c>
-    </row>
-    <row r="53" ht="23" customHeight="1">
-      <c r="A53" s="10"/>
-      <c r="B53" s="11"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
-      <c r="N53" s="10"/>
-      <c r="O53" s="10"/>
-      <c r="P53" s="10"/>
-      <c r="Q53" s="10"/>
-      <c r="R53" s="10"/>
-      <c r="S53" s="13">
-        <f>SUM(S6:S52)</f>
+      <c r="R71" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S71" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C72" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D72" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E72" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F72" s="8">
+        <v>3</v>
+      </c>
+      <c r="G72" s="8">
+        <v>3</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="K72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O72" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q72" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R72" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S72" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B73" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C73" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D73" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E73" s="7">
+        <v>46164</v>
+      </c>
+      <c r="F73" s="8">
+        <v>3</v>
+      </c>
+      <c r="G73" s="8">
+        <v>3</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="K73" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L73" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M73" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N73" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O73" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P73" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q73" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R73" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S73" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B74" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C74" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D74" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E74" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F74" s="8">
+        <v>3</v>
+      </c>
+      <c r="G74" s="8">
+        <v>3</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J74" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P74" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q74" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R74" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S74" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B75" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C75" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D75" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E75" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F75" s="8">
+        <v>3</v>
+      </c>
+      <c r="G75" s="8">
+        <v>3</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="K75" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L75" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="M75" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N75" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O75" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P75" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q75" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R75" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S75" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B76" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C76" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D76" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E76" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F76" s="8">
+        <v>3</v>
+      </c>
+      <c r="G76" s="8">
+        <v>3</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J76" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K76" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O76" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P76" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q76" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R76" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S76" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B77" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C77" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D77" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E77" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F77" s="8">
+        <v>3</v>
+      </c>
+      <c r="G77" s="8">
+        <v>3</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J77" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K77" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L77" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="M77" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N77" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O77" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P77" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q77" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R77" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S77" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B78" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C78" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D78" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E78" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F78" s="8">
+        <v>3</v>
+      </c>
+      <c r="G78" s="8">
+        <v>3</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N78" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O78" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q78" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R78" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S78" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C79" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D79" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E79" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F79" s="8">
+        <v>3</v>
+      </c>
+      <c r="G79" s="8">
+        <v>3</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L79" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="M79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N79" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O79" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q79" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R79" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S79" s="9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C80" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D80" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E80" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F80" s="8">
+        <v>3</v>
+      </c>
+      <c r="G80" s="8">
+        <v>3</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J80" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="K80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O80" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q80" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R80" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S80" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C81" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D81" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E81" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F81" s="8">
+        <v>3</v>
+      </c>
+      <c r="G81" s="8">
+        <v>3</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J81" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="K81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L81" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N81" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O81" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q81" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R81" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S81" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C82" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D82" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E82" s="7">
+        <v>46164</v>
+      </c>
+      <c r="F82" s="8">
+        <v>3</v>
+      </c>
+      <c r="G82" s="8">
+        <v>3</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q82" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R82" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S82" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C83" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D83" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E83" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F83" s="8">
+        <v>3</v>
+      </c>
+      <c r="G83" s="8">
+        <v>3</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="K83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L83" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="M83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N83" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O83" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q83" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R83" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S83" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C84" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D84" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E84" s="7">
+        <v>46113</v>
+      </c>
+      <c r="F84" s="8">
+        <v>3</v>
+      </c>
+      <c r="G84" s="8">
+        <v>3</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J84" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q84" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R84" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S84" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C85" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D85" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E85" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F85" s="8">
+        <v>3</v>
+      </c>
+      <c r="G85" s="8">
+        <v>3</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J85" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="K85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L85" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="M85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N85" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O85" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P85" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q85" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R85" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S85" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C86" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D86" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E86" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F86" s="8">
+        <v>3</v>
+      </c>
+      <c r="G86" s="8">
+        <v>3</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J86" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="K86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q86" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R86" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="S86" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B87" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C87" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D87" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E87" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F87" s="8">
+        <v>3</v>
+      </c>
+      <c r="G87" s="8">
+        <v>3</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J87" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="K87" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M87" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N87" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O87" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P87" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q87" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R87" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="S87" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B88" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C88" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D88" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E88" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F88" s="8">
+        <v>3</v>
+      </c>
+      <c r="G88" s="8">
+        <v>3</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J88" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q88" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R88" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="S88" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B89" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C89" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D89" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E89" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F89" s="8">
+        <v>3</v>
+      </c>
+      <c r="G89" s="8">
+        <v>3</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="K89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L89" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="M89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N89" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O89" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q89" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R89" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="S89" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B90" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C90" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D90" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E90" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F90" s="8">
+        <v>3</v>
+      </c>
+      <c r="G90" s="8">
+        <v>3</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O90" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P90" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q90" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R90" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="S90" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C91" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D91" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E91" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F91" s="8">
+        <v>3</v>
+      </c>
+      <c r="G91" s="8">
+        <v>3</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="K91" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L91" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="M91" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N91" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O91" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P91" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q91" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="R91" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="S91" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B92" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C92" s="7">
+        <v>46143</v>
+      </c>
+      <c r="D92" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E92" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F92" s="8">
+        <v>3</v>
+      </c>
+      <c r="G92" s="8">
+        <v>3</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J92" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="K92" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N92" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="O92" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="P92" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q92" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="R92" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S92" s="9">
+        <v>2969.17</v>
+      </c>
+    </row>
+    <row r="93" ht="23" customHeight="1">
+      <c r="A93" s="10"/>
+      <c r="B93" s="11"/>
+      <c r="C93" s="11"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="11"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
+      <c r="H93" s="10"/>
+      <c r="I93" s="10"/>
+      <c r="J93" s="10"/>
+      <c r="K93" s="10"/>
+      <c r="L93" s="10"/>
+      <c r="M93" s="10"/>
+      <c r="N93" s="10"/>
+      <c r="O93" s="10"/>
+      <c r="P93" s="10"/>
+      <c r="Q93" s="10"/>
+      <c r="R93" s="10"/>
+      <c r="S93" s="13">
+        <f>SUM(S6:S92)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$93</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$84</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -151,310 +151,286 @@
     <t>FA-11562</t>
   </si>
   <si>
-    <t>FA-11773</t>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>FA-11668</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>ND-11700</t>
+  </si>
+  <si>
+    <t>JOAO PAULO CONSORCIOS</t>
+  </si>
+  <si>
+    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
+  </si>
+  <si>
+    <t>FA-11473</t>
   </si>
   <si>
     <t>DERICK PEDRO BEZERRA DA ROCHA</t>
   </si>
   <si>
-    <t>FA-11676</t>
+    <t>FA-11754</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11402</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11565</t>
+  </si>
+  <si>
+    <t>FA-11480</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11617</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11709</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>FA-11780</t>
+  </si>
+  <si>
+    <t>FA-11566</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11717</t>
+  </si>
+  <si>
+    <t>FA-11669</t>
+  </si>
+  <si>
+    <t>FA-11794</t>
+  </si>
+  <si>
+    <t>FA-11711</t>
+  </si>
+  <si>
+    <t>FA-11774</t>
+  </si>
+  <si>
+    <t>FA-11677</t>
   </si>
   <si>
     <t>RAMON TALLES BARBALHO DE FRANÇA</t>
   </si>
   <si>
-    <t>FA-11691</t>
+    <t>FA-11712</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11772</t>
+  </si>
+  <si>
+    <t>FA-11567</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11692</t>
   </si>
   <si>
     <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
   </si>
   <si>
-    <t>FA-11690</t>
-  </si>
-  <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>FA-11668</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>ND-11700</t>
-  </si>
-  <si>
-    <t>JOAO PAULO CONSORCIOS</t>
-  </si>
-  <si>
-    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
-  </si>
-  <si>
-    <t>FA-11473</t>
-  </si>
-  <si>
-    <t>FA-11754</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11402</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11480</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11617</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11709</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>FA-11780</t>
-  </si>
-  <si>
-    <t>FA-11565</t>
-  </si>
-  <si>
-    <t>FA-11566</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11717</t>
-  </si>
-  <si>
-    <t>FA-11669</t>
-  </si>
-  <si>
-    <t>FA-11794</t>
-  </si>
-  <si>
-    <t>FA-11684</t>
+    <t>FA-11804</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11760</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>ND-11699</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LOCACAO DE ATIVOS</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA EMPREENDIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>FA-11722</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11784</t>
+  </si>
+  <si>
+    <t>FA-11747</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11568</t>
+  </si>
+  <si>
+    <t>FA-11569</t>
+  </si>
+  <si>
+    <t>FA-11805</t>
+  </si>
+  <si>
+    <t>FA-11725</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11720</t>
+  </si>
+  <si>
+    <t>FA-11723</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11781</t>
+  </si>
+  <si>
+    <t>FA-11670</t>
+  </si>
+  <si>
+    <t>FA-11685</t>
   </si>
   <si>
     <t>GILVAN RODRIGUES MACHADO</t>
   </si>
   <si>
-    <t>FA-11622</t>
+    <t>FA-11796</t>
+  </si>
+  <si>
+    <t>FA-11755</t>
+  </si>
+  <si>
+    <t>FA-11795</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11506</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11623</t>
   </si>
   <si>
     <t>DANILO DE ALMEIDA TORRES</t>
   </si>
   <si>
-    <t>FA-11711</t>
-  </si>
-  <si>
-    <t>FA-11774</t>
-  </si>
-  <si>
-    <t>FA-11567</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11692</t>
-  </si>
-  <si>
-    <t>FA-11712</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11677</t>
-  </si>
-  <si>
-    <t>FA-11772</t>
-  </si>
-  <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>FA-11537</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
+    <t>FA-11658</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>FA-11775</t>
+  </si>
+  <si>
+    <t>FA-11436</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11414</t>
+  </si>
+  <si>
+    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11570</t>
+  </si>
+  <si>
+    <t>FA-11809</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11693</t>
+  </si>
+  <si>
+    <t>FA-11678</t>
+  </si>
+  <si>
+    <t>FA-11763</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11782</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11603</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
   </si>
   <si>
     <t>JOÃO PAULO CONSÓRCIOS</t>
   </si>
   <si>
-    <t>FA-11602</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>1.3 UBER SUPPLIER</t>
-  </si>
-  <si>
-    <t>FA-11808</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11804</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11760</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>ND-11699</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LOCACAO DE ATIVOS</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA EMPREENDIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>FA-11722</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11784</t>
-  </si>
-  <si>
-    <t>FA-11747</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11568</t>
-  </si>
-  <si>
-    <t>FA-11569</t>
-  </si>
-  <si>
-    <t>FA-11805</t>
-  </si>
-  <si>
-    <t>FA-11725</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11720</t>
-  </si>
-  <si>
-    <t>FA-11723</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11670</t>
-  </si>
-  <si>
-    <t>FA-11755</t>
-  </si>
-  <si>
-    <t>FA-11781</t>
-  </si>
-  <si>
-    <t>FA-11796</t>
-  </si>
-  <si>
-    <t>FA-11685</t>
-  </si>
-  <si>
-    <t>FA-11795</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11623</t>
-  </si>
-  <si>
-    <t>FA-11506</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11775</t>
-  </si>
-  <si>
-    <t>FA-11658</t>
-  </si>
-  <si>
-    <t>LUCA ZOLI</t>
-  </si>
-  <si>
-    <t>FA-11436</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11570</t>
-  </si>
-  <si>
-    <t>FA-11693</t>
-  </si>
-  <si>
-    <t>FA-11678</t>
-  </si>
-  <si>
-    <t>FA-11809</t>
-  </si>
-  <si>
-    <t>FA-11414</t>
-  </si>
-  <si>
-    <t>DAVI HENRIQUE DANTAS DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11782</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11763</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11603</t>
+    <t>FA-11634</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
   </si>
   <si>
     <t>FA-11580</t>
@@ -463,22 +439,10 @@
     <t>ADRIANO TEOTONIO DA SILVA</t>
   </si>
   <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
     <t>FA-11593</t>
   </si>
   <si>
     <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>FA-11634</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
   </si>
   <si>
     <t>FA-11646</t>
@@ -630,7 +594,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S93"/>
+  <dimension ref="A1:S84"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -1266,22 +1230,22 @@
         <v>22</v>
       </c>
       <c r="B15" s="7">
-        <v>46167</v>
+        <v>46172</v>
       </c>
       <c r="C15" s="7">
-        <v>46167</v>
+        <v>45930</v>
       </c>
       <c r="D15" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E15" s="7">
-        <v>46170</v>
+        <v>46172</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F15" s="8">
-        <v>-11</v>
+        <v>-6</v>
       </c>
       <c r="G15" s="8">
-        <v>-11</v>
+        <v>-6</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>30</v>
@@ -1290,16 +1254,16 @@
         <v>30</v>
       </c>
       <c r="J15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="K15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>40</v>
-      </c>
       <c r="M15" s="6" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N15" s="6" t="s">
         <v>27</v>
@@ -1311,13 +1275,13 @@
         <v>25</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="S15" s="9">
-        <v>650</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="16">
@@ -1325,7 +1289,7 @@
         <v>22</v>
       </c>
       <c r="B16" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="C16" s="7">
         <v>46167</v>
@@ -1333,14 +1297,14 @@
       <c r="D16" s="7">
         <v>46167</v>
       </c>
-      <c r="E16" s="7">
-        <v>46164</v>
+      <c r="E16" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F16" s="8">
         <v>-11</v>
       </c>
       <c r="G16" s="8">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>30</v>
@@ -1349,14 +1313,14 @@
         <v>30</v>
       </c>
       <c r="J16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="K16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>42</v>
-      </c>
       <c r="M16" s="6" t="s">
         <v>25</v>
       </c>
@@ -1370,13 +1334,13 @@
         <v>25</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S16" s="9">
-        <v>680</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
@@ -1384,22 +1348,22 @@
         <v>22</v>
       </c>
       <c r="B17" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="C17" s="7">
-        <v>46167</v>
+        <v>46143</v>
       </c>
       <c r="D17" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="E17" s="7">
         <v>46167</v>
       </c>
       <c r="F17" s="8">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="G17" s="8">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>30</v>
@@ -1408,13 +1372,13 @@
         <v>30</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>25</v>
@@ -1429,13 +1393,13 @@
         <v>25</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>34</v>
       </c>
       <c r="S17" s="9">
-        <v>680</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
@@ -1443,22 +1407,22 @@
         <v>22</v>
       </c>
       <c r="B18" s="7">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="C18" s="7">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="D18" s="7">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F18" s="8">
-        <v>-18</v>
+        <v>-4</v>
       </c>
       <c r="G18" s="8">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>30</v>
@@ -1467,17 +1431,17 @@
         <v>30</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="K18" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M18" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="M18" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="N18" s="6" t="s">
         <v>27</v>
       </c>
@@ -1491,10 +1455,10 @@
         <v>25</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="S18" s="9">
-        <v>233.82</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
@@ -1502,22 +1466,22 @@
         <v>22</v>
       </c>
       <c r="B19" s="7">
-        <v>46172</v>
+        <v>46174</v>
       </c>
       <c r="C19" s="7">
-        <v>45930</v>
+        <v>46174</v>
       </c>
       <c r="D19" s="7">
-        <v>46172</v>
+        <v>46174</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="8">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="G19" s="8">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>30</v>
@@ -1532,10 +1496,10 @@
         <v>25</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="N19" s="6" t="s">
         <v>27</v>
@@ -1553,7 +1517,7 @@
         <v>25</v>
       </c>
       <c r="S19" s="9">
-        <v>185.5</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20">
@@ -1564,16 +1528,16 @@
         <v>46174</v>
       </c>
       <c r="C20" s="7">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="D20" s="7">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="8">
-        <v>-11</v>
+        <v>-25</v>
       </c>
       <c r="G20" s="8">
         <v>-4</v>
@@ -1585,16 +1549,16 @@
         <v>30</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="N20" s="6" t="s">
         <v>27</v>
@@ -1612,7 +1576,7 @@
         <v>34</v>
       </c>
       <c r="S20" s="9">
-        <v>80</v>
+        <v>129.12</v>
       </c>
     </row>
     <row r="21">
@@ -1623,13 +1587,13 @@
         <v>46174</v>
       </c>
       <c r="C21" s="7">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="D21" s="7">
         <v>46174</v>
       </c>
       <c r="E21" s="7">
-        <v>46167</v>
+        <v>46097</v>
       </c>
       <c r="F21" s="8">
         <v>-4</v>
@@ -1644,13 +1608,13 @@
         <v>30</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>25</v>
@@ -1668,10 +1632,10 @@
         <v>28</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="S21" s="9">
-        <v>100</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="22">
@@ -1703,16 +1667,16 @@
         <v>30</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N22" s="6" t="s">
         <v>27</v>
@@ -1727,10 +1691,10 @@
         <v>25</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="S22" s="9">
-        <v>120</v>
+        <v>164.07</v>
       </c>
     </row>
     <row r="23">
@@ -1741,16 +1705,16 @@
         <v>46174</v>
       </c>
       <c r="C23" s="7">
-        <v>46174</v>
+        <v>46160</v>
       </c>
       <c r="D23" s="7">
-        <v>46174</v>
+        <v>46160</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F23" s="8">
-        <v>-4</v>
+        <v>-18</v>
       </c>
       <c r="G23" s="8">
         <v>-4</v>
@@ -1762,7 +1726,7 @@
         <v>30</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>25</v>
@@ -1771,7 +1735,7 @@
         <v>50</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N23" s="6" t="s">
         <v>27</v>
@@ -1786,10 +1750,10 @@
         <v>25</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="S23" s="9">
-        <v>120</v>
+        <v>172.72</v>
       </c>
     </row>
     <row r="24">
@@ -1800,16 +1764,16 @@
         <v>46174</v>
       </c>
       <c r="C24" s="7">
-        <v>46153</v>
+        <v>46174</v>
       </c>
       <c r="D24" s="7">
-        <v>46153</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>25</v>
+        <v>46174</v>
+      </c>
+      <c r="E24" s="7">
+        <v>46141</v>
       </c>
       <c r="F24" s="8">
-        <v>-25</v>
+        <v>-4</v>
       </c>
       <c r="G24" s="8">
         <v>-4</v>
@@ -1821,16 +1785,16 @@
         <v>30</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>27</v>
@@ -1842,13 +1806,13 @@
         <v>25</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>34</v>
       </c>
       <c r="S24" s="9">
-        <v>129.12</v>
+        <v>310</v>
       </c>
     </row>
     <row r="25">
@@ -1859,16 +1823,16 @@
         <v>46174</v>
       </c>
       <c r="C25" s="7">
-        <v>46082</v>
+        <v>46167</v>
       </c>
       <c r="D25" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E25" s="7">
-        <v>46097</v>
+        <v>46167</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F25" s="8">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="G25" s="8">
         <v>-4</v>
@@ -1880,16 +1844,16 @@
         <v>30</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>27</v>
@@ -1901,13 +1865,13 @@
         <v>25</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S25" s="9">
-        <v>146.55</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26">
@@ -1918,16 +1882,16 @@
         <v>46174</v>
       </c>
       <c r="C26" s="7">
-        <v>46174</v>
+        <v>46167</v>
       </c>
       <c r="D26" s="7">
-        <v>46174</v>
+        <v>46167</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F26" s="8">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="G26" s="8">
         <v>-4</v>
@@ -1939,13 +1903,13 @@
         <v>30</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>25</v>
@@ -1966,7 +1930,7 @@
         <v>34</v>
       </c>
       <c r="S26" s="9">
-        <v>164.07</v>
+        <v>393.43</v>
       </c>
     </row>
     <row r="27">
@@ -1977,16 +1941,16 @@
         <v>46174</v>
       </c>
       <c r="C27" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D27" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F27" s="8">
-        <v>-18</v>
+        <v>-11</v>
       </c>
       <c r="G27" s="8">
         <v>-4</v>
@@ -1998,13 +1962,13 @@
         <v>30</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>25</v>
@@ -2022,10 +1986,10 @@
         <v>25</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="S27" s="9">
-        <v>172.72</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28">
@@ -2036,16 +2000,16 @@
         <v>46174</v>
       </c>
       <c r="C28" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="D28" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>25</v>
+        <v>46174</v>
+      </c>
+      <c r="E28" s="7">
+        <v>46170</v>
       </c>
       <c r="F28" s="8">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="G28" s="8">
         <v>-4</v>
@@ -2057,16 +2021,16 @@
         <v>30</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>27</v>
@@ -2078,13 +2042,13 @@
         <v>25</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>34</v>
       </c>
       <c r="S28" s="9">
-        <v>350</v>
+        <v>600</v>
       </c>
     </row>
     <row r="29">
@@ -2095,16 +2059,16 @@
         <v>46174</v>
       </c>
       <c r="C29" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="D29" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>25</v>
+        <v>46174</v>
+      </c>
+      <c r="E29" s="7">
+        <v>46141</v>
       </c>
       <c r="F29" s="8">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="G29" s="8">
         <v>-4</v>
@@ -2125,7 +2089,7 @@
         <v>60</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>27</v>
@@ -2137,13 +2101,13 @@
         <v>25</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>34</v>
       </c>
       <c r="S29" s="9">
-        <v>393.43</v>
+        <v>620</v>
       </c>
     </row>
     <row r="30">
@@ -2154,16 +2118,16 @@
         <v>46174</v>
       </c>
       <c r="C30" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="D30" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>25</v>
+        <v>46174</v>
+      </c>
+      <c r="E30" s="7">
+        <v>46169</v>
       </c>
       <c r="F30" s="8">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="G30" s="8">
         <v>-4</v>
@@ -2181,7 +2145,7 @@
         <v>25</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>25</v>
@@ -2196,13 +2160,13 @@
         <v>25</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S30" s="9">
-        <v>400</v>
+        <v>630</v>
       </c>
     </row>
     <row r="31">
@@ -2219,7 +2183,7 @@
         <v>46174</v>
       </c>
       <c r="E31" s="7">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="F31" s="8">
         <v>-4</v>
@@ -2234,16 +2198,16 @@
         <v>30</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>27</v>
@@ -2261,7 +2225,7 @@
         <v>34</v>
       </c>
       <c r="S31" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="32">
@@ -2278,7 +2242,7 @@
         <v>46174</v>
       </c>
       <c r="E32" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="F32" s="8">
         <v>-4</v>
@@ -2293,13 +2257,13 @@
         <v>30</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>25</v>
@@ -2320,7 +2284,7 @@
         <v>34</v>
       </c>
       <c r="S32" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="33">
@@ -2337,7 +2301,7 @@
         <v>46174</v>
       </c>
       <c r="E33" s="7">
-        <v>46141</v>
+        <v>46168</v>
       </c>
       <c r="F33" s="8">
         <v>-4</v>
@@ -2352,16 +2316,16 @@
         <v>30</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>27</v>
@@ -2376,10 +2340,10 @@
         <v>33</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="S33" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="34">
@@ -2396,7 +2360,7 @@
         <v>46174</v>
       </c>
       <c r="E34" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F34" s="8">
         <v>-4</v>
@@ -2411,16 +2375,16 @@
         <v>30</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>27</v>
@@ -2438,7 +2402,7 @@
         <v>34</v>
       </c>
       <c r="S34" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="35">
@@ -2455,7 +2419,7 @@
         <v>46174</v>
       </c>
       <c r="E35" s="7">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F35" s="8">
         <v>-4</v>
@@ -2470,13 +2434,13 @@
         <v>30</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>25</v>
@@ -2494,10 +2458,10 @@
         <v>33</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="S35" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="36">
@@ -2514,7 +2478,7 @@
         <v>46174</v>
       </c>
       <c r="E36" s="7">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="F36" s="8">
         <v>-4</v>
@@ -2529,13 +2493,13 @@
         <v>30</v>
       </c>
       <c r="J36" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L36" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>25</v>
@@ -2556,7 +2520,7 @@
         <v>34</v>
       </c>
       <c r="S36" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="37">
@@ -2573,7 +2537,7 @@
         <v>46174</v>
       </c>
       <c r="E37" s="7">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="F37" s="8">
         <v>-4</v>
@@ -2594,7 +2558,7 @@
         <v>25</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>25</v>
@@ -2615,7 +2579,7 @@
         <v>34</v>
       </c>
       <c r="S37" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="38">
@@ -2632,7 +2596,7 @@
         <v>46174</v>
       </c>
       <c r="E38" s="7">
-        <v>46153</v>
+        <v>46141</v>
       </c>
       <c r="F38" s="8">
         <v>-4</v>
@@ -2647,13 +2611,13 @@
         <v>30</v>
       </c>
       <c r="J38" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L38" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="K38" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L38" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>25</v>
@@ -2671,10 +2635,10 @@
         <v>33</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="S38" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="39">
@@ -2691,7 +2655,7 @@
         <v>46174</v>
       </c>
       <c r="E39" s="7">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="F39" s="8">
         <v>-4</v>
@@ -2706,13 +2670,13 @@
         <v>30</v>
       </c>
       <c r="J39" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L39" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="K39" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L39" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>25</v>
@@ -2730,10 +2694,10 @@
         <v>33</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S39" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="40">
@@ -2741,7 +2705,7 @@
         <v>22</v>
       </c>
       <c r="B40" s="7">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C40" s="7">
         <v>46174</v>
@@ -2749,14 +2713,14 @@
       <c r="D40" s="7">
         <v>46174</v>
       </c>
-      <c r="E40" s="7">
-        <v>46170</v>
+      <c r="E40" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F40" s="8">
         <v>-4</v>
       </c>
       <c r="G40" s="8">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>30</v>
@@ -2771,10 +2735,10 @@
         <v>25</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>27</v>
@@ -2786,13 +2750,13 @@
         <v>25</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="S40" s="9">
-        <v>650</v>
+        <v>228.2</v>
       </c>
     </row>
     <row r="41">
@@ -2800,7 +2764,7 @@
         <v>22</v>
       </c>
       <c r="B41" s="7">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C41" s="7">
         <v>46174</v>
@@ -2808,14 +2772,14 @@
       <c r="D41" s="7">
         <v>46174</v>
       </c>
-      <c r="E41" s="7">
-        <v>46141</v>
+      <c r="E41" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F41" s="8">
         <v>-4</v>
       </c>
       <c r="G41" s="8">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>30</v>
@@ -2824,13 +2788,13 @@
         <v>30</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>25</v>
@@ -2845,13 +2809,13 @@
         <v>25</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S41" s="9">
-        <v>680</v>
+        <v>301.57</v>
       </c>
     </row>
     <row r="42">
@@ -2859,58 +2823,58 @@
         <v>22</v>
       </c>
       <c r="B42" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C42" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D42" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E42" s="7">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="F42" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G42" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>34</v>
       </c>
       <c r="S42" s="9">
-        <v>680</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43">
@@ -2918,58 +2882,58 @@
         <v>22</v>
       </c>
       <c r="B43" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C43" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D43" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E43" s="7">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="F43" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G43" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>34</v>
       </c>
       <c r="S43" s="9">
-        <v>680</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
@@ -2977,58 +2941,58 @@
         <v>22</v>
       </c>
       <c r="B44" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C44" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D44" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E44" s="7">
-        <v>46164</v>
+        <v>46181</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F44" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G44" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="S44" s="9">
-        <v>680</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45">
@@ -3036,223 +3000,223 @@
         <v>22</v>
       </c>
       <c r="B45" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C45" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D45" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E45" s="7">
-        <v>46170</v>
+        <v>46181</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="F45" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G45" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="S45" s="9">
-        <v>680</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="B46" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C46" s="7">
-        <v>46174</v>
+        <v>46082</v>
       </c>
       <c r="D46" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E46" s="7">
-        <v>46129</v>
+        <v>46097</v>
       </c>
       <c r="F46" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G46" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>86</v>
+        <v>29</v>
       </c>
       <c r="S46" s="9">
-        <v>800</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C47" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D47" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="8">
+        <v>3</v>
+      </c>
+      <c r="G47" s="8">
+        <v>3</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L47" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B47" s="7">
-        <v>46174</v>
-      </c>
-      <c r="C47" s="7">
-        <v>46174</v>
-      </c>
-      <c r="D47" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E47" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F47" s="8">
-        <v>-4</v>
-      </c>
-      <c r="G47" s="8">
-        <v>-4</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J47" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="K47" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L47" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="M47" s="6" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>86</v>
+        <v>25</v>
       </c>
       <c r="S47" s="9">
-        <v>800</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="B48" s="7">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="C48" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D48" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F48" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G48" s="8">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>25</v>
@@ -3261,10 +3225,10 @@
         <v>25</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="S48" s="9">
-        <v>117.45</v>
+        <v>180</v>
       </c>
     </row>
     <row r="49">
@@ -3272,46 +3236,46 @@
         <v>22</v>
       </c>
       <c r="B49" s="7">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="C49" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D49" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F49" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G49" s="8">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>25</v>
@@ -3320,10 +3284,10 @@
         <v>25</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="S49" s="9">
-        <v>228.2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="50">
@@ -3331,46 +3295,46 @@
         <v>22</v>
       </c>
       <c r="B50" s="7">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="C50" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D50" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>25</v>
       </c>
       <c r="F50" s="8">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="G50" s="8">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>94</v>
+        <v>25</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>25</v>
+        <v>84</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>25</v>
@@ -3379,10 +3343,10 @@
         <v>25</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="S50" s="9">
-        <v>301.57</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51">
@@ -3393,13 +3357,13 @@
         <v>46181</v>
       </c>
       <c r="C51" s="7">
-        <v>46143</v>
+        <v>46181</v>
       </c>
       <c r="D51" s="7">
         <v>46181</v>
       </c>
       <c r="E51" s="7">
-        <v>46153</v>
+        <v>46169</v>
       </c>
       <c r="F51" s="8">
         <v>3</v>
@@ -3414,34 +3378,34 @@
         <v>25</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>25</v>
+        <v>86</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>34</v>
       </c>
       <c r="S51" s="9">
-        <v>50</v>
+        <v>600</v>
       </c>
     </row>
     <row r="52">
@@ -3452,13 +3416,13 @@
         <v>46181</v>
       </c>
       <c r="C52" s="7">
-        <v>46143</v>
+        <v>46181</v>
       </c>
       <c r="D52" s="7">
         <v>46181</v>
       </c>
       <c r="E52" s="7">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="F52" s="8">
         <v>3</v>
@@ -3473,34 +3437,34 @@
         <v>25</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>34</v>
       </c>
       <c r="S52" s="9">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="53">
@@ -3516,8 +3480,8 @@
       <c r="D53" s="7">
         <v>46181</v>
       </c>
-      <c r="E53" s="7" t="s">
-        <v>25</v>
+      <c r="E53" s="7">
+        <v>46169</v>
       </c>
       <c r="F53" s="8">
         <v>3</v>
@@ -3532,34 +3496,34 @@
         <v>25</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="S53" s="9">
-        <v>120</v>
+        <v>600</v>
       </c>
     </row>
     <row r="54">
@@ -3575,8 +3539,8 @@
       <c r="D54" s="7">
         <v>46181</v>
       </c>
-      <c r="E54" s="7" t="s">
-        <v>25</v>
+      <c r="E54" s="7">
+        <v>46141</v>
       </c>
       <c r="F54" s="8">
         <v>3</v>
@@ -3591,34 +3555,34 @@
         <v>25</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q54" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="S54" s="9">
-        <v>120</v>
+        <v>620</v>
       </c>
     </row>
     <row r="55">
@@ -3629,13 +3593,13 @@
         <v>46181</v>
       </c>
       <c r="C55" s="7">
-        <v>46082</v>
+        <v>46181</v>
       </c>
       <c r="D55" s="7">
         <v>46181</v>
       </c>
       <c r="E55" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F55" s="8">
         <v>3</v>
@@ -3650,34 +3614,34 @@
         <v>25</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q55" s="6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S55" s="9">
-        <v>146.55</v>
+        <v>620</v>
       </c>
     </row>
     <row r="56">
@@ -3693,8 +3657,8 @@
       <c r="D56" s="7">
         <v>46181</v>
       </c>
-      <c r="E56" s="7" t="s">
-        <v>25</v>
+      <c r="E56" s="7">
+        <v>46176</v>
       </c>
       <c r="F56" s="8">
         <v>3</v>
@@ -3709,34 +3673,34 @@
         <v>25</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S56" s="9">
-        <v>180</v>
+        <v>620</v>
       </c>
     </row>
     <row r="57">
@@ -3752,8 +3716,8 @@
       <c r="D57" s="7">
         <v>46181</v>
       </c>
-      <c r="E57" s="7" t="s">
-        <v>25</v>
+      <c r="E57" s="7">
+        <v>46169</v>
       </c>
       <c r="F57" s="8">
         <v>3</v>
@@ -3768,34 +3732,34 @@
         <v>25</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="S57" s="9">
-        <v>180</v>
+        <v>630</v>
       </c>
     </row>
     <row r="58">
@@ -3811,8 +3775,8 @@
       <c r="D58" s="7">
         <v>46181</v>
       </c>
-      <c r="E58" s="7" t="s">
-        <v>25</v>
+      <c r="E58" s="7">
+        <v>46169</v>
       </c>
       <c r="F58" s="8">
         <v>3</v>
@@ -3827,34 +3791,34 @@
         <v>25</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="S58" s="9">
-        <v>180</v>
+        <v>630</v>
       </c>
     </row>
     <row r="59">
@@ -3870,8 +3834,8 @@
       <c r="D59" s="7">
         <v>46181</v>
       </c>
-      <c r="E59" s="7" t="s">
-        <v>25</v>
+      <c r="E59" s="7">
+        <v>46169</v>
       </c>
       <c r="F59" s="8">
         <v>3</v>
@@ -3886,34 +3850,34 @@
         <v>25</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>25</v>
+        <v>96</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="S59" s="9">
-        <v>180</v>
+        <v>630</v>
       </c>
     </row>
     <row r="60">
@@ -3930,7 +3894,7 @@
         <v>46181</v>
       </c>
       <c r="E60" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F60" s="8">
         <v>3</v>
@@ -3945,25 +3909,25 @@
         <v>25</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="Q60" s="6" t="s">
         <v>33</v>
@@ -3972,7 +3936,7 @@
         <v>34</v>
       </c>
       <c r="S60" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="61">
@@ -3989,7 +3953,7 @@
         <v>46181</v>
       </c>
       <c r="E61" s="7">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="F61" s="8">
         <v>3</v>
@@ -4004,22 +3968,22 @@
         <v>25</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>25</v>
@@ -4031,7 +3995,7 @@
         <v>34</v>
       </c>
       <c r="S61" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="62">
@@ -4048,7 +4012,7 @@
         <v>46181</v>
       </c>
       <c r="E62" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F62" s="8">
         <v>3</v>
@@ -4063,22 +4027,22 @@
         <v>25</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>106</v>
+        <v>25</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>25</v>
@@ -4090,7 +4054,7 @@
         <v>34</v>
       </c>
       <c r="S62" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="63">
@@ -4107,7 +4071,7 @@
         <v>46181</v>
       </c>
       <c r="E63" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="F63" s="8">
         <v>3</v>
@@ -4122,22 +4086,22 @@
         <v>25</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>25</v>
@@ -4149,7 +4113,7 @@
         <v>34</v>
       </c>
       <c r="S63" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="64">
@@ -4166,7 +4130,7 @@
         <v>46181</v>
       </c>
       <c r="E64" s="7">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="F64" s="8">
         <v>3</v>
@@ -4181,22 +4145,22 @@
         <v>25</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>25</v>
@@ -4208,7 +4172,7 @@
         <v>34</v>
       </c>
       <c r="S64" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="65">
@@ -4225,7 +4189,7 @@
         <v>46181</v>
       </c>
       <c r="E65" s="7">
-        <v>46176</v>
+        <v>46170</v>
       </c>
       <c r="F65" s="8">
         <v>3</v>
@@ -4240,22 +4204,22 @@
         <v>25</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>25</v>
@@ -4264,10 +4228,10 @@
         <v>33</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S65" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="66">
@@ -4284,7 +4248,7 @@
         <v>46181</v>
       </c>
       <c r="E66" s="7">
-        <v>46169</v>
+        <v>46127</v>
       </c>
       <c r="F66" s="8">
         <v>3</v>
@@ -4299,22 +4263,22 @@
         <v>25</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="M66" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>25</v>
@@ -4326,7 +4290,7 @@
         <v>34</v>
       </c>
       <c r="S66" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="67">
@@ -4343,7 +4307,7 @@
         <v>46181</v>
       </c>
       <c r="E67" s="7">
-        <v>46169</v>
+        <v>46153</v>
       </c>
       <c r="F67" s="8">
         <v>3</v>
@@ -4358,22 +4322,22 @@
         <v>25</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="M67" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>25</v>
@@ -4385,7 +4349,7 @@
         <v>34</v>
       </c>
       <c r="S67" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="68">
@@ -4402,7 +4366,7 @@
         <v>46181</v>
       </c>
       <c r="E68" s="7">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="F68" s="8">
         <v>3</v>
@@ -4417,22 +4381,22 @@
         <v>25</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M68" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>25</v>
@@ -4444,7 +4408,7 @@
         <v>34</v>
       </c>
       <c r="S68" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="69">
@@ -4461,7 +4425,7 @@
         <v>46181</v>
       </c>
       <c r="E69" s="7">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="F69" s="8">
         <v>3</v>
@@ -4476,22 +4440,22 @@
         <v>25</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>25</v>
@@ -4503,7 +4467,7 @@
         <v>34</v>
       </c>
       <c r="S69" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="70">
@@ -4520,7 +4484,7 @@
         <v>46181</v>
       </c>
       <c r="E70" s="7">
-        <v>46169</v>
+        <v>46119</v>
       </c>
       <c r="F70" s="8">
         <v>3</v>
@@ -4535,22 +4499,22 @@
         <v>25</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>25</v>
@@ -4562,7 +4526,7 @@
         <v>34</v>
       </c>
       <c r="S70" s="9">
-        <v>630</v>
+        <v>670</v>
       </c>
     </row>
     <row r="71">
@@ -4579,7 +4543,7 @@
         <v>46181</v>
       </c>
       <c r="E71" s="7">
-        <v>46170</v>
+        <v>46113</v>
       </c>
       <c r="F71" s="8">
         <v>3</v>
@@ -4594,25 +4558,25 @@
         <v>25</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="Q71" s="6" t="s">
         <v>33</v>
@@ -4621,7 +4585,7 @@
         <v>34</v>
       </c>
       <c r="S71" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="72">
@@ -4638,7 +4602,7 @@
         <v>46181</v>
       </c>
       <c r="E72" s="7">
-        <v>46170</v>
+        <v>46141</v>
       </c>
       <c r="F72" s="8">
         <v>3</v>
@@ -4653,22 +4617,22 @@
         <v>25</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>25</v>
@@ -4677,10 +4641,10 @@
         <v>33</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="S72" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="73">
@@ -4697,7 +4661,7 @@
         <v>46181</v>
       </c>
       <c r="E73" s="7">
-        <v>46164</v>
+        <v>46176</v>
       </c>
       <c r="F73" s="8">
         <v>3</v>
@@ -4712,22 +4676,22 @@
         <v>25</v>
       </c>
       <c r="J73" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="K73" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L73" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="K73" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L73" s="6" t="s">
-        <v>71</v>
-      </c>
       <c r="M73" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>25</v>
@@ -4739,7 +4703,7 @@
         <v>34</v>
       </c>
       <c r="S73" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="74">
@@ -4756,7 +4720,7 @@
         <v>46181</v>
       </c>
       <c r="E74" s="7">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="F74" s="8">
         <v>3</v>
@@ -4777,16 +4741,16 @@
         <v>25</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>25</v>
@@ -4798,7 +4762,7 @@
         <v>34</v>
       </c>
       <c r="S74" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="75">
@@ -4815,7 +4779,7 @@
         <v>46181</v>
       </c>
       <c r="E75" s="7">
-        <v>46153</v>
+        <v>46164</v>
       </c>
       <c r="F75" s="8">
         <v>3</v>
@@ -4830,22 +4794,22 @@
         <v>25</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>25</v>
@@ -4854,10 +4818,10 @@
         <v>33</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="S75" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="76">
@@ -4874,7 +4838,7 @@
         <v>46181</v>
       </c>
       <c r="E76" s="7">
-        <v>46127</v>
+        <v>46170</v>
       </c>
       <c r="F76" s="8">
         <v>3</v>
@@ -4889,22 +4853,22 @@
         <v>25</v>
       </c>
       <c r="J76" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="K76" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L76" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="K76" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L76" s="6" t="s">
-        <v>124</v>
-      </c>
       <c r="M76" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>25</v>
@@ -4916,7 +4880,7 @@
         <v>34</v>
       </c>
       <c r="S76" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="77">
@@ -4948,25 +4912,25 @@
         <v>25</v>
       </c>
       <c r="J77" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="K77" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L77" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="K77" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L77" s="6" t="s">
-        <v>40</v>
-      </c>
       <c r="M77" s="6" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="Q77" s="6" t="s">
         <v>33</v>
@@ -4975,7 +4939,7 @@
         <v>34</v>
       </c>
       <c r="S77" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="78">
@@ -4992,7 +4956,7 @@
         <v>46181</v>
       </c>
       <c r="E78" s="7">
-        <v>46160</v>
+        <v>46148</v>
       </c>
       <c r="F78" s="8">
         <v>3</v>
@@ -5019,10 +4983,10 @@
         <v>25</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>25</v>
@@ -5031,10 +4995,10 @@
         <v>33</v>
       </c>
       <c r="R78" s="6" t="s">
-        <v>34</v>
+        <v>128</v>
       </c>
       <c r="S78" s="9">
-        <v>650</v>
+        <v>800</v>
       </c>
     </row>
     <row r="79">
@@ -5051,7 +5015,7 @@
         <v>46181</v>
       </c>
       <c r="E79" s="7">
-        <v>46119</v>
+        <v>46160</v>
       </c>
       <c r="F79" s="8">
         <v>3</v>
@@ -5066,34 +5030,34 @@
         <v>25</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="Q79" s="6" t="s">
         <v>33</v>
       </c>
       <c r="R79" s="6" t="s">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="S79" s="9">
-        <v>670</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="80">
@@ -5110,7 +5074,7 @@
         <v>46181</v>
       </c>
       <c r="E80" s="7">
-        <v>46141</v>
+        <v>46148</v>
       </c>
       <c r="F80" s="8">
         <v>3</v>
@@ -5125,22 +5089,22 @@
         <v>25</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>25</v>
@@ -5149,10 +5113,10 @@
         <v>33</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="S80" s="9">
-        <v>680</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="81">
@@ -5169,7 +5133,7 @@
         <v>46181</v>
       </c>
       <c r="E81" s="7">
-        <v>46167</v>
+        <v>46148</v>
       </c>
       <c r="F81" s="8">
         <v>3</v>
@@ -5184,22 +5148,22 @@
         <v>25</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>25</v>
@@ -5208,10 +5172,10 @@
         <v>33</v>
       </c>
       <c r="R81" s="6" t="s">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="S81" s="9">
-        <v>680</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="82">
@@ -5228,7 +5192,7 @@
         <v>46181</v>
       </c>
       <c r="E82" s="7">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="F82" s="8">
         <v>3</v>
@@ -5243,34 +5207,34 @@
         <v>25</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>42</v>
+        <v>138</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="Q82" s="6" t="s">
         <v>33</v>
       </c>
       <c r="R82" s="6" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="S82" s="9">
-        <v>680</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="83">
@@ -5281,13 +5245,13 @@
         <v>46181</v>
       </c>
       <c r="C83" s="7">
-        <v>46181</v>
+        <v>46143</v>
       </c>
       <c r="D83" s="7">
         <v>46181</v>
       </c>
       <c r="E83" s="7">
-        <v>46176</v>
+        <v>46170</v>
       </c>
       <c r="F83" s="8">
         <v>3</v>
@@ -5302,588 +5266,57 @@
         <v>25</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>25</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>25</v>
       </c>
       <c r="Q83" s="6" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="R83" s="6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="S83" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B84" s="7">
-        <v>46181</v>
-      </c>
-      <c r="C84" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D84" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E84" s="7">
-        <v>46113</v>
-      </c>
-      <c r="F84" s="8">
-        <v>3</v>
-      </c>
-      <c r="G84" s="8">
-        <v>3</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I84" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J84" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="K84" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L84" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="M84" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="N84" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q84" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="R84" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="S84" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B85" s="7">
-        <v>46181</v>
-      </c>
-      <c r="C85" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D85" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E85" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F85" s="8">
-        <v>3</v>
-      </c>
-      <c r="G85" s="8">
-        <v>3</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I85" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J85" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="K85" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L85" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="M85" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N85" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="O85" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="P85" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q85" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="R85" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="S85" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B86" s="7">
-        <v>46181</v>
-      </c>
-      <c r="C86" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D86" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E86" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F86" s="8">
-        <v>3</v>
-      </c>
-      <c r="G86" s="8">
-        <v>3</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I86" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J86" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="K86" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L86" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="M86" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N86" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q86" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="R86" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="S86" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B87" s="7">
-        <v>46181</v>
-      </c>
-      <c r="C87" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D87" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E87" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F87" s="8">
-        <v>3</v>
-      </c>
-      <c r="G87" s="8">
-        <v>3</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I87" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J87" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="K87" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L87" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="M87" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N87" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="O87" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="P87" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q87" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="R87" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="S87" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B88" s="7">
-        <v>46181</v>
-      </c>
-      <c r="C88" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D88" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E88" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F88" s="8">
-        <v>3</v>
-      </c>
-      <c r="G88" s="8">
-        <v>3</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I88" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J88" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="K88" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="M88" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N88" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q88" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="R88" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="S88" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B89" s="7">
-        <v>46181</v>
-      </c>
-      <c r="C89" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D89" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E89" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F89" s="8">
-        <v>3</v>
-      </c>
-      <c r="G89" s="8">
-        <v>3</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I89" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J89" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="K89" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L89" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="M89" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N89" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="O89" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="P89" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q89" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="R89" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="S89" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B90" s="7">
-        <v>46181</v>
-      </c>
-      <c r="C90" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D90" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E90" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F90" s="8">
-        <v>3</v>
-      </c>
-      <c r="G90" s="8">
-        <v>3</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K90" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L90" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="M90" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N90" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q90" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="R90" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="S90" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B91" s="7">
-        <v>46181</v>
-      </c>
-      <c r="C91" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D91" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E91" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F91" s="8">
-        <v>3</v>
-      </c>
-      <c r="G91" s="8">
-        <v>3</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J91" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="K91" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L91" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="M91" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N91" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="O91" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="P91" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q91" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="R91" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="S91" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B92" s="7">
-        <v>46181</v>
-      </c>
-      <c r="C92" s="7">
-        <v>46143</v>
-      </c>
-      <c r="D92" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E92" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F92" s="8">
-        <v>3</v>
-      </c>
-      <c r="G92" s="8">
-        <v>3</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J92" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="K92" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M92" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N92" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="O92" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="P92" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q92" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="R92" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="S92" s="9">
         <v>2969.17</v>
       </c>
     </row>
-    <row r="93" ht="23" customHeight="1">
-      <c r="A93" s="10"/>
-      <c r="B93" s="11"/>
-      <c r="C93" s="11"/>
-      <c r="D93" s="11"/>
-      <c r="E93" s="11"/>
-      <c r="F93" s="12"/>
-      <c r="G93" s="12"/>
-      <c r="H93" s="10"/>
-      <c r="I93" s="10"/>
-      <c r="J93" s="10"/>
-      <c r="K93" s="10"/>
-      <c r="L93" s="10"/>
-      <c r="M93" s="10"/>
-      <c r="N93" s="10"/>
-      <c r="O93" s="10"/>
-      <c r="P93" s="10"/>
-      <c r="Q93" s="10"/>
-      <c r="R93" s="10"/>
-      <c r="S93" s="13">
-        <f>SUM(S6:S92)</f>
+    <row r="84" ht="23" customHeight="1">
+      <c r="A84" s="10"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="11"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+      <c r="H84" s="10"/>
+      <c r="I84" s="10"/>
+      <c r="J84" s="10"/>
+      <c r="K84" s="10"/>
+      <c r="L84" s="10"/>
+      <c r="M84" s="10"/>
+      <c r="N84" s="10"/>
+      <c r="O84" s="10"/>
+      <c r="P84" s="10"/>
+      <c r="Q84" s="10"/>
+      <c r="R84" s="10"/>
+      <c r="S84" s="13">
+        <f>SUM(S6:S83)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em sexta-feira, 5 de junho de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em sábado, 6 de junho de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -711,10 +711,10 @@
         <v>46097</v>
       </c>
       <c r="F6" s="8">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="G6" s="8">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>23</v>
@@ -770,10 +770,10 @@
         <v>46097</v>
       </c>
       <c r="F7" s="8">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="G7" s="8">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>30</v>
@@ -829,10 +829,10 @@
         <v>46141</v>
       </c>
       <c r="F8" s="8">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="G8" s="8">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>30</v>
@@ -888,10 +888,10 @@
         <v>46097</v>
       </c>
       <c r="F9" s="8">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="G9" s="8">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>30</v>
@@ -947,10 +947,10 @@
         <v>46141</v>
       </c>
       <c r="F10" s="8">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="G10" s="8">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>30</v>
@@ -1006,10 +1006,10 @@
         <v>25</v>
       </c>
       <c r="F11" s="8">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="G11" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>23</v>
@@ -1065,10 +1065,10 @@
         <v>46097</v>
       </c>
       <c r="F12" s="8">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="G12" s="8">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>30</v>
@@ -1124,10 +1124,10 @@
         <v>25</v>
       </c>
       <c r="F13" s="8">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="G13" s="8">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>30</v>
@@ -1183,10 +1183,10 @@
         <v>46141</v>
       </c>
       <c r="F14" s="8">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="G14" s="8">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>30</v>
@@ -1242,10 +1242,10 @@
         <v>25</v>
       </c>
       <c r="F15" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="G15" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>30</v>
@@ -1301,10 +1301,10 @@
         <v>25</v>
       </c>
       <c r="F16" s="8">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="G16" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>30</v>
@@ -1360,10 +1360,10 @@
         <v>46167</v>
       </c>
       <c r="F17" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G17" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>30</v>
@@ -1419,10 +1419,10 @@
         <v>25</v>
       </c>
       <c r="F18" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G18" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>30</v>
@@ -1478,10 +1478,10 @@
         <v>25</v>
       </c>
       <c r="F19" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G19" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>30</v>
@@ -1537,10 +1537,10 @@
         <v>25</v>
       </c>
       <c r="F20" s="8">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="G20" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>30</v>
@@ -1596,10 +1596,10 @@
         <v>46097</v>
       </c>
       <c r="F21" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G21" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>30</v>
@@ -1655,10 +1655,10 @@
         <v>25</v>
       </c>
       <c r="F22" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G22" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>30</v>
@@ -1714,10 +1714,10 @@
         <v>25</v>
       </c>
       <c r="F23" s="8">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="G23" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>30</v>
@@ -1773,10 +1773,10 @@
         <v>46141</v>
       </c>
       <c r="F24" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G24" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>30</v>
@@ -1832,10 +1832,10 @@
         <v>25</v>
       </c>
       <c r="F25" s="8">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="G25" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>30</v>
@@ -1891,10 +1891,10 @@
         <v>25</v>
       </c>
       <c r="F26" s="8">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="G26" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>30</v>
@@ -1950,10 +1950,10 @@
         <v>25</v>
       </c>
       <c r="F27" s="8">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="G27" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>30</v>
@@ -2009,10 +2009,10 @@
         <v>46170</v>
       </c>
       <c r="F28" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G28" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>30</v>
@@ -2068,10 +2068,10 @@
         <v>46141</v>
       </c>
       <c r="F29" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G29" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>30</v>
@@ -2127,10 +2127,10 @@
         <v>46169</v>
       </c>
       <c r="F30" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G30" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>30</v>
@@ -2186,10 +2186,10 @@
         <v>46163</v>
       </c>
       <c r="F31" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G31" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>30</v>
@@ -2245,10 +2245,10 @@
         <v>46170</v>
       </c>
       <c r="F32" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G32" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>30</v>
@@ -2304,10 +2304,10 @@
         <v>46168</v>
       </c>
       <c r="F33" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G33" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>30</v>
@@ -2363,10 +2363,10 @@
         <v>46170</v>
       </c>
       <c r="F34" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G34" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>30</v>
@@ -2422,10 +2422,10 @@
         <v>46164</v>
       </c>
       <c r="F35" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G35" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>30</v>
@@ -2481,10 +2481,10 @@
         <v>46168</v>
       </c>
       <c r="F36" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G36" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>30</v>
@@ -2540,10 +2540,10 @@
         <v>46170</v>
       </c>
       <c r="F37" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G37" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>30</v>
@@ -2599,10 +2599,10 @@
         <v>46141</v>
       </c>
       <c r="F38" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G38" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>30</v>
@@ -2658,10 +2658,10 @@
         <v>46167</v>
       </c>
       <c r="F39" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G39" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>30</v>
@@ -2717,10 +2717,10 @@
         <v>25</v>
       </c>
       <c r="F40" s="8">
+        <v>-5</v>
+      </c>
+      <c r="G40" s="8">
         <v>-4</v>
-      </c>
-      <c r="G40" s="8">
-        <v>-3</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>30</v>
@@ -2776,10 +2776,10 @@
         <v>25</v>
       </c>
       <c r="F41" s="8">
+        <v>-5</v>
+      </c>
+      <c r="G41" s="8">
         <v>-4</v>
-      </c>
-      <c r="G41" s="8">
-        <v>-3</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>30</v>
@@ -2835,10 +2835,10 @@
         <v>46153</v>
       </c>
       <c r="F42" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>25</v>
@@ -2894,10 +2894,10 @@
         <v>46167</v>
       </c>
       <c r="F43" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G43" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>25</v>
@@ -2953,10 +2953,10 @@
         <v>25</v>
       </c>
       <c r="F44" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G44" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>25</v>
@@ -3012,10 +3012,10 @@
         <v>25</v>
       </c>
       <c r="F45" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G45" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>25</v>
@@ -3071,10 +3071,10 @@
         <v>46097</v>
       </c>
       <c r="F46" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>25</v>
@@ -3130,10 +3130,10 @@
         <v>25</v>
       </c>
       <c r="F47" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>25</v>
@@ -3189,10 +3189,10 @@
         <v>25</v>
       </c>
       <c r="F48" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>25</v>
@@ -3248,10 +3248,10 @@
         <v>25</v>
       </c>
       <c r="F49" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>25</v>
@@ -3307,10 +3307,10 @@
         <v>25</v>
       </c>
       <c r="F50" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G50" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>25</v>
@@ -3366,10 +3366,10 @@
         <v>46169</v>
       </c>
       <c r="F51" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G51" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>25</v>
@@ -3425,10 +3425,10 @@
         <v>46170</v>
       </c>
       <c r="F52" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G52" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>25</v>
@@ -3484,10 +3484,10 @@
         <v>46169</v>
       </c>
       <c r="F53" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G53" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>25</v>
@@ -3543,10 +3543,10 @@
         <v>46141</v>
       </c>
       <c r="F54" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G54" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>25</v>
@@ -3602,10 +3602,10 @@
         <v>46141</v>
       </c>
       <c r="F55" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G55" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>25</v>
@@ -3661,10 +3661,10 @@
         <v>46176</v>
       </c>
       <c r="F56" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G56" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>25</v>
@@ -3720,10 +3720,10 @@
         <v>46169</v>
       </c>
       <c r="F57" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G57" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>25</v>
@@ -3779,10 +3779,10 @@
         <v>46169</v>
       </c>
       <c r="F58" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G58" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>25</v>
@@ -3838,10 +3838,10 @@
         <v>46169</v>
       </c>
       <c r="F59" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G59" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>25</v>
@@ -3897,10 +3897,10 @@
         <v>46170</v>
       </c>
       <c r="F60" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G60" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>25</v>
@@ -3956,10 +3956,10 @@
         <v>46163</v>
       </c>
       <c r="F61" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G61" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>25</v>
@@ -4015,10 +4015,10 @@
         <v>46164</v>
       </c>
       <c r="F62" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>25</v>
@@ -4074,10 +4074,10 @@
         <v>46170</v>
       </c>
       <c r="F63" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G63" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>25</v>
@@ -4133,10 +4133,10 @@
         <v>46169</v>
       </c>
       <c r="F64" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G64" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>25</v>
@@ -4192,10 +4192,10 @@
         <v>46170</v>
       </c>
       <c r="F65" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G65" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>25</v>
@@ -4251,10 +4251,10 @@
         <v>46127</v>
       </c>
       <c r="F66" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G66" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>25</v>
@@ -4310,10 +4310,10 @@
         <v>46153</v>
       </c>
       <c r="F67" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G67" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>25</v>
@@ -4369,10 +4369,10 @@
         <v>46160</v>
       </c>
       <c r="F68" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G68" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>25</v>
@@ -4428,10 +4428,10 @@
         <v>46170</v>
       </c>
       <c r="F69" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G69" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>25</v>
@@ -4487,10 +4487,10 @@
         <v>46119</v>
       </c>
       <c r="F70" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G70" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>25</v>
@@ -4546,10 +4546,10 @@
         <v>46113</v>
       </c>
       <c r="F71" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G71" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>25</v>
@@ -4605,10 +4605,10 @@
         <v>46141</v>
       </c>
       <c r="F72" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G72" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>25</v>
@@ -4664,10 +4664,10 @@
         <v>46176</v>
       </c>
       <c r="F73" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G73" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>25</v>
@@ -4723,10 +4723,10 @@
         <v>46167</v>
       </c>
       <c r="F74" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G74" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>25</v>
@@ -4782,10 +4782,10 @@
         <v>46164</v>
       </c>
       <c r="F75" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G75" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>25</v>
@@ -4841,10 +4841,10 @@
         <v>46170</v>
       </c>
       <c r="F76" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G76" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>25</v>
@@ -4900,10 +4900,10 @@
         <v>46170</v>
       </c>
       <c r="F77" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G77" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>25</v>
@@ -4959,10 +4959,10 @@
         <v>46148</v>
       </c>
       <c r="F78" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G78" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>25</v>
@@ -5018,10 +5018,10 @@
         <v>46160</v>
       </c>
       <c r="F79" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G79" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>25</v>
@@ -5077,10 +5077,10 @@
         <v>46148</v>
       </c>
       <c r="F80" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G80" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>25</v>
@@ -5136,10 +5136,10 @@
         <v>46148</v>
       </c>
       <c r="F81" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G81" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>25</v>
@@ -5195,10 +5195,10 @@
         <v>46160</v>
       </c>
       <c r="F82" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G82" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>25</v>
@@ -5254,10 +5254,10 @@
         <v>46170</v>
       </c>
       <c r="F83" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G83" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>25</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$106</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,7 +36,7 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Final: 07/06/2026</t>
+      <t>Data Inicial: 01/04/2026, Data Final: 15/06/2026</t>
     </r>
   </si>
   <si>
@@ -209,6 +209,318 @@
   </si>
   <si>
     <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>ND-11699</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>ND-11700</t>
+  </si>
+  <si>
+    <t>JOAO PAULO CONSORCIOS</t>
+  </si>
+  <si>
+    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LOCACAO DE ATIVOS</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA EMPREENDIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>FA-11617</t>
+  </si>
+  <si>
+    <t>FA-11709</t>
+  </si>
+  <si>
+    <t>FA-11717</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11692</t>
+  </si>
+  <si>
+    <t>FA-11774</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11784</t>
+  </si>
+  <si>
+    <t>FA-11569</t>
+  </si>
+  <si>
+    <t>FA-11568</t>
+  </si>
+  <si>
+    <t>FA-11796</t>
+  </si>
+  <si>
+    <t>FA-11685</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
+    <t>FA-11720</t>
+  </si>
+  <si>
+    <t>FA-11670</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11775</t>
+  </si>
+  <si>
+    <t>FA-11795</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11693</t>
+  </si>
+  <si>
+    <t>FA-11570</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11815</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11814</t>
+  </si>
+  <si>
+    <t>FA-11678</t>
+  </si>
+  <si>
+    <t>FA-11782</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11763</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>FA-11816</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11603</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>FA-11593</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>ND-11801</t>
+  </si>
+  <si>
+    <t>FA-11755</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>FA-11805</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11813</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-11748</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11787</t>
+  </si>
+  <si>
+    <t>FA-11726</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11572</t>
+  </si>
+  <si>
+    <t>FA-11806</t>
+  </si>
+  <si>
+    <t>FA-11571</t>
+  </si>
+  <si>
+    <t>FA-11786</t>
+  </si>
+  <si>
+    <t>FA-11798</t>
+  </si>
+  <si>
+    <t>FA-11686</t>
+  </si>
+  <si>
+    <t>FA-11756</t>
+  </si>
+  <si>
+    <t>FA-11671</t>
+  </si>
+  <si>
+    <t>FA-11729</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11724</t>
+  </si>
+  <si>
+    <t>FA-11727</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11776</t>
+  </si>
+  <si>
+    <t>FA-11659</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>FA-11624</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11797</t>
+  </si>
+  <si>
+    <t>FA-11507</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11437</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11694</t>
+  </si>
+  <si>
+    <t>FA-11810</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11819</t>
+  </si>
+  <si>
+    <t>FA-11573</t>
+  </si>
+  <si>
+    <t>FA-11817</t>
+  </si>
+  <si>
+    <t>FA-11679</t>
+  </si>
+  <si>
+    <t>FA-11818</t>
+  </si>
+  <si>
+    <t>FA-11785</t>
+  </si>
+  <si>
+    <t>FA-11764</t>
+  </si>
+  <si>
+    <t>FA-11604</t>
+  </si>
+  <si>
+    <t>FA-11820</t>
+  </si>
+  <si>
+    <t>FA-11581</t>
+  </si>
+  <si>
+    <t>ADRIANO TEOTONIO DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11635</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>FA-11594</t>
+  </si>
+  <si>
+    <t>FA-11647</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
   </si>
 </sst>
 </file>
@@ -351,7 +663,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S30"/>
+  <dimension ref="A1:S106"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -366,12 +678,12 @@
     <col min="10" max="10" width="21" customWidth="1" style="1"/>
     <col min="11" max="11" width="13" customWidth="1" style="1"/>
     <col min="12" max="12" width="39" customWidth="1" style="1"/>
-    <col min="13" max="13" width="27" customWidth="1" style="1"/>
+    <col min="13" max="13" width="55" customWidth="1" style="1"/>
     <col min="14" max="14" width="31" customWidth="1" style="1"/>
     <col min="15" max="15" width="26" customWidth="1" style="1"/>
     <col min="16" max="16" width="14" customWidth="1" style="1"/>
     <col min="17" max="17" width="16" customWidth="1" style="1"/>
-    <col min="18" max="18" width="20" customWidth="1" style="1"/>
+    <col min="18" max="18" width="23" customWidth="1" style="1"/>
     <col min="19" max="19" width="16" customWidth="1" style="1"/>
     <col min="20" max="16384" width="9.140625" customWidth="1" style="1"/>
   </cols>
@@ -1867,27 +2179,4511 @@
         <v>680</v>
       </c>
     </row>
-    <row r="30" ht="23" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="10"/>
-      <c r="M30" s="10"/>
-      <c r="N30" s="10"/>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="10"/>
-      <c r="S30" s="13">
-        <f>SUM(S6:S29)</f>
+    <row r="30">
+      <c r="A30" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C30" s="7">
+        <v>46143</v>
+      </c>
+      <c r="D30" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E30" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F30" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G30" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P30" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q30" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S30" s="9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C31" s="7">
+        <v>46143</v>
+      </c>
+      <c r="D31" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E31" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F31" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G31" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N31" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O31" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q31" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S31" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C32" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D32" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G32" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O32" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S32" s="9">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C33" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D33" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G33" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N33" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S33" s="9">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C34" s="7">
+        <v>46082</v>
+      </c>
+      <c r="D34" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E34" s="7">
+        <v>46097</v>
+      </c>
+      <c r="F34" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G34" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q34" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R34" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S34" s="9">
+        <v>146.55</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C35" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D35" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G35" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S35" s="9">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B36" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C36" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D36" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G36" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S36" s="9">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C37" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D37" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F37" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G37" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="N37" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O37" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S37" s="9">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C38" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D38" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F38" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G38" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S38" s="9">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C39" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D39" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" s="8">
+        <v>-15</v>
+      </c>
+      <c r="G39" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P39" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q39" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S39" s="9">
+        <v>193.43</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C40" s="7">
+        <v>46167</v>
+      </c>
+      <c r="D40" s="7">
+        <v>46167</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F40" s="8">
+        <v>-15</v>
+      </c>
+      <c r="G40" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N40" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R40" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S40" s="9">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C41" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D41" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41" s="8">
+        <v>-8</v>
+      </c>
+      <c r="G41" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I41" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N41" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q41" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R41" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S41" s="9">
+        <v>302.72</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C42" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D42" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="8">
+        <v>-8</v>
+      </c>
+      <c r="G42" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R42" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S42" s="9">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C43" s="7">
+        <v>46174</v>
+      </c>
+      <c r="D43" s="7">
+        <v>46174</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F43" s="8">
+        <v>-8</v>
+      </c>
+      <c r="G43" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I43" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="N43" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R43" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S43" s="9">
+        <v>579.12</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C44" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D44" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E44" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F44" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G44" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="N44" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q44" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S44" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C45" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D45" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E45" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F45" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G45" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I45" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J45" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N45" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O45" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q45" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R45" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S45" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C46" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D46" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E46" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F46" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G46" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I46" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N46" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q46" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S46" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C47" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D47" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E47" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F47" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G47" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N47" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O47" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q47" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R47" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S47" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B48" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C48" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D48" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E48" s="7">
+        <v>46164</v>
+      </c>
+      <c r="F48" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G48" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I48" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q48" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R48" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S48" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C49" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D49" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E49" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F49" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G49" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M49" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N49" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O49" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P49" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q49" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R49" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S49" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C50" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D50" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E50" s="7">
+        <v>46163</v>
+      </c>
+      <c r="F50" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G50" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I50" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N50" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O50" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q50" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R50" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S50" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C51" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D51" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E51" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F51" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G51" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I51" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J51" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="M51" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="N51" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O51" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q51" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R51" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S51" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B52" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C52" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D52" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E52" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F52" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G52" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O52" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q52" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R52" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S52" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C53" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D53" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E53" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F53" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G53" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I53" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N53" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O53" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q53" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S53" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C54" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D54" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E54" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F54" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G54" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I54" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J54" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O54" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q54" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R54" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S54" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B55" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C55" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D55" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E55" s="7">
+        <v>46182</v>
+      </c>
+      <c r="F55" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G55" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I55" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J55" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="M55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N55" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O55" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q55" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R55" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S55" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B56" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C56" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D56" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E56" s="7">
+        <v>46182</v>
+      </c>
+      <c r="F56" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G56" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I56" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J56" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O56" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q56" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R56" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S56" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B57" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C57" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D57" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E57" s="7">
+        <v>46164</v>
+      </c>
+      <c r="F57" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G57" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J57" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="K57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N57" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O57" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q57" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R57" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S57" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B58" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C58" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D58" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E58" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F58" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G58" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O58" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P58" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q58" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R58" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S58" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C59" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D59" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E59" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F59" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G59" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I59" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J59" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="M59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N59" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O59" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q59" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R59" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S59" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B60" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C60" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D60" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E60" s="7">
+        <v>46182</v>
+      </c>
+      <c r="F60" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G60" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I60" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J60" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="K60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O60" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q60" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R60" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="S60" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B61" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C61" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D61" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E61" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F61" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G61" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I61" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J61" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N61" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O61" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q61" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R61" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="S61" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B62" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C62" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D62" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E62" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F62" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G62" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I62" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J62" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O62" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P62" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q62" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R62" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="S62" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B63" s="7">
+        <v>46181</v>
+      </c>
+      <c r="C63" s="7">
+        <v>46143</v>
+      </c>
+      <c r="D63" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E63" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F63" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G63" s="8">
+        <v>-1</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I63" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J63" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N63" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O63" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P63" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q63" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R63" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S63" s="9">
+        <v>2969.17</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B64" s="7">
+        <v>46182</v>
+      </c>
+      <c r="C64" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D64" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F64" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G64" s="8">
+        <v>0</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O64" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R64" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S64" s="9">
+        <v>215.07</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" s="7">
+        <v>46182</v>
+      </c>
+      <c r="C65" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D65" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F65" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G65" s="8">
+        <v>0</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J65" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="N65" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O65" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R65" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S65" s="9">
+        <v>237.36</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B66" s="7">
+        <v>46182</v>
+      </c>
+      <c r="C66" s="7">
+        <v>46181</v>
+      </c>
+      <c r="D66" s="7">
+        <v>46181</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F66" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G66" s="8">
+        <v>0</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J66" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O66" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R66" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S66" s="9">
+        <v>431.06</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C67" s="7">
+        <v>46143</v>
+      </c>
+      <c r="D67" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E67" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F67" s="8">
+        <v>6</v>
+      </c>
+      <c r="G67" s="8">
+        <v>6</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J67" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N67" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O67" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P67" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q67" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R67" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S67" s="9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C68" s="7">
+        <v>46143</v>
+      </c>
+      <c r="D68" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E68" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F68" s="8">
+        <v>6</v>
+      </c>
+      <c r="G68" s="8">
+        <v>6</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J68" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O68" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q68" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R68" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S68" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B69" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C69" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D69" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F69" s="8">
+        <v>6</v>
+      </c>
+      <c r="G69" s="8">
+        <v>6</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M69" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="N69" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O69" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S69" s="9">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C70" s="7">
+        <v>46082</v>
+      </c>
+      <c r="D70" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E70" s="7">
+        <v>46097</v>
+      </c>
+      <c r="F70" s="8">
+        <v>6</v>
+      </c>
+      <c r="G70" s="8">
+        <v>6</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J70" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O70" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q70" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R70" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S70" s="9">
+        <v>146.55</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B71" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C71" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D71" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E71" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F71" s="8">
+        <v>6</v>
+      </c>
+      <c r="G71" s="8">
+        <v>6</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J71" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="K71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="M71" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="N71" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O71" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q71" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R71" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S71" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B72" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C72" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D72" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E72" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F72" s="8">
+        <v>6</v>
+      </c>
+      <c r="G72" s="8">
+        <v>6</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J72" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="K72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O72" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P72" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q72" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R72" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S72" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B73" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C73" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D73" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E73" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F73" s="8">
+        <v>6</v>
+      </c>
+      <c r="G73" s="8">
+        <v>6</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="K73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="M73" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="N73" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O73" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q73" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R73" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S73" s="9">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B74" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C74" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D74" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E74" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F74" s="8">
+        <v>6</v>
+      </c>
+      <c r="G74" s="8">
+        <v>6</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J74" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q74" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R74" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S74" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B75" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C75" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D75" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E75" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F75" s="8">
+        <v>6</v>
+      </c>
+      <c r="G75" s="8">
+        <v>6</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J75" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="K75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M75" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="N75" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O75" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q75" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R75" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S75" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B76" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C76" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D76" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E76" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F76" s="8">
+        <v>6</v>
+      </c>
+      <c r="G76" s="8">
+        <v>6</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J76" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="K76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O76" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P76" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q76" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R76" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S76" s="9">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B77" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C77" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D77" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E77" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F77" s="8">
+        <v>6</v>
+      </c>
+      <c r="G77" s="8">
+        <v>6</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J77" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="K77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M77" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N77" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O77" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P77" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q77" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R77" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S77" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B78" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C78" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D78" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E78" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F78" s="8">
+        <v>6</v>
+      </c>
+      <c r="G78" s="8">
+        <v>6</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J78" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N78" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O78" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P78" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q78" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R78" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S78" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C79" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D79" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E79" s="7">
+        <v>46164</v>
+      </c>
+      <c r="F79" s="8">
+        <v>6</v>
+      </c>
+      <c r="G79" s="8">
+        <v>6</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J79" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="K79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="M79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N79" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O79" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q79" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R79" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S79" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C80" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D80" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E80" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F80" s="8">
+        <v>6</v>
+      </c>
+      <c r="G80" s="8">
+        <v>6</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J80" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="K80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O80" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P80" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q80" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R80" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S80" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C81" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D81" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E81" s="7">
+        <v>46163</v>
+      </c>
+      <c r="F81" s="8">
+        <v>6</v>
+      </c>
+      <c r="G81" s="8">
+        <v>6</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J81" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="K81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N81" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O81" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P81" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q81" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R81" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S81" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C82" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D82" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E82" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F82" s="8">
+        <v>6</v>
+      </c>
+      <c r="G82" s="8">
+        <v>6</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J82" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q82" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R82" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S82" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C83" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D83" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E83" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F83" s="8">
+        <v>6</v>
+      </c>
+      <c r="G83" s="8">
+        <v>6</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J83" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="K83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N83" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O83" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P83" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q83" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R83" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S83" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C84" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D84" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E84" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F84" s="8">
+        <v>6</v>
+      </c>
+      <c r="G84" s="8">
+        <v>6</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J84" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="K84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q84" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R84" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S84" s="9">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C85" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D85" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E85" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F85" s="8">
+        <v>6</v>
+      </c>
+      <c r="G85" s="8">
+        <v>6</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J85" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="K85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="M85" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="N85" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O85" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q85" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R85" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S85" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C86" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D86" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E86" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F86" s="8">
+        <v>6</v>
+      </c>
+      <c r="G86" s="8">
+        <v>6</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J86" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N86" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q86" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R86" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S86" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B87" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C87" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D87" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E87" s="7">
+        <v>46153</v>
+      </c>
+      <c r="F87" s="8">
+        <v>6</v>
+      </c>
+      <c r="G87" s="8">
+        <v>6</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J87" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="K87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="M87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N87" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O87" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P87" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q87" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R87" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S87" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B88" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C88" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D88" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E88" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F88" s="8">
+        <v>6</v>
+      </c>
+      <c r="G88" s="8">
+        <v>6</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J88" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q88" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R88" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S88" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B89" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C89" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D89" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E89" s="7">
+        <v>46127</v>
+      </c>
+      <c r="F89" s="8">
+        <v>6</v>
+      </c>
+      <c r="G89" s="8">
+        <v>6</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N89" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O89" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P89" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q89" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R89" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S89" s="9">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B90" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C90" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D90" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E90" s="7">
+        <v>46119</v>
+      </c>
+      <c r="F90" s="8">
+        <v>6</v>
+      </c>
+      <c r="G90" s="8">
+        <v>6</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J90" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="K90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N90" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O90" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P90" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q90" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R90" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S90" s="9">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B91" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C91" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D91" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E91" s="7">
+        <v>46167</v>
+      </c>
+      <c r="F91" s="8">
+        <v>6</v>
+      </c>
+      <c r="G91" s="8">
+        <v>6</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J91" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="K91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N91" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O91" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P91" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q91" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R91" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S91" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B92" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C92" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D92" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E92" s="7">
+        <v>46176</v>
+      </c>
+      <c r="F92" s="8">
+        <v>6</v>
+      </c>
+      <c r="G92" s="8">
+        <v>6</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J92" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="K92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N92" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O92" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P92" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q92" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R92" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S92" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B93" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C93" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D93" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E93" s="7">
+        <v>46182</v>
+      </c>
+      <c r="F93" s="8">
+        <v>6</v>
+      </c>
+      <c r="G93" s="8">
+        <v>6</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J93" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="M93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N93" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O93" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q93" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R93" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S93" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C94" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D94" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E94" s="7">
+        <v>46141</v>
+      </c>
+      <c r="F94" s="8">
+        <v>6</v>
+      </c>
+      <c r="G94" s="8">
+        <v>6</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J94" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N94" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P94" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q94" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R94" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S94" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B95" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C95" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D95" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E95" s="7">
+        <v>46182</v>
+      </c>
+      <c r="F95" s="8">
+        <v>6</v>
+      </c>
+      <c r="G95" s="8">
+        <v>6</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J95" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="K95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="M95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N95" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O95" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P95" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q95" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R95" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S95" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C96" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D96" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E96" s="7">
+        <v>46164</v>
+      </c>
+      <c r="F96" s="8">
+        <v>6</v>
+      </c>
+      <c r="G96" s="8">
+        <v>6</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J96" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="K96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N96" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O96" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P96" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q96" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R96" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="S96" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C97" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D97" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E97" s="7">
+        <v>46182</v>
+      </c>
+      <c r="F97" s="8">
+        <v>6</v>
+      </c>
+      <c r="G97" s="8">
+        <v>6</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J97" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="K97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="M97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N97" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O97" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P97" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q97" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R97" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S97" s="9">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B98" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C98" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D98" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E98" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F98" s="8">
+        <v>6</v>
+      </c>
+      <c r="G98" s="8">
+        <v>6</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J98" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="K98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M98" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N98" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O98" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P98" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q98" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R98" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S98" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C99" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D99" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E99" s="7">
+        <v>46170</v>
+      </c>
+      <c r="F99" s="8">
+        <v>6</v>
+      </c>
+      <c r="G99" s="8">
+        <v>6</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J99" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="K99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L99" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="M99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N99" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O99" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P99" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q99" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R99" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S99" s="9">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B100" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C100" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D100" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E100" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F100" s="8">
+        <v>6</v>
+      </c>
+      <c r="G100" s="8">
+        <v>6</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J100" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L100" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N100" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O100" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P100" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q100" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R100" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="S100" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B101" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C101" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D101" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E101" s="7">
+        <v>46182</v>
+      </c>
+      <c r="F101" s="8">
+        <v>6</v>
+      </c>
+      <c r="G101" s="8">
+        <v>6</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J101" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L101" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="M101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N101" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O101" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P101" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q101" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R101" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="S101" s="9">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B102" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C102" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D102" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E102" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F102" s="8">
+        <v>6</v>
+      </c>
+      <c r="G102" s="8">
+        <v>6</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J102" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="K102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L102" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N102" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O102" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q102" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R102" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="S102" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B103" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C103" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D103" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E103" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F103" s="8">
+        <v>6</v>
+      </c>
+      <c r="G103" s="8">
+        <v>6</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J103" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="K103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L103" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="M103" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N103" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O103" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P103" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q103" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R103" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="S103" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B104" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C104" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D104" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E104" s="7">
+        <v>46148</v>
+      </c>
+      <c r="F104" s="8">
+        <v>6</v>
+      </c>
+      <c r="G104" s="8">
+        <v>6</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J104" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="K104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L104" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="M104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N104" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O104" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q104" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R104" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="S104" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B105" s="7">
+        <v>46188</v>
+      </c>
+      <c r="C105" s="7">
+        <v>46188</v>
+      </c>
+      <c r="D105" s="7">
+        <v>46188</v>
+      </c>
+      <c r="E105" s="7">
+        <v>46160</v>
+      </c>
+      <c r="F105" s="8">
+        <v>6</v>
+      </c>
+      <c r="G105" s="8">
+        <v>6</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I105" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J105" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="K105" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L105" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="M105" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N105" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="O105" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="P105" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q105" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="R105" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="S105" s="9">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="106" ht="23" customHeight="1">
+      <c r="A106" s="10"/>
+      <c r="B106" s="11"/>
+      <c r="C106" s="11"/>
+      <c r="D106" s="11"/>
+      <c r="E106" s="11"/>
+      <c r="F106" s="12"/>
+      <c r="G106" s="12"/>
+      <c r="H106" s="10"/>
+      <c r="I106" s="10"/>
+      <c r="J106" s="10"/>
+      <c r="K106" s="10"/>
+      <c r="L106" s="10"/>
+      <c r="M106" s="10"/>
+      <c r="N106" s="10"/>
+      <c r="O106" s="10"/>
+      <c r="P106" s="10"/>
+      <c r="Q106" s="10"/>
+      <c r="R106" s="10"/>
+      <c r="S106" s="13">
+        <f>SUM(S6:S105)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$61</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -172,15 +172,12 @@
     <t>FA-11565</t>
   </si>
   <si>
-    <t>FA-11480</t>
+    <t>FA-11780</t>
   </si>
   <si>
     <t>YAGO ELIAS COSTA BATISTA</t>
   </si>
   <si>
-    <t>FA-11780</t>
-  </si>
-  <si>
     <t>FA-11566</t>
   </si>
   <si>
@@ -235,12 +232,21 @@
     <t>FA-11709</t>
   </si>
   <si>
+    <t>FA-11568</t>
+  </si>
+  <si>
     <t>FA-11670</t>
   </si>
   <si>
     <t>RICARDO ARAUJO DE MIRANDA</t>
   </si>
   <si>
+    <t>FA-11685</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
     <t>FA-11692</t>
   </si>
   <si>
@@ -259,9 +265,6 @@
     <t>FA-11784</t>
   </si>
   <si>
-    <t>FA-11568</t>
-  </si>
-  <si>
     <t>FA-11569</t>
   </si>
   <si>
@@ -274,31 +277,22 @@
     <t>FA-11796</t>
   </si>
   <si>
-    <t>FA-11685</t>
-  </si>
-  <si>
-    <t>GILVAN RODRIGUES MACHADO</t>
-  </si>
-  <si>
-    <t>FA-11795</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
     <t>FA-11775</t>
   </si>
   <si>
+    <t>FA-11815</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11814</t>
+  </si>
+  <si>
     <t>FA-11678</t>
   </si>
   <si>
-    <t>FA-11815</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11814</t>
+    <t>FA-11693</t>
   </si>
   <si>
     <t>FA-11570</t>
@@ -307,9 +301,6 @@
     <t>ELSON VIEIRA DA SILVA</t>
   </si>
   <si>
-    <t>FA-11693</t>
-  </si>
-  <si>
     <t>FA-11782</t>
   </si>
   <si>
@@ -328,15 +319,15 @@
     <t>JOÃO PAULO CONSÓRCIOS</t>
   </si>
   <si>
-    <t>FA-11603</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
     <t>ND-11801</t>
   </si>
   <si>
+    <t>FA-11813</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
     <t>FA-11755</t>
   </si>
   <si>
@@ -347,12 +338,6 @@
   </si>
   <si>
     <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11813</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
   </si>
   <si>
     <t>FA-11593</t>
@@ -507,7 +492,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:S61"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -1618,16 +1603,16 @@
         <v>46174</v>
       </c>
       <c r="C23" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="D23" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>23</v>
+        <v>46174</v>
+      </c>
+      <c r="E23" s="7">
+        <v>46170</v>
       </c>
       <c r="F23" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="G23" s="8">
         <v>-9</v>
@@ -1660,13 +1645,13 @@
         <v>23</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S23" s="9">
-        <v>350</v>
+        <v>600</v>
       </c>
     </row>
     <row r="24">
@@ -1683,7 +1668,7 @@
         <v>46174</v>
       </c>
       <c r="E24" s="7">
-        <v>46170</v>
+        <v>46141</v>
       </c>
       <c r="F24" s="8">
         <v>-9</v>
@@ -1704,10 +1689,10 @@
         <v>23</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>27</v>
@@ -1725,7 +1710,7 @@
         <v>37</v>
       </c>
       <c r="S24" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="25">
@@ -1742,7 +1727,7 @@
         <v>46174</v>
       </c>
       <c r="E25" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="F25" s="8">
         <v>-9</v>
@@ -1757,16 +1742,16 @@
         <v>33</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>27</v>
@@ -1784,7 +1769,7 @@
         <v>37</v>
       </c>
       <c r="S25" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="26">
@@ -1801,7 +1786,7 @@
         <v>46174</v>
       </c>
       <c r="E26" s="7">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="F26" s="8">
         <v>-9</v>
@@ -1816,13 +1801,13 @@
         <v>33</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>23</v>
@@ -1840,10 +1825,10 @@
         <v>36</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S26" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="27">
@@ -1860,7 +1845,7 @@
         <v>46174</v>
       </c>
       <c r="E27" s="7">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="F27" s="8">
         <v>-9</v>
@@ -1875,13 +1860,13 @@
         <v>33</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -1899,10 +1884,10 @@
         <v>36</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S27" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="28">
@@ -1910,22 +1895,22 @@
         <v>22</v>
       </c>
       <c r="B28" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C28" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D28" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E28" s="7">
-        <v>46170</v>
+        <v>46153</v>
       </c>
       <c r="F28" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G28" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>33</v>
@@ -1934,13 +1919,13 @@
         <v>33</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>23</v>
@@ -1952,16 +1937,16 @@
         <v>27</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S28" s="9">
-        <v>680</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
@@ -1978,7 +1963,7 @@
         <v>46181</v>
       </c>
       <c r="E29" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="F29" s="8">
         <v>-2</v>
@@ -1993,13 +1978,13 @@
         <v>33</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>23</v>
@@ -2011,7 +1996,7 @@
         <v>27</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="Q29" s="6" t="s">
         <v>29</v>
@@ -2020,7 +2005,7 @@
         <v>37</v>
       </c>
       <c r="S29" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
@@ -2031,13 +2016,13 @@
         <v>46181</v>
       </c>
       <c r="C30" s="7">
-        <v>46143</v>
+        <v>46181</v>
       </c>
       <c r="D30" s="7">
         <v>46181</v>
       </c>
-      <c r="E30" s="7">
-        <v>46167</v>
+      <c r="E30" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F30" s="8">
         <v>-2</v>
@@ -2052,16 +2037,16 @@
         <v>33</v>
       </c>
       <c r="J30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="K30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>56</v>
-      </c>
       <c r="M30" s="6" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -2073,13 +2058,13 @@
         <v>23</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="S30" s="9">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31">
@@ -2117,10 +2102,10 @@
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M31" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="M31" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>27</v>
@@ -2149,13 +2134,13 @@
         <v>46181</v>
       </c>
       <c r="C32" s="7">
-        <v>46181</v>
+        <v>46082</v>
       </c>
       <c r="D32" s="7">
         <v>46181</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>23</v>
+      <c r="E32" s="7">
+        <v>46097</v>
       </c>
       <c r="F32" s="8">
         <v>-2</v>
@@ -2170,16 +2155,16 @@
         <v>33</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>27</v>
@@ -2191,13 +2176,13 @@
         <v>23</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="S32" s="9">
-        <v>120</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="33">
@@ -2208,13 +2193,13 @@
         <v>46181</v>
       </c>
       <c r="C33" s="7">
-        <v>46082</v>
+        <v>46181</v>
       </c>
       <c r="D33" s="7">
         <v>46181</v>
       </c>
-      <c r="E33" s="7">
-        <v>46097</v>
+      <c r="E33" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F33" s="8">
         <v>-2</v>
@@ -2229,16 +2214,16 @@
         <v>33</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>27</v>
@@ -2250,13 +2235,13 @@
         <v>23</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="S33" s="9">
-        <v>146.55</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34">
@@ -2294,10 +2279,10 @@
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M34" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="M34" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>27</v>
@@ -2353,10 +2338,10 @@
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M35" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="M35" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="N35" s="6" t="s">
         <v>27</v>
@@ -2385,16 +2370,16 @@
         <v>46181</v>
       </c>
       <c r="C36" s="7">
-        <v>46181</v>
+        <v>46167</v>
       </c>
       <c r="D36" s="7">
-        <v>46181</v>
+        <v>46167</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-2</v>
+        <v>-16</v>
       </c>
       <c r="G36" s="8">
         <v>-2</v>
@@ -2406,16 +2391,16 @@
         <v>33</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>27</v>
@@ -2430,10 +2415,10 @@
         <v>23</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="S36" s="9">
-        <v>180</v>
+        <v>193.43</v>
       </c>
     </row>
     <row r="37">
@@ -2444,16 +2429,16 @@
         <v>46181</v>
       </c>
       <c r="C37" s="7">
-        <v>46181</v>
+        <v>46167</v>
       </c>
       <c r="D37" s="7">
-        <v>46181</v>
+        <v>46167</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F37" s="8">
-        <v>-2</v>
+        <v>-16</v>
       </c>
       <c r="G37" s="8">
         <v>-2</v>
@@ -2465,16 +2450,16 @@
         <v>33</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>27</v>
@@ -2489,10 +2474,10 @@
         <v>23</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="S37" s="9">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38">
@@ -2503,16 +2488,16 @@
         <v>46181</v>
       </c>
       <c r="C38" s="7">
-        <v>46167</v>
+        <v>46181</v>
       </c>
       <c r="D38" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>23</v>
+        <v>46181</v>
+      </c>
+      <c r="E38" s="7">
+        <v>46141</v>
       </c>
       <c r="F38" s="8">
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="G38" s="8">
         <v>-2</v>
@@ -2524,13 +2509,13 @@
         <v>33</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>23</v>
@@ -2545,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S38" s="9">
-        <v>193.43</v>
+        <v>310</v>
       </c>
     </row>
     <row r="39">
@@ -2562,16 +2547,16 @@
         <v>46181</v>
       </c>
       <c r="C39" s="7">
-        <v>46167</v>
+        <v>46181</v>
       </c>
       <c r="D39" s="7">
-        <v>46167</v>
+        <v>46181</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F39" s="8">
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="G39" s="8">
         <v>-2</v>
@@ -2583,13 +2568,13 @@
         <v>33</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>23</v>
@@ -2607,10 +2592,10 @@
         <v>23</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S39" s="9">
-        <v>200</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40">
@@ -2626,8 +2611,8 @@
       <c r="D40" s="7">
         <v>46181</v>
       </c>
-      <c r="E40" s="7" t="s">
-        <v>23</v>
+      <c r="E40" s="7">
+        <v>46164</v>
       </c>
       <c r="F40" s="8">
         <v>-2</v>
@@ -2642,13 +2627,13 @@
         <v>33</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>23</v>
@@ -2663,13 +2648,13 @@
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S40" s="9">
-        <v>340</v>
+        <v>346.5</v>
       </c>
     </row>
     <row r="41">
@@ -2701,7 +2686,7 @@
         <v>33</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
@@ -2760,13 +2745,13 @@
         <v>33</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -2819,16 +2804,16 @@
         <v>33</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>27</v>
@@ -2878,7 +2863,7 @@
         <v>33</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
@@ -2937,16 +2922,16 @@
         <v>33</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>27</v>
@@ -2981,7 +2966,7 @@
         <v>46181</v>
       </c>
       <c r="E46" s="7">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="F46" s="8">
         <v>-2</v>
@@ -2996,16 +2981,16 @@
         <v>33</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>27</v>
@@ -3023,7 +3008,7 @@
         <v>37</v>
       </c>
       <c r="S46" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="47">
@@ -3040,7 +3025,7 @@
         <v>46181</v>
       </c>
       <c r="E47" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F47" s="8">
         <v>-2</v>
@@ -3055,13 +3040,13 @@
         <v>33</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>23</v>
@@ -3114,16 +3099,16 @@
         <v>33</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="N48" s="6" t="s">
         <v>27</v>
@@ -3141,7 +3126,7 @@
         <v>37</v>
       </c>
       <c r="S48" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="49">
@@ -3158,7 +3143,7 @@
         <v>46181</v>
       </c>
       <c r="E49" s="7">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="F49" s="8">
         <v>-2</v>
@@ -3173,13 +3158,13 @@
         <v>33</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>23</v>
@@ -3200,7 +3185,7 @@
         <v>37</v>
       </c>
       <c r="S49" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="50">
@@ -3217,7 +3202,7 @@
         <v>46181</v>
       </c>
       <c r="E50" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F50" s="8">
         <v>-2</v>
@@ -3232,13 +3217,13 @@
         <v>33</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>23</v>
@@ -3259,7 +3244,7 @@
         <v>37</v>
       </c>
       <c r="S50" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="51">
@@ -3276,7 +3261,7 @@
         <v>46181</v>
       </c>
       <c r="E51" s="7">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="F51" s="8">
         <v>-2</v>
@@ -3291,7 +3276,7 @@
         <v>33</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
@@ -3300,7 +3285,7 @@
         <v>73</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="N51" s="6" t="s">
         <v>27</v>
@@ -3315,10 +3300,10 @@
         <v>36</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S51" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="52">
@@ -3335,7 +3320,7 @@
         <v>46181</v>
       </c>
       <c r="E52" s="7">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F52" s="8">
         <v>-2</v>
@@ -3350,13 +3335,13 @@
         <v>33</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="M52" s="6" t="s">
         <v>23</v>
@@ -3374,7 +3359,7 @@
         <v>36</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="S52" s="9">
         <v>680</v>
@@ -3394,7 +3379,7 @@
         <v>46181</v>
       </c>
       <c r="E53" s="7">
-        <v>46182</v>
+        <v>46141</v>
       </c>
       <c r="F53" s="8">
         <v>-2</v>
@@ -3409,13 +3394,13 @@
         <v>33</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
@@ -3433,7 +3418,7 @@
         <v>36</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S53" s="9">
         <v>680</v>
@@ -3453,7 +3438,7 @@
         <v>46181</v>
       </c>
       <c r="E54" s="7">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="F54" s="8">
         <v>-2</v>
@@ -3468,13 +3453,13 @@
         <v>33</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
@@ -3486,7 +3471,7 @@
         <v>27</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="Q54" s="6" t="s">
         <v>36</v>
@@ -3495,12 +3480,12 @@
         <v>37</v>
       </c>
       <c r="S54" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="B55" s="7">
         <v>46181</v>
@@ -3512,7 +3497,7 @@
         <v>46181</v>
       </c>
       <c r="E55" s="7">
-        <v>46141</v>
+        <v>46182</v>
       </c>
       <c r="F55" s="8">
         <v>-2</v>
@@ -3527,13 +3512,13 @@
         <v>33</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
@@ -3551,10 +3536,10 @@
         <v>36</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="S55" s="9">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="56">
@@ -3565,13 +3550,13 @@
         <v>46181</v>
       </c>
       <c r="C56" s="7">
-        <v>46181</v>
+        <v>46143</v>
       </c>
       <c r="D56" s="7">
         <v>46181</v>
       </c>
       <c r="E56" s="7">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="F56" s="8">
         <v>-2</v>
@@ -3586,13 +3571,13 @@
         <v>33</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
@@ -3607,13 +3592,13 @@
         <v>23</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S56" s="9">
-        <v>680</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="57">
@@ -3621,7 +3606,7 @@
         <v>22</v>
       </c>
       <c r="B57" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C57" s="7">
         <v>46181</v>
@@ -3629,14 +3614,14 @@
       <c r="D57" s="7">
         <v>46181</v>
       </c>
-      <c r="E57" s="7">
-        <v>46170</v>
+      <c r="E57" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F57" s="8">
         <v>-2</v>
       </c>
       <c r="G57" s="8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>33</v>
@@ -3645,13 +3630,13 @@
         <v>33</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>23</v>
@@ -3663,24 +3648,24 @@
         <v>27</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>37</v>
       </c>
       <c r="S57" s="9">
-        <v>700</v>
+        <v>129.49</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="B58" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C58" s="7">
         <v>46181</v>
@@ -3688,14 +3673,14 @@
       <c r="D58" s="7">
         <v>46181</v>
       </c>
-      <c r="E58" s="7">
-        <v>46182</v>
+      <c r="E58" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F58" s="8">
         <v>-2</v>
       </c>
       <c r="G58" s="8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>33</v>
@@ -3704,13 +3689,13 @@
         <v>33</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>23</v>
@@ -3725,13 +3710,13 @@
         <v>23</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>97</v>
+        <v>37</v>
       </c>
       <c r="S58" s="9">
-        <v>800</v>
+        <v>215.07</v>
       </c>
     </row>
     <row r="59">
@@ -3739,7 +3724,7 @@
         <v>22</v>
       </c>
       <c r="B59" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C59" s="7">
         <v>46181</v>
@@ -3747,14 +3732,14 @@
       <c r="D59" s="7">
         <v>46181</v>
       </c>
-      <c r="E59" s="7">
-        <v>46148</v>
+      <c r="E59" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F59" s="8">
         <v>-2</v>
       </c>
       <c r="G59" s="8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>33</v>
@@ -3763,16 +3748,16 @@
         <v>33</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>23</v>
+        <v>101</v>
       </c>
       <c r="N59" s="6" t="s">
         <v>27</v>
@@ -3784,13 +3769,13 @@
         <v>23</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>97</v>
+        <v>28</v>
       </c>
       <c r="S59" s="9">
-        <v>800</v>
+        <v>237.36</v>
       </c>
     </row>
     <row r="60">
@@ -3798,37 +3783,37 @@
         <v>22</v>
       </c>
       <c r="B60" s="7">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="C60" s="7">
-        <v>46143</v>
+        <v>46181</v>
       </c>
       <c r="D60" s="7">
         <v>46181</v>
       </c>
-      <c r="E60" s="7">
-        <v>46170</v>
+      <c r="E60" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F60" s="8">
         <v>-2</v>
       </c>
       <c r="G60" s="8">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>33</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>23</v>
@@ -3837,278 +3822,42 @@
         <v>27</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>27</v>
+        <v>104</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q60" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>28</v>
+        <v>105</v>
       </c>
       <c r="S60" s="9">
-        <v>2969.17</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B61" s="7">
-        <v>46182</v>
-      </c>
-      <c r="C61" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D61" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F61" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G61" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I61" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J61" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="K61" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L61" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="M61" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N61" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O61" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P61" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q61" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R61" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="S61" s="9">
-        <v>215.07</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B62" s="7">
-        <v>46182</v>
-      </c>
-      <c r="C62" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D62" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F62" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G62" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I62" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J62" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="K62" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L62" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="M62" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="N62" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O62" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q62" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R62" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S62" s="9">
-        <v>237.36</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B63" s="7">
-        <v>46182</v>
-      </c>
-      <c r="C63" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D63" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F63" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G63" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H63" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I63" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J63" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="K63" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L63" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="M63" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N63" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O63" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P63" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q63" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R63" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="S63" s="9">
-        <v>431.06</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B64" s="7">
-        <v>46183</v>
-      </c>
-      <c r="C64" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D64" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F64" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G64" s="8">
-        <v>0</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J64" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="K64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="M64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N64" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O64" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R64" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="S64" s="9">
         <v>660</v>
       </c>
     </row>
-    <row r="65" ht="23" customHeight="1">
-      <c r="A65" s="10"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="12"/>
-      <c r="G65" s="12"/>
-      <c r="H65" s="10"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10"/>
-      <c r="K65" s="10"/>
-      <c r="L65" s="10"/>
-      <c r="M65" s="10"/>
-      <c r="N65" s="10"/>
-      <c r="O65" s="10"/>
-      <c r="P65" s="10"/>
-      <c r="Q65" s="10"/>
-      <c r="R65" s="10"/>
-      <c r="S65" s="13">
-        <f>SUM(S6:S64)</f>
+    <row r="61" ht="23" customHeight="1">
+      <c r="A61" s="10"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="11"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="12"/>
+      <c r="H61" s="10"/>
+      <c r="I61" s="10"/>
+      <c r="J61" s="10"/>
+      <c r="K61" s="10"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="10"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
+      <c r="S61" s="13">
+        <f>SUM(S6:S60)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$54</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quarta-feira, 10 de junho de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em quinta-feira, 11 de junho de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -133,21 +133,21 @@
     <t>FA-11446</t>
   </si>
   <si>
+    <t>FA-11557</t>
+  </si>
+  <si>
+    <t>YURI BATISTA DA COSTA</t>
+  </si>
+  <si>
+    <t>FATURA</t>
+  </si>
+  <si>
+    <t>ATIVUZ VEÍCULOS</t>
+  </si>
+  <si>
     <t>VENCIDO ATÉ 30 DIAS</t>
   </si>
   <si>
-    <t>FA-11557</t>
-  </si>
-  <si>
-    <t>YURI BATISTA DA COSTA</t>
-  </si>
-  <si>
-    <t>FATURA</t>
-  </si>
-  <si>
-    <t>ATIVUZ VEÍCULOS</t>
-  </si>
-  <si>
     <t>FA-11559</t>
   </si>
   <si>
@@ -157,127 +157,115 @@
     <t>FA-11562</t>
   </si>
   <si>
-    <t>Z. CONTA GERENCIAL</t>
-  </si>
-  <si>
-    <t>FA-11691</t>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>FA-11565</t>
+  </si>
+  <si>
+    <t>FA-11566</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11794</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11711</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>FA-11772</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>ND-11699</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>ND-11700</t>
+  </si>
+  <si>
+    <t>FA-11709</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LOCACAO DE ATIVOS</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA EMPREENDIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>FA-11670</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11568</t>
+  </si>
+  <si>
+    <t>FA-11677</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11774</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11784</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11569</t>
+  </si>
+  <si>
+    <t>FA-11720</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11796</t>
+  </si>
+  <si>
+    <t>FA-11775</t>
+  </si>
+  <si>
+    <t>FA-11692</t>
   </si>
   <si>
     <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
   </si>
   <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>FA-11565</t>
-  </si>
-  <si>
-    <t>FA-11780</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11566</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11794</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11711</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>FA-11772</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>ND-11699</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>ND-11700</t>
-  </si>
-  <si>
-    <t>JOAO PAULO CONSORCIOS</t>
-  </si>
-  <si>
-    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LOCACAO DE ATIVOS</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA EMPREENDIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>FA-11617</t>
-  </si>
-  <si>
-    <t>FA-11709</t>
-  </si>
-  <si>
-    <t>FA-11568</t>
-  </si>
-  <si>
-    <t>FA-11670</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11685</t>
-  </si>
-  <si>
-    <t>GILVAN RODRIGUES MACHADO</t>
-  </si>
-  <si>
-    <t>FA-11692</t>
-  </si>
-  <si>
-    <t>FA-11677</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11774</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11784</t>
-  </si>
-  <si>
-    <t>FA-11569</t>
-  </si>
-  <si>
-    <t>FA-11720</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11796</t>
-  </si>
-  <si>
-    <t>FA-11775</t>
+    <t>FA-11570</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11693</t>
+  </si>
+  <si>
+    <t>FA-11678</t>
   </si>
   <si>
     <t>FA-11815</t>
@@ -289,36 +277,12 @@
     <t>FA-11814</t>
   </si>
   <si>
-    <t>FA-11678</t>
-  </si>
-  <si>
-    <t>FA-11693</t>
-  </si>
-  <si>
-    <t>FA-11570</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
     <t>FA-11782</t>
   </si>
   <si>
     <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
   </si>
   <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>FA-11816</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
     <t>ND-11801</t>
   </si>
   <si>
@@ -344,9 +308,6 @@
   </si>
   <si>
     <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>HOJE</t>
   </si>
   <si>
     <t>LUZ DIVINA LTDA</t>
@@ -492,7 +453,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -507,12 +468,12 @@
     <col min="10" max="10" width="21" customWidth="1" style="1"/>
     <col min="11" max="11" width="13" customWidth="1" style="1"/>
     <col min="12" max="12" width="39" customWidth="1" style="1"/>
-    <col min="13" max="13" width="55" customWidth="1" style="1"/>
+    <col min="13" max="13" width="35" customWidth="1" style="1"/>
     <col min="14" max="14" width="31" customWidth="1" style="1"/>
     <col min="15" max="15" width="26" customWidth="1" style="1"/>
     <col min="16" max="16" width="14" customWidth="1" style="1"/>
     <col min="17" max="17" width="16" customWidth="1" style="1"/>
-    <col min="18" max="18" width="23" customWidth="1" style="1"/>
+    <col min="18" max="18" width="20" customWidth="1" style="1"/>
     <col min="19" max="19" width="16" customWidth="1" style="1"/>
     <col min="20" max="16384" width="9.140625" customWidth="1" style="1"/>
   </cols>
@@ -609,10 +570,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-58</v>
+        <v>-59</v>
       </c>
       <c r="G6" s="8">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -668,10 +629,10 @@
         <v>46097</v>
       </c>
       <c r="F7" s="8">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="G7" s="8">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>24</v>
@@ -727,10 +688,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="G8" s="8">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -786,10 +747,10 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-72</v>
+        <v>-73</v>
       </c>
       <c r="G9" s="8">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>24</v>
@@ -845,10 +806,10 @@
         <v>23</v>
       </c>
       <c r="F10" s="8">
-        <v>-58</v>
+        <v>-59</v>
       </c>
       <c r="G10" s="8">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>24</v>
@@ -904,10 +865,10 @@
         <v>46097</v>
       </c>
       <c r="F11" s="8">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="G11" s="8">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>24</v>
@@ -963,16 +924,16 @@
         <v>46097</v>
       </c>
       <c r="F12" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="G12" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>25</v>
@@ -1022,43 +983,43 @@
         <v>46141</v>
       </c>
       <c r="F13" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="G13" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="H13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J13" s="6" t="s">
+      <c r="K13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L13" s="6" t="s">
+      <c r="M13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q13" s="6" t="s">
+      <c r="R13" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="S13" s="9">
         <v>310</v>
@@ -1081,16 +1042,16 @@
         <v>46097</v>
       </c>
       <c r="F14" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G14" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>25</v>
@@ -1140,16 +1101,16 @@
         <v>46141</v>
       </c>
       <c r="F15" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G15" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J15" s="6" t="s">
         <v>38</v>
@@ -1158,25 +1119,25 @@
         <v>23</v>
       </c>
       <c r="L15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M15" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q15" s="6" t="s">
+      <c r="R15" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="R15" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="S15" s="9">
         <v>310</v>
@@ -1199,16 +1160,16 @@
         <v>23</v>
       </c>
       <c r="F16" s="8">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="G16" s="8">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>24</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>39</v>
@@ -1217,7 +1178,7 @@
         <v>23</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>23</v>
@@ -1235,7 +1196,7 @@
         <v>23</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S16" s="9">
         <v>210</v>
@@ -1258,16 +1219,16 @@
         <v>46097</v>
       </c>
       <c r="F17" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G17" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>25</v>
@@ -1317,16 +1278,16 @@
         <v>46141</v>
       </c>
       <c r="F18" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G18" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>40</v>
@@ -1335,25 +1296,25 @@
         <v>23</v>
       </c>
       <c r="L18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q18" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q18" s="6" t="s">
+      <c r="R18" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="R18" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="S18" s="9">
         <v>310</v>
@@ -1361,41 +1322,41 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="7">
+        <v>46172</v>
+      </c>
+      <c r="C19" s="7">
+        <v>45930</v>
+      </c>
+      <c r="D19" s="7">
+        <v>46172</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="8">
+        <v>-12</v>
+      </c>
+      <c r="G19" s="8">
+        <v>-12</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="7">
-        <v>46167</v>
-      </c>
-      <c r="C19" s="7">
-        <v>46167</v>
-      </c>
-      <c r="D19" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E19" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F19" s="8">
-        <v>-16</v>
-      </c>
-      <c r="G19" s="8">
-        <v>-16</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="M19" s="6" t="s">
         <v>23</v>
       </c>
@@ -1409,13 +1370,13 @@
         <v>23</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="S19" s="9">
-        <v>680</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="20">
@@ -1423,37 +1384,37 @@
         <v>22</v>
       </c>
       <c r="B20" s="7">
-        <v>46172</v>
+        <v>46174</v>
       </c>
       <c r="C20" s="7">
-        <v>45930</v>
+        <v>46082</v>
       </c>
       <c r="D20" s="7">
-        <v>46172</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>23</v>
+        <v>46174</v>
+      </c>
+      <c r="E20" s="7">
+        <v>46097</v>
       </c>
       <c r="F20" s="8">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="G20" s="8">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>23</v>
@@ -1468,13 +1429,13 @@
         <v>23</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="S20" s="9">
-        <v>185.5</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="21">
@@ -1485,34 +1446,34 @@
         <v>46174</v>
       </c>
       <c r="C21" s="7">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="D21" s="7">
         <v>46174</v>
       </c>
       <c r="E21" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F21" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G21" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>23</v>
@@ -1527,13 +1488,13 @@
         <v>23</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S21" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22">
@@ -1553,46 +1514,46 @@
         <v>46141</v>
       </c>
       <c r="F22" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G22" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="N22" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q22" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O22" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q22" s="6" t="s">
+      <c r="R22" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="R22" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S22" s="9">
-        <v>310</v>
+        <v>620</v>
       </c>
     </row>
     <row r="23">
@@ -1612,28 +1573,28 @@
         <v>46170</v>
       </c>
       <c r="F23" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G23" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J23" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="K23" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>47</v>
-      </c>
       <c r="M23" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="N23" s="6" t="s">
         <v>27</v>
@@ -1645,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="Q23" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R23" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="R23" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S23" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="24">
@@ -1668,31 +1629,31 @@
         <v>46174</v>
       </c>
       <c r="E24" s="7">
-        <v>46141</v>
+        <v>46168</v>
       </c>
       <c r="F24" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G24" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J24" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="K24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="M24" s="6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>27</v>
@@ -1704,13 +1665,13 @@
         <v>23</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S24" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="25">
@@ -1730,26 +1691,26 @@
         <v>46170</v>
       </c>
       <c r="F25" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G25" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J25" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K25" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="M25" s="6" t="s">
         <v>23</v>
       </c>
@@ -1763,13 +1724,13 @@
         <v>23</v>
       </c>
       <c r="Q25" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R25" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="R25" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S25" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="26">
@@ -1777,58 +1738,58 @@
         <v>22</v>
       </c>
       <c r="B26" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C26" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D26" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E26" s="7">
-        <v>46168</v>
+        <v>46153</v>
       </c>
       <c r="F26" s="8">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="G26" s="8">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="K26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L26" s="6" t="s">
+      <c r="M26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P26" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="M26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P26" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="Q26" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R26" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="R26" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="S26" s="9">
-        <v>650</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -1836,28 +1797,28 @@
         <v>22</v>
       </c>
       <c r="B27" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C27" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D27" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E27" s="7">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="F27" s="8">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="G27" s="8">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>54</v>
@@ -1866,7 +1827,7 @@
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -1881,13 +1842,13 @@
         <v>23</v>
       </c>
       <c r="Q27" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R27" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="R27" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S27" s="9">
-        <v>680</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28">
@@ -1898,34 +1859,34 @@
         <v>46181</v>
       </c>
       <c r="C28" s="7">
-        <v>46143</v>
+        <v>46167</v>
       </c>
       <c r="D28" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E28" s="7">
-        <v>46153</v>
+        <v>46167</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F28" s="8">
-        <v>-2</v>
+        <v>-17</v>
       </c>
       <c r="G28" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>23</v>
@@ -1937,16 +1898,16 @@
         <v>27</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S28" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
@@ -1957,34 +1918,34 @@
         <v>46181</v>
       </c>
       <c r="C29" s="7">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="D29" s="7">
         <v>46181</v>
       </c>
       <c r="E29" s="7">
-        <v>46167</v>
+        <v>46097</v>
       </c>
       <c r="F29" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G29" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>23</v>
@@ -2002,10 +1963,10 @@
         <v>29</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S29" s="9">
-        <v>100</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="30">
@@ -2025,16 +1986,16 @@
         <v>23</v>
       </c>
       <c r="F30" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G30" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>23</v>
@@ -2043,10 +2004,10 @@
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -2064,7 +2025,7 @@
         <v>23</v>
       </c>
       <c r="S30" s="9">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31">
@@ -2084,16 +2045,16 @@
         <v>23</v>
       </c>
       <c r="F31" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G31" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>23</v>
@@ -2102,10 +2063,10 @@
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>27</v>
@@ -2123,7 +2084,7 @@
         <v>23</v>
       </c>
       <c r="S31" s="9">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="32">
@@ -2134,37 +2095,37 @@
         <v>46181</v>
       </c>
       <c r="C32" s="7">
-        <v>46082</v>
+        <v>46181</v>
       </c>
       <c r="D32" s="7">
         <v>46181</v>
       </c>
-      <c r="E32" s="7">
-        <v>46097</v>
+      <c r="E32" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F32" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G32" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>27</v>
@@ -2176,13 +2137,13 @@
         <v>23</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="S32" s="9">
-        <v>146.55</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33">
@@ -2202,28 +2163,28 @@
         <v>23</v>
       </c>
       <c r="F33" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G33" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>27</v>
@@ -2238,10 +2199,10 @@
         <v>23</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="S33" s="9">
-        <v>180</v>
+        <v>230</v>
       </c>
     </row>
     <row r="34">
@@ -2257,32 +2218,32 @@
       <c r="D34" s="7">
         <v>46181</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>23</v>
+      <c r="E34" s="7">
+        <v>46141</v>
       </c>
       <c r="F34" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G34" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>27</v>
@@ -2294,13 +2255,13 @@
         <v>23</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="S34" s="9">
-        <v>180</v>
+        <v>310</v>
       </c>
     </row>
     <row r="35">
@@ -2311,28 +2272,28 @@
         <v>46181</v>
       </c>
       <c r="C35" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="D35" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F35" s="8">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="G35" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
@@ -2341,7 +2302,7 @@
         <v>62</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="N35" s="6" t="s">
         <v>27</v>
@@ -2356,10 +2317,10 @@
         <v>23</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="S35" s="9">
-        <v>180</v>
+        <v>410</v>
       </c>
     </row>
     <row r="36">
@@ -2370,37 +2331,37 @@
         <v>46181</v>
       </c>
       <c r="C36" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="D36" s="7">
-        <v>46167</v>
+        <v>46174</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="G36" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J36" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K36" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="M36" s="6" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>27</v>
@@ -2415,10 +2376,10 @@
         <v>23</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S36" s="9">
-        <v>193.43</v>
+        <v>579.12</v>
       </c>
     </row>
     <row r="37">
@@ -2429,25 +2390,25 @@
         <v>46181</v>
       </c>
       <c r="C37" s="7">
-        <v>46167</v>
+        <v>46181</v>
       </c>
       <c r="D37" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>23</v>
+        <v>46181</v>
+      </c>
+      <c r="E37" s="7">
+        <v>46170</v>
       </c>
       <c r="F37" s="8">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="G37" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>65</v>
@@ -2456,10 +2417,10 @@
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>27</v>
@@ -2471,13 +2432,13 @@
         <v>23</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S37" s="9">
-        <v>200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="38">
@@ -2497,46 +2458,46 @@
         <v>46141</v>
       </c>
       <c r="F38" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G38" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q38" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M38" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N38" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O38" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P38" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q38" s="6" t="s">
+      <c r="R38" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="R38" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S38" s="9">
-        <v>310</v>
+        <v>620</v>
       </c>
     </row>
     <row r="39">
@@ -2552,29 +2513,29 @@
       <c r="D39" s="7">
         <v>46181</v>
       </c>
-      <c r="E39" s="7" t="s">
-        <v>23</v>
+      <c r="E39" s="7">
+        <v>46169</v>
       </c>
       <c r="F39" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G39" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>23</v>
@@ -2589,13 +2550,13 @@
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S39" s="9">
-        <v>340</v>
+        <v>630</v>
       </c>
     </row>
     <row r="40">
@@ -2612,28 +2573,28 @@
         <v>46181</v>
       </c>
       <c r="E40" s="7">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="F40" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G40" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>23</v>
@@ -2648,13 +2609,13 @@
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R40" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="R40" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S40" s="9">
-        <v>346.5</v>
+        <v>630</v>
       </c>
     </row>
     <row r="41">
@@ -2665,25 +2626,25 @@
         <v>46181</v>
       </c>
       <c r="C41" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D41" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>23</v>
+        <v>46181</v>
+      </c>
+      <c r="E41" s="7">
+        <v>46170</v>
       </c>
       <c r="F41" s="8">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="G41" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>71</v>
@@ -2692,10 +2653,10 @@
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>27</v>
@@ -2707,13 +2668,13 @@
         <v>23</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S41" s="9">
-        <v>380</v>
+        <v>650</v>
       </c>
     </row>
     <row r="42">
@@ -2733,16 +2694,16 @@
         <v>23</v>
       </c>
       <c r="F42" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G42" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>72</v>
@@ -2769,10 +2730,10 @@
         <v>23</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S42" s="9">
-        <v>410</v>
+        <v>660</v>
       </c>
     </row>
     <row r="43">
@@ -2783,25 +2744,25 @@
         <v>46181</v>
       </c>
       <c r="C43" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D43" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>23</v>
+        <v>46181</v>
+      </c>
+      <c r="E43" s="7">
+        <v>46141</v>
       </c>
       <c r="F43" s="8">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="G43" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J43" s="6" t="s">
         <v>74</v>
@@ -2813,7 +2774,7 @@
         <v>75</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>27</v>
@@ -2825,13 +2786,13 @@
         <v>23</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S43" s="9">
-        <v>579.12</v>
+        <v>680</v>
       </c>
     </row>
     <row r="44">
@@ -2848,19 +2809,19 @@
         <v>46181</v>
       </c>
       <c r="E44" s="7">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="F44" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G44" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J44" s="6" t="s">
         <v>76</v>
@@ -2869,10 +2830,10 @@
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>27</v>
@@ -2884,13 +2845,13 @@
         <v>23</v>
       </c>
       <c r="Q44" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="R44" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S44" s="9">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="45">
@@ -2907,19 +2868,19 @@
         <v>46181</v>
       </c>
       <c r="E45" s="7">
-        <v>46141</v>
+        <v>46164</v>
       </c>
       <c r="F45" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G45" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J45" s="6" t="s">
         <v>77</v>
@@ -2928,10 +2889,10 @@
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>27</v>
@@ -2943,13 +2904,13 @@
         <v>23</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S45" s="9">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="46">
@@ -2966,19 +2927,19 @@
         <v>46181</v>
       </c>
       <c r="E46" s="7">
-        <v>46169</v>
+        <v>46182</v>
       </c>
       <c r="F46" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G46" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>78</v>
@@ -3002,13 +2963,13 @@
         <v>23</v>
       </c>
       <c r="Q46" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R46" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="R46" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S46" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="47">
@@ -3025,19 +2986,19 @@
         <v>46181</v>
       </c>
       <c r="E47" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F47" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G47" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J47" s="6" t="s">
         <v>80</v>
@@ -3046,7 +3007,7 @@
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>23</v>
@@ -3061,13 +3022,13 @@
         <v>23</v>
       </c>
       <c r="Q47" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R47" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="R47" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S47" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="48">
@@ -3087,16 +3048,16 @@
         <v>46170</v>
       </c>
       <c r="F48" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G48" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>81</v>
@@ -3105,10 +3066,10 @@
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="N48" s="6" t="s">
         <v>27</v>
@@ -3117,16 +3078,16 @@
         <v>27</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="Q48" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R48" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="R48" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S48" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="49">
@@ -3137,34 +3098,34 @@
         <v>46181</v>
       </c>
       <c r="C49" s="7">
-        <v>46181</v>
+        <v>46143</v>
       </c>
       <c r="D49" s="7">
         <v>46181</v>
       </c>
       <c r="E49" s="7">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="F49" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G49" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>23</v>
@@ -3179,13 +3140,13 @@
         <v>23</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S49" s="9">
-        <v>680</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="50">
@@ -3193,7 +3154,7 @@
         <v>22</v>
       </c>
       <c r="B50" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C50" s="7">
         <v>46181</v>
@@ -3201,20 +3162,20 @@
       <c r="D50" s="7">
         <v>46181</v>
       </c>
-      <c r="E50" s="7">
-        <v>46182</v>
+      <c r="E50" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F50" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G50" s="8">
         <v>-2</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J50" s="6" t="s">
         <v>84</v>
@@ -3223,7 +3184,7 @@
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>23</v>
@@ -3238,13 +3199,13 @@
         <v>23</v>
       </c>
       <c r="Q50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R50" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="R50" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="S50" s="9">
-        <v>680</v>
+        <v>129.49</v>
       </c>
     </row>
     <row r="51">
@@ -3252,7 +3213,7 @@
         <v>22</v>
       </c>
       <c r="B51" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C51" s="7">
         <v>46181</v>
@@ -3260,29 +3221,29 @@
       <c r="D51" s="7">
         <v>46181</v>
       </c>
-      <c r="E51" s="7">
-        <v>46164</v>
+      <c r="E51" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F51" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G51" s="8">
         <v>-2</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>23</v>
@@ -3297,13 +3258,13 @@
         <v>23</v>
       </c>
       <c r="Q51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R51" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="R51" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="S51" s="9">
-        <v>680</v>
+        <v>215.07</v>
       </c>
     </row>
     <row r="52">
@@ -3311,7 +3272,7 @@
         <v>22</v>
       </c>
       <c r="B52" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C52" s="7">
         <v>46181</v>
@@ -3319,32 +3280,32 @@
       <c r="D52" s="7">
         <v>46181</v>
       </c>
-      <c r="E52" s="7">
-        <v>46167</v>
+      <c r="E52" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F52" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G52" s="8">
         <v>-2</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="N52" s="6" t="s">
         <v>27</v>
@@ -3356,13 +3317,13 @@
         <v>23</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S52" s="9">
-        <v>680</v>
+        <v>237.36</v>
       </c>
     </row>
     <row r="53">
@@ -3370,7 +3331,7 @@
         <v>22</v>
       </c>
       <c r="B53" s="7">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="C53" s="7">
         <v>46181</v>
@@ -3378,29 +3339,29 @@
       <c r="D53" s="7">
         <v>46181</v>
       </c>
-      <c r="E53" s="7">
-        <v>46141</v>
+      <c r="E53" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F53" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G53" s="8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
@@ -3415,449 +3376,36 @@
         <v>23</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="S53" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B54" s="7">
-        <v>46181</v>
-      </c>
-      <c r="C54" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D54" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E54" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F54" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G54" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I54" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J54" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="K54" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L54" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="M54" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N54" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O54" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P54" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q54" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R54" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="S54" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="B55" s="7">
-        <v>46181</v>
-      </c>
-      <c r="C55" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D55" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E55" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F55" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G55" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H55" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I55" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J55" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="K55" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L55" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="M55" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N55" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O55" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P55" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q55" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="R55" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="S55" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B56" s="7">
-        <v>46181</v>
-      </c>
-      <c r="C56" s="7">
-        <v>46143</v>
-      </c>
-      <c r="D56" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E56" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F56" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G56" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J56" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M56" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N56" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O56" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P56" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q56" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="R56" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S56" s="9">
-        <v>2969.17</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B57" s="7">
-        <v>46182</v>
-      </c>
-      <c r="C57" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D57" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F57" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G57" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I57" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J57" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="K57" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L57" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="M57" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N57" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O57" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P57" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q57" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R57" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="S57" s="9">
-        <v>129.49</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B58" s="7">
-        <v>46182</v>
-      </c>
-      <c r="C58" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D58" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F58" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G58" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I58" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J58" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="M58" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N58" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O58" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q58" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R58" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="S58" s="9">
-        <v>215.07</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B59" s="7">
-        <v>46182</v>
-      </c>
-      <c r="C59" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D59" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F59" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G59" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I59" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J59" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="K59" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L59" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="M59" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="N59" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O59" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P59" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q59" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R59" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S59" s="9">
-        <v>237.36</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B60" s="7">
-        <v>46183</v>
-      </c>
-      <c r="C60" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D60" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F60" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G60" s="8">
-        <v>0</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J60" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L60" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="M60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N60" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O60" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q60" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R60" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="S60" s="9">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="61" ht="23" customHeight="1">
-      <c r="A61" s="10"/>
-      <c r="B61" s="11"/>
-      <c r="C61" s="11"/>
-      <c r="D61" s="11"/>
-      <c r="E61" s="11"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="10"/>
-      <c r="M61" s="10"/>
-      <c r="N61" s="10"/>
-      <c r="O61" s="10"/>
-      <c r="P61" s="10"/>
-      <c r="Q61" s="10"/>
-      <c r="R61" s="10"/>
-      <c r="S61" s="13">
-        <f>SUM(S6:S60)</f>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="54" ht="23" customHeight="1">
+      <c r="A54" s="10"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="10"/>
+      <c r="R54" s="10"/>
+      <c r="S54" s="13">
+        <f>SUM(S6:S53)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$48</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quinta-feira, 11 de junho de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em sexta-feira, 12 de junho de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -163,154 +163,133 @@
     <t>FA-11565</t>
   </si>
   <si>
-    <t>FA-11566</t>
+    <t>FA-11711</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>FA-11772</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>ND-11699</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>FA-11709</t>
+  </si>
+  <si>
+    <t>ND-11700</t>
+  </si>
+  <si>
+    <t>FA-11568</t>
+  </si>
+  <si>
+    <t>FA-11677</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11774</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11784</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11796</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11720</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11775</t>
+  </si>
+  <si>
+    <t>FA-11692</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11678</t>
+  </si>
+  <si>
+    <t>FA-11815</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11814</t>
+  </si>
+  <si>
+    <t>FA-11570</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11693</t>
+  </si>
+  <si>
+    <t>FA-11782</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>ND-11801</t>
+  </si>
+  <si>
+    <t>FA-11813</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11755</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11805</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11569</t>
   </si>
   <si>
     <t>DIEGO TAYAO DANTAS</t>
   </si>
   <si>
+    <t>HOJE</t>
+  </si>
+  <si>
     <t>FA-11794</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11711</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>FA-11772</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>ND-11699</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>ND-11700</t>
-  </si>
-  <si>
-    <t>FA-11709</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LOCACAO DE ATIVOS</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA EMPREENDIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>FA-11670</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11568</t>
-  </si>
-  <si>
-    <t>FA-11677</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11774</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11784</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11569</t>
-  </si>
-  <si>
-    <t>FA-11720</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11796</t>
-  </si>
-  <si>
-    <t>FA-11775</t>
-  </si>
-  <si>
-    <t>FA-11692</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11570</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11693</t>
-  </si>
-  <si>
-    <t>FA-11678</t>
-  </si>
-  <si>
-    <t>FA-11815</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11814</t>
-  </si>
-  <si>
-    <t>FA-11782</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>ND-11801</t>
-  </si>
-  <si>
-    <t>FA-11813</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11755</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11805</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11593</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
   </si>
 </sst>
 </file>
@@ -453,7 +432,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:S48"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -570,10 +549,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-59</v>
+        <v>-60</v>
       </c>
       <c r="G6" s="8">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -629,10 +608,10 @@
         <v>46097</v>
       </c>
       <c r="F7" s="8">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="G7" s="8">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>24</v>
@@ -688,10 +667,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="G8" s="8">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -747,10 +726,10 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-73</v>
+        <v>-74</v>
       </c>
       <c r="G9" s="8">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>24</v>
@@ -806,10 +785,10 @@
         <v>23</v>
       </c>
       <c r="F10" s="8">
-        <v>-59</v>
+        <v>-60</v>
       </c>
       <c r="G10" s="8">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>24</v>
@@ -865,10 +844,10 @@
         <v>46097</v>
       </c>
       <c r="F11" s="8">
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="G11" s="8">
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>24</v>
@@ -924,10 +903,10 @@
         <v>46097</v>
       </c>
       <c r="F12" s="8">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="G12" s="8">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>24</v>
@@ -983,10 +962,10 @@
         <v>46141</v>
       </c>
       <c r="F13" s="8">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="G13" s="8">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>24</v>
@@ -1042,10 +1021,10 @@
         <v>46097</v>
       </c>
       <c r="F14" s="8">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="G14" s="8">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>37</v>
@@ -1101,10 +1080,10 @@
         <v>46141</v>
       </c>
       <c r="F15" s="8">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="G15" s="8">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>37</v>
@@ -1160,10 +1139,10 @@
         <v>23</v>
       </c>
       <c r="F16" s="8">
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="G16" s="8">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>24</v>
@@ -1219,10 +1198,10 @@
         <v>46097</v>
       </c>
       <c r="F17" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G17" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>37</v>
@@ -1278,10 +1257,10 @@
         <v>46141</v>
       </c>
       <c r="F18" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G18" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>37</v>
@@ -1337,10 +1316,10 @@
         <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="G19" s="8">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>37</v>
@@ -1396,10 +1375,10 @@
         <v>46097</v>
       </c>
       <c r="F20" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G20" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>37</v>
@@ -1455,10 +1434,10 @@
         <v>46141</v>
       </c>
       <c r="F21" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G21" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>37</v>
@@ -1511,13 +1490,13 @@
         <v>46174</v>
       </c>
       <c r="E22" s="7">
-        <v>46141</v>
+        <v>46168</v>
       </c>
       <c r="F22" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G22" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>37</v>
@@ -1535,7 +1514,7 @@
         <v>44</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="N22" s="6" t="s">
         <v>27</v>
@@ -1550,10 +1529,10 @@
         <v>35</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S22" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="23">
@@ -1573,10 +1552,10 @@
         <v>46170</v>
       </c>
       <c r="F23" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G23" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>37</v>
@@ -1612,7 +1591,7 @@
         <v>36</v>
       </c>
       <c r="S23" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="24">
@@ -1620,22 +1599,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C24" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D24" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E24" s="7">
-        <v>46168</v>
+        <v>46153</v>
       </c>
       <c r="F24" s="8">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="G24" s="8">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>37</v>
@@ -1662,16 +1641,16 @@
         <v>27</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S24" s="9">
-        <v>650</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -1679,22 +1658,22 @@
         <v>22</v>
       </c>
       <c r="B25" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C25" s="7">
-        <v>46174</v>
+        <v>46167</v>
       </c>
       <c r="D25" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E25" s="7">
-        <v>46170</v>
+        <v>46167</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F25" s="8">
-        <v>-10</v>
+        <v>-18</v>
       </c>
       <c r="G25" s="8">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>37</v>
@@ -1703,13 +1682,13 @@
         <v>37</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>23</v>
@@ -1724,13 +1703,13 @@
         <v>23</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S25" s="9">
-        <v>680</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
@@ -1747,13 +1726,13 @@
         <v>46181</v>
       </c>
       <c r="E26" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="F26" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G26" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>37</v>
@@ -1768,7 +1747,7 @@
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>23</v>
@@ -1780,7 +1759,7 @@
         <v>27</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="Q26" s="6" t="s">
         <v>29</v>
@@ -1789,7 +1768,7 @@
         <v>36</v>
       </c>
       <c r="S26" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -1800,19 +1779,19 @@
         <v>46181</v>
       </c>
       <c r="C27" s="7">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="D27" s="7">
         <v>46181</v>
       </c>
       <c r="E27" s="7">
-        <v>46167</v>
+        <v>46097</v>
       </c>
       <c r="F27" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G27" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>37</v>
@@ -1821,13 +1800,13 @@
         <v>37</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -1845,10 +1824,10 @@
         <v>29</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S27" s="9">
-        <v>100</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="28">
@@ -1859,19 +1838,19 @@
         <v>46181</v>
       </c>
       <c r="C28" s="7">
-        <v>46167</v>
+        <v>46181</v>
       </c>
       <c r="D28" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>23</v>
+        <v>46181</v>
+      </c>
+      <c r="E28" s="7">
+        <v>46141</v>
       </c>
       <c r="F28" s="8">
-        <v>-17</v>
+        <v>-4</v>
       </c>
       <c r="G28" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>37</v>
@@ -1880,13 +1859,13 @@
         <v>37</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>23</v>
@@ -1901,13 +1880,13 @@
         <v>23</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S28" s="9">
-        <v>100</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29">
@@ -1918,19 +1897,19 @@
         <v>46181</v>
       </c>
       <c r="C29" s="7">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="D29" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E29" s="7">
-        <v>46097</v>
+        <v>46174</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F29" s="8">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="G29" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>37</v>
@@ -1939,13 +1918,13 @@
         <v>37</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>23</v>
@@ -1960,13 +1939,13 @@
         <v>23</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="S29" s="9">
-        <v>146.55</v>
+        <v>410</v>
       </c>
     </row>
     <row r="30">
@@ -1977,19 +1956,19 @@
         <v>46181</v>
       </c>
       <c r="C30" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="D30" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F30" s="8">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="G30" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>37</v>
@@ -1998,7 +1977,7 @@
         <v>37</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>23</v>
@@ -2007,7 +1986,7 @@
         <v>56</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -2022,10 +2001,10 @@
         <v>23</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="S30" s="9">
-        <v>180</v>
+        <v>579.12</v>
       </c>
     </row>
     <row r="31">
@@ -2041,14 +2020,14 @@
       <c r="D31" s="7">
         <v>46181</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>23</v>
+      <c r="E31" s="7">
+        <v>46170</v>
       </c>
       <c r="F31" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G31" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>37</v>
@@ -2057,16 +2036,16 @@
         <v>37</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>27</v>
@@ -2078,13 +2057,13 @@
         <v>23</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="S31" s="9">
-        <v>180</v>
+        <v>600</v>
       </c>
     </row>
     <row r="32">
@@ -2100,14 +2079,14 @@
       <c r="D32" s="7">
         <v>46181</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>23</v>
+      <c r="E32" s="7">
+        <v>46170</v>
       </c>
       <c r="F32" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G32" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>37</v>
@@ -2116,16 +2095,16 @@
         <v>37</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>27</v>
@@ -2137,13 +2116,13 @@
         <v>23</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="S32" s="9">
-        <v>180</v>
+        <v>630</v>
       </c>
     </row>
     <row r="33">
@@ -2159,14 +2138,14 @@
       <c r="D33" s="7">
         <v>46181</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>23</v>
+      <c r="E33" s="7">
+        <v>46169</v>
       </c>
       <c r="F33" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G33" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>37</v>
@@ -2175,13 +2154,13 @@
         <v>37</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>23</v>
@@ -2196,13 +2175,13 @@
         <v>23</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S33" s="9">
-        <v>230</v>
+        <v>630</v>
       </c>
     </row>
     <row r="34">
@@ -2219,13 +2198,13 @@
         <v>46181</v>
       </c>
       <c r="E34" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="F34" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G34" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>37</v>
@@ -2234,16 +2213,16 @@
         <v>37</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>27</v>
@@ -2261,7 +2240,7 @@
         <v>36</v>
       </c>
       <c r="S34" s="9">
-        <v>310</v>
+        <v>650</v>
       </c>
     </row>
     <row r="35">
@@ -2281,10 +2260,10 @@
         <v>23</v>
       </c>
       <c r="F35" s="8">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="G35" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>37</v>
@@ -2293,13 +2272,13 @@
         <v>37</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2317,10 +2296,10 @@
         <v>23</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S35" s="9">
-        <v>410</v>
+        <v>660</v>
       </c>
     </row>
     <row r="36">
@@ -2331,19 +2310,19 @@
         <v>46181</v>
       </c>
       <c r="C36" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D36" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>23</v>
+        <v>46181</v>
+      </c>
+      <c r="E36" s="7">
+        <v>46164</v>
       </c>
       <c r="F36" s="8">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="G36" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>37</v>
@@ -2352,16 +2331,16 @@
         <v>37</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>27</v>
@@ -2373,13 +2352,13 @@
         <v>23</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S36" s="9">
-        <v>579.12</v>
+        <v>680</v>
       </c>
     </row>
     <row r="37">
@@ -2396,13 +2375,13 @@
         <v>46181</v>
       </c>
       <c r="E37" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F37" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G37" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>37</v>
@@ -2411,16 +2390,16 @@
         <v>37</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>27</v>
@@ -2438,7 +2417,7 @@
         <v>36</v>
       </c>
       <c r="S37" s="9">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="38">
@@ -2455,13 +2434,13 @@
         <v>46181</v>
       </c>
       <c r="E38" s="7">
-        <v>46141</v>
+        <v>46182</v>
       </c>
       <c r="F38" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G38" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>37</v>
@@ -2470,16 +2449,16 @@
         <v>37</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>27</v>
@@ -2497,7 +2476,7 @@
         <v>36</v>
       </c>
       <c r="S38" s="9">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="39">
@@ -2514,13 +2493,13 @@
         <v>46181</v>
       </c>
       <c r="E39" s="7">
-        <v>46169</v>
+        <v>46141</v>
       </c>
       <c r="F39" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G39" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>37</v>
@@ -2529,13 +2508,13 @@
         <v>37</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>23</v>
@@ -2553,10 +2532,10 @@
         <v>35</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S39" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="40">
@@ -2573,13 +2552,13 @@
         <v>46181</v>
       </c>
       <c r="E40" s="7">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="F40" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G40" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>37</v>
@@ -2588,13 +2567,13 @@
         <v>37</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>23</v>
@@ -2615,7 +2594,7 @@
         <v>36</v>
       </c>
       <c r="S40" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="41">
@@ -2635,10 +2614,10 @@
         <v>46170</v>
       </c>
       <c r="F41" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G41" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>37</v>
@@ -2647,16 +2626,16 @@
         <v>37</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>27</v>
@@ -2665,7 +2644,7 @@
         <v>27</v>
       </c>
       <c r="P41" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="Q41" s="6" t="s">
         <v>35</v>
@@ -2674,7 +2653,7 @@
         <v>36</v>
       </c>
       <c r="S41" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="42">
@@ -2685,19 +2664,19 @@
         <v>46181</v>
       </c>
       <c r="C42" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D42" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>23</v>
+        <v>46181</v>
+      </c>
+      <c r="E42" s="7">
+        <v>46170</v>
       </c>
       <c r="F42" s="8">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="G42" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>37</v>
@@ -2706,13 +2685,13 @@
         <v>37</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -2727,13 +2706,13 @@
         <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S42" s="9">
-        <v>660</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="43">
@@ -2741,7 +2720,7 @@
         <v>22</v>
       </c>
       <c r="B43" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C43" s="7">
         <v>46181</v>
@@ -2749,11 +2728,11 @@
       <c r="D43" s="7">
         <v>46181</v>
       </c>
-      <c r="E43" s="7">
-        <v>46141</v>
+      <c r="E43" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F43" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G43" s="8">
         <v>-3</v>
@@ -2765,13 +2744,13 @@
         <v>37</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>23</v>
@@ -2786,13 +2765,13 @@
         <v>23</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S43" s="9">
-        <v>680</v>
+        <v>129.49</v>
       </c>
     </row>
     <row r="44">
@@ -2800,7 +2779,7 @@
         <v>22</v>
       </c>
       <c r="B44" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C44" s="7">
         <v>46181</v>
@@ -2808,11 +2787,11 @@
       <c r="D44" s="7">
         <v>46181</v>
       </c>
-      <c r="E44" s="7">
-        <v>46167</v>
+      <c r="E44" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F44" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G44" s="8">
         <v>-3</v>
@@ -2824,13 +2803,13 @@
         <v>37</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>23</v>
@@ -2845,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S44" s="9">
-        <v>680</v>
+        <v>215.07</v>
       </c>
     </row>
     <row r="45">
@@ -2859,7 +2838,7 @@
         <v>22</v>
       </c>
       <c r="B45" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C45" s="7">
         <v>46181</v>
@@ -2867,11 +2846,11 @@
       <c r="D45" s="7">
         <v>46181</v>
       </c>
-      <c r="E45" s="7">
-        <v>46164</v>
+      <c r="E45" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F45" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G45" s="8">
         <v>-3</v>
@@ -2883,16 +2862,16 @@
         <v>37</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>27</v>
@@ -2904,13 +2883,13 @@
         <v>23</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="S45" s="9">
-        <v>680</v>
+        <v>237.36</v>
       </c>
     </row>
     <row r="46">
@@ -2918,7 +2897,7 @@
         <v>22</v>
       </c>
       <c r="B46" s="7">
-        <v>46181</v>
+        <v>46185</v>
       </c>
       <c r="C46" s="7">
         <v>46181</v>
@@ -2926,50 +2905,50 @@
       <c r="D46" s="7">
         <v>46181</v>
       </c>
-      <c r="E46" s="7">
-        <v>46182</v>
+      <c r="E46" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F46" s="8">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G46" s="8">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S46" s="9">
-        <v>680</v>
+        <v>220</v>
       </c>
     </row>
     <row r="47">
@@ -2977,37 +2956,37 @@
         <v>22</v>
       </c>
       <c r="B47" s="7">
-        <v>46181</v>
+        <v>46185</v>
       </c>
       <c r="C47" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="D47" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E47" s="7">
-        <v>46182</v>
+        <v>46174</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F47" s="8">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="G47" s="8">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>23</v>
@@ -3016,396 +2995,42 @@
         <v>27</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S47" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B48" s="7">
-        <v>46181</v>
-      </c>
-      <c r="C48" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D48" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E48" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F48" s="8">
-        <v>-3</v>
-      </c>
-      <c r="G48" s="8">
-        <v>-3</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I48" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J48" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="K48" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="M48" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q48" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R48" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S48" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B49" s="7">
-        <v>46181</v>
-      </c>
-      <c r="C49" s="7">
-        <v>46143</v>
-      </c>
-      <c r="D49" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E49" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F49" s="8">
-        <v>-3</v>
-      </c>
-      <c r="G49" s="8">
-        <v>-3</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I49" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J49" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="K49" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L49" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M49" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N49" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O49" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P49" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q49" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="R49" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S49" s="9">
-        <v>2969.17</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B50" s="7">
-        <v>46182</v>
-      </c>
-      <c r="C50" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D50" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F50" s="8">
-        <v>-3</v>
-      </c>
-      <c r="G50" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I50" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J50" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="K50" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="M50" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N50" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O50" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q50" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R50" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S50" s="9">
-        <v>129.49</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B51" s="7">
-        <v>46182</v>
-      </c>
-      <c r="C51" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D51" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F51" s="8">
-        <v>-3</v>
-      </c>
-      <c r="G51" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I51" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J51" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="K51" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L51" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="M51" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N51" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O51" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P51" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q51" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R51" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S51" s="9">
-        <v>215.07</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B52" s="7">
-        <v>46182</v>
-      </c>
-      <c r="C52" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D52" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F52" s="8">
-        <v>-3</v>
-      </c>
-      <c r="G52" s="8">
-        <v>-2</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J52" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="K52" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="M52" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="N52" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O52" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q52" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R52" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S52" s="9">
-        <v>237.36</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B53" s="7">
-        <v>46183</v>
-      </c>
-      <c r="C53" s="7">
-        <v>46181</v>
-      </c>
-      <c r="D53" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F53" s="8">
-        <v>-3</v>
-      </c>
-      <c r="G53" s="8">
-        <v>-1</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I53" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J53" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="K53" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L53" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="M53" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N53" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O53" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P53" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q53" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R53" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="S53" s="9">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="54" ht="23" customHeight="1">
-      <c r="A54" s="10"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
-      <c r="N54" s="10"/>
-      <c r="O54" s="10"/>
-      <c r="P54" s="10"/>
-      <c r="Q54" s="10"/>
-      <c r="R54" s="10"/>
-      <c r="S54" s="13">
-        <f>SUM(S6:S53)</f>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="48" ht="23" customHeight="1">
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="12"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="10"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
+      <c r="S48" s="13">
+        <f>SUM(S6:S47)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$47</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -217,76 +217,70 @@
     <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
   </si>
   <si>
-    <t>FA-11720</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
     <t>FA-11775</t>
   </si>
   <si>
+    <t>FA-11678</t>
+  </si>
+  <si>
+    <t>FA-11815</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11814</t>
+  </si>
+  <si>
+    <t>FA-11570</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11693</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11782</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>ND-11801</t>
+  </si>
+  <si>
+    <t>FA-11813</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11755</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11805</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11569</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>HOJE</t>
+  </si>
+  <si>
     <t>FA-11692</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11678</t>
-  </si>
-  <si>
-    <t>FA-11815</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11814</t>
-  </si>
-  <si>
-    <t>FA-11570</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11693</t>
-  </si>
-  <si>
-    <t>FA-11782</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>ND-11801</t>
-  </si>
-  <si>
-    <t>FA-11813</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11755</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11805</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11569</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>HOJE</t>
   </si>
   <si>
     <t>FA-11794</t>
@@ -432,7 +426,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S48"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -2139,7 +2133,7 @@
         <v>46181</v>
       </c>
       <c r="E33" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F33" s="8">
         <v>-4</v>
@@ -2160,10 +2154,10 @@
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>27</v>
@@ -2181,7 +2175,7 @@
         <v>36</v>
       </c>
       <c r="S33" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="34">
@@ -2198,7 +2192,7 @@
         <v>46181</v>
       </c>
       <c r="E34" s="7">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="F34" s="8">
         <v>-4</v>
@@ -2213,16 +2207,16 @@
         <v>37</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>27</v>
@@ -2237,10 +2231,10 @@
         <v>35</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S34" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="35">
@@ -2251,16 +2245,16 @@
         <v>46181</v>
       </c>
       <c r="C35" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D35" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>23</v>
+        <v>46181</v>
+      </c>
+      <c r="E35" s="7">
+        <v>46182</v>
       </c>
       <c r="F35" s="8">
-        <v>-11</v>
+        <v>-4</v>
       </c>
       <c r="G35" s="8">
         <v>-4</v>
@@ -2272,14 +2266,14 @@
         <v>37</v>
       </c>
       <c r="J35" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="K35" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>65</v>
-      </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
       </c>
@@ -2293,13 +2287,13 @@
         <v>23</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S35" s="9">
-        <v>660</v>
+        <v>680</v>
       </c>
     </row>
     <row r="36">
@@ -2316,7 +2310,7 @@
         <v>46181</v>
       </c>
       <c r="E36" s="7">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="F36" s="8">
         <v>-4</v>
@@ -2331,13 +2325,13 @@
         <v>37</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>23</v>
@@ -2355,7 +2349,7 @@
         <v>35</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S36" s="9">
         <v>680</v>
@@ -2375,7 +2369,7 @@
         <v>46181</v>
       </c>
       <c r="E37" s="7">
-        <v>46182</v>
+        <v>46141</v>
       </c>
       <c r="F37" s="8">
         <v>-4</v>
@@ -2390,13 +2384,13 @@
         <v>37</v>
       </c>
       <c r="J37" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="K37" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>68</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>23</v>
@@ -2414,7 +2408,7 @@
         <v>35</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S37" s="9">
         <v>680</v>
@@ -2434,7 +2428,7 @@
         <v>46181</v>
       </c>
       <c r="E38" s="7">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="F38" s="8">
         <v>-4</v>
@@ -2449,13 +2443,13 @@
         <v>37</v>
       </c>
       <c r="J38" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="K38" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L38" s="6" t="s">
-        <v>46</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>23</v>
@@ -2493,7 +2487,7 @@
         <v>46181</v>
       </c>
       <c r="E39" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="F39" s="8">
         <v>-4</v>
@@ -2526,16 +2520,16 @@
         <v>27</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="Q39" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S39" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="40">
@@ -2546,13 +2540,13 @@
         <v>46181</v>
       </c>
       <c r="C40" s="7">
-        <v>46181</v>
+        <v>46143</v>
       </c>
       <c r="D40" s="7">
         <v>46181</v>
       </c>
       <c r="E40" s="7">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="F40" s="8">
         <v>-4</v>
@@ -2573,7 +2567,7 @@
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>23</v>
@@ -2588,13 +2582,13 @@
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S40" s="9">
-        <v>680</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="41">
@@ -2602,7 +2596,7 @@
         <v>22</v>
       </c>
       <c r="B41" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C41" s="7">
         <v>46181</v>
@@ -2610,14 +2604,14 @@
       <c r="D41" s="7">
         <v>46181</v>
       </c>
-      <c r="E41" s="7">
-        <v>46170</v>
+      <c r="E41" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F41" s="8">
         <v>-4</v>
       </c>
       <c r="G41" s="8">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>37</v>
@@ -2644,16 +2638,16 @@
         <v>27</v>
       </c>
       <c r="P41" s="6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S41" s="9">
-        <v>700</v>
+        <v>129.49</v>
       </c>
     </row>
     <row r="42">
@@ -2661,22 +2655,22 @@
         <v>22</v>
       </c>
       <c r="B42" s="7">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="C42" s="7">
-        <v>46143</v>
+        <v>46181</v>
       </c>
       <c r="D42" s="7">
         <v>46181</v>
       </c>
-      <c r="E42" s="7">
-        <v>46170</v>
+      <c r="E42" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F42" s="8">
         <v>-4</v>
       </c>
       <c r="G42" s="8">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>37</v>
@@ -2691,7 +2685,7 @@
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -2706,13 +2700,13 @@
         <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S42" s="9">
-        <v>2969.17</v>
+        <v>215.07</v>
       </c>
     </row>
     <row r="43">
@@ -2744,16 +2738,16 @@
         <v>37</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>27</v>
@@ -2768,10 +2762,10 @@
         <v>23</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S43" s="9">
-        <v>129.49</v>
+        <v>237.36</v>
       </c>
     </row>
     <row r="44">
@@ -2779,7 +2773,7 @@
         <v>22</v>
       </c>
       <c r="B44" s="7">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="C44" s="7">
         <v>46181</v>
@@ -2794,31 +2788,31 @@
         <v>-4</v>
       </c>
       <c r="G44" s="8">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>23</v>
@@ -2830,7 +2824,7 @@
         <v>36</v>
       </c>
       <c r="S44" s="9">
-        <v>215.07</v>
+        <v>220</v>
       </c>
     </row>
     <row r="45">
@@ -2838,47 +2832,47 @@
         <v>22</v>
       </c>
       <c r="B45" s="7">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="C45" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="D45" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F45" s="8">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="G45" s="8">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N45" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O45" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="M45" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="N45" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O45" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="P45" s="6" t="s">
         <v>23</v>
       </c>
@@ -2886,10 +2880,10 @@
         <v>23</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S45" s="9">
-        <v>237.36</v>
+        <v>360</v>
       </c>
     </row>
     <row r="46">
@@ -2900,16 +2894,16 @@
         <v>46185</v>
       </c>
       <c r="C46" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="D46" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F46" s="8">
-        <v>-4</v>
+        <v>-11</v>
       </c>
       <c r="G46" s="8">
         <v>0</v>
@@ -2921,22 +2915,22 @@
         <v>23</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>83</v>
+        <v>23</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>23</v>
@@ -2948,89 +2942,30 @@
         <v>36</v>
       </c>
       <c r="S46" s="9">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B47" s="7">
-        <v>46185</v>
-      </c>
-      <c r="C47" s="7">
-        <v>46174</v>
-      </c>
-      <c r="D47" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F47" s="8">
-        <v>-11</v>
-      </c>
-      <c r="G47" s="8">
-        <v>0</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I47" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J47" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K47" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L47" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="M47" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N47" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O47" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="P47" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q47" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R47" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S47" s="9">
         <v>480</v>
       </c>
     </row>
-    <row r="48" ht="23" customHeight="1">
-      <c r="A48" s="10"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
-      <c r="N48" s="10"/>
-      <c r="O48" s="10"/>
-      <c r="P48" s="10"/>
-      <c r="Q48" s="10"/>
-      <c r="R48" s="10"/>
-      <c r="S48" s="13">
-        <f>SUM(S6:S47)</f>
+    <row r="47" ht="23" customHeight="1">
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="13">
+        <f>SUM(S6:S46)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$144</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$133</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em segunda-feira, 15 de junho de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em terça-feira, 16 de junho de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -169,259 +169,352 @@
     <t>ANDRE CAVALCANTI DA FE</t>
   </si>
   <si>
+    <t>ND-11700</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11568</t>
+  </si>
+  <si>
+    <t>FA-11796</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11847</t>
+  </si>
+  <si>
+    <t>FA-11775</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11815</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11814</t>
+  </si>
+  <si>
+    <t>FA-11693</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11782</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>ND-11801</t>
+  </si>
+  <si>
+    <t>FA-11569</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11692</t>
+  </si>
+  <si>
+    <t>FA-11810</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>ND-11699</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11806</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>JOAO PAULO CONSORCIOS</t>
+  </si>
+  <si>
+    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
+  </si>
+  <si>
+    <t>FA-11794</t>
+  </si>
+  <si>
+    <t>FA-11784</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11846</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-11774</t>
+  </si>
+  <si>
+    <t>FA-11678</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11797</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
     <t>FA-11772</t>
   </si>
   <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>ND-11700</t>
-  </si>
-  <si>
-    <t>FA-11568</t>
-  </si>
-  <si>
-    <t>FA-11796</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11775</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11847</t>
-  </si>
-  <si>
-    <t>FA-11815</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11814</t>
-  </si>
-  <si>
-    <t>FA-11693</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11782</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>ND-11801</t>
-  </si>
-  <si>
-    <t>FA-11755</t>
+    <t>FA-11787</t>
+  </si>
+  <si>
+    <t>FA-11571</t>
+  </si>
+  <si>
+    <t>FA-11572</t>
+  </si>
+  <si>
+    <t>FA-11724</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11671</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11798</t>
+  </si>
+  <si>
+    <t>FA-11686</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
+    <t>FA-11624</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11848</t>
+  </si>
+  <si>
+    <t>FA-11776</t>
+  </si>
+  <si>
+    <t>FA-11679</t>
+  </si>
+  <si>
+    <t>FA-11819</t>
+  </si>
+  <si>
+    <t>FA-11818</t>
+  </si>
+  <si>
+    <t>FA-11573</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11694</t>
+  </si>
+  <si>
+    <t>FA-11764</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11849</t>
+  </si>
+  <si>
+    <t>FA-11785</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>FA-11820</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>ND-11844</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>ND-11845</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11756</t>
   </si>
   <si>
     <t>MARIO EWERTON CANDIDO DE SOUZA</t>
   </si>
   <si>
-    <t>FA-11805</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11569</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11692</t>
-  </si>
-  <si>
-    <t>ND-11699</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>HOJE</t>
-  </si>
-  <si>
-    <t>JOAO PAULO CONSORCIOS</t>
-  </si>
-  <si>
-    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
-  </si>
-  <si>
-    <t>FA-11794</t>
-  </si>
-  <si>
-    <t>FA-11784</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11817</t>
+    <t>FA-11842</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-11730</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11791</t>
+  </si>
+  <si>
+    <t>FA-11749</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11807</t>
+  </si>
+  <si>
+    <t>FA-11733</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11731</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11728</t>
+  </si>
+  <si>
+    <t>FA-11672</t>
+  </si>
+  <si>
+    <t>FA-11790</t>
+  </si>
+  <si>
+    <t>FA-11800</t>
+  </si>
+  <si>
+    <t>FA-11687</t>
+  </si>
+  <si>
+    <t>FA-11799</t>
+  </si>
+  <si>
+    <t>FA-11625</t>
+  </si>
+  <si>
+    <t>FA-11508</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11660</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>FA-11850</t>
+  </si>
+  <si>
+    <t>FA-11438</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11695</t>
+  </si>
+  <si>
+    <t>FA-11811</t>
+  </si>
+  <si>
+    <t>FA-11821</t>
   </si>
   <si>
     <t>ANDERSON QUEIROZ PINHEIRO</t>
   </si>
   <si>
-    <t>FA-11846</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-11678</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11774</t>
-  </si>
-  <si>
-    <t>FA-11726</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11787</t>
-  </si>
-  <si>
-    <t>FA-11571</t>
-  </si>
-  <si>
-    <t>FA-11806</t>
-  </si>
-  <si>
-    <t>FA-11572</t>
-  </si>
-  <si>
-    <t>FA-11727</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11724</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11729</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11671</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11798</t>
-  </si>
-  <si>
-    <t>FA-11756</t>
-  </si>
-  <si>
-    <t>FA-11686</t>
-  </si>
-  <si>
-    <t>GILVAN RODRIGUES MACHADO</t>
-  </si>
-  <si>
-    <t>FA-11797</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11507</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11624</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>FA-11848</t>
-  </si>
-  <si>
-    <t>FA-11776</t>
-  </si>
-  <si>
-    <t>FA-11679</t>
-  </si>
-  <si>
-    <t>FA-11818</t>
-  </si>
-  <si>
-    <t>FA-11573</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11694</t>
-  </si>
-  <si>
-    <t>FA-11810</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11819</t>
-  </si>
-  <si>
-    <t>FA-11764</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11849</t>
-  </si>
-  <si>
-    <t>FA-11785</t>
-  </si>
-  <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>FA-11820</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11604</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>FA-11635</t>
+    <t>FA-11680</t>
+  </si>
+  <si>
+    <t>FA-11822</t>
+  </si>
+  <si>
+    <t>FA-11823</t>
+  </si>
+  <si>
+    <t>FA-11789</t>
+  </si>
+  <si>
+    <t>FA-11851</t>
+  </si>
+  <si>
+    <t>FA-11765</t>
+  </si>
+  <si>
+    <t>FA-11824</t>
+  </si>
+  <si>
+    <t>FA-11605</t>
+  </si>
+  <si>
+    <t>FA-11595</t>
+  </si>
+  <si>
+    <t>FA-11636</t>
   </si>
   <si>
     <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
@@ -430,138 +523,12 @@
     <t>PÚBLICO</t>
   </si>
   <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11594</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>FA-11647</t>
+    <t>FA-11648</t>
   </si>
   <si>
     <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
   </si>
   <si>
-    <t>ND-11844</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>ND-11845</t>
-  </si>
-  <si>
-    <t>FA-11842</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
-    <t>FA-11730</t>
-  </si>
-  <si>
-    <t>FA-11749</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11791</t>
-  </si>
-  <si>
-    <t>FA-11807</t>
-  </si>
-  <si>
-    <t>FA-11672</t>
-  </si>
-  <si>
-    <t>FA-11800</t>
-  </si>
-  <si>
-    <t>FA-11790</t>
-  </si>
-  <si>
-    <t>FA-11733</t>
-  </si>
-  <si>
-    <t>FA-11731</t>
-  </si>
-  <si>
-    <t>FA-11728</t>
-  </si>
-  <si>
-    <t>FA-11687</t>
-  </si>
-  <si>
-    <t>FA-11625</t>
-  </si>
-  <si>
-    <t>FA-11799</t>
-  </si>
-  <si>
-    <t>FA-11508</t>
-  </si>
-  <si>
-    <t>FA-11660</t>
-  </si>
-  <si>
-    <t>LUCA ZOLI</t>
-  </si>
-  <si>
-    <t>FA-11850</t>
-  </si>
-  <si>
-    <t>FA-11438</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11821</t>
-  </si>
-  <si>
-    <t>FA-11811</t>
-  </si>
-  <si>
-    <t>FA-11823</t>
-  </si>
-  <si>
-    <t>FA-11695</t>
-  </si>
-  <si>
-    <t>FA-11822</t>
-  </si>
-  <si>
-    <t>FA-11680</t>
-  </si>
-  <si>
-    <t>FA-11789</t>
-  </si>
-  <si>
-    <t>FA-11765</t>
-  </si>
-  <si>
-    <t>FA-11851</t>
-  </si>
-  <si>
-    <t>FA-11605</t>
-  </si>
-  <si>
-    <t>FA-11824</t>
-  </si>
-  <si>
-    <t>FA-11595</t>
-  </si>
-  <si>
-    <t>FA-11636</t>
-  </si>
-  <si>
-    <t>FA-11648</t>
-  </si>
-  <si>
     <t>FA-11843</t>
   </si>
   <si>
@@ -580,12 +547,12 @@
     <t>FA-11673</t>
   </si>
   <si>
+    <t>FA-11737</t>
+  </si>
+  <si>
     <t>FA-11732</t>
   </si>
   <si>
-    <t>FA-11737</t>
-  </si>
-  <si>
     <t>FA-11734</t>
   </si>
   <si>
@@ -595,12 +562,12 @@
     <t>FA-11661</t>
   </si>
   <si>
+    <t>FA-11509</t>
+  </si>
+  <si>
     <t>FA-11626</t>
   </si>
   <si>
-    <t>FA-11509</t>
-  </si>
-  <si>
     <t>FA-11852</t>
   </si>
   <si>
@@ -610,15 +577,15 @@
     <t>FA-11826</t>
   </si>
   <si>
+    <t>FA-11827</t>
+  </si>
+  <si>
+    <t>FA-11696</t>
+  </si>
+  <si>
     <t>FA-11825</t>
   </si>
   <si>
-    <t>FA-11827</t>
-  </si>
-  <si>
-    <t>FA-11696</t>
-  </si>
-  <si>
     <t>FA-11853</t>
   </si>
   <si>
@@ -631,10 +598,10 @@
     <t>FA-11606</t>
   </si>
   <si>
+    <t>FA-11596</t>
+  </si>
+  <si>
     <t>FA-11637</t>
-  </si>
-  <si>
-    <t>FA-11596</t>
   </si>
   <si>
     <t>FA-11649</t>
@@ -780,7 +747,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S144"/>
+  <dimension ref="A1:S133"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -897,10 +864,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-63</v>
+        <v>-64</v>
       </c>
       <c r="G6" s="8">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -956,10 +923,10 @@
         <v>46097</v>
       </c>
       <c r="F7" s="8">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="G7" s="8">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>24</v>
@@ -1015,10 +982,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-56</v>
+        <v>-57</v>
       </c>
       <c r="G8" s="8">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -1074,10 +1041,10 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-77</v>
+        <v>-78</v>
       </c>
       <c r="G9" s="8">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>24</v>
@@ -1133,10 +1100,10 @@
         <v>23</v>
       </c>
       <c r="F10" s="8">
-        <v>-63</v>
+        <v>-64</v>
       </c>
       <c r="G10" s="8">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>24</v>
@@ -1192,10 +1159,10 @@
         <v>46097</v>
       </c>
       <c r="F11" s="8">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="G11" s="8">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>24</v>
@@ -1251,10 +1218,10 @@
         <v>46097</v>
       </c>
       <c r="F12" s="8">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="G12" s="8">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>24</v>
@@ -1310,10 +1277,10 @@
         <v>46141</v>
       </c>
       <c r="F13" s="8">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="G13" s="8">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>24</v>
@@ -1369,10 +1336,10 @@
         <v>46097</v>
       </c>
       <c r="F14" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G14" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>37</v>
@@ -1428,10 +1395,10 @@
         <v>46141</v>
       </c>
       <c r="F15" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="G15" s="8">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>37</v>
@@ -1487,10 +1454,10 @@
         <v>23</v>
       </c>
       <c r="F16" s="8">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="G16" s="8">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>24</v>
@@ -1546,10 +1513,10 @@
         <v>46097</v>
       </c>
       <c r="F17" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="G17" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>37</v>
@@ -1605,10 +1572,10 @@
         <v>46141</v>
       </c>
       <c r="F18" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="G18" s="8">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>37</v>
@@ -1664,10 +1631,10 @@
         <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G19" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>37</v>
@@ -1723,10 +1690,10 @@
         <v>46097</v>
       </c>
       <c r="F20" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="G20" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>37</v>
@@ -1782,10 +1749,10 @@
         <v>46141</v>
       </c>
       <c r="F21" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="G21" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>37</v>
@@ -1841,10 +1808,10 @@
         <v>46168</v>
       </c>
       <c r="F22" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="G22" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>37</v>
@@ -1888,22 +1855,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C23" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D23" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E23" s="7">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="F23" s="8">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="G23" s="8">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>37</v>
@@ -1933,13 +1900,13 @@
         <v>23</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S23" s="9">
-        <v>680</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
@@ -1950,19 +1917,19 @@
         <v>46181</v>
       </c>
       <c r="C24" s="7">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="D24" s="7">
         <v>46181</v>
       </c>
       <c r="E24" s="7">
-        <v>46167</v>
+        <v>46097</v>
       </c>
       <c r="F24" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G24" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>37</v>
@@ -1971,13 +1938,13 @@
         <v>37</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>23</v>
@@ -1995,10 +1962,10 @@
         <v>29</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S24" s="9">
-        <v>100</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="25">
@@ -2009,19 +1976,19 @@
         <v>46181</v>
       </c>
       <c r="C25" s="7">
-        <v>46082</v>
+        <v>46181</v>
       </c>
       <c r="D25" s="7">
         <v>46181</v>
       </c>
       <c r="E25" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F25" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G25" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>37</v>
@@ -2030,13 +1997,13 @@
         <v>37</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>23</v>
@@ -2051,13 +2018,13 @@
         <v>23</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S25" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26">
@@ -2074,13 +2041,13 @@
         <v>46181</v>
       </c>
       <c r="E26" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="F26" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G26" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>37</v>
@@ -2095,7 +2062,7 @@
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>23</v>
@@ -2116,7 +2083,7 @@
         <v>36</v>
       </c>
       <c r="S26" s="9">
-        <v>310</v>
+        <v>630</v>
       </c>
     </row>
     <row r="27">
@@ -2133,13 +2100,13 @@
         <v>46181</v>
       </c>
       <c r="E27" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F27" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G27" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>37</v>
@@ -2148,13 +2115,13 @@
         <v>37</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -2172,10 +2139,10 @@
         <v>35</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S27" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="28">
@@ -2195,10 +2162,10 @@
         <v>46170</v>
       </c>
       <c r="F28" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G28" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>37</v>
@@ -2251,13 +2218,13 @@
         <v>46181</v>
       </c>
       <c r="E29" s="7">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="F29" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G29" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>37</v>
@@ -2272,7 +2239,7 @@
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>23</v>
@@ -2290,10 +2257,10 @@
         <v>35</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S29" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="30">
@@ -2313,10 +2280,10 @@
         <v>46182</v>
       </c>
       <c r="F30" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G30" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>37</v>
@@ -2325,13 +2292,13 @@
         <v>37</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>23</v>
@@ -2369,13 +2336,13 @@
         <v>46181</v>
       </c>
       <c r="E31" s="7">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="F31" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G31" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>37</v>
@@ -2390,7 +2357,7 @@
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>23</v>
@@ -2428,13 +2395,13 @@
         <v>46181</v>
       </c>
       <c r="E32" s="7">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="F32" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G32" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>37</v>
@@ -2443,13 +2410,13 @@
         <v>37</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>23</v>
@@ -2461,7 +2428,7 @@
         <v>27</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q32" s="6" t="s">
         <v>35</v>
@@ -2470,7 +2437,7 @@
         <v>36</v>
       </c>
       <c r="S32" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="33">
@@ -2481,7 +2448,7 @@
         <v>46181</v>
       </c>
       <c r="C33" s="7">
-        <v>46181</v>
+        <v>46143</v>
       </c>
       <c r="D33" s="7">
         <v>46181</v>
@@ -2490,10 +2457,10 @@
         <v>46170</v>
       </c>
       <c r="F33" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G33" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>37</v>
@@ -2502,13 +2469,13 @@
         <v>37</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>23</v>
@@ -2520,16 +2487,16 @@
         <v>27</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S33" s="9">
-        <v>700</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="34">
@@ -2537,22 +2504,22 @@
         <v>22</v>
       </c>
       <c r="B34" s="7">
+        <v>46185</v>
+      </c>
+      <c r="C34" s="7">
         <v>46181</v>
-      </c>
-      <c r="C34" s="7">
-        <v>46143</v>
       </c>
       <c r="D34" s="7">
         <v>46181</v>
       </c>
-      <c r="E34" s="7">
-        <v>46170</v>
+      <c r="E34" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F34" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G34" s="8">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>37</v>
@@ -2567,10 +2534,10 @@
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>27</v>
@@ -2582,13 +2549,13 @@
         <v>23</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S34" s="9">
-        <v>2969.17</v>
+        <v>220</v>
       </c>
     </row>
     <row r="35">
@@ -2596,22 +2563,22 @@
         <v>22</v>
       </c>
       <c r="B35" s="7">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="C35" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="D35" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F35" s="8">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="G35" s="8">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>37</v>
@@ -2620,13 +2587,13 @@
         <v>37</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2647,7 +2614,7 @@
         <v>36</v>
       </c>
       <c r="S35" s="9">
-        <v>215.07</v>
+        <v>360</v>
       </c>
     </row>
     <row r="36">
@@ -2655,22 +2622,22 @@
         <v>22</v>
       </c>
       <c r="B36" s="7">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="C36" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="D36" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="G36" s="8">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>37</v>
@@ -2688,7 +2655,7 @@
         <v>66</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>27</v>
@@ -2703,10 +2670,10 @@
         <v>23</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S36" s="9">
-        <v>237.36</v>
+        <v>38.45</v>
       </c>
     </row>
     <row r="37">
@@ -2714,22 +2681,22 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C37" s="7">
-        <v>46181</v>
+        <v>46143</v>
       </c>
       <c r="D37" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>23</v>
+        <v>46188</v>
+      </c>
+      <c r="E37" s="7">
+        <v>46153</v>
       </c>
       <c r="F37" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="G37" s="8">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>37</v>
@@ -2747,7 +2714,7 @@
         <v>68</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>27</v>
@@ -2756,16 +2723,16 @@
         <v>27</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S37" s="9">
-        <v>220</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
@@ -2773,22 +2740,22 @@
         <v>22</v>
       </c>
       <c r="B38" s="7">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C38" s="7">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="D38" s="7">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-14</v>
+        <v>-1</v>
       </c>
       <c r="G38" s="8">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>37</v>
@@ -2803,10 +2770,10 @@
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>27</v>
@@ -2821,10 +2788,10 @@
         <v>23</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S38" s="9">
-        <v>360</v>
+        <v>70.07</v>
       </c>
     </row>
     <row r="39">
@@ -2841,40 +2808,40 @@
         <v>46188</v>
       </c>
       <c r="E39" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="F39" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G39" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
         <v>29</v>
@@ -2883,7 +2850,7 @@
         <v>36</v>
       </c>
       <c r="S39" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40">
@@ -2894,55 +2861,55 @@
         <v>46188</v>
       </c>
       <c r="C40" s="7">
-        <v>46143</v>
+        <v>46188</v>
       </c>
       <c r="D40" s="7">
         <v>46188</v>
       </c>
-      <c r="E40" s="7">
-        <v>46167</v>
+      <c r="E40" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F40" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G40" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="S40" s="9">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="41">
@@ -2953,55 +2920,55 @@
         <v>46188</v>
       </c>
       <c r="C41" s="7">
-        <v>46188</v>
+        <v>46082</v>
       </c>
       <c r="D41" s="7">
         <v>46188</v>
       </c>
-      <c r="E41" s="7" t="s">
-        <v>23</v>
+      <c r="E41" s="7">
+        <v>46097</v>
       </c>
       <c r="F41" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G41" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="S41" s="9">
-        <v>120</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="42">
@@ -3012,55 +2979,55 @@
         <v>46188</v>
       </c>
       <c r="C42" s="7">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="D42" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E42" s="7">
-        <v>46097</v>
+        <v>46174</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F42" s="8">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="G42" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S42" s="9">
-        <v>146.55</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43">
@@ -3071,43 +3038,43 @@
         <v>46188</v>
       </c>
       <c r="C43" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D43" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F43" s="8">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="G43" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J43" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K43" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="M43" s="6" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>23</v>
@@ -3119,7 +3086,7 @@
         <v>36</v>
       </c>
       <c r="S43" s="9">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44">
@@ -3139,16 +3106,16 @@
         <v>23</v>
       </c>
       <c r="F44" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G44" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J44" s="6" t="s">
         <v>76</v>
@@ -3160,13 +3127,13 @@
         <v>77</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>23</v>
@@ -3175,10 +3142,10 @@
         <v>23</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S44" s="9">
-        <v>200</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45">
@@ -3189,25 +3156,25 @@
         <v>46188</v>
       </c>
       <c r="C45" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D45" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F45" s="8">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="G45" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J45" s="6" t="s">
         <v>78</v>
@@ -3216,16 +3183,16 @@
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>23</v>
@@ -3237,7 +3204,7 @@
         <v>36</v>
       </c>
       <c r="S45" s="9">
-        <v>213.23</v>
+        <v>279.12</v>
       </c>
     </row>
     <row r="46">
@@ -3257,26 +3224,26 @@
         <v>23</v>
       </c>
       <c r="F46" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G46" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J46" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="K46" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L46" s="6" t="s">
-        <v>81</v>
-      </c>
       <c r="M46" s="6" t="s">
         <v>23</v>
       </c>
@@ -3284,7 +3251,7 @@
         <v>27</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>23</v>
@@ -3296,7 +3263,7 @@
         <v>28</v>
       </c>
       <c r="S46" s="9">
-        <v>250</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47">
@@ -3307,35 +3274,35 @@
         <v>46188</v>
       </c>
       <c r="C47" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="D47" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F47" s="8">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="G47" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J47" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="K47" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L47" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="M47" s="6" t="s">
         <v>23</v>
       </c>
@@ -3343,7 +3310,7 @@
         <v>27</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>23</v>
@@ -3352,10 +3319,10 @@
         <v>23</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S47" s="9">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="48">
@@ -3375,34 +3342,34 @@
         <v>23</v>
       </c>
       <c r="F48" s="8">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="G48" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>37</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="N48" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>23</v>
@@ -3414,7 +3381,7 @@
         <v>36</v>
       </c>
       <c r="S48" s="9">
-        <v>379.12</v>
+        <v>410.54</v>
       </c>
     </row>
     <row r="49">
@@ -3431,37 +3398,37 @@
         <v>46188</v>
       </c>
       <c r="E49" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F49" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G49" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>23</v>
@@ -3490,37 +3457,37 @@
         <v>46188</v>
       </c>
       <c r="E50" s="7">
-        <v>46170</v>
+        <v>46141</v>
       </c>
       <c r="F50" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G50" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>23</v>
@@ -3532,7 +3499,7 @@
         <v>36</v>
       </c>
       <c r="S50" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="51">
@@ -3552,34 +3519,34 @@
         <v>46141</v>
       </c>
       <c r="F51" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G51" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>23</v>
@@ -3608,37 +3575,37 @@
         <v>46188</v>
       </c>
       <c r="E52" s="7">
-        <v>46176</v>
+        <v>46169</v>
       </c>
       <c r="F52" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G52" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>23</v>
@@ -3647,10 +3614,10 @@
         <v>35</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S52" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="53">
@@ -3667,37 +3634,37 @@
         <v>46188</v>
       </c>
       <c r="E53" s="7">
-        <v>46141</v>
+        <v>46163</v>
       </c>
       <c r="F53" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G53" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J53" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="K53" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L53" s="6" t="s">
-        <v>68</v>
-      </c>
       <c r="M53" s="6" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>23</v>
@@ -3709,7 +3676,7 @@
         <v>36</v>
       </c>
       <c r="S53" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="54">
@@ -3726,19 +3693,19 @@
         <v>46188</v>
       </c>
       <c r="E54" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F54" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G54" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J54" s="6" t="s">
         <v>91</v>
@@ -3747,16 +3714,16 @@
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>23</v>
@@ -3785,37 +3752,37 @@
         <v>46188</v>
       </c>
       <c r="E55" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F55" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G55" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J55" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="K55" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="K55" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L55" s="6" t="s">
-        <v>94</v>
-      </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>23</v>
@@ -3844,37 +3811,37 @@
         <v>46188</v>
       </c>
       <c r="E56" s="7">
-        <v>46169</v>
+        <v>46153</v>
       </c>
       <c r="F56" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G56" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J56" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="K56" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L56" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>23</v>
@@ -3886,7 +3853,7 @@
         <v>36</v>
       </c>
       <c r="S56" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="57">
@@ -3903,37 +3870,37 @@
         <v>46188</v>
       </c>
       <c r="E57" s="7">
-        <v>46163</v>
+        <v>46188</v>
       </c>
       <c r="F57" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G57" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>23</v>
@@ -3942,10 +3909,10 @@
         <v>35</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S57" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="58">
@@ -3965,34 +3932,34 @@
         <v>46170</v>
       </c>
       <c r="F58" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G58" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>23</v>
@@ -4004,7 +3971,7 @@
         <v>36</v>
       </c>
       <c r="S58" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="59">
@@ -4021,37 +3988,37 @@
         <v>46188</v>
       </c>
       <c r="E59" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F59" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G59" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>23</v>
@@ -4060,10 +4027,10 @@
         <v>35</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S59" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="60">
@@ -4080,37 +4047,37 @@
         <v>46188</v>
       </c>
       <c r="E60" s="7">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="F60" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G60" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>23</v>
@@ -4122,7 +4089,7 @@
         <v>36</v>
       </c>
       <c r="S60" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="61">
@@ -4139,37 +4106,37 @@
         <v>46188</v>
       </c>
       <c r="E61" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F61" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G61" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
@@ -4181,7 +4148,7 @@
         <v>36</v>
       </c>
       <c r="S61" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="62">
@@ -4198,37 +4165,37 @@
         <v>46188</v>
       </c>
       <c r="E62" s="7">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="F62" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G62" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>23</v>
@@ -4237,10 +4204,10 @@
         <v>35</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S62" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="63">
@@ -4257,37 +4224,37 @@
         <v>46188</v>
       </c>
       <c r="E63" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="F63" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G63" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
@@ -4299,7 +4266,7 @@
         <v>36</v>
       </c>
       <c r="S63" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="64">
@@ -4316,37 +4283,37 @@
         <v>46188</v>
       </c>
       <c r="E64" s="7">
-        <v>46188</v>
+        <v>46170</v>
       </c>
       <c r="F64" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G64" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>44</v>
+        <v>105</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
@@ -4355,10 +4322,10 @@
         <v>35</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S64" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="65">
@@ -4375,37 +4342,37 @@
         <v>46188</v>
       </c>
       <c r="E65" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F65" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G65" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
@@ -4414,10 +4381,10 @@
         <v>35</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S65" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="66">
@@ -4434,54 +4401,54 @@
         <v>46188</v>
       </c>
       <c r="E66" s="7">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="F66" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G66" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="M66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q66" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S66" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="B67" s="7">
         <v>46188</v>
@@ -4496,34 +4463,34 @@
         <v>46182</v>
       </c>
       <c r="F67" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G67" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="M67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>23</v>
@@ -4532,10 +4499,10 @@
         <v>35</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="S67" s="9">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="68">
@@ -4543,16 +4510,16 @@
         <v>22</v>
       </c>
       <c r="B68" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C68" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D68" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="E68" s="7">
-        <v>46141</v>
+        <v>46185</v>
       </c>
       <c r="F68" s="8">
         <v>0</v>
@@ -4567,34 +4534,34 @@
         <v>23</v>
       </c>
       <c r="J68" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="K68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="K68" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L68" s="6" t="s">
+      <c r="M68" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N68" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="M68" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N68" s="6" t="s">
-        <v>72</v>
-      </c>
       <c r="O68" s="6" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q68" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="S68" s="9">
-        <v>680</v>
+        <v>170.96</v>
       </c>
     </row>
     <row r="69">
@@ -4602,16 +4569,16 @@
         <v>22</v>
       </c>
       <c r="B69" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C69" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D69" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="E69" s="7">
-        <v>46167</v>
+        <v>46185</v>
       </c>
       <c r="F69" s="8">
         <v>0</v>
@@ -4632,28 +4599,28 @@
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="M69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q69" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="S69" s="9">
-        <v>680</v>
+        <v>250</v>
       </c>
     </row>
     <row r="70">
@@ -4661,7 +4628,7 @@
         <v>22</v>
       </c>
       <c r="B70" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C70" s="7">
         <v>46188</v>
@@ -4669,50 +4636,50 @@
       <c r="D70" s="7">
         <v>46188</v>
       </c>
-      <c r="E70" s="7">
-        <v>46176</v>
+      <c r="E70" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F70" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G70" s="8">
         <v>0</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q70" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S70" s="9">
-        <v>680</v>
+        <v>500.78</v>
       </c>
     </row>
     <row r="71">
@@ -4720,22 +4687,22 @@
         <v>22</v>
       </c>
       <c r="B71" s="7">
-        <v>46188</v>
+        <v>46192</v>
       </c>
       <c r="C71" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D71" s="7">
-        <v>46188</v>
+        <v>46192</v>
       </c>
       <c r="E71" s="7">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="F71" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G71" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4744,22 +4711,22 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
@@ -4771,7 +4738,7 @@
         <v>36</v>
       </c>
       <c r="S71" s="9">
-        <v>680</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="72">
@@ -4779,22 +4746,22 @@
         <v>22</v>
       </c>
       <c r="B72" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C72" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D72" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E72" s="7">
-        <v>46170</v>
+        <v>46153</v>
       </c>
       <c r="F72" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G72" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4803,34 +4770,34 @@
         <v>23</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q72" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S72" s="9">
-        <v>700</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73">
@@ -4838,22 +4805,22 @@
         <v>22</v>
       </c>
       <c r="B73" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C73" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D73" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E73" s="7">
-        <v>46188</v>
+        <v>46167</v>
       </c>
       <c r="F73" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G73" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4862,34 +4829,34 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>121</v>
+        <v>45</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q73" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S73" s="9">
-        <v>700</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74">
@@ -4897,22 +4864,22 @@
         <v>22</v>
       </c>
       <c r="B74" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C74" s="7">
-        <v>46188</v>
+        <v>46082</v>
       </c>
       <c r="D74" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E74" s="7">
-        <v>46170</v>
+        <v>46097</v>
       </c>
       <c r="F74" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G74" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4921,81 +4888,81 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>122</v>
+        <v>25</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="Q74" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S74" s="9">
-        <v>700</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B75" s="7">
+        <v>46195</v>
+      </c>
+      <c r="C75" s="7">
+        <v>46195</v>
+      </c>
+      <c r="D75" s="7">
+        <v>46195</v>
+      </c>
+      <c r="E75" s="7">
+        <v>46169</v>
+      </c>
+      <c r="F75" s="8">
+        <v>6</v>
+      </c>
+      <c r="G75" s="8">
+        <v>6</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J75" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B75" s="7">
-        <v>46188</v>
-      </c>
-      <c r="C75" s="7">
-        <v>46188</v>
-      </c>
-      <c r="D75" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E75" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F75" s="8">
-        <v>0</v>
-      </c>
-      <c r="G75" s="8">
-        <v>0</v>
-      </c>
-      <c r="H75" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I75" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J75" s="6" t="s">
+      <c r="K75" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="K75" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L75" s="6" t="s">
-        <v>125</v>
-      </c>
       <c r="M75" s="6" t="s">
-        <v>23</v>
+        <v>124</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>23</v>
@@ -5004,10 +4971,10 @@
         <v>35</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>126</v>
+        <v>36</v>
       </c>
       <c r="S75" s="9">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="76">
@@ -5015,22 +4982,22 @@
         <v>22</v>
       </c>
       <c r="B76" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C76" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="D76" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E76" s="7">
-        <v>46148</v>
+        <v>46170</v>
       </c>
       <c r="F76" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G76" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -5039,22 +5006,22 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -5063,10 +5030,10 @@
         <v>35</v>
       </c>
       <c r="R76" s="6" t="s">
-        <v>126</v>
+        <v>36</v>
       </c>
       <c r="S76" s="9">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="77">
@@ -5074,22 +5041,22 @@
         <v>22</v>
       </c>
       <c r="B77" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C77" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="D77" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E77" s="7">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="F77" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G77" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -5098,34 +5065,34 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="Q77" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R77" s="6" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="S77" s="9">
-        <v>1200</v>
+        <v>600</v>
       </c>
     </row>
     <row r="78">
@@ -5133,22 +5100,22 @@
         <v>22</v>
       </c>
       <c r="B78" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C78" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="D78" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E78" s="7">
-        <v>46148</v>
+        <v>46176</v>
       </c>
       <c r="F78" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G78" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -5157,22 +5124,22 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>23</v>
@@ -5181,10 +5148,10 @@
         <v>35</v>
       </c>
       <c r="R78" s="6" t="s">
-        <v>132</v>
+        <v>28</v>
       </c>
       <c r="S78" s="9">
-        <v>1200</v>
+        <v>620</v>
       </c>
     </row>
     <row r="79">
@@ -5192,22 +5159,22 @@
         <v>22</v>
       </c>
       <c r="B79" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C79" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="D79" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E79" s="7">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="F79" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G79" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>23</v>
@@ -5216,34 +5183,34 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="Q79" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R79" s="6" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="S79" s="9">
-        <v>1200</v>
+        <v>630</v>
       </c>
     </row>
     <row r="80">
@@ -5251,22 +5218,22 @@
         <v>22</v>
       </c>
       <c r="B80" s="7">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="C80" s="7">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="D80" s="7">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="E80" s="7">
-        <v>46185</v>
+        <v>46169</v>
       </c>
       <c r="F80" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G80" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>23</v>
@@ -5275,34 +5242,34 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q80" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>126</v>
+        <v>36</v>
       </c>
       <c r="S80" s="9">
-        <v>170.96</v>
+        <v>630</v>
       </c>
     </row>
     <row r="81">
@@ -5310,22 +5277,22 @@
         <v>22</v>
       </c>
       <c r="B81" s="7">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="C81" s="7">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="D81" s="7">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="E81" s="7">
-        <v>46185</v>
+        <v>46169</v>
       </c>
       <c r="F81" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G81" s="8">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>23</v>
@@ -5334,34 +5301,34 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q81" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R81" s="6" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="S81" s="9">
-        <v>250</v>
+        <v>630</v>
       </c>
     </row>
     <row r="82">
@@ -5369,22 +5336,22 @@
         <v>22</v>
       </c>
       <c r="B82" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C82" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D82" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="E82" s="7">
-        <v>46185</v>
+        <v>46163</v>
       </c>
       <c r="F82" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G82" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>23</v>
@@ -5393,22 +5360,22 @@
         <v>23</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>141</v>
+        <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>23</v>
@@ -5420,7 +5387,7 @@
         <v>36</v>
       </c>
       <c r="S82" s="9">
-        <v>2100</v>
+        <v>630</v>
       </c>
     </row>
     <row r="83">
@@ -5431,19 +5398,19 @@
         <v>46195</v>
       </c>
       <c r="C83" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D83" s="7">
         <v>46195</v>
       </c>
       <c r="E83" s="7">
-        <v>46153</v>
+        <v>46170</v>
       </c>
       <c r="F83" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G83" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>23</v>
@@ -5452,34 +5419,34 @@
         <v>23</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q83" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S83" s="9">
-        <v>50</v>
+        <v>630</v>
       </c>
     </row>
     <row r="84">
@@ -5490,19 +5457,19 @@
         <v>46195</v>
       </c>
       <c r="C84" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D84" s="7">
         <v>46195</v>
       </c>
       <c r="E84" s="7">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="F84" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G84" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>23</v>
@@ -5511,34 +5478,34 @@
         <v>23</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q84" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S84" s="9">
-        <v>100</v>
+        <v>630</v>
       </c>
     </row>
     <row r="85">
@@ -5549,19 +5516,19 @@
         <v>46195</v>
       </c>
       <c r="C85" s="7">
-        <v>46082</v>
+        <v>46195</v>
       </c>
       <c r="D85" s="7">
         <v>46195</v>
       </c>
       <c r="E85" s="7">
-        <v>46097</v>
+        <v>46164</v>
       </c>
       <c r="F85" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G85" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>23</v>
@@ -5570,34 +5537,34 @@
         <v>23</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>25</v>
+        <v>137</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="M85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q85" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R85" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S85" s="9">
-        <v>146.55</v>
+        <v>630</v>
       </c>
     </row>
     <row r="86">
@@ -5614,13 +5581,13 @@
         <v>46195</v>
       </c>
       <c r="E86" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F86" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G86" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>23</v>
@@ -5629,22 +5596,22 @@
         <v>23</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>23</v>
@@ -5656,7 +5623,7 @@
         <v>36</v>
       </c>
       <c r="S86" s="9">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row r="87">
@@ -5673,13 +5640,13 @@
         <v>46195</v>
       </c>
       <c r="E87" s="7">
-        <v>46169</v>
+        <v>46153</v>
       </c>
       <c r="F87" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G87" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H87" s="6" t="s">
         <v>23</v>
@@ -5688,22 +5655,22 @@
         <v>23</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="K87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="N87" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P87" s="6" t="s">
         <v>23</v>
@@ -5715,7 +5682,7 @@
         <v>36</v>
       </c>
       <c r="S87" s="9">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row r="88">
@@ -5732,13 +5699,13 @@
         <v>46195</v>
       </c>
       <c r="E88" s="7">
-        <v>46170</v>
+        <v>46127</v>
       </c>
       <c r="F88" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G88" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>23</v>
@@ -5747,22 +5714,22 @@
         <v>23</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>23</v>
@@ -5774,7 +5741,7 @@
         <v>36</v>
       </c>
       <c r="S88" s="9">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row r="89">
@@ -5791,13 +5758,13 @@
         <v>46195</v>
       </c>
       <c r="E89" s="7">
-        <v>46176</v>
+        <v>46160</v>
       </c>
       <c r="F89" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G89" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>23</v>
@@ -5806,22 +5773,22 @@
         <v>23</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="K89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N89" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O89" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P89" s="6" t="s">
         <v>23</v>
@@ -5830,10 +5797,10 @@
         <v>35</v>
       </c>
       <c r="R89" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S89" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="90">
@@ -5850,13 +5817,13 @@
         <v>46195</v>
       </c>
       <c r="E90" s="7">
-        <v>46163</v>
+        <v>46188</v>
       </c>
       <c r="F90" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G90" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>23</v>
@@ -5865,22 +5832,22 @@
         <v>23</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="M90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>23</v>
@@ -5889,10 +5856,10 @@
         <v>35</v>
       </c>
       <c r="R90" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S90" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="91">
@@ -5909,13 +5876,13 @@
         <v>46195</v>
       </c>
       <c r="E91" s="7">
-        <v>46170</v>
+        <v>46119</v>
       </c>
       <c r="F91" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G91" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>23</v>
@@ -5924,22 +5891,22 @@
         <v>23</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N91" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O91" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P91" s="6" t="s">
         <v>23</v>
@@ -5951,7 +5918,7 @@
         <v>36</v>
       </c>
       <c r="S91" s="9">
-        <v>630</v>
+        <v>670</v>
       </c>
     </row>
     <row r="92">
@@ -5968,13 +5935,13 @@
         <v>46195</v>
       </c>
       <c r="E92" s="7">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="F92" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G92" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>23</v>
@@ -5983,25 +5950,25 @@
         <v>23</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="M92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="Q92" s="6" t="s">
         <v>35</v>
@@ -6010,7 +5977,7 @@
         <v>36</v>
       </c>
       <c r="S92" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="93">
@@ -6027,13 +5994,13 @@
         <v>46195</v>
       </c>
       <c r="E93" s="7">
-        <v>46169</v>
+        <v>46176</v>
       </c>
       <c r="F93" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G93" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>23</v>
@@ -6042,22 +6009,22 @@
         <v>23</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="M93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N93" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O93" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P93" s="6" t="s">
         <v>23</v>
@@ -6069,7 +6036,7 @@
         <v>36</v>
       </c>
       <c r="S93" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="94">
@@ -6086,13 +6053,13 @@
         <v>46195</v>
       </c>
       <c r="E94" s="7">
-        <v>46169</v>
+        <v>46182</v>
       </c>
       <c r="F94" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G94" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>23</v>
@@ -6101,22 +6068,22 @@
         <v>23</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="M94" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>23</v>
@@ -6128,7 +6095,7 @@
         <v>36</v>
       </c>
       <c r="S94" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="95">
@@ -6145,13 +6112,13 @@
         <v>46195</v>
       </c>
       <c r="E95" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F95" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G95" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>23</v>
@@ -6160,22 +6127,22 @@
         <v>23</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="M95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N95" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O95" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P95" s="6" t="s">
         <v>23</v>
@@ -6184,10 +6151,10 @@
         <v>35</v>
       </c>
       <c r="R95" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S95" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="96">
@@ -6204,13 +6171,13 @@
         <v>46195</v>
       </c>
       <c r="E96" s="7">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="F96" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G96" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>23</v>
@@ -6219,22 +6186,22 @@
         <v>23</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="M96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>23</v>
@@ -6246,7 +6213,7 @@
         <v>36</v>
       </c>
       <c r="S96" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="97">
@@ -6263,13 +6230,13 @@
         <v>46195</v>
       </c>
       <c r="E97" s="7">
-        <v>46153</v>
+        <v>46182</v>
       </c>
       <c r="F97" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G97" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H97" s="6" t="s">
         <v>23</v>
@@ -6278,22 +6245,22 @@
         <v>23</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="M97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N97" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O97" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P97" s="6" t="s">
         <v>23</v>
@@ -6305,7 +6272,7 @@
         <v>36</v>
       </c>
       <c r="S97" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="98">
@@ -6325,10 +6292,10 @@
         <v>46170</v>
       </c>
       <c r="F98" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G98" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>23</v>
@@ -6337,25 +6304,25 @@
         <v>23</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="M98" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q98" s="6" t="s">
         <v>35</v>
@@ -6364,7 +6331,7 @@
         <v>36</v>
       </c>
       <c r="S98" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="99">
@@ -6381,13 +6348,13 @@
         <v>46195</v>
       </c>
       <c r="E99" s="7">
-        <v>46127</v>
+        <v>46188</v>
       </c>
       <c r="F99" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G99" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>23</v>
@@ -6396,22 +6363,22 @@
         <v>23</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="M99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N99" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O99" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P99" s="6" t="s">
         <v>23</v>
@@ -6420,10 +6387,10 @@
         <v>35</v>
       </c>
       <c r="R99" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S99" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="100">
@@ -6440,13 +6407,13 @@
         <v>46195</v>
       </c>
       <c r="E100" s="7">
-        <v>46160</v>
+        <v>46170</v>
       </c>
       <c r="F100" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G100" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H100" s="6" t="s">
         <v>23</v>
@@ -6455,22 +6422,22 @@
         <v>23</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="M100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>23</v>
@@ -6482,12 +6449,12 @@
         <v>36</v>
       </c>
       <c r="S100" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="B101" s="7">
         <v>46195</v>
@@ -6499,13 +6466,13 @@
         <v>46195</v>
       </c>
       <c r="E101" s="7">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="F101" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G101" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H101" s="6" t="s">
         <v>23</v>
@@ -6514,22 +6481,22 @@
         <v>23</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="M101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N101" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O101" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P101" s="6" t="s">
         <v>23</v>
@@ -6538,10 +6505,10 @@
         <v>35</v>
       </c>
       <c r="R101" s="6" t="s">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="S101" s="9">
-        <v>650</v>
+        <v>800</v>
       </c>
     </row>
     <row r="102">
@@ -6558,13 +6525,13 @@
         <v>46195</v>
       </c>
       <c r="E102" s="7">
-        <v>46119</v>
+        <v>46148</v>
       </c>
       <c r="F102" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G102" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H102" s="6" t="s">
         <v>23</v>
@@ -6573,22 +6540,22 @@
         <v>23</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K102" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>161</v>
+        <v>113</v>
       </c>
       <c r="M102" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>23</v>
@@ -6597,10 +6564,10 @@
         <v>35</v>
       </c>
       <c r="R102" s="6" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="S102" s="9">
-        <v>670</v>
+        <v>800</v>
       </c>
     </row>
     <row r="103">
@@ -6617,13 +6584,13 @@
         <v>46195</v>
       </c>
       <c r="E103" s="7">
-        <v>46182</v>
+        <v>46148</v>
       </c>
       <c r="F103" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G103" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H103" s="6" t="s">
         <v>23</v>
@@ -6632,22 +6599,22 @@
         <v>23</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K103" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="M103" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N103" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O103" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P103" s="6" t="s">
         <v>23</v>
@@ -6656,10 +6623,10 @@
         <v>35</v>
       </c>
       <c r="R103" s="6" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="S103" s="9">
-        <v>680</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="104">
@@ -6676,13 +6643,13 @@
         <v>46195</v>
       </c>
       <c r="E104" s="7">
-        <v>46176</v>
+        <v>46160</v>
       </c>
       <c r="F104" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G104" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>23</v>
@@ -6691,34 +6658,34 @@
         <v>23</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L104" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="M104" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N104" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="O104" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="P104" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q104" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="R104" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="M104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N104" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="O104" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q104" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R104" s="6" t="s">
-        <v>36</v>
-      </c>
       <c r="S104" s="9">
-        <v>680</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="105">
@@ -6735,13 +6702,13 @@
         <v>46195</v>
       </c>
       <c r="E105" s="7">
-        <v>46182</v>
+        <v>46160</v>
       </c>
       <c r="F105" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G105" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>23</v>
@@ -6750,34 +6717,34 @@
         <v>23</v>
       </c>
       <c r="J105" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="K105" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L105" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="K105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L105" s="6" t="s">
-        <v>46</v>
-      </c>
       <c r="M105" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N105" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O105" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P105" s="6" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="Q105" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R105" s="6" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="S105" s="9">
-        <v>680</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="106">
@@ -6785,22 +6752,22 @@
         <v>22</v>
       </c>
       <c r="B106" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="C106" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D106" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="E106" s="7">
-        <v>46167</v>
+        <v>46185</v>
       </c>
       <c r="F106" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G106" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>23</v>
@@ -6815,16 +6782,16 @@
         <v>23</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>58</v>
+        <v>166</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>23</v>
+        <v>167</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>23</v>
@@ -6836,7 +6803,7 @@
         <v>36</v>
       </c>
       <c r="S106" s="9">
-        <v>680</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="107">
@@ -6844,22 +6811,22 @@
         <v>22</v>
       </c>
       <c r="B107" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C107" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D107" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E107" s="7">
-        <v>46182</v>
+        <v>46153</v>
       </c>
       <c r="F107" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G107" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>23</v>
@@ -6868,34 +6835,34 @@
         <v>23</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>166</v>
+        <v>67</v>
       </c>
       <c r="K107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="M107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N107" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O107" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P107" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q107" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R107" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S107" s="9">
-        <v>680</v>
+        <v>50</v>
       </c>
     </row>
     <row r="108">
@@ -6903,22 +6870,22 @@
         <v>22</v>
       </c>
       <c r="B108" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C108" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D108" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E108" s="7">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F108" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G108" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H108" s="6" t="s">
         <v>23</v>
@@ -6927,34 +6894,34 @@
         <v>23</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>167</v>
+        <v>45</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="M108" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q108" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R108" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S108" s="9">
-        <v>680</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109">
@@ -6962,22 +6929,22 @@
         <v>22</v>
       </c>
       <c r="B109" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C109" s="7">
-        <v>46195</v>
+        <v>46082</v>
       </c>
       <c r="D109" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E109" s="7">
-        <v>46170</v>
+        <v>46097</v>
       </c>
       <c r="F109" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G109" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>23</v>
@@ -6986,34 +6953,34 @@
         <v>23</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>168</v>
+        <v>25</v>
       </c>
       <c r="K109" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="M109" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N109" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O109" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P109" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="Q109" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R109" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S109" s="9">
-        <v>700</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="110">
@@ -7021,22 +6988,22 @@
         <v>22</v>
       </c>
       <c r="B110" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C110" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D110" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E110" s="7">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="F110" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G110" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>23</v>
@@ -7045,22 +7012,22 @@
         <v>23</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="M110" s="6" t="s">
-        <v>23</v>
+        <v>124</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>23</v>
@@ -7072,7 +7039,7 @@
         <v>36</v>
       </c>
       <c r="S110" s="9">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="111">
@@ -7080,22 +7047,22 @@
         <v>22</v>
       </c>
       <c r="B111" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C111" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D111" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E111" s="7">
-        <v>46188</v>
+        <v>46169</v>
       </c>
       <c r="F111" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G111" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>23</v>
@@ -7104,22 +7071,22 @@
         <v>23</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K111" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="M111" s="6" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="N111" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O111" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P111" s="6" t="s">
         <v>23</v>
@@ -7128,10 +7095,10 @@
         <v>35</v>
       </c>
       <c r="R111" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S111" s="9">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="112">
@@ -7139,22 +7106,22 @@
         <v>22</v>
       </c>
       <c r="B112" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C112" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D112" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E112" s="7">
-        <v>46148</v>
+        <v>46163</v>
       </c>
       <c r="F112" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G112" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H112" s="6" t="s">
         <v>23</v>
@@ -7163,22 +7130,22 @@
         <v>23</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K112" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L112" s="6" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="M112" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>23</v>
@@ -7187,33 +7154,33 @@
         <v>35</v>
       </c>
       <c r="R112" s="6" t="s">
-        <v>126</v>
+        <v>36</v>
       </c>
       <c r="S112" s="9">
-        <v>800</v>
+        <v>630</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="B113" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C113" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D113" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E113" s="7">
-        <v>46182</v>
+        <v>46169</v>
       </c>
       <c r="F113" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G113" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>23</v>
@@ -7222,22 +7189,22 @@
         <v>23</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="M113" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N113" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O113" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P113" s="6" t="s">
         <v>23</v>
@@ -7246,10 +7213,10 @@
         <v>35</v>
       </c>
       <c r="R113" s="6" t="s">
-        <v>126</v>
+        <v>36</v>
       </c>
       <c r="S113" s="9">
-        <v>800</v>
+        <v>630</v>
       </c>
     </row>
     <row r="114">
@@ -7257,22 +7224,22 @@
         <v>22</v>
       </c>
       <c r="B114" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C114" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D114" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E114" s="7">
-        <v>46148</v>
+        <v>46169</v>
       </c>
       <c r="F114" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G114" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H114" s="6" t="s">
         <v>23</v>
@@ -7281,22 +7248,22 @@
         <v>23</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K114" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="M114" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>23</v>
@@ -7305,10 +7272,10 @@
         <v>35</v>
       </c>
       <c r="R114" s="6" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="S114" s="9">
-        <v>1200</v>
+        <v>630</v>
       </c>
     </row>
     <row r="115">
@@ -7316,22 +7283,22 @@
         <v>22</v>
       </c>
       <c r="B115" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C115" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D115" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E115" s="7">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="F115" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G115" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H115" s="6" t="s">
         <v>23</v>
@@ -7340,34 +7307,34 @@
         <v>23</v>
       </c>
       <c r="J115" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K115" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M115" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N115" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O115" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P115" s="6" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="Q115" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R115" s="6" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="S115" s="9">
-        <v>1200</v>
+        <v>630</v>
       </c>
     </row>
     <row r="116">
@@ -7375,22 +7342,22 @@
         <v>22</v>
       </c>
       <c r="B116" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C116" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D116" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E116" s="7">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="F116" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G116" s="8">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H116" s="6" t="s">
         <v>23</v>
@@ -7399,34 +7366,34 @@
         <v>23</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K116" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L116" s="6" t="s">
-        <v>136</v>
+        <v>93</v>
       </c>
       <c r="M116" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="Q116" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R116" s="6" t="s">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="S116" s="9">
-        <v>1200</v>
+        <v>630</v>
       </c>
     </row>
     <row r="117">
@@ -7434,22 +7401,22 @@
         <v>22</v>
       </c>
       <c r="B117" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="C117" s="7">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D117" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="E117" s="7">
-        <v>46185</v>
+        <v>46160</v>
       </c>
       <c r="F117" s="8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G117" s="8">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H117" s="6" t="s">
         <v>23</v>
@@ -7458,22 +7425,22 @@
         <v>23</v>
       </c>
       <c r="J117" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K117" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L117" s="6" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="M117" s="6" t="s">
-        <v>178</v>
+        <v>23</v>
       </c>
       <c r="N117" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O117" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P117" s="6" t="s">
         <v>23</v>
@@ -7485,7 +7452,7 @@
         <v>36</v>
       </c>
       <c r="S117" s="9">
-        <v>4400</v>
+        <v>650</v>
       </c>
     </row>
     <row r="118">
@@ -7496,19 +7463,19 @@
         <v>46202</v>
       </c>
       <c r="C118" s="7">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D118" s="7">
         <v>46202</v>
       </c>
       <c r="E118" s="7">
-        <v>46153</v>
+        <v>46127</v>
       </c>
       <c r="F118" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G118" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H118" s="6" t="s">
         <v>23</v>
@@ -7517,34 +7484,34 @@
         <v>23</v>
       </c>
       <c r="J118" s="6" t="s">
-        <v>70</v>
+        <v>176</v>
       </c>
       <c r="K118" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L118" s="6" t="s">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="M118" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
       <c r="Q118" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R118" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S118" s="9">
-        <v>50</v>
+        <v>650</v>
       </c>
     </row>
     <row r="119">
@@ -7555,19 +7522,19 @@
         <v>46202</v>
       </c>
       <c r="C119" s="7">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D119" s="7">
         <v>46202</v>
       </c>
       <c r="E119" s="7">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="F119" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G119" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H119" s="6" t="s">
         <v>23</v>
@@ -7576,34 +7543,34 @@
         <v>23</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>47</v>
+        <v>177</v>
       </c>
       <c r="K119" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L119" s="6" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="M119" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N119" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O119" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P119" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q119" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R119" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S119" s="9">
-        <v>100</v>
+        <v>650</v>
       </c>
     </row>
     <row r="120">
@@ -7614,19 +7581,19 @@
         <v>46202</v>
       </c>
       <c r="C120" s="7">
-        <v>46082</v>
+        <v>46202</v>
       </c>
       <c r="D120" s="7">
         <v>46202</v>
       </c>
       <c r="E120" s="7">
-        <v>46097</v>
+        <v>46188</v>
       </c>
       <c r="F120" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G120" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H120" s="6" t="s">
         <v>23</v>
@@ -7635,34 +7602,34 @@
         <v>23</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>25</v>
+        <v>178</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L120" s="6" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="M120" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q120" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R120" s="6" t="s">
         <v>28</v>
       </c>
       <c r="S120" s="9">
-        <v>146.55</v>
+        <v>650</v>
       </c>
     </row>
     <row r="121">
@@ -7679,13 +7646,13 @@
         <v>46202</v>
       </c>
       <c r="E121" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F121" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G121" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H121" s="6" t="s">
         <v>23</v>
@@ -7700,16 +7667,16 @@
         <v>23</v>
       </c>
       <c r="L121" s="6" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="M121" s="6" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="N121" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O121" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P121" s="6" t="s">
         <v>23</v>
@@ -7718,10 +7685,10 @@
         <v>35</v>
       </c>
       <c r="R121" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S121" s="9">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="122">
@@ -7738,13 +7705,13 @@
         <v>46202</v>
       </c>
       <c r="E122" s="7">
-        <v>46169</v>
+        <v>46182</v>
       </c>
       <c r="F122" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G122" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H122" s="6" t="s">
         <v>23</v>
@@ -7759,16 +7726,16 @@
         <v>23</v>
       </c>
       <c r="L122" s="6" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="M122" s="6" t="s">
-        <v>144</v>
+        <v>23</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>23</v>
@@ -7780,7 +7747,7 @@
         <v>36</v>
       </c>
       <c r="S122" s="9">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="123">
@@ -7797,13 +7764,13 @@
         <v>46202</v>
       </c>
       <c r="E123" s="7">
-        <v>46163</v>
+        <v>46182</v>
       </c>
       <c r="F123" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G123" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H123" s="6" t="s">
         <v>23</v>
@@ -7818,16 +7785,16 @@
         <v>23</v>
       </c>
       <c r="L123" s="6" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="M123" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N123" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O123" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P123" s="6" t="s">
         <v>23</v>
@@ -7839,7 +7806,7 @@
         <v>36</v>
       </c>
       <c r="S123" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="124">
@@ -7856,13 +7823,13 @@
         <v>46202</v>
       </c>
       <c r="E124" s="7">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="F124" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G124" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H124" s="6" t="s">
         <v>23</v>
@@ -7877,16 +7844,16 @@
         <v>23</v>
       </c>
       <c r="L124" s="6" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="M124" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>23</v>
@@ -7898,7 +7865,7 @@
         <v>36</v>
       </c>
       <c r="S124" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="125">
@@ -7915,13 +7882,13 @@
         <v>46202</v>
       </c>
       <c r="E125" s="7">
-        <v>46169</v>
+        <v>46182</v>
       </c>
       <c r="F125" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G125" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H125" s="6" t="s">
         <v>23</v>
@@ -7936,16 +7903,16 @@
         <v>23</v>
       </c>
       <c r="L125" s="6" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="M125" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N125" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O125" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P125" s="6" t="s">
         <v>23</v>
@@ -7957,7 +7924,7 @@
         <v>36</v>
       </c>
       <c r="S125" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="126">
@@ -7974,13 +7941,13 @@
         <v>46202</v>
       </c>
       <c r="E126" s="7">
-        <v>46169</v>
+        <v>46188</v>
       </c>
       <c r="F126" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G126" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H126" s="6" t="s">
         <v>23</v>
@@ -7995,16 +7962,16 @@
         <v>23</v>
       </c>
       <c r="L126" s="6" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="M126" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>23</v>
@@ -8013,10 +7980,10 @@
         <v>35</v>
       </c>
       <c r="R126" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S126" s="9">
-        <v>630</v>
+        <v>700</v>
       </c>
     </row>
     <row r="127">
@@ -8033,13 +8000,13 @@
         <v>46202</v>
       </c>
       <c r="E127" s="7">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="F127" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G127" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H127" s="6" t="s">
         <v>23</v>
@@ -8054,16 +8021,16 @@
         <v>23</v>
       </c>
       <c r="L127" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M127" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N127" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O127" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P127" s="6" t="s">
         <v>23</v>
@@ -8075,12 +8042,12 @@
         <v>36</v>
       </c>
       <c r="S127" s="9">
-        <v>630</v>
+        <v>700</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="B128" s="7">
         <v>46202</v>
@@ -8092,13 +8059,13 @@
         <v>46202</v>
       </c>
       <c r="E128" s="7">
-        <v>46160</v>
+        <v>46182</v>
       </c>
       <c r="F128" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G128" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H128" s="6" t="s">
         <v>23</v>
@@ -8113,16 +8080,16 @@
         <v>23</v>
       </c>
       <c r="L128" s="6" t="s">
-        <v>158</v>
+        <v>110</v>
       </c>
       <c r="M128" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>23</v>
@@ -8131,10 +8098,10 @@
         <v>35</v>
       </c>
       <c r="R128" s="6" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="S128" s="9">
-        <v>650</v>
+        <v>800</v>
       </c>
     </row>
     <row r="129">
@@ -8151,13 +8118,13 @@
         <v>46202</v>
       </c>
       <c r="E129" s="7">
-        <v>46153</v>
+        <v>46148</v>
       </c>
       <c r="F129" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G129" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H129" s="6" t="s">
         <v>23</v>
@@ -8172,16 +8139,16 @@
         <v>23</v>
       </c>
       <c r="L129" s="6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="M129" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N129" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O129" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P129" s="6" t="s">
         <v>23</v>
@@ -8190,10 +8157,10 @@
         <v>35</v>
       </c>
       <c r="R129" s="6" t="s">
-        <v>36</v>
+        <v>111</v>
       </c>
       <c r="S129" s="9">
-        <v>650</v>
+        <v>800</v>
       </c>
     </row>
     <row r="130">
@@ -8210,13 +8177,13 @@
         <v>46202</v>
       </c>
       <c r="E130" s="7">
-        <v>46127</v>
+        <v>46148</v>
       </c>
       <c r="F130" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G130" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H130" s="6" t="s">
         <v>23</v>
@@ -8231,16 +8198,16 @@
         <v>23</v>
       </c>
       <c r="L130" s="6" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="M130" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>23</v>
@@ -8249,10 +8216,10 @@
         <v>35</v>
       </c>
       <c r="R130" s="6" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="S130" s="9">
-        <v>650</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="131">
@@ -8269,13 +8236,13 @@
         <v>46202</v>
       </c>
       <c r="E131" s="7">
-        <v>46188</v>
+        <v>46160</v>
       </c>
       <c r="F131" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G131" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H131" s="6" t="s">
         <v>23</v>
@@ -8290,28 +8257,28 @@
         <v>23</v>
       </c>
       <c r="L131" s="6" t="s">
-        <v>44</v>
+        <v>161</v>
       </c>
       <c r="M131" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N131" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O131" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P131" s="6" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="Q131" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R131" s="6" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="S131" s="9">
-        <v>650</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="132">
@@ -8328,13 +8295,13 @@
         <v>46202</v>
       </c>
       <c r="E132" s="7">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="F132" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G132" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H132" s="6" t="s">
         <v>23</v>
@@ -8349,700 +8316,51 @@
         <v>23</v>
       </c>
       <c r="L132" s="6" t="s">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="M132" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>23</v>
+        <v>162</v>
       </c>
       <c r="Q132" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R132" s="6" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="S132" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B133" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C133" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D133" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E133" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F133" s="8">
-        <v>14</v>
-      </c>
-      <c r="G133" s="8">
-        <v>14</v>
-      </c>
-      <c r="H133" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I133" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J133" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="K133" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L133" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="M133" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N133" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="O133" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="P133" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q133" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R133" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S133" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B134" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C134" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D134" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E134" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F134" s="8">
-        <v>14</v>
-      </c>
-      <c r="G134" s="8">
-        <v>14</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I134" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J134" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="K134" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L134" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="M134" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N134" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="O134" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="P134" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q134" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R134" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S134" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B135" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C135" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D135" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E135" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F135" s="8">
-        <v>14</v>
-      </c>
-      <c r="G135" s="8">
-        <v>14</v>
-      </c>
-      <c r="H135" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I135" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J135" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="K135" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L135" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="M135" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N135" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="O135" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="P135" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q135" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R135" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S135" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B136" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C136" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D136" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E136" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F136" s="8">
-        <v>14</v>
-      </c>
-      <c r="G136" s="8">
-        <v>14</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I136" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J136" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="K136" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L136" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="M136" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N136" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="O136" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="P136" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q136" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R136" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S136" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B137" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C137" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D137" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E137" s="7">
-        <v>46188</v>
-      </c>
-      <c r="F137" s="8">
-        <v>14</v>
-      </c>
-      <c r="G137" s="8">
-        <v>14</v>
-      </c>
-      <c r="H137" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I137" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J137" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="K137" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L137" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="M137" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N137" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="O137" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="P137" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q137" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R137" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S137" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B138" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C138" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D138" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E138" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F138" s="8">
-        <v>14</v>
-      </c>
-      <c r="G138" s="8">
-        <v>14</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I138" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J138" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="K138" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L138" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="M138" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N138" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="O138" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="P138" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q138" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R138" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S138" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B139" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C139" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D139" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E139" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F139" s="8">
-        <v>14</v>
-      </c>
-      <c r="G139" s="8">
-        <v>14</v>
-      </c>
-      <c r="H139" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I139" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J139" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="K139" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L139" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="M139" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N139" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="O139" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="P139" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q139" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R139" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="S139" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B140" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C140" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D140" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E140" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F140" s="8">
-        <v>14</v>
-      </c>
-      <c r="G140" s="8">
-        <v>14</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I140" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J140" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="K140" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L140" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="M140" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N140" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="O140" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="P140" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q140" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R140" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="S140" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B141" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C141" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D141" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E141" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F141" s="8">
-        <v>14</v>
-      </c>
-      <c r="G141" s="8">
-        <v>14</v>
-      </c>
-      <c r="H141" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I141" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J141" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="K141" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L141" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="M141" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N141" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="O141" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="P141" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q141" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R141" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="S141" s="9">
         <v>1200</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B142" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C142" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D142" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E142" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F142" s="8">
-        <v>14</v>
-      </c>
-      <c r="G142" s="8">
-        <v>14</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I142" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J142" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="K142" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L142" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="M142" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N142" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="O142" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="P142" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q142" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R142" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="S142" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B143" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C143" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D143" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E143" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F143" s="8">
-        <v>14</v>
-      </c>
-      <c r="G143" s="8">
-        <v>14</v>
-      </c>
-      <c r="H143" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I143" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J143" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="K143" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L143" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="M143" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N143" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="O143" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="P143" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q143" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R143" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="S143" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="144" ht="23" customHeight="1">
-      <c r="A144" s="10"/>
-      <c r="B144" s="11"/>
-      <c r="C144" s="11"/>
-      <c r="D144" s="11"/>
-      <c r="E144" s="11"/>
-      <c r="F144" s="12"/>
-      <c r="G144" s="12"/>
-      <c r="H144" s="10"/>
-      <c r="I144" s="10"/>
-      <c r="J144" s="10"/>
-      <c r="K144" s="10"/>
-      <c r="L144" s="10"/>
-      <c r="M144" s="10"/>
-      <c r="N144" s="10"/>
-      <c r="O144" s="10"/>
-      <c r="P144" s="10"/>
-      <c r="Q144" s="10"/>
-      <c r="R144" s="10"/>
-      <c r="S144" s="13">
-        <f>SUM(S6:S143)</f>
+    <row r="133" ht="23" customHeight="1">
+      <c r="A133" s="10"/>
+      <c r="B133" s="11"/>
+      <c r="C133" s="11"/>
+      <c r="D133" s="11"/>
+      <c r="E133" s="11"/>
+      <c r="F133" s="12"/>
+      <c r="G133" s="12"/>
+      <c r="H133" s="10"/>
+      <c r="I133" s="10"/>
+      <c r="J133" s="10"/>
+      <c r="K133" s="10"/>
+      <c r="L133" s="10"/>
+      <c r="M133" s="10"/>
+      <c r="N133" s="10"/>
+      <c r="O133" s="10"/>
+      <c r="P133" s="10"/>
+      <c r="Q133" s="10"/>
+      <c r="R133" s="10"/>
+      <c r="S133" s="13">
+        <f>SUM(S6:S132)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$133</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$132</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em terça-feira, 16 de junho de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em quarta-feira, 17 de junho de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -184,15 +184,15 @@
     <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
   </si>
   <si>
+    <t>FA-11775</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
     <t>FA-11847</t>
   </si>
   <si>
-    <t>FA-11775</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
     <t>FA-11815</t>
   </si>
   <si>
@@ -262,6 +262,12 @@
     <t>YAGO ELIAS COSTA BATISTA</t>
   </si>
   <si>
+    <t>FA-11671</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
     <t>FA-11846</t>
   </si>
   <si>
@@ -301,12 +307,6 @@
     <t>ADRIANO SANTOS DE CARVALHO</t>
   </si>
   <si>
-    <t>FA-11671</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
     <t>FA-11798</t>
   </si>
   <si>
@@ -331,12 +331,12 @@
     <t>FA-11679</t>
   </si>
   <si>
+    <t>FA-11818</t>
+  </si>
+  <si>
     <t>FA-11819</t>
   </si>
   <si>
-    <t>FA-11818</t>
-  </si>
-  <si>
     <t>FA-11573</t>
   </si>
   <si>
@@ -346,183 +346,177 @@
     <t>FA-11694</t>
   </si>
   <si>
-    <t>FA-11764</t>
+    <t>FA-11849</t>
+  </si>
+  <si>
+    <t>FA-11785</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>FA-11820</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>ND-11844</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>ND-11845</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11756</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11842</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-11730</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11791</t>
+  </si>
+  <si>
+    <t>FA-11749</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11807</t>
+  </si>
+  <si>
+    <t>FA-11733</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11731</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11728</t>
+  </si>
+  <si>
+    <t>FA-11672</t>
+  </si>
+  <si>
+    <t>FA-11790</t>
+  </si>
+  <si>
+    <t>FA-11800</t>
+  </si>
+  <si>
+    <t>FA-11687</t>
+  </si>
+  <si>
+    <t>FA-11799</t>
+  </si>
+  <si>
+    <t>FA-11508</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11625</t>
+  </si>
+  <si>
+    <t>FA-11660</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>FA-11850</t>
+  </si>
+  <si>
+    <t>FA-11438</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11811</t>
+  </si>
+  <si>
+    <t>FA-11821</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11823</t>
+  </si>
+  <si>
+    <t>FA-11695</t>
+  </si>
+  <si>
+    <t>FA-11680</t>
+  </si>
+  <si>
+    <t>FA-11822</t>
+  </si>
+  <si>
+    <t>FA-11789</t>
+  </si>
+  <si>
+    <t>FA-11851</t>
+  </si>
+  <si>
+    <t>FA-11765</t>
   </si>
   <si>
     <t>ANNY KATARINA ACIOLE DA SILVA</t>
   </si>
   <si>
-    <t>FA-11849</t>
-  </si>
-  <si>
-    <t>FA-11785</t>
-  </si>
-  <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>FA-11820</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>ND-11844</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>HOJE</t>
-  </si>
-  <si>
-    <t>ND-11845</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11756</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11842</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>FA-11730</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11791</t>
-  </si>
-  <si>
-    <t>FA-11749</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11807</t>
-  </si>
-  <si>
-    <t>FA-11733</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11731</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11728</t>
-  </si>
-  <si>
-    <t>FA-11672</t>
-  </si>
-  <si>
-    <t>FA-11790</t>
-  </si>
-  <si>
-    <t>FA-11800</t>
-  </si>
-  <si>
-    <t>FA-11687</t>
-  </si>
-  <si>
-    <t>FA-11799</t>
-  </si>
-  <si>
-    <t>FA-11625</t>
-  </si>
-  <si>
-    <t>FA-11508</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11660</t>
-  </si>
-  <si>
-    <t>LUCA ZOLI</t>
-  </si>
-  <si>
-    <t>FA-11850</t>
-  </si>
-  <si>
-    <t>FA-11438</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11695</t>
-  </si>
-  <si>
-    <t>FA-11811</t>
-  </si>
-  <si>
-    <t>FA-11821</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11680</t>
-  </si>
-  <si>
-    <t>FA-11822</t>
-  </si>
-  <si>
-    <t>FA-11823</t>
-  </si>
-  <si>
-    <t>FA-11789</t>
-  </si>
-  <si>
-    <t>FA-11851</t>
-  </si>
-  <si>
-    <t>FA-11765</t>
-  </si>
-  <si>
     <t>FA-11824</t>
   </si>
   <si>
     <t>FA-11605</t>
   </si>
   <si>
+    <t>FA-11636</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
     <t>FA-11595</t>
   </si>
   <si>
-    <t>FA-11636</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
     <t>FA-11648</t>
   </si>
   <si>
@@ -559,18 +553,21 @@
     <t>FA-11688</t>
   </si>
   <si>
+    <t>FA-11509</t>
+  </si>
+  <si>
+    <t>FA-11626</t>
+  </si>
+  <si>
     <t>FA-11661</t>
   </si>
   <si>
-    <t>FA-11509</t>
-  </si>
-  <si>
-    <t>FA-11626</t>
-  </si>
-  <si>
     <t>FA-11852</t>
   </si>
   <si>
+    <t>FA-11825</t>
+  </si>
+  <si>
     <t>FA-11681</t>
   </si>
   <si>
@@ -583,25 +580,22 @@
     <t>FA-11696</t>
   </si>
   <si>
-    <t>FA-11825</t>
+    <t>FA-11766</t>
   </si>
   <si>
     <t>FA-11853</t>
   </si>
   <si>
-    <t>FA-11766</t>
-  </si>
-  <si>
     <t>FA-11828</t>
   </si>
   <si>
     <t>FA-11606</t>
   </si>
   <si>
+    <t>FA-11637</t>
+  </si>
+  <si>
     <t>FA-11596</t>
-  </si>
-  <si>
-    <t>FA-11637</t>
   </si>
   <si>
     <t>FA-11649</t>
@@ -747,7 +741,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S133"/>
+  <dimension ref="A1:S132"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -864,10 +858,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-64</v>
+        <v>-65</v>
       </c>
       <c r="G6" s="8">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -923,10 +917,10 @@
         <v>46097</v>
       </c>
       <c r="F7" s="8">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="G7" s="8">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>24</v>
@@ -982,10 +976,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-57</v>
+        <v>-58</v>
       </c>
       <c r="G8" s="8">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -1041,10 +1035,10 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-78</v>
+        <v>-79</v>
       </c>
       <c r="G9" s="8">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>24</v>
@@ -1100,10 +1094,10 @@
         <v>23</v>
       </c>
       <c r="F10" s="8">
-        <v>-64</v>
+        <v>-65</v>
       </c>
       <c r="G10" s="8">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>24</v>
@@ -1159,10 +1153,10 @@
         <v>46097</v>
       </c>
       <c r="F11" s="8">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="G11" s="8">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>24</v>
@@ -1218,10 +1212,10 @@
         <v>46097</v>
       </c>
       <c r="F12" s="8">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="G12" s="8">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>24</v>
@@ -1277,10 +1271,10 @@
         <v>46141</v>
       </c>
       <c r="F13" s="8">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="G13" s="8">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>24</v>
@@ -1336,10 +1330,10 @@
         <v>46097</v>
       </c>
       <c r="F14" s="8">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="G14" s="8">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>37</v>
@@ -1395,10 +1389,10 @@
         <v>46141</v>
       </c>
       <c r="F15" s="8">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="G15" s="8">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>37</v>
@@ -1454,10 +1448,10 @@
         <v>23</v>
       </c>
       <c r="F16" s="8">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="G16" s="8">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>24</v>
@@ -1513,10 +1507,10 @@
         <v>46097</v>
       </c>
       <c r="F17" s="8">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="G17" s="8">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>37</v>
@@ -1572,10 +1566,10 @@
         <v>46141</v>
       </c>
       <c r="F18" s="8">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="G18" s="8">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>37</v>
@@ -1631,10 +1625,10 @@
         <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="G19" s="8">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>37</v>
@@ -1690,10 +1684,10 @@
         <v>46097</v>
       </c>
       <c r="F20" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G20" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>37</v>
@@ -1749,10 +1743,10 @@
         <v>46141</v>
       </c>
       <c r="F21" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G21" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>37</v>
@@ -1804,14 +1798,14 @@
       <c r="D22" s="7">
         <v>46174</v>
       </c>
-      <c r="E22" s="7">
-        <v>46168</v>
+      <c r="E22" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F22" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G22" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>37</v>
@@ -1841,13 +1835,13 @@
         <v>23</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="S22" s="9">
-        <v>650</v>
+        <v>550</v>
       </c>
     </row>
     <row r="23">
@@ -1867,10 +1861,10 @@
         <v>46167</v>
       </c>
       <c r="F23" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G23" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>37</v>
@@ -1926,10 +1920,10 @@
         <v>46097</v>
       </c>
       <c r="F24" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G24" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>37</v>
@@ -1985,10 +1979,10 @@
         <v>46141</v>
       </c>
       <c r="F25" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G25" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>37</v>
@@ -2044,10 +2038,10 @@
         <v>46170</v>
       </c>
       <c r="F26" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G26" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>37</v>
@@ -2100,13 +2094,13 @@
         <v>46181</v>
       </c>
       <c r="E27" s="7">
-        <v>46188</v>
+        <v>46170</v>
       </c>
       <c r="F27" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G27" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>37</v>
@@ -2121,10 +2115,10 @@
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="N27" s="6" t="s">
         <v>27</v>
@@ -2139,7 +2133,7 @@
         <v>35</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S27" s="9">
         <v>650</v>
@@ -2159,13 +2153,13 @@
         <v>46181</v>
       </c>
       <c r="E28" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F28" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G28" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>37</v>
@@ -2174,16 +2168,16 @@
         <v>37</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>27</v>
@@ -2198,7 +2192,7 @@
         <v>35</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S28" s="9">
         <v>650</v>
@@ -2221,10 +2215,10 @@
         <v>46182</v>
       </c>
       <c r="F29" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G29" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>37</v>
@@ -2280,10 +2274,10 @@
         <v>46182</v>
       </c>
       <c r="F30" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G30" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>37</v>
@@ -2339,10 +2333,10 @@
         <v>46167</v>
       </c>
       <c r="F31" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G31" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>37</v>
@@ -2398,10 +2392,10 @@
         <v>46170</v>
       </c>
       <c r="F32" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G32" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>37</v>
@@ -2457,10 +2451,10 @@
         <v>46170</v>
       </c>
       <c r="F33" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G33" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>37</v>
@@ -2516,10 +2510,10 @@
         <v>23</v>
       </c>
       <c r="F34" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G34" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>37</v>
@@ -2575,10 +2569,10 @@
         <v>23</v>
       </c>
       <c r="F35" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G35" s="8">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>37</v>
@@ -2634,10 +2628,10 @@
         <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G36" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>37</v>
@@ -2693,10 +2687,10 @@
         <v>46153</v>
       </c>
       <c r="F37" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G37" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>37</v>
@@ -2752,10 +2746,10 @@
         <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G38" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>37</v>
@@ -2811,10 +2805,10 @@
         <v>46167</v>
       </c>
       <c r="F39" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G39" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>37</v>
@@ -2870,10 +2864,10 @@
         <v>23</v>
       </c>
       <c r="F40" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G40" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>37</v>
@@ -2929,10 +2923,10 @@
         <v>46097</v>
       </c>
       <c r="F41" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G41" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>37</v>
@@ -2988,10 +2982,10 @@
         <v>23</v>
       </c>
       <c r="F42" s="8">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="G42" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>37</v>
@@ -3047,10 +3041,10 @@
         <v>23</v>
       </c>
       <c r="F43" s="8">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="G43" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>37</v>
@@ -3097,19 +3091,19 @@
         <v>46188</v>
       </c>
       <c r="C44" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="D44" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F44" s="8">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="G44" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>37</v>
@@ -3142,10 +3136,10 @@
         <v>23</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S44" s="9">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row r="45">
@@ -3156,19 +3150,19 @@
         <v>46188</v>
       </c>
       <c r="C45" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D45" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F45" s="8">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="G45" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>37</v>
@@ -3183,10 +3177,10 @@
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="N45" s="6" t="s">
         <v>27</v>
@@ -3201,10 +3195,10 @@
         <v>23</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S45" s="9">
-        <v>279.12</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46">
@@ -3215,19 +3209,19 @@
         <v>46188</v>
       </c>
       <c r="C46" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="D46" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F46" s="8">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="G46" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>37</v>
@@ -3236,16 +3230,16 @@
         <v>37</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>27</v>
@@ -3260,10 +3254,10 @@
         <v>23</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S46" s="9">
-        <v>310</v>
+        <v>279.12</v>
       </c>
     </row>
     <row r="47">
@@ -3274,19 +3268,19 @@
         <v>46188</v>
       </c>
       <c r="C47" s="7">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="D47" s="7">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F47" s="8">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="G47" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>37</v>
@@ -3319,10 +3313,10 @@
         <v>23</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S47" s="9">
-        <v>330</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48">
@@ -3333,19 +3327,19 @@
         <v>46188</v>
       </c>
       <c r="C48" s="7">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="D48" s="7">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F48" s="8">
-        <v>-15</v>
+        <v>-2</v>
       </c>
       <c r="G48" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>37</v>
@@ -3360,7 +3354,7 @@
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>23</v>
@@ -3381,7 +3375,7 @@
         <v>36</v>
       </c>
       <c r="S48" s="9">
-        <v>410.54</v>
+        <v>330</v>
       </c>
     </row>
     <row r="49">
@@ -3392,19 +3386,19 @@
         <v>46188</v>
       </c>
       <c r="C49" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D49" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E49" s="7">
-        <v>46170</v>
+        <v>46174</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F49" s="8">
-        <v>-1</v>
+        <v>-16</v>
       </c>
       <c r="G49" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>37</v>
@@ -3413,16 +3407,16 @@
         <v>37</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="N49" s="6" t="s">
         <v>27</v>
@@ -3434,13 +3428,13 @@
         <v>23</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S49" s="9">
-        <v>600</v>
+        <v>410.54</v>
       </c>
     </row>
     <row r="50">
@@ -3457,13 +3451,13 @@
         <v>46188</v>
       </c>
       <c r="E50" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="F50" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G50" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>37</v>
@@ -3472,16 +3466,16 @@
         <v>37</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="N50" s="6" t="s">
         <v>27</v>
@@ -3499,7 +3493,7 @@
         <v>36</v>
       </c>
       <c r="S50" s="9">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="51">
@@ -3519,10 +3513,10 @@
         <v>46141</v>
       </c>
       <c r="F51" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G51" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>37</v>
@@ -3531,16 +3525,16 @@
         <v>37</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="N51" s="6" t="s">
         <v>27</v>
@@ -3575,13 +3569,13 @@
         <v>46188</v>
       </c>
       <c r="E52" s="7">
-        <v>46169</v>
+        <v>46141</v>
       </c>
       <c r="F52" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G52" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>37</v>
@@ -3590,16 +3584,16 @@
         <v>37</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="N52" s="6" t="s">
         <v>27</v>
@@ -3617,7 +3611,7 @@
         <v>36</v>
       </c>
       <c r="S52" s="9">
-        <v>630</v>
+        <v>620</v>
       </c>
     </row>
     <row r="53">
@@ -3634,13 +3628,13 @@
         <v>46188</v>
       </c>
       <c r="E53" s="7">
-        <v>46163</v>
+        <v>46169</v>
       </c>
       <c r="F53" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G53" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>37</v>
@@ -3696,10 +3690,10 @@
         <v>46170</v>
       </c>
       <c r="F54" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G54" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>37</v>
@@ -3755,10 +3749,10 @@
         <v>46164</v>
       </c>
       <c r="F55" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G55" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>37</v>
@@ -3814,10 +3808,10 @@
         <v>46153</v>
       </c>
       <c r="F56" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G56" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>37</v>
@@ -3873,10 +3867,10 @@
         <v>46188</v>
       </c>
       <c r="F57" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G57" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>37</v>
@@ -3932,10 +3926,10 @@
         <v>46170</v>
       </c>
       <c r="F58" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G58" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>37</v>
@@ -3950,10 +3944,10 @@
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N58" s="6" t="s">
         <v>27</v>
@@ -3991,10 +3985,10 @@
         <v>46164</v>
       </c>
       <c r="F59" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G59" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>37</v>
@@ -4009,7 +4003,7 @@
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>23</v>
@@ -4050,10 +4044,10 @@
         <v>46182</v>
       </c>
       <c r="F60" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G60" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>37</v>
@@ -4068,7 +4062,7 @@
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>23</v>
@@ -4109,10 +4103,10 @@
         <v>46182</v>
       </c>
       <c r="F61" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G61" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>37</v>
@@ -4127,7 +4121,7 @@
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>23</v>
@@ -4168,10 +4162,10 @@
         <v>46141</v>
       </c>
       <c r="F62" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G62" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>37</v>
@@ -4227,10 +4221,10 @@
         <v>46167</v>
       </c>
       <c r="F63" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G63" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>37</v>
@@ -4283,13 +4277,13 @@
         <v>46188</v>
       </c>
       <c r="E64" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F64" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G64" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>37</v>
@@ -4304,7 +4298,7 @@
         <v>23</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>23</v>
@@ -4322,7 +4316,7 @@
         <v>35</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S64" s="9">
         <v>700</v>
@@ -4342,13 +4336,13 @@
         <v>46188</v>
       </c>
       <c r="E65" s="7">
-        <v>46188</v>
+        <v>46170</v>
       </c>
       <c r="F65" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G65" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>37</v>
@@ -4357,13 +4351,13 @@
         <v>37</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="M65" s="6" t="s">
         <v>23</v>
@@ -4375,13 +4369,13 @@
         <v>27</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q65" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S65" s="9">
         <v>700</v>
@@ -4389,7 +4383,7 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="B66" s="7">
         <v>46188</v>
@@ -4401,13 +4395,13 @@
         <v>46188</v>
       </c>
       <c r="E66" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F66" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="G66" s="8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>37</v>
@@ -4422,7 +4416,7 @@
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="M66" s="6" t="s">
         <v>23</v>
@@ -4434,33 +4428,33 @@
         <v>27</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q66" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="S66" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="B67" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C67" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D67" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="E67" s="7">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="F67" s="8">
         <v>-1</v>
@@ -4475,34 +4469,34 @@
         <v>37</v>
       </c>
       <c r="J67" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="K67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N67" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O67" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P67" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q67" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="R67" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="K67" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L67" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="M67" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N67" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O67" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P67" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q67" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R67" s="6" t="s">
-        <v>111</v>
-      </c>
       <c r="S67" s="9">
-        <v>800</v>
+        <v>170.96</v>
       </c>
     </row>
     <row r="68">
@@ -4522,16 +4516,16 @@
         <v>46185</v>
       </c>
       <c r="F68" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G68" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J68" s="6" t="s">
         <v>112</v>
@@ -4546,10 +4540,10 @@
         <v>23</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
@@ -4558,10 +4552,10 @@
         <v>29</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="S68" s="9">
-        <v>170.96</v>
+        <v>250</v>
       </c>
     </row>
     <row r="69">
@@ -4572,25 +4566,25 @@
         <v>46189</v>
       </c>
       <c r="C69" s="7">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="D69" s="7">
-        <v>46189</v>
-      </c>
-      <c r="E69" s="7">
-        <v>46185</v>
+        <v>46188</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F69" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G69" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J69" s="6" t="s">
         <v>115</v>
@@ -4605,22 +4599,22 @@
         <v>23</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q69" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="S69" s="9">
-        <v>250</v>
+        <v>500.78</v>
       </c>
     </row>
     <row r="70">
@@ -4628,58 +4622,58 @@
         <v>22</v>
       </c>
       <c r="B70" s="7">
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="C70" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D70" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>23</v>
+        <v>46192</v>
+      </c>
+      <c r="E70" s="7">
+        <v>46185</v>
       </c>
       <c r="F70" s="8">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G70" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J70" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="K70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="K70" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L70" s="6" t="s">
-        <v>119</v>
-      </c>
       <c r="M70" s="6" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>27</v>
+        <v>119</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q70" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S70" s="9">
-        <v>500.78</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="71">
@@ -4687,22 +4681,22 @@
         <v>22</v>
       </c>
       <c r="B71" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C71" s="7">
         <v>46143</v>
       </c>
       <c r="D71" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="E71" s="7">
-        <v>46185</v>
+        <v>46153</v>
       </c>
       <c r="F71" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G71" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4711,34 +4705,34 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q71" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S71" s="9">
-        <v>2100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72">
@@ -4755,13 +4749,13 @@
         <v>46195</v>
       </c>
       <c r="E72" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="F72" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G72" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4770,25 +4764,25 @@
         <v>23</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q72" s="6" t="s">
         <v>29</v>
@@ -4797,7 +4791,7 @@
         <v>36</v>
       </c>
       <c r="S72" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73">
@@ -4808,19 +4802,19 @@
         <v>46195</v>
       </c>
       <c r="C73" s="7">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="D73" s="7">
         <v>46195</v>
       </c>
       <c r="E73" s="7">
-        <v>46167</v>
+        <v>46097</v>
       </c>
       <c r="F73" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G73" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4829,22 +4823,22 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4853,10 +4847,10 @@
         <v>29</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S73" s="9">
-        <v>100</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="74">
@@ -4867,19 +4861,19 @@
         <v>46195</v>
       </c>
       <c r="C74" s="7">
-        <v>46082</v>
+        <v>46195</v>
       </c>
       <c r="D74" s="7">
         <v>46195</v>
       </c>
       <c r="E74" s="7">
-        <v>46097</v>
+        <v>46169</v>
       </c>
       <c r="F74" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G74" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4888,34 +4882,34 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q74" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S74" s="9">
-        <v>146.55</v>
+        <v>600</v>
       </c>
     </row>
     <row r="75">
@@ -4932,13 +4926,13 @@
         <v>46195</v>
       </c>
       <c r="E75" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F75" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G75" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>23</v>
@@ -4947,22 +4941,22 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>23</v>
@@ -4991,13 +4985,13 @@
         <v>46195</v>
       </c>
       <c r="E76" s="7">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="F76" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G76" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -5006,22 +5000,22 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -5050,13 +5044,13 @@
         <v>46195</v>
       </c>
       <c r="E77" s="7">
-        <v>46169</v>
+        <v>46176</v>
       </c>
       <c r="F77" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G77" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -5065,22 +5059,22 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -5089,10 +5083,10 @@
         <v>35</v>
       </c>
       <c r="R77" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S77" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="78">
@@ -5109,13 +5103,13 @@
         <v>46195</v>
       </c>
       <c r="E78" s="7">
-        <v>46176</v>
+        <v>46169</v>
       </c>
       <c r="F78" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G78" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -5124,22 +5118,22 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>70</v>
+        <v>127</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>23</v>
@@ -5148,10 +5142,10 @@
         <v>35</v>
       </c>
       <c r="R78" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S78" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="79">
@@ -5171,10 +5165,10 @@
         <v>46169</v>
       </c>
       <c r="F79" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G79" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>23</v>
@@ -5183,22 +5177,22 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="K79" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="K79" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L79" s="6" t="s">
-        <v>130</v>
-      </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
@@ -5230,10 +5224,10 @@
         <v>46169</v>
       </c>
       <c r="F80" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G80" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>23</v>
@@ -5242,22 +5236,22 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
@@ -5286,13 +5280,13 @@
         <v>46195</v>
       </c>
       <c r="E81" s="7">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="F81" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G81" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>23</v>
@@ -5301,22 +5295,22 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>23</v>
@@ -5345,13 +5339,13 @@
         <v>46195</v>
       </c>
       <c r="E82" s="7">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="F82" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G82" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>23</v>
@@ -5360,25 +5354,25 @@
         <v>23</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q82" s="6" t="s">
         <v>35</v>
@@ -5407,10 +5401,10 @@
         <v>46170</v>
       </c>
       <c r="F83" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G83" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>23</v>
@@ -5419,25 +5413,25 @@
         <v>23</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q83" s="6" t="s">
         <v>35</v>
@@ -5463,13 +5457,13 @@
         <v>46195</v>
       </c>
       <c r="E84" s="7">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="F84" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G84" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>23</v>
@@ -5478,22 +5472,22 @@
         <v>23</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="M84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>23</v>
@@ -5522,13 +5516,13 @@
         <v>46195</v>
       </c>
       <c r="E85" s="7">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="F85" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G85" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>23</v>
@@ -5537,22 +5531,22 @@
         <v>23</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="M85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P85" s="6" t="s">
         <v>23</v>
@@ -5564,7 +5558,7 @@
         <v>36</v>
       </c>
       <c r="S85" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="86">
@@ -5581,13 +5575,13 @@
         <v>46195</v>
       </c>
       <c r="E86" s="7">
-        <v>46170</v>
+        <v>46127</v>
       </c>
       <c r="F86" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G86" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>23</v>
@@ -5596,22 +5590,22 @@
         <v>23</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>23</v>
@@ -5643,10 +5637,10 @@
         <v>46153</v>
       </c>
       <c r="F87" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G87" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H87" s="6" t="s">
         <v>23</v>
@@ -5655,7 +5649,7 @@
         <v>23</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K87" s="6" t="s">
         <v>23</v>
@@ -5667,10 +5661,10 @@
         <v>23</v>
       </c>
       <c r="N87" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P87" s="6" t="s">
         <v>23</v>
@@ -5699,13 +5693,13 @@
         <v>46195</v>
       </c>
       <c r="E88" s="7">
-        <v>46127</v>
+        <v>46160</v>
       </c>
       <c r="F88" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G88" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>23</v>
@@ -5714,22 +5708,22 @@
         <v>23</v>
       </c>
       <c r="J88" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="K88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="M88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>23</v>
@@ -5758,13 +5752,13 @@
         <v>46195</v>
       </c>
       <c r="E89" s="7">
-        <v>46160</v>
+        <v>46188</v>
       </c>
       <c r="F89" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G89" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>23</v>
@@ -5773,22 +5767,22 @@
         <v>23</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="M89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N89" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O89" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P89" s="6" t="s">
         <v>23</v>
@@ -5797,7 +5791,7 @@
         <v>35</v>
       </c>
       <c r="R89" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S89" s="9">
         <v>650</v>
@@ -5817,13 +5811,13 @@
         <v>46195</v>
       </c>
       <c r="E90" s="7">
-        <v>46188</v>
+        <v>46119</v>
       </c>
       <c r="F90" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G90" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>23</v>
@@ -5832,22 +5826,22 @@
         <v>23</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>44</v>
+        <v>143</v>
       </c>
       <c r="M90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>23</v>
@@ -5856,10 +5850,10 @@
         <v>35</v>
       </c>
       <c r="R90" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S90" s="9">
-        <v>650</v>
+        <v>670</v>
       </c>
     </row>
     <row r="91">
@@ -5876,13 +5870,13 @@
         <v>46195</v>
       </c>
       <c r="E91" s="7">
-        <v>46119</v>
+        <v>46176</v>
       </c>
       <c r="F91" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G91" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>23</v>
@@ -5891,22 +5885,22 @@
         <v>23</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>146</v>
+        <v>66</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N91" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O91" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P91" s="6" t="s">
         <v>23</v>
@@ -5918,7 +5912,7 @@
         <v>36</v>
       </c>
       <c r="S91" s="9">
-        <v>670</v>
+        <v>680</v>
       </c>
     </row>
     <row r="92">
@@ -5935,13 +5929,13 @@
         <v>46195</v>
       </c>
       <c r="E92" s="7">
-        <v>46167</v>
+        <v>46182</v>
       </c>
       <c r="F92" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G92" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>23</v>
@@ -5950,22 +5944,22 @@
         <v>23</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="M92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>23</v>
@@ -5994,13 +5988,13 @@
         <v>46195</v>
       </c>
       <c r="E93" s="7">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="F93" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G93" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>23</v>
@@ -6009,22 +6003,22 @@
         <v>23</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="M93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N93" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O93" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P93" s="6" t="s">
         <v>23</v>
@@ -6053,13 +6047,13 @@
         <v>46195</v>
       </c>
       <c r="E94" s="7">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="F94" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G94" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>23</v>
@@ -6068,22 +6062,22 @@
         <v>23</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>150</v>
+        <v>57</v>
       </c>
       <c r="M94" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>23</v>
@@ -6115,10 +6109,10 @@
         <v>46164</v>
       </c>
       <c r="F95" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G95" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>23</v>
@@ -6127,22 +6121,22 @@
         <v>23</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N95" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O95" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P95" s="6" t="s">
         <v>23</v>
@@ -6174,10 +6168,10 @@
         <v>46182</v>
       </c>
       <c r="F96" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G96" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>23</v>
@@ -6186,7 +6180,7 @@
         <v>23</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>23</v>
@@ -6198,10 +6192,10 @@
         <v>23</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>23</v>
@@ -6230,13 +6224,13 @@
         <v>46195</v>
       </c>
       <c r="E97" s="7">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="F97" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G97" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H97" s="6" t="s">
         <v>23</v>
@@ -6245,25 +6239,25 @@
         <v>23</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="M97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N97" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O97" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q97" s="6" t="s">
         <v>35</v>
@@ -6272,7 +6266,7 @@
         <v>36</v>
       </c>
       <c r="S97" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="98">
@@ -6289,13 +6283,13 @@
         <v>46195</v>
       </c>
       <c r="E98" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F98" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G98" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>23</v>
@@ -6304,31 +6298,31 @@
         <v>23</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="M98" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q98" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R98" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S98" s="9">
         <v>700</v>
@@ -6348,13 +6342,13 @@
         <v>46195</v>
       </c>
       <c r="E99" s="7">
-        <v>46188</v>
+        <v>46170</v>
       </c>
       <c r="F99" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G99" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>23</v>
@@ -6363,22 +6357,22 @@
         <v>23</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="M99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N99" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O99" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P99" s="6" t="s">
         <v>23</v>
@@ -6387,7 +6381,7 @@
         <v>35</v>
       </c>
       <c r="R99" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S99" s="9">
         <v>700</v>
@@ -6395,7 +6389,7 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="B100" s="7">
         <v>46195</v>
@@ -6407,13 +6401,13 @@
         <v>46195</v>
       </c>
       <c r="E100" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F100" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G100" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H100" s="6" t="s">
         <v>23</v>
@@ -6422,22 +6416,22 @@
         <v>23</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>23</v>
@@ -6446,15 +6440,15 @@
         <v>35</v>
       </c>
       <c r="R100" s="6" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="S100" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="B101" s="7">
         <v>46195</v>
@@ -6466,13 +6460,13 @@
         <v>46195</v>
       </c>
       <c r="E101" s="7">
-        <v>46182</v>
+        <v>46148</v>
       </c>
       <c r="F101" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G101" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H101" s="6" t="s">
         <v>23</v>
@@ -6481,22 +6475,22 @@
         <v>23</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N101" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O101" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P101" s="6" t="s">
         <v>23</v>
@@ -6505,7 +6499,7 @@
         <v>35</v>
       </c>
       <c r="R101" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="S101" s="9">
         <v>800</v>
@@ -6525,13 +6519,13 @@
         <v>46195</v>
       </c>
       <c r="E102" s="7">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="F102" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G102" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H102" s="6" t="s">
         <v>23</v>
@@ -6540,34 +6534,34 @@
         <v>23</v>
       </c>
       <c r="J102" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="K102" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L102" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="K102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L102" s="6" t="s">
-        <v>113</v>
-      </c>
       <c r="M102" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>23</v>
+        <v>159</v>
       </c>
       <c r="Q102" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R102" s="6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="S102" s="9">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="103">
@@ -6587,10 +6581,10 @@
         <v>46148</v>
       </c>
       <c r="F103" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G103" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H103" s="6" t="s">
         <v>23</v>
@@ -6599,22 +6593,22 @@
         <v>23</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K103" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M103" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N103" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O103" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P103" s="6" t="s">
         <v>23</v>
@@ -6623,7 +6617,7 @@
         <v>35</v>
       </c>
       <c r="R103" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="S103" s="9">
         <v>1200</v>
@@ -6646,10 +6640,10 @@
         <v>46160</v>
       </c>
       <c r="F104" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G104" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>23</v>
@@ -6658,31 +6652,31 @@
         <v>23</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M104" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q104" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R104" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="S104" s="9">
         <v>1200</v>
@@ -6693,22 +6687,22 @@
         <v>22</v>
       </c>
       <c r="B105" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="C105" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D105" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="E105" s="7">
-        <v>46160</v>
+        <v>46185</v>
       </c>
       <c r="F105" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G105" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>23</v>
@@ -6726,25 +6720,25 @@
         <v>164</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>23</v>
+        <v>165</v>
       </c>
       <c r="N105" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O105" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P105" s="6" t="s">
-        <v>162</v>
+        <v>23</v>
       </c>
       <c r="Q105" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R105" s="6" t="s">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="S105" s="9">
-        <v>1200</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="106">
@@ -6752,22 +6746,22 @@
         <v>22</v>
       </c>
       <c r="B106" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="C106" s="7">
         <v>46143</v>
       </c>
       <c r="D106" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="E106" s="7">
-        <v>46185</v>
+        <v>46153</v>
       </c>
       <c r="F106" s="8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G106" s="8">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>23</v>
@@ -6776,34 +6770,34 @@
         <v>23</v>
       </c>
       <c r="J106" s="6" t="s">
-        <v>165</v>
+        <v>67</v>
       </c>
       <c r="K106" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>166</v>
+        <v>68</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>167</v>
+        <v>23</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q106" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R106" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S106" s="9">
-        <v>4400</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107">
@@ -6820,13 +6814,13 @@
         <v>46202</v>
       </c>
       <c r="E107" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="F107" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G107" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>23</v>
@@ -6835,25 +6829,25 @@
         <v>23</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="K107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="M107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N107" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O107" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P107" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q107" s="6" t="s">
         <v>29</v>
@@ -6862,7 +6856,7 @@
         <v>36</v>
       </c>
       <c r="S107" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108">
@@ -6873,19 +6867,19 @@
         <v>46202</v>
       </c>
       <c r="C108" s="7">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="D108" s="7">
         <v>46202</v>
       </c>
       <c r="E108" s="7">
-        <v>46167</v>
+        <v>46097</v>
       </c>
       <c r="F108" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G108" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H108" s="6" t="s">
         <v>23</v>
@@ -6894,22 +6888,22 @@
         <v>23</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="M108" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>23</v>
@@ -6918,10 +6912,10 @@
         <v>29</v>
       </c>
       <c r="R108" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S108" s="9">
-        <v>100</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="109">
@@ -6932,19 +6926,19 @@
         <v>46202</v>
       </c>
       <c r="C109" s="7">
-        <v>46082</v>
+        <v>46202</v>
       </c>
       <c r="D109" s="7">
         <v>46202</v>
       </c>
       <c r="E109" s="7">
-        <v>46097</v>
+        <v>46169</v>
       </c>
       <c r="F109" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G109" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>23</v>
@@ -6953,34 +6947,34 @@
         <v>23</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>25</v>
+        <v>166</v>
       </c>
       <c r="K109" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="M109" s="6" t="s">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="N109" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O109" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P109" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q109" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R109" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S109" s="9">
-        <v>146.55</v>
+        <v>600</v>
       </c>
     </row>
     <row r="110">
@@ -7000,10 +6994,10 @@
         <v>46169</v>
       </c>
       <c r="F110" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G110" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>23</v>
@@ -7012,7 +7006,7 @@
         <v>23</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>23</v>
@@ -7024,10 +7018,10 @@
         <v>124</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>23</v>
@@ -7056,13 +7050,13 @@
         <v>46202</v>
       </c>
       <c r="E111" s="7">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="F111" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G111" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>23</v>
@@ -7071,22 +7065,22 @@
         <v>23</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K111" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="M111" s="6" t="s">
-        <v>127</v>
+        <v>23</v>
       </c>
       <c r="N111" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O111" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P111" s="6" t="s">
         <v>23</v>
@@ -7098,7 +7092,7 @@
         <v>36</v>
       </c>
       <c r="S111" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="112">
@@ -7115,13 +7109,13 @@
         <v>46202</v>
       </c>
       <c r="E112" s="7">
-        <v>46163</v>
+        <v>46169</v>
       </c>
       <c r="F112" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G112" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H112" s="6" t="s">
         <v>23</v>
@@ -7130,22 +7124,22 @@
         <v>23</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K112" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L112" s="6" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="M112" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>23</v>
@@ -7177,10 +7171,10 @@
         <v>46169</v>
       </c>
       <c r="F113" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G113" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>23</v>
@@ -7189,22 +7183,22 @@
         <v>23</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="M113" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N113" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O113" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P113" s="6" t="s">
         <v>23</v>
@@ -7236,10 +7230,10 @@
         <v>46169</v>
       </c>
       <c r="F114" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G114" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H114" s="6" t="s">
         <v>23</v>
@@ -7248,22 +7242,22 @@
         <v>23</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K114" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="M114" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>23</v>
@@ -7292,13 +7286,13 @@
         <v>46202</v>
       </c>
       <c r="E115" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F115" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G115" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H115" s="6" t="s">
         <v>23</v>
@@ -7307,22 +7301,22 @@
         <v>23</v>
       </c>
       <c r="J115" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K115" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="M115" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N115" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O115" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P115" s="6" t="s">
         <v>23</v>
@@ -7351,13 +7345,13 @@
         <v>46202</v>
       </c>
       <c r="E116" s="7">
-        <v>46164</v>
+        <v>46127</v>
       </c>
       <c r="F116" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G116" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H116" s="6" t="s">
         <v>23</v>
@@ -7366,22 +7360,22 @@
         <v>23</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K116" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L116" s="6" t="s">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="M116" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>23</v>
@@ -7393,7 +7387,7 @@
         <v>36</v>
       </c>
       <c r="S116" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="117">
@@ -7410,13 +7404,13 @@
         <v>46202</v>
       </c>
       <c r="E117" s="7">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="F117" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G117" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H117" s="6" t="s">
         <v>23</v>
@@ -7425,22 +7419,22 @@
         <v>23</v>
       </c>
       <c r="J117" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K117" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L117" s="6" t="s">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="M117" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N117" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O117" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P117" s="6" t="s">
         <v>23</v>
@@ -7469,13 +7463,13 @@
         <v>46202</v>
       </c>
       <c r="E118" s="7">
-        <v>46127</v>
+        <v>46160</v>
       </c>
       <c r="F118" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G118" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H118" s="6" t="s">
         <v>23</v>
@@ -7484,22 +7478,22 @@
         <v>23</v>
       </c>
       <c r="J118" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K118" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L118" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M118" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>23</v>
@@ -7528,13 +7522,13 @@
         <v>46202</v>
       </c>
       <c r="E119" s="7">
-        <v>46153</v>
+        <v>46188</v>
       </c>
       <c r="F119" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G119" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H119" s="6" t="s">
         <v>23</v>
@@ -7543,22 +7537,22 @@
         <v>23</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K119" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L119" s="6" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="M119" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N119" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O119" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P119" s="6" t="s">
         <v>23</v>
@@ -7567,7 +7561,7 @@
         <v>35</v>
       </c>
       <c r="R119" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S119" s="9">
         <v>650</v>
@@ -7587,13 +7581,13 @@
         <v>46202</v>
       </c>
       <c r="E120" s="7">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="F120" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G120" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H120" s="6" t="s">
         <v>23</v>
@@ -7602,22 +7596,22 @@
         <v>23</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L120" s="6" t="s">
-        <v>44</v>
+        <v>146</v>
       </c>
       <c r="M120" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>23</v>
@@ -7626,10 +7620,10 @@
         <v>35</v>
       </c>
       <c r="R120" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S120" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="121">
@@ -7649,10 +7643,10 @@
         <v>46164</v>
       </c>
       <c r="F121" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G121" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H121" s="6" t="s">
         <v>23</v>
@@ -7661,22 +7655,22 @@
         <v>23</v>
       </c>
       <c r="J121" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K121" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L121" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M121" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N121" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O121" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P121" s="6" t="s">
         <v>23</v>
@@ -7708,10 +7702,10 @@
         <v>46182</v>
       </c>
       <c r="F122" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G122" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H122" s="6" t="s">
         <v>23</v>
@@ -7720,7 +7714,7 @@
         <v>23</v>
       </c>
       <c r="J122" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K122" s="6" t="s">
         <v>23</v>
@@ -7732,10 +7726,10 @@
         <v>23</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>23</v>
@@ -7767,10 +7761,10 @@
         <v>46182</v>
       </c>
       <c r="F123" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G123" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H123" s="6" t="s">
         <v>23</v>
@@ -7779,7 +7773,7 @@
         <v>23</v>
       </c>
       <c r="J123" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K123" s="6" t="s">
         <v>23</v>
@@ -7791,10 +7785,10 @@
         <v>23</v>
       </c>
       <c r="N123" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O123" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P123" s="6" t="s">
         <v>23</v>
@@ -7826,10 +7820,10 @@
         <v>46167</v>
       </c>
       <c r="F124" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G124" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H124" s="6" t="s">
         <v>23</v>
@@ -7838,7 +7832,7 @@
         <v>23</v>
       </c>
       <c r="J124" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K124" s="6" t="s">
         <v>23</v>
@@ -7850,10 +7844,10 @@
         <v>23</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>23</v>
@@ -7882,13 +7876,13 @@
         <v>46202</v>
       </c>
       <c r="E125" s="7">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="F125" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G125" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H125" s="6" t="s">
         <v>23</v>
@@ -7897,22 +7891,22 @@
         <v>23</v>
       </c>
       <c r="J125" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K125" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L125" s="6" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="M125" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N125" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O125" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P125" s="6" t="s">
         <v>23</v>
@@ -7924,7 +7918,7 @@
         <v>36</v>
       </c>
       <c r="S125" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="126">
@@ -7944,10 +7938,10 @@
         <v>46188</v>
       </c>
       <c r="F126" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G126" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H126" s="6" t="s">
         <v>23</v>
@@ -7956,22 +7950,22 @@
         <v>23</v>
       </c>
       <c r="J126" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K126" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L126" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M126" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>23</v>
@@ -7988,7 +7982,7 @@
     </row>
     <row r="127">
       <c r="A127" s="6" t="s">
-        <v>22</v>
+        <v>106</v>
       </c>
       <c r="B127" s="7">
         <v>46202</v>
@@ -8000,13 +7994,13 @@
         <v>46202</v>
       </c>
       <c r="E127" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F127" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G127" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H127" s="6" t="s">
         <v>23</v>
@@ -8015,22 +8009,22 @@
         <v>23</v>
       </c>
       <c r="J127" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K127" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L127" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M127" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N127" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O127" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P127" s="6" t="s">
         <v>23</v>
@@ -8039,15 +8033,15 @@
         <v>35</v>
       </c>
       <c r="R127" s="6" t="s">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="S127" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="s">
-        <v>108</v>
+        <v>22</v>
       </c>
       <c r="B128" s="7">
         <v>46202</v>
@@ -8059,13 +8053,13 @@
         <v>46202</v>
       </c>
       <c r="E128" s="7">
-        <v>46182</v>
+        <v>46148</v>
       </c>
       <c r="F128" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G128" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H128" s="6" t="s">
         <v>23</v>
@@ -8074,22 +8068,22 @@
         <v>23</v>
       </c>
       <c r="J128" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K128" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L128" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M128" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P128" s="6" t="s">
         <v>23</v>
@@ -8098,7 +8092,7 @@
         <v>35</v>
       </c>
       <c r="R128" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="S128" s="9">
         <v>800</v>
@@ -8118,13 +8112,13 @@
         <v>46202</v>
       </c>
       <c r="E129" s="7">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="F129" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G129" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H129" s="6" t="s">
         <v>23</v>
@@ -8133,34 +8127,34 @@
         <v>23</v>
       </c>
       <c r="J129" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K129" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L129" s="6" t="s">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="M129" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N129" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O129" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P129" s="6" t="s">
-        <v>23</v>
+        <v>159</v>
       </c>
       <c r="Q129" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R129" s="6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="S129" s="9">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="130">
@@ -8180,10 +8174,10 @@
         <v>46148</v>
       </c>
       <c r="F130" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G130" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H130" s="6" t="s">
         <v>23</v>
@@ -8192,22 +8186,22 @@
         <v>23</v>
       </c>
       <c r="J130" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K130" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L130" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M130" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P130" s="6" t="s">
         <v>23</v>
@@ -8216,7 +8210,7 @@
         <v>35</v>
       </c>
       <c r="R130" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="S130" s="9">
         <v>1200</v>
@@ -8239,10 +8233,10 @@
         <v>46160</v>
       </c>
       <c r="F131" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G131" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H131" s="6" t="s">
         <v>23</v>
@@ -8251,116 +8245,57 @@
         <v>23</v>
       </c>
       <c r="J131" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="K131" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L131" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M131" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N131" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O131" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="P131" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="Q131" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R131" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="S131" s="9">
         <v>1200</v>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B132" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C132" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D132" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E132" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F132" s="8">
-        <v>13</v>
-      </c>
-      <c r="G132" s="8">
-        <v>13</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I132" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J132" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="K132" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L132" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="M132" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N132" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="O132" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="P132" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q132" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R132" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="S132" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="133" ht="23" customHeight="1">
-      <c r="A133" s="10"/>
-      <c r="B133" s="11"/>
-      <c r="C133" s="11"/>
-      <c r="D133" s="11"/>
-      <c r="E133" s="11"/>
-      <c r="F133" s="12"/>
-      <c r="G133" s="12"/>
-      <c r="H133" s="10"/>
-      <c r="I133" s="10"/>
-      <c r="J133" s="10"/>
-      <c r="K133" s="10"/>
-      <c r="L133" s="10"/>
-      <c r="M133" s="10"/>
-      <c r="N133" s="10"/>
-      <c r="O133" s="10"/>
-      <c r="P133" s="10"/>
-      <c r="Q133" s="10"/>
-      <c r="R133" s="10"/>
-      <c r="S133" s="13">
-        <f>SUM(S6:S132)</f>
+    <row r="132" ht="23" customHeight="1">
+      <c r="A132" s="10"/>
+      <c r="B132" s="11"/>
+      <c r="C132" s="11"/>
+      <c r="D132" s="11"/>
+      <c r="E132" s="11"/>
+      <c r="F132" s="12"/>
+      <c r="G132" s="12"/>
+      <c r="H132" s="10"/>
+      <c r="I132" s="10"/>
+      <c r="J132" s="10"/>
+      <c r="K132" s="10"/>
+      <c r="L132" s="10"/>
+      <c r="M132" s="10"/>
+      <c r="N132" s="10"/>
+      <c r="O132" s="10"/>
+      <c r="P132" s="10"/>
+      <c r="Q132" s="10"/>
+      <c r="R132" s="10"/>
+      <c r="S132" s="13">
+        <f>SUM(S6:S131)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$132</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$128</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quarta-feira, 17 de junho de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em quinta-feira, 18 de junho de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -145,12 +145,12 @@
     <t>ATIVUZ VEÍCULOS</t>
   </si>
   <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
     <t>VENCIDO ATÉ 30 DIAS</t>
   </si>
   <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
     <t>FA-11553</t>
   </si>
   <si>
@@ -193,345 +193,330 @@
     <t>FA-11847</t>
   </si>
   <si>
-    <t>FA-11815</t>
+    <t>FA-11814</t>
+  </si>
+  <si>
+    <t>FA-11693</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>ND-11801</t>
+  </si>
+  <si>
+    <t>FA-11569</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11810</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>ND-11699</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>FA-11806</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>JOAO PAULO CONSORCIOS</t>
+  </si>
+  <si>
+    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
+  </si>
+  <si>
+    <t>FA-11794</t>
+  </si>
+  <si>
+    <t>FA-11784</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11671</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11774</t>
+  </si>
+  <si>
+    <t>FA-11571</t>
+  </si>
+  <si>
+    <t>FA-11678</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11797</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11772</t>
+  </si>
+  <si>
+    <t>FA-11787</t>
+  </si>
+  <si>
+    <t>FA-11572</t>
+  </si>
+  <si>
+    <t>FA-11724</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11798</t>
+  </si>
+  <si>
+    <t>FA-11686</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
+    <t>FA-11848</t>
+  </si>
+  <si>
+    <t>FA-11776</t>
+  </si>
+  <si>
+    <t>FA-11679</t>
+  </si>
+  <si>
+    <t>FA-11818</t>
   </si>
   <si>
     <t>LEONARDO GOMES DO NASCIMENTO</t>
   </si>
   <si>
-    <t>FA-11814</t>
-  </si>
-  <si>
-    <t>FA-11693</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11782</t>
+    <t>FA-11819</t>
+  </si>
+  <si>
+    <t>FA-11694</t>
+  </si>
+  <si>
+    <t>FA-11573</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>ND-11844</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11756</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11692</t>
+  </si>
+  <si>
+    <t>FA-11785</t>
   </si>
   <si>
     <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
   </si>
   <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>ND-11801</t>
-  </si>
-  <si>
-    <t>FA-11569</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11692</t>
-  </si>
-  <si>
-    <t>FA-11810</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>ND-11699</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11806</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>JOAO PAULO CONSORCIOS</t>
-  </si>
-  <si>
-    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
-  </si>
-  <si>
-    <t>FA-11794</t>
-  </si>
-  <si>
-    <t>FA-11784</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11671</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11846</t>
+    <t>FA-11842</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>ND-11870</t>
+  </si>
+  <si>
+    <t>FA-11730</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11791</t>
+  </si>
+  <si>
+    <t>FA-11749</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11807</t>
+  </si>
+  <si>
+    <t>FA-11672</t>
+  </si>
+  <si>
+    <t>FA-11790</t>
+  </si>
+  <si>
+    <t>FA-11733</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11731</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11728</t>
+  </si>
+  <si>
+    <t>FA-11687</t>
+  </si>
+  <si>
+    <t>FA-11800</t>
+  </si>
+  <si>
+    <t>FA-11799</t>
+  </si>
+  <si>
+    <t>FA-11508</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11625</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11660</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>FA-11850</t>
+  </si>
+  <si>
+    <t>FA-11438</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11695</t>
+  </si>
+  <si>
+    <t>FA-11823</t>
+  </si>
+  <si>
+    <t>FA-11811</t>
+  </si>
+  <si>
+    <t>FA-11821</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11822</t>
+  </si>
+  <si>
+    <t>FA-11680</t>
+  </si>
+  <si>
+    <t>FA-11789</t>
+  </si>
+  <si>
+    <t>FA-11851</t>
   </si>
   <si>
     <t>MAICON LOPES SILVA</t>
   </si>
   <si>
-    <t>FA-11774</t>
-  </si>
-  <si>
-    <t>FA-11678</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11797</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11772</t>
-  </si>
-  <si>
-    <t>FA-11787</t>
-  </si>
-  <si>
-    <t>FA-11571</t>
-  </si>
-  <si>
-    <t>FA-11572</t>
-  </si>
-  <si>
-    <t>FA-11724</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11798</t>
-  </si>
-  <si>
-    <t>FA-11686</t>
-  </si>
-  <si>
-    <t>GILVAN RODRIGUES MACHADO</t>
-  </si>
-  <si>
-    <t>FA-11624</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>FA-11848</t>
-  </si>
-  <si>
-    <t>FA-11776</t>
-  </si>
-  <si>
-    <t>FA-11679</t>
-  </si>
-  <si>
-    <t>FA-11818</t>
-  </si>
-  <si>
-    <t>FA-11819</t>
-  </si>
-  <si>
-    <t>FA-11573</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11694</t>
+    <t>FA-11765</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>FA-11824</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>FA-11605</t>
+  </si>
+  <si>
+    <t>FA-11595</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11648</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>FA-11636</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11843</t>
+  </si>
+  <si>
+    <t>SEGCOMP</t>
+  </si>
+  <si>
+    <t>SEGCOMP TECNOLOGIA LTDA</t>
   </si>
   <si>
     <t>FA-11849</t>
   </si>
   <si>
-    <t>FA-11785</t>
-  </si>
-  <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>FA-11820</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>ND-11844</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>ND-11845</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11756</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11842</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>FA-11730</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11791</t>
-  </si>
-  <si>
-    <t>FA-11749</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11807</t>
-  </si>
-  <si>
-    <t>FA-11733</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11731</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11728</t>
-  </si>
-  <si>
-    <t>FA-11672</t>
-  </si>
-  <si>
-    <t>FA-11790</t>
-  </si>
-  <si>
-    <t>FA-11800</t>
-  </si>
-  <si>
-    <t>FA-11687</t>
-  </si>
-  <si>
-    <t>FA-11799</t>
-  </si>
-  <si>
-    <t>FA-11508</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11625</t>
-  </si>
-  <si>
-    <t>FA-11660</t>
-  </si>
-  <si>
-    <t>LUCA ZOLI</t>
-  </si>
-  <si>
-    <t>FA-11850</t>
-  </si>
-  <si>
-    <t>FA-11438</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11811</t>
-  </si>
-  <si>
-    <t>FA-11821</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11823</t>
-  </si>
-  <si>
-    <t>FA-11695</t>
-  </si>
-  <si>
-    <t>FA-11680</t>
-  </si>
-  <si>
-    <t>FA-11822</t>
-  </si>
-  <si>
-    <t>FA-11789</t>
-  </si>
-  <si>
-    <t>FA-11851</t>
-  </si>
-  <si>
-    <t>FA-11765</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11824</t>
-  </si>
-  <si>
-    <t>FA-11605</t>
-  </si>
-  <si>
-    <t>FA-11636</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-11595</t>
-  </si>
-  <si>
-    <t>FA-11648</t>
-  </si>
-  <si>
-    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11843</t>
-  </si>
-  <si>
-    <t>SEGCOMP</t>
-  </si>
-  <si>
-    <t>SEGCOMP TECNOLOGIA LTDA</t>
-  </si>
-  <si>
     <t>FA-11735</t>
   </si>
   <si>
@@ -544,58 +529,58 @@
     <t>FA-11737</t>
   </si>
   <si>
+    <t>FA-11734</t>
+  </si>
+  <si>
     <t>FA-11732</t>
   </si>
   <si>
-    <t>FA-11734</t>
-  </si>
-  <si>
     <t>FA-11688</t>
   </si>
   <si>
+    <t>FA-11661</t>
+  </si>
+  <si>
+    <t>FA-11626</t>
+  </si>
+  <si>
     <t>FA-11509</t>
   </si>
   <si>
-    <t>FA-11626</t>
-  </si>
-  <si>
-    <t>FA-11661</t>
-  </si>
-  <si>
     <t>FA-11852</t>
   </si>
   <si>
+    <t>FA-11681</t>
+  </si>
+  <si>
+    <t>FA-11826</t>
+  </si>
+  <si>
+    <t>FA-11827</t>
+  </si>
+  <si>
     <t>FA-11825</t>
   </si>
   <si>
-    <t>FA-11681</t>
-  </si>
-  <si>
-    <t>FA-11826</t>
-  </si>
-  <si>
-    <t>FA-11827</t>
-  </si>
-  <si>
     <t>FA-11696</t>
   </si>
   <si>
+    <t>FA-11853</t>
+  </si>
+  <si>
     <t>FA-11766</t>
   </si>
   <si>
-    <t>FA-11853</t>
-  </si>
-  <si>
     <t>FA-11828</t>
   </si>
   <si>
     <t>FA-11606</t>
   </si>
   <si>
+    <t>FA-11596</t>
+  </si>
+  <si>
     <t>FA-11637</t>
-  </si>
-  <si>
-    <t>FA-11596</t>
   </si>
   <si>
     <t>FA-11649</t>
@@ -741,7 +726,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S132"/>
+  <dimension ref="A1:S128"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -858,10 +843,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-65</v>
+        <v>-66</v>
       </c>
       <c r="G6" s="8">
-        <v>-56</v>
+        <v>-57</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -917,10 +902,10 @@
         <v>46097</v>
       </c>
       <c r="F7" s="8">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="G7" s="8">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>24</v>
@@ -976,10 +961,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-58</v>
+        <v>-59</v>
       </c>
       <c r="G8" s="8">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -1035,10 +1020,10 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-79</v>
+        <v>-80</v>
       </c>
       <c r="G9" s="8">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>24</v>
@@ -1094,10 +1079,10 @@
         <v>23</v>
       </c>
       <c r="F10" s="8">
-        <v>-65</v>
+        <v>-66</v>
       </c>
       <c r="G10" s="8">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>24</v>
@@ -1153,10 +1138,10 @@
         <v>46097</v>
       </c>
       <c r="F11" s="8">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="G11" s="8">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>24</v>
@@ -1212,10 +1197,10 @@
         <v>46097</v>
       </c>
       <c r="F12" s="8">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="G12" s="8">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>24</v>
@@ -1271,10 +1256,10 @@
         <v>46141</v>
       </c>
       <c r="F13" s="8">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="G13" s="8">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>24</v>
@@ -1330,16 +1315,16 @@
         <v>46097</v>
       </c>
       <c r="F14" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="G14" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>25</v>
@@ -1389,19 +1374,19 @@
         <v>46141</v>
       </c>
       <c r="F15" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="G15" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="H15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J15" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="K15" s="6" t="s">
         <v>23</v>
@@ -1448,16 +1433,16 @@
         <v>23</v>
       </c>
       <c r="F16" s="8">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="G16" s="8">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>24</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>39</v>
@@ -1507,16 +1492,16 @@
         <v>46097</v>
       </c>
       <c r="F17" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G17" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>25</v>
@@ -1566,16 +1551,16 @@
         <v>46141</v>
       </c>
       <c r="F18" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G18" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>40</v>
@@ -1625,16 +1610,16 @@
         <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="G19" s="8">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>23</v>
@@ -1684,16 +1669,16 @@
         <v>46097</v>
       </c>
       <c r="F20" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G20" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>25</v>
@@ -1743,16 +1728,16 @@
         <v>46141</v>
       </c>
       <c r="F21" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G21" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>42</v>
@@ -1802,16 +1787,16 @@
         <v>23</v>
       </c>
       <c r="F22" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G22" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>43</v>
@@ -1861,16 +1846,16 @@
         <v>46167</v>
       </c>
       <c r="F23" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G23" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>45</v>
@@ -1900,7 +1885,7 @@
         <v>36</v>
       </c>
       <c r="S23" s="9">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
@@ -1920,16 +1905,16 @@
         <v>46097</v>
       </c>
       <c r="F24" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G24" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>25</v>
@@ -1979,16 +1964,16 @@
         <v>46141</v>
       </c>
       <c r="F25" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G25" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>47</v>
@@ -2038,16 +2023,16 @@
         <v>46170</v>
       </c>
       <c r="F26" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G26" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>48</v>
@@ -2097,16 +2082,16 @@
         <v>46170</v>
       </c>
       <c r="F27" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G27" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>50</v>
@@ -2156,16 +2141,16 @@
         <v>46188</v>
       </c>
       <c r="F28" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G28" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>52</v>
@@ -2215,16 +2200,16 @@
         <v>46182</v>
       </c>
       <c r="F29" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G29" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>53</v>
@@ -2233,7 +2218,7 @@
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>23</v>
@@ -2271,28 +2256,28 @@
         <v>46181</v>
       </c>
       <c r="E30" s="7">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="F30" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G30" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J30" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>46</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>23</v>
@@ -2324,25 +2309,25 @@
         <v>46181</v>
       </c>
       <c r="C31" s="7">
-        <v>46181</v>
+        <v>46143</v>
       </c>
       <c r="D31" s="7">
         <v>46181</v>
       </c>
       <c r="E31" s="7">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="F31" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G31" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>56</v>
@@ -2351,7 +2336,7 @@
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>23</v>
@@ -2366,13 +2351,13 @@
         <v>23</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S31" s="9">
-        <v>680</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="32">
@@ -2380,7 +2365,7 @@
         <v>22</v>
       </c>
       <c r="B32" s="7">
-        <v>46181</v>
+        <v>46185</v>
       </c>
       <c r="C32" s="7">
         <v>46181</v>
@@ -2388,32 +2373,32 @@
       <c r="D32" s="7">
         <v>46181</v>
       </c>
-      <c r="E32" s="7">
-        <v>46170</v>
+      <c r="E32" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F32" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G32" s="8">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J32" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="K32" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>59</v>
-      </c>
       <c r="M32" s="6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>27</v>
@@ -2422,16 +2407,16 @@
         <v>27</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S32" s="9">
-        <v>700</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33">
@@ -2439,37 +2424,37 @@
         <v>22</v>
       </c>
       <c r="B33" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="C33" s="7">
-        <v>46143</v>
+        <v>46188</v>
       </c>
       <c r="D33" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E33" s="7">
-        <v>46170</v>
+        <v>46188</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F33" s="8">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="G33" s="8">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>23</v>
@@ -2484,13 +2469,13 @@
         <v>23</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S33" s="9">
-        <v>2969.17</v>
+        <v>38.45</v>
       </c>
     </row>
     <row r="34">
@@ -2498,58 +2483,58 @@
         <v>22</v>
       </c>
       <c r="B34" s="7">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C34" s="7">
-        <v>46181</v>
+        <v>46143</v>
       </c>
       <c r="D34" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>23</v>
+        <v>46188</v>
+      </c>
+      <c r="E34" s="7">
+        <v>46153</v>
       </c>
       <c r="F34" s="8">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="G34" s="8">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J34" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="K34" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L34" s="6" t="s">
+      <c r="M34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N34" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P34" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="M34" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="N34" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O34" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P34" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="Q34" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S34" s="9">
-        <v>220</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
@@ -2557,28 +2542,28 @@
         <v>22</v>
       </c>
       <c r="B35" s="7">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C35" s="7">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="D35" s="7">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F35" s="8">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="G35" s="8">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J35" s="6" t="s">
         <v>64</v>
@@ -2587,10 +2572,10 @@
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="N35" s="6" t="s">
         <v>27</v>
@@ -2605,10 +2590,10 @@
         <v>23</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S35" s="9">
-        <v>360</v>
+        <v>70.07</v>
       </c>
     </row>
     <row r="36">
@@ -2628,19 +2613,19 @@
         <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G36" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
@@ -2649,7 +2634,7 @@
         <v>66</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>27</v>
@@ -2664,10 +2649,10 @@
         <v>23</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="S36" s="9">
-        <v>38.45</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="37">
@@ -2678,34 +2663,34 @@
         <v>46188</v>
       </c>
       <c r="C37" s="7">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="D37" s="7">
         <v>46188</v>
       </c>
       <c r="E37" s="7">
-        <v>46153</v>
+        <v>46097</v>
       </c>
       <c r="F37" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G37" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>23</v>
@@ -2717,16 +2702,16 @@
         <v>27</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q37" s="6" t="s">
         <v>29</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S37" s="9">
-        <v>50</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="38">
@@ -2737,37 +2722,37 @@
         <v>46188</v>
       </c>
       <c r="C38" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D38" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-2</v>
+        <v>-17</v>
       </c>
       <c r="G38" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>27</v>
@@ -2782,10 +2767,10 @@
         <v>23</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S38" s="9">
-        <v>70.07</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39">
@@ -2796,37 +2781,37 @@
         <v>46188</v>
       </c>
       <c r="C39" s="7">
-        <v>46143</v>
+        <v>46181</v>
       </c>
       <c r="D39" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E39" s="7">
-        <v>46167</v>
+        <v>46181</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F39" s="8">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="G39" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>27</v>
@@ -2838,13 +2823,13 @@
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S39" s="9">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40">
@@ -2864,28 +2849,28 @@
         <v>23</v>
       </c>
       <c r="F40" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G40" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>72</v>
+        <v>23</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>27</v>
@@ -2900,10 +2885,10 @@
         <v>23</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="S40" s="9">
-        <v>120</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41">
@@ -2914,37 +2899,37 @@
         <v>46188</v>
       </c>
       <c r="C41" s="7">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="D41" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E41" s="7">
-        <v>46097</v>
+        <v>46174</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F41" s="8">
-        <v>-2</v>
+        <v>-17</v>
       </c>
       <c r="G41" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>27</v>
@@ -2956,13 +2941,13 @@
         <v>23</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S41" s="9">
-        <v>146.55</v>
+        <v>279.12</v>
       </c>
     </row>
     <row r="42">
@@ -2973,34 +2958,34 @@
         <v>46188</v>
       </c>
       <c r="C42" s="7">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="D42" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>23</v>
+        <v>46188</v>
+      </c>
+      <c r="E42" s="7">
+        <v>46141</v>
       </c>
       <c r="F42" s="8">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="G42" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -3015,13 +3000,13 @@
         <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S42" s="9">
-        <v>180</v>
+        <v>310</v>
       </c>
     </row>
     <row r="43">
@@ -3041,28 +3026,28 @@
         <v>23</v>
       </c>
       <c r="F43" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G43" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>27</v>
@@ -3077,10 +3062,10 @@
         <v>23</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S43" s="9">
-        <v>200</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44">
@@ -3100,25 +3085,25 @@
         <v>23</v>
       </c>
       <c r="F44" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G44" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>23</v>
@@ -3139,7 +3124,7 @@
         <v>36</v>
       </c>
       <c r="S44" s="9">
-        <v>230</v>
+        <v>330</v>
       </c>
     </row>
     <row r="45">
@@ -3150,34 +3135,34 @@
         <v>46188</v>
       </c>
       <c r="C45" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="D45" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F45" s="8">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="G45" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>23</v>
@@ -3195,10 +3180,10 @@
         <v>23</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S45" s="9">
-        <v>250</v>
+        <v>410.54</v>
       </c>
     </row>
     <row r="46">
@@ -3209,25 +3194,25 @@
         <v>46188</v>
       </c>
       <c r="C46" s="7">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="D46" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>23</v>
+        <v>46188</v>
+      </c>
+      <c r="E46" s="7">
+        <v>46170</v>
       </c>
       <c r="F46" s="8">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="G46" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>80</v>
@@ -3236,10 +3221,10 @@
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>27</v>
@@ -3251,13 +3236,13 @@
         <v>23</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S46" s="9">
-        <v>279.12</v>
+        <v>600</v>
       </c>
     </row>
     <row r="47">
@@ -3268,25 +3253,25 @@
         <v>46188</v>
       </c>
       <c r="C47" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="D47" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>23</v>
+        <v>46188</v>
+      </c>
+      <c r="E47" s="7">
+        <v>46141</v>
       </c>
       <c r="F47" s="8">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="G47" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J47" s="6" t="s">
         <v>81</v>
@@ -3295,10 +3280,10 @@
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="N47" s="6" t="s">
         <v>27</v>
@@ -3310,13 +3295,13 @@
         <v>23</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S47" s="9">
-        <v>310</v>
+        <v>620</v>
       </c>
     </row>
     <row r="48">
@@ -3332,30 +3317,30 @@
       <c r="D48" s="7">
         <v>46188</v>
       </c>
-      <c r="E48" s="7" t="s">
-        <v>23</v>
+      <c r="E48" s="7">
+        <v>46169</v>
       </c>
       <c r="F48" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G48" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J48" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="K48" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>84</v>
-      </c>
       <c r="M48" s="6" t="s">
         <v>23</v>
       </c>
@@ -3369,13 +3354,13 @@
         <v>23</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S48" s="9">
-        <v>330</v>
+        <v>630</v>
       </c>
     </row>
     <row r="49">
@@ -3386,34 +3371,34 @@
         <v>46188</v>
       </c>
       <c r="C49" s="7">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="D49" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>23</v>
+        <v>46188</v>
+      </c>
+      <c r="E49" s="7">
+        <v>46170</v>
       </c>
       <c r="F49" s="8">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="G49" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>23</v>
@@ -3428,13 +3413,13 @@
         <v>23</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S49" s="9">
-        <v>410.54</v>
+        <v>630</v>
       </c>
     </row>
     <row r="50">
@@ -3451,31 +3436,31 @@
         <v>46188</v>
       </c>
       <c r="E50" s="7">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="F50" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G50" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J50" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="K50" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>75</v>
-      </c>
       <c r="M50" s="6" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="N50" s="6" t="s">
         <v>27</v>
@@ -3493,7 +3478,7 @@
         <v>36</v>
       </c>
       <c r="S50" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="51">
@@ -3510,19 +3495,19 @@
         <v>46188</v>
       </c>
       <c r="E51" s="7">
-        <v>46141</v>
+        <v>46188</v>
       </c>
       <c r="F51" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G51" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J51" s="6" t="s">
         <v>87</v>
@@ -3531,7 +3516,7 @@
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>23</v>
@@ -3549,10 +3534,10 @@
         <v>35</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S51" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="52">
@@ -3569,19 +3554,19 @@
         <v>46188</v>
       </c>
       <c r="E52" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="F52" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G52" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>88</v>
@@ -3590,10 +3575,10 @@
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="N52" s="6" t="s">
         <v>27</v>
@@ -3611,7 +3596,7 @@
         <v>36</v>
       </c>
       <c r="S52" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="53">
@@ -3628,19 +3613,19 @@
         <v>46188</v>
       </c>
       <c r="E53" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F53" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G53" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J53" s="6" t="s">
         <v>89</v>
@@ -3649,7 +3634,7 @@
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
@@ -3667,10 +3652,10 @@
         <v>35</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S53" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="54">
@@ -3687,28 +3672,28 @@
         <v>46188</v>
       </c>
       <c r="E54" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F54" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G54" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J54" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="K54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="K54" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L54" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
@@ -3729,7 +3714,7 @@
         <v>36</v>
       </c>
       <c r="S54" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="55">
@@ -3746,19 +3731,19 @@
         <v>46188</v>
       </c>
       <c r="E55" s="7">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="F55" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G55" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J55" s="6" t="s">
         <v>92</v>
@@ -3767,7 +3752,7 @@
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
@@ -3788,7 +3773,7 @@
         <v>36</v>
       </c>
       <c r="S55" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="56">
@@ -3805,28 +3790,28 @@
         <v>46188</v>
       </c>
       <c r="E56" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="F56" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G56" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
@@ -3847,7 +3832,7 @@
         <v>36</v>
       </c>
       <c r="S56" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="57">
@@ -3864,28 +3849,28 @@
         <v>46188</v>
       </c>
       <c r="E57" s="7">
-        <v>46188</v>
+        <v>46141</v>
       </c>
       <c r="F57" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G57" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>23</v>
@@ -3906,7 +3891,7 @@
         <v>28</v>
       </c>
       <c r="S57" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="58">
@@ -3914,16 +3899,16 @@
         <v>22</v>
       </c>
       <c r="B58" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C58" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D58" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="E58" s="7">
-        <v>46170</v>
+        <v>46185</v>
       </c>
       <c r="F58" s="8">
         <v>-2</v>
@@ -3932,22 +3917,22 @@
         <v>-2</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J58" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="K58" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L58" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="M58" s="6" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="N58" s="6" t="s">
         <v>27</v>
@@ -3959,13 +3944,13 @@
         <v>23</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="S58" s="9">
-        <v>650</v>
+        <v>170.96</v>
       </c>
     </row>
     <row r="59">
@@ -3973,7 +3958,7 @@
         <v>22</v>
       </c>
       <c r="B59" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C59" s="7">
         <v>46188</v>
@@ -3981,29 +3966,29 @@
       <c r="D59" s="7">
         <v>46188</v>
       </c>
-      <c r="E59" s="7">
-        <v>46164</v>
+      <c r="E59" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F59" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G59" s="8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>23</v>
@@ -4018,13 +4003,13 @@
         <v>23</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S59" s="9">
-        <v>680</v>
+        <v>134.74</v>
       </c>
     </row>
     <row r="60">
@@ -4032,37 +4017,37 @@
         <v>22</v>
       </c>
       <c r="B60" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C60" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D60" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E60" s="7">
-        <v>46182</v>
+        <v>46174</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F60" s="8">
-        <v>-2</v>
+        <v>-17</v>
       </c>
       <c r="G60" s="8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>23</v>
@@ -4077,13 +4062,13 @@
         <v>23</v>
       </c>
       <c r="Q60" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S60" s="9">
-        <v>680</v>
+        <v>160</v>
       </c>
     </row>
     <row r="61">
@@ -4091,7 +4076,7 @@
         <v>22</v>
       </c>
       <c r="B61" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C61" s="7">
         <v>46188</v>
@@ -4099,29 +4084,29 @@
       <c r="D61" s="7">
         <v>46188</v>
       </c>
-      <c r="E61" s="7">
-        <v>46182</v>
+      <c r="E61" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F61" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G61" s="8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>23</v>
@@ -4133,16 +4118,16 @@
         <v>27</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="Q61" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S61" s="9">
-        <v>680</v>
+        <v>190</v>
       </c>
     </row>
     <row r="62">
@@ -4150,46 +4135,46 @@
         <v>22</v>
       </c>
       <c r="B62" s="7">
-        <v>46188</v>
+        <v>46192</v>
       </c>
       <c r="C62" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D62" s="7">
-        <v>46188</v>
+        <v>46192</v>
       </c>
       <c r="E62" s="7">
-        <v>46141</v>
+        <v>46185</v>
       </c>
       <c r="F62" s="8">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="G62" s="8">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>23</v>
+        <v>105</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>23</v>
@@ -4198,10 +4183,10 @@
         <v>35</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S62" s="9">
-        <v>680</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="63">
@@ -4209,58 +4194,58 @@
         <v>22</v>
       </c>
       <c r="B63" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C63" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D63" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E63" s="7">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="F63" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G63" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I63" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="Q63" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S63" s="9">
-        <v>680</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64">
@@ -4268,58 +4253,58 @@
         <v>22</v>
       </c>
       <c r="B64" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C64" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D64" s="7">
-        <v>46188</v>
+        <v>46211</v>
       </c>
       <c r="E64" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="F64" s="8">
-        <v>-2</v>
+        <v>20</v>
       </c>
       <c r="G64" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q64" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S64" s="9">
-        <v>700</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65">
@@ -4327,117 +4312,117 @@
         <v>22</v>
       </c>
       <c r="B65" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C65" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D65" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E65" s="7">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="F65" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G65" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I65" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="M65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q65" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R65" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S65" s="9">
-        <v>700</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="s">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="B66" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C66" s="7">
-        <v>46188</v>
+        <v>46082</v>
       </c>
       <c r="D66" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E66" s="7">
-        <v>46182</v>
+        <v>46097</v>
       </c>
       <c r="F66" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G66" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>108</v>
+        <v>26</v>
       </c>
       <c r="M66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q66" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="S66" s="9">
-        <v>800</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="67">
@@ -4445,58 +4430,58 @@
         <v>22</v>
       </c>
       <c r="B67" s="7">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="C67" s="7">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="D67" s="7">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="E67" s="7">
-        <v>46185</v>
+        <v>46169</v>
       </c>
       <c r="F67" s="8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G67" s="8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I67" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q67" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="S67" s="9">
-        <v>170.96</v>
+        <v>600</v>
       </c>
     </row>
     <row r="68">
@@ -4504,58 +4489,58 @@
         <v>22</v>
       </c>
       <c r="B68" s="7">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="C68" s="7">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="D68" s="7">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="E68" s="7">
-        <v>46185</v>
+        <v>46170</v>
       </c>
       <c r="F68" s="8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="G68" s="8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q68" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="S68" s="9">
-        <v>250</v>
+        <v>600</v>
       </c>
     </row>
     <row r="69">
@@ -4563,58 +4548,58 @@
         <v>22</v>
       </c>
       <c r="B69" s="7">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="C69" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="D69" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>23</v>
+        <v>46195</v>
+      </c>
+      <c r="E69" s="7">
+        <v>46169</v>
       </c>
       <c r="F69" s="8">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="G69" s="8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="I69" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>27</v>
+        <v>106</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q69" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S69" s="9">
-        <v>500.78</v>
+        <v>600</v>
       </c>
     </row>
     <row r="70">
@@ -4622,22 +4607,22 @@
         <v>22</v>
       </c>
       <c r="B70" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C70" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D70" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="E70" s="7">
-        <v>46185</v>
+        <v>46176</v>
       </c>
       <c r="F70" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G70" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>23</v>
@@ -4646,22 +4631,22 @@
         <v>23</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4670,10 +4655,10 @@
         <v>35</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S70" s="9">
-        <v>2100</v>
+        <v>620</v>
       </c>
     </row>
     <row r="71">
@@ -4684,19 +4669,19 @@
         <v>46195</v>
       </c>
       <c r="C71" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D71" s="7">
         <v>46195</v>
       </c>
       <c r="E71" s="7">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="F71" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G71" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4705,34 +4690,34 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q71" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S71" s="9">
-        <v>50</v>
+        <v>630</v>
       </c>
     </row>
     <row r="72">
@@ -4743,19 +4728,19 @@
         <v>46195</v>
       </c>
       <c r="C72" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D72" s="7">
         <v>46195</v>
       </c>
       <c r="E72" s="7">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="F72" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G72" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4764,34 +4749,34 @@
         <v>23</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="Q72" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S72" s="9">
-        <v>100</v>
+        <v>630</v>
       </c>
     </row>
     <row r="73">
@@ -4802,19 +4787,19 @@
         <v>46195</v>
       </c>
       <c r="C73" s="7">
-        <v>46082</v>
+        <v>46195</v>
       </c>
       <c r="D73" s="7">
         <v>46195</v>
       </c>
       <c r="E73" s="7">
-        <v>46097</v>
+        <v>46169</v>
       </c>
       <c r="F73" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G73" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4823,34 +4808,34 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>25</v>
+        <v>116</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q73" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S73" s="9">
-        <v>146.55</v>
+        <v>630</v>
       </c>
     </row>
     <row r="74">
@@ -4870,10 +4855,10 @@
         <v>46169</v>
       </c>
       <c r="F74" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G74" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4882,22 +4867,22 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4909,7 +4894,7 @@
         <v>36</v>
       </c>
       <c r="S74" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="75">
@@ -4926,13 +4911,13 @@
         <v>46195</v>
       </c>
       <c r="E75" s="7">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="F75" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G75" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>23</v>
@@ -4941,22 +4926,22 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>23</v>
@@ -4968,7 +4953,7 @@
         <v>36</v>
       </c>
       <c r="S75" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="76">
@@ -4985,13 +4970,13 @@
         <v>46195</v>
       </c>
       <c r="E76" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F76" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G76" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -5000,22 +4985,22 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -5027,7 +5012,7 @@
         <v>36</v>
       </c>
       <c r="S76" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="77">
@@ -5044,13 +5029,13 @@
         <v>46195</v>
       </c>
       <c r="E77" s="7">
-        <v>46176</v>
+        <v>46170</v>
       </c>
       <c r="F77" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G77" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -5059,22 +5044,22 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -5083,10 +5068,10 @@
         <v>35</v>
       </c>
       <c r="R77" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S77" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="78">
@@ -5103,13 +5088,13 @@
         <v>46195</v>
       </c>
       <c r="E78" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F78" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G78" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -5118,22 +5103,22 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="M78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>23</v>
@@ -5145,7 +5130,7 @@
         <v>36</v>
       </c>
       <c r="S78" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="79">
@@ -5162,13 +5147,13 @@
         <v>46195</v>
       </c>
       <c r="E79" s="7">
-        <v>46169</v>
+        <v>46127</v>
       </c>
       <c r="F79" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G79" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>23</v>
@@ -5177,22 +5162,22 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
@@ -5204,7 +5189,7 @@
         <v>36</v>
       </c>
       <c r="S79" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="80">
@@ -5221,13 +5206,13 @@
         <v>46195</v>
       </c>
       <c r="E80" s="7">
-        <v>46169</v>
+        <v>46153</v>
       </c>
       <c r="F80" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G80" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>23</v>
@@ -5236,22 +5221,22 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
@@ -5263,7 +5248,7 @@
         <v>36</v>
       </c>
       <c r="S80" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="81">
@@ -5280,13 +5265,13 @@
         <v>46195</v>
       </c>
       <c r="E81" s="7">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="F81" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G81" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>23</v>
@@ -5295,22 +5280,22 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>23</v>
@@ -5322,7 +5307,7 @@
         <v>36</v>
       </c>
       <c r="S81" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="82">
@@ -5339,13 +5324,13 @@
         <v>46195</v>
       </c>
       <c r="E82" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F82" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G82" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>23</v>
@@ -5354,34 +5339,34 @@
         <v>23</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q82" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R82" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S82" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="83">
@@ -5398,13 +5383,13 @@
         <v>46195</v>
       </c>
       <c r="E83" s="7">
-        <v>46170</v>
+        <v>46119</v>
       </c>
       <c r="F83" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G83" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>23</v>
@@ -5413,22 +5398,22 @@
         <v>23</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>23</v>
@@ -5440,7 +5425,7 @@
         <v>36</v>
       </c>
       <c r="S83" s="9">
-        <v>630</v>
+        <v>670</v>
       </c>
     </row>
     <row r="84">
@@ -5457,13 +5442,13 @@
         <v>46195</v>
       </c>
       <c r="E84" s="7">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="F84" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G84" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>23</v>
@@ -5472,22 +5457,22 @@
         <v>23</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="M84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>23</v>
@@ -5499,7 +5484,7 @@
         <v>36</v>
       </c>
       <c r="S84" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="85">
@@ -5516,13 +5501,13 @@
         <v>46195</v>
       </c>
       <c r="E85" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F85" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G85" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>23</v>
@@ -5531,22 +5516,22 @@
         <v>23</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="M85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P85" s="6" t="s">
         <v>23</v>
@@ -5558,7 +5543,7 @@
         <v>36</v>
       </c>
       <c r="S85" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="86">
@@ -5575,13 +5560,13 @@
         <v>46195</v>
       </c>
       <c r="E86" s="7">
-        <v>46127</v>
+        <v>46176</v>
       </c>
       <c r="F86" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G86" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>23</v>
@@ -5590,22 +5575,22 @@
         <v>23</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>23</v>
@@ -5617,7 +5602,7 @@
         <v>36</v>
       </c>
       <c r="S86" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="87">
@@ -5634,13 +5619,13 @@
         <v>46195</v>
       </c>
       <c r="E87" s="7">
-        <v>46153</v>
+        <v>46182</v>
       </c>
       <c r="F87" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G87" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H87" s="6" t="s">
         <v>23</v>
@@ -5649,22 +5634,22 @@
         <v>23</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="M87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N87" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P87" s="6" t="s">
         <v>23</v>
@@ -5676,7 +5661,7 @@
         <v>36</v>
       </c>
       <c r="S87" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="88">
@@ -5693,13 +5678,13 @@
         <v>46195</v>
       </c>
       <c r="E88" s="7">
-        <v>46160</v>
+        <v>46182</v>
       </c>
       <c r="F88" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G88" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>23</v>
@@ -5708,22 +5693,22 @@
         <v>23</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="M88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>23</v>
@@ -5735,7 +5720,7 @@
         <v>36</v>
       </c>
       <c r="S88" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="89">
@@ -5752,13 +5737,13 @@
         <v>46195</v>
       </c>
       <c r="E89" s="7">
-        <v>46188</v>
+        <v>46164</v>
       </c>
       <c r="F89" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G89" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>23</v>
@@ -5767,22 +5752,22 @@
         <v>23</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="M89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N89" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O89" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P89" s="6" t="s">
         <v>23</v>
@@ -5794,7 +5779,7 @@
         <v>28</v>
       </c>
       <c r="S89" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="90">
@@ -5811,13 +5796,13 @@
         <v>46195</v>
       </c>
       <c r="E90" s="7">
-        <v>46119</v>
+        <v>46170</v>
       </c>
       <c r="F90" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G90" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>23</v>
@@ -5826,25 +5811,25 @@
         <v>23</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="M90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="Q90" s="6" t="s">
         <v>35</v>
@@ -5853,7 +5838,7 @@
         <v>36</v>
       </c>
       <c r="S90" s="9">
-        <v>670</v>
+        <v>700</v>
       </c>
     </row>
     <row r="91">
@@ -5870,13 +5855,13 @@
         <v>46195</v>
       </c>
       <c r="E91" s="7">
-        <v>46176</v>
+        <v>46188</v>
       </c>
       <c r="F91" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G91" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>23</v>
@@ -5885,22 +5870,22 @@
         <v>23</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N91" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O91" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P91" s="6" t="s">
         <v>23</v>
@@ -5909,10 +5894,10 @@
         <v>35</v>
       </c>
       <c r="R91" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S91" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="92">
@@ -5929,13 +5914,13 @@
         <v>46195</v>
       </c>
       <c r="E92" s="7">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="F92" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G92" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>23</v>
@@ -5944,22 +5929,22 @@
         <v>23</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>23</v>
@@ -5971,12 +5956,12 @@
         <v>36</v>
       </c>
       <c r="S92" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="s">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="B93" s="7">
         <v>46195</v>
@@ -5991,10 +5976,10 @@
         <v>46182</v>
       </c>
       <c r="F93" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G93" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>23</v>
@@ -6003,22 +5988,22 @@
         <v>23</v>
       </c>
       <c r="J93" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K93" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="K93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L93" s="6" t="s">
-        <v>46</v>
-      </c>
       <c r="M93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N93" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O93" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P93" s="6" t="s">
         <v>23</v>
@@ -6027,10 +6012,10 @@
         <v>35</v>
       </c>
       <c r="R93" s="6" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="S93" s="9">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="94">
@@ -6047,13 +6032,13 @@
         <v>46195</v>
       </c>
       <c r="E94" s="7">
-        <v>46167</v>
+        <v>46148</v>
       </c>
       <c r="F94" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G94" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>23</v>
@@ -6068,16 +6053,16 @@
         <v>23</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="M94" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>23</v>
@@ -6086,10 +6071,10 @@
         <v>35</v>
       </c>
       <c r="R94" s="6" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="S94" s="9">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="95">
@@ -6106,13 +6091,13 @@
         <v>46195</v>
       </c>
       <c r="E95" s="7">
-        <v>46164</v>
+        <v>46148</v>
       </c>
       <c r="F95" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G95" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>23</v>
@@ -6127,16 +6112,16 @@
         <v>23</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="M95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N95" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O95" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P95" s="6" t="s">
         <v>23</v>
@@ -6145,10 +6130,10 @@
         <v>35</v>
       </c>
       <c r="R95" s="6" t="s">
-        <v>28</v>
+        <v>151</v>
       </c>
       <c r="S95" s="9">
-        <v>680</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="96">
@@ -6165,13 +6150,13 @@
         <v>46195</v>
       </c>
       <c r="E96" s="7">
-        <v>46182</v>
+        <v>46160</v>
       </c>
       <c r="F96" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G96" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>23</v>
@@ -6180,34 +6165,34 @@
         <v>23</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="M96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="Q96" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R96" s="6" t="s">
-        <v>36</v>
+        <v>151</v>
       </c>
       <c r="S96" s="9">
-        <v>680</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="97">
@@ -6224,13 +6209,13 @@
         <v>46195</v>
       </c>
       <c r="E97" s="7">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="F97" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G97" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H97" s="6" t="s">
         <v>23</v>
@@ -6239,34 +6224,34 @@
         <v>23</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="M97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N97" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O97" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="Q97" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R97" s="6" t="s">
-        <v>36</v>
+        <v>151</v>
       </c>
       <c r="S97" s="9">
-        <v>700</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="98">
@@ -6274,22 +6259,22 @@
         <v>22</v>
       </c>
       <c r="B98" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="C98" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D98" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="E98" s="7">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="F98" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G98" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>23</v>
@@ -6298,22 +6283,22 @@
         <v>23</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>23</v>
+        <v>159</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>23</v>
@@ -6322,10 +6307,10 @@
         <v>35</v>
       </c>
       <c r="R98" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S98" s="9">
-        <v>700</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="99">
@@ -6333,22 +6318,22 @@
         <v>22</v>
       </c>
       <c r="B99" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C99" s="7">
-        <v>46195</v>
+        <v>46174</v>
       </c>
       <c r="D99" s="7">
-        <v>46195</v>
+        <v>46218</v>
       </c>
       <c r="E99" s="7">
-        <v>46170</v>
+        <v>46190</v>
       </c>
       <c r="F99" s="8">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="G99" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>23</v>
@@ -6357,57 +6342,57 @@
         <v>23</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>153</v>
+        <v>107</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="N99" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O99" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q99" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R99" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S99" s="9">
-        <v>700</v>
+        <v>50</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="s">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="B100" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C100" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D100" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E100" s="7">
-        <v>46182</v>
+        <v>46153</v>
       </c>
       <c r="F100" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G100" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H100" s="6" t="s">
         <v>23</v>
@@ -6416,34 +6401,34 @@
         <v>23</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>108</v>
+        <v>62</v>
       </c>
       <c r="M100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="Q100" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R100" s="6" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="S100" s="9">
-        <v>800</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101">
@@ -6451,22 +6436,22 @@
         <v>22</v>
       </c>
       <c r="B101" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C101" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D101" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E101" s="7">
-        <v>46148</v>
+        <v>46167</v>
       </c>
       <c r="F101" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G101" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H101" s="6" t="s">
         <v>23</v>
@@ -6475,34 +6460,34 @@
         <v>23</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>156</v>
+        <v>45</v>
       </c>
       <c r="K101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="M101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N101" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O101" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q101" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R101" s="6" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="S101" s="9">
-        <v>800</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102">
@@ -6510,58 +6495,58 @@
         <v>22</v>
       </c>
       <c r="B102" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C102" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D102" s="7">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="E102" s="7">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="F102" s="8">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="G102" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I102" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="K102" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>158</v>
+        <v>46</v>
       </c>
       <c r="M102" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>119</v>
+        <v>27</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>159</v>
+        <v>23</v>
       </c>
       <c r="Q102" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R102" s="6" t="s">
-        <v>114</v>
+        <v>36</v>
       </c>
       <c r="S102" s="9">
-        <v>1200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103">
@@ -6569,22 +6554,22 @@
         <v>22</v>
       </c>
       <c r="B103" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C103" s="7">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="D103" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E103" s="7">
-        <v>46148</v>
+        <v>46188</v>
       </c>
       <c r="F103" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G103" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H103" s="6" t="s">
         <v>23</v>
@@ -6599,16 +6584,16 @@
         <v>23</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="M103" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N103" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O103" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P103" s="6" t="s">
         <v>23</v>
@@ -6617,10 +6602,10 @@
         <v>35</v>
       </c>
       <c r="R103" s="6" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="S103" s="9">
-        <v>1200</v>
+        <v>116.66</v>
       </c>
     </row>
     <row r="104">
@@ -6628,22 +6613,22 @@
         <v>22</v>
       </c>
       <c r="B104" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C104" s="7">
-        <v>46195</v>
+        <v>46082</v>
       </c>
       <c r="D104" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E104" s="7">
-        <v>46160</v>
+        <v>46097</v>
       </c>
       <c r="F104" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G104" s="8">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>23</v>
@@ -6652,34 +6637,34 @@
         <v>23</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>161</v>
+        <v>25</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>162</v>
+        <v>26</v>
       </c>
       <c r="M104" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>159</v>
+        <v>23</v>
       </c>
       <c r="Q104" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R104" s="6" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="S104" s="9">
-        <v>1200</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="105">
@@ -6687,22 +6672,22 @@
         <v>22</v>
       </c>
       <c r="B105" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="C105" s="7">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D105" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="E105" s="7">
-        <v>46185</v>
+        <v>46169</v>
       </c>
       <c r="F105" s="8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G105" s="8">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>23</v>
@@ -6711,22 +6696,22 @@
         <v>23</v>
       </c>
       <c r="J105" s="6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K105" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>165</v>
+        <v>109</v>
       </c>
       <c r="N105" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O105" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P105" s="6" t="s">
         <v>23</v>
@@ -6738,7 +6723,7 @@
         <v>36</v>
       </c>
       <c r="S105" s="9">
-        <v>4400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="106">
@@ -6749,19 +6734,19 @@
         <v>46202</v>
       </c>
       <c r="C106" s="7">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D106" s="7">
         <v>46202</v>
       </c>
       <c r="E106" s="7">
-        <v>46153</v>
+        <v>46169</v>
       </c>
       <c r="F106" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G106" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>23</v>
@@ -6770,34 +6755,34 @@
         <v>23</v>
       </c>
       <c r="J106" s="6" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="K106" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q106" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R106" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S106" s="9">
-        <v>50</v>
+        <v>600</v>
       </c>
     </row>
     <row r="107">
@@ -6808,19 +6793,19 @@
         <v>46202</v>
       </c>
       <c r="C107" s="7">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D107" s="7">
         <v>46202</v>
       </c>
       <c r="E107" s="7">
-        <v>46167</v>
+        <v>46163</v>
       </c>
       <c r="F107" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G107" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>23</v>
@@ -6829,34 +6814,34 @@
         <v>23</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>45</v>
+        <v>163</v>
       </c>
       <c r="K107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="M107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N107" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O107" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q107" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R107" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S107" s="9">
-        <v>100</v>
+        <v>630</v>
       </c>
     </row>
     <row r="108">
@@ -6867,19 +6852,19 @@
         <v>46202</v>
       </c>
       <c r="C108" s="7">
-        <v>46082</v>
+        <v>46202</v>
       </c>
       <c r="D108" s="7">
         <v>46202</v>
       </c>
       <c r="E108" s="7">
-        <v>46097</v>
+        <v>46169</v>
       </c>
       <c r="F108" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G108" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H108" s="6" t="s">
         <v>23</v>
@@ -6888,34 +6873,34 @@
         <v>23</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>25</v>
+        <v>164</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>26</v>
+        <v>117</v>
       </c>
       <c r="M108" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q108" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R108" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S108" s="9">
-        <v>146.55</v>
+        <v>630</v>
       </c>
     </row>
     <row r="109">
@@ -6935,10 +6920,10 @@
         <v>46169</v>
       </c>
       <c r="F109" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G109" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>23</v>
@@ -6947,22 +6932,22 @@
         <v>23</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K109" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M109" s="6" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="N109" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O109" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P109" s="6" t="s">
         <v>23</v>
@@ -6974,7 +6959,7 @@
         <v>36</v>
       </c>
       <c r="S109" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="110">
@@ -6994,10 +6979,10 @@
         <v>46169</v>
       </c>
       <c r="F110" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G110" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>23</v>
@@ -7006,22 +6991,22 @@
         <v>23</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="M110" s="6" t="s">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>23</v>
@@ -7033,7 +7018,7 @@
         <v>36</v>
       </c>
       <c r="S110" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="111">
@@ -7050,13 +7035,13 @@
         <v>46202</v>
       </c>
       <c r="E111" s="7">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F111" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G111" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>23</v>
@@ -7065,22 +7050,22 @@
         <v>23</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K111" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="M111" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N111" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O111" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P111" s="6" t="s">
         <v>23</v>
@@ -7109,13 +7094,13 @@
         <v>46202</v>
       </c>
       <c r="E112" s="7">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="F112" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G112" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H112" s="6" t="s">
         <v>23</v>
@@ -7124,22 +7109,22 @@
         <v>23</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K112" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L112" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="M112" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>23</v>
@@ -7151,7 +7136,7 @@
         <v>36</v>
       </c>
       <c r="S112" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="113">
@@ -7168,13 +7153,13 @@
         <v>46202</v>
       </c>
       <c r="E113" s="7">
-        <v>46169</v>
+        <v>46153</v>
       </c>
       <c r="F113" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G113" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>23</v>
@@ -7183,22 +7168,22 @@
         <v>23</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="M113" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N113" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O113" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P113" s="6" t="s">
         <v>23</v>
@@ -7210,7 +7195,7 @@
         <v>36</v>
       </c>
       <c r="S113" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="114">
@@ -7227,13 +7212,13 @@
         <v>46202</v>
       </c>
       <c r="E114" s="7">
-        <v>46169</v>
+        <v>46127</v>
       </c>
       <c r="F114" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G114" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H114" s="6" t="s">
         <v>23</v>
@@ -7242,22 +7227,22 @@
         <v>23</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K114" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="M114" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>23</v>
@@ -7269,7 +7254,7 @@
         <v>36</v>
       </c>
       <c r="S114" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="115">
@@ -7286,13 +7271,13 @@
         <v>46202</v>
       </c>
       <c r="E115" s="7">
-        <v>46164</v>
+        <v>46188</v>
       </c>
       <c r="F115" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G115" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H115" s="6" t="s">
         <v>23</v>
@@ -7301,22 +7286,22 @@
         <v>23</v>
       </c>
       <c r="J115" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="K115" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="M115" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N115" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O115" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P115" s="6" t="s">
         <v>23</v>
@@ -7325,10 +7310,10 @@
         <v>35</v>
       </c>
       <c r="R115" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S115" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="116">
@@ -7345,13 +7330,13 @@
         <v>46202</v>
       </c>
       <c r="E116" s="7">
-        <v>46127</v>
+        <v>46164</v>
       </c>
       <c r="F116" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G116" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H116" s="6" t="s">
         <v>23</v>
@@ -7360,22 +7345,22 @@
         <v>23</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K116" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L116" s="6" t="s">
-        <v>137</v>
+        <v>76</v>
       </c>
       <c r="M116" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>23</v>
@@ -7384,10 +7369,10 @@
         <v>35</v>
       </c>
       <c r="R116" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S116" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="117">
@@ -7404,13 +7389,13 @@
         <v>46202</v>
       </c>
       <c r="E117" s="7">
-        <v>46153</v>
+        <v>46182</v>
       </c>
       <c r="F117" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G117" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H117" s="6" t="s">
         <v>23</v>
@@ -7419,22 +7404,22 @@
         <v>23</v>
       </c>
       <c r="J117" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K117" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L117" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M117" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N117" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O117" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P117" s="6" t="s">
         <v>23</v>
@@ -7446,7 +7431,7 @@
         <v>36</v>
       </c>
       <c r="S117" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="118">
@@ -7463,13 +7448,13 @@
         <v>46202</v>
       </c>
       <c r="E118" s="7">
-        <v>46160</v>
+        <v>46182</v>
       </c>
       <c r="F118" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G118" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H118" s="6" t="s">
         <v>23</v>
@@ -7478,22 +7463,22 @@
         <v>23</v>
       </c>
       <c r="J118" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K118" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L118" s="6" t="s">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="M118" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>23</v>
@@ -7505,7 +7490,7 @@
         <v>36</v>
       </c>
       <c r="S118" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="119">
@@ -7522,13 +7507,13 @@
         <v>46202</v>
       </c>
       <c r="E119" s="7">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="F119" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G119" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H119" s="6" t="s">
         <v>23</v>
@@ -7537,22 +7522,22 @@
         <v>23</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="K119" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L119" s="6" t="s">
-        <v>44</v>
+        <v>137</v>
       </c>
       <c r="M119" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N119" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O119" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P119" s="6" t="s">
         <v>23</v>
@@ -7561,10 +7546,10 @@
         <v>35</v>
       </c>
       <c r="R119" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S119" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="120">
@@ -7581,13 +7566,13 @@
         <v>46202</v>
       </c>
       <c r="E120" s="7">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="F120" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G120" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H120" s="6" t="s">
         <v>23</v>
@@ -7596,22 +7581,22 @@
         <v>23</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L120" s="6" t="s">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="M120" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>23</v>
@@ -7640,13 +7625,13 @@
         <v>46202</v>
       </c>
       <c r="E121" s="7">
-        <v>46164</v>
+        <v>46188</v>
       </c>
       <c r="F121" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G121" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H121" s="6" t="s">
         <v>23</v>
@@ -7655,22 +7640,22 @@
         <v>23</v>
       </c>
       <c r="J121" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K121" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L121" s="6" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="M121" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N121" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O121" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P121" s="6" t="s">
         <v>23</v>
@@ -7682,7 +7667,7 @@
         <v>28</v>
       </c>
       <c r="S121" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="122">
@@ -7699,13 +7684,13 @@
         <v>46202</v>
       </c>
       <c r="E122" s="7">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="F122" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G122" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H122" s="6" t="s">
         <v>23</v>
@@ -7714,22 +7699,22 @@
         <v>23</v>
       </c>
       <c r="J122" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K122" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L122" s="6" t="s">
-        <v>54</v>
+        <v>144</v>
       </c>
       <c r="M122" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>23</v>
@@ -7741,12 +7726,12 @@
         <v>36</v>
       </c>
       <c r="S122" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="s">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="B123" s="7">
         <v>46202</v>
@@ -7761,10 +7746,10 @@
         <v>46182</v>
       </c>
       <c r="F123" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G123" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H123" s="6" t="s">
         <v>23</v>
@@ -7773,22 +7758,22 @@
         <v>23</v>
       </c>
       <c r="J123" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K123" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L123" s="6" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="M123" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N123" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O123" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P123" s="6" t="s">
         <v>23</v>
@@ -7797,10 +7782,10 @@
         <v>35</v>
       </c>
       <c r="R123" s="6" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="S123" s="9">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="124">
@@ -7817,13 +7802,13 @@
         <v>46202</v>
       </c>
       <c r="E124" s="7">
-        <v>46167</v>
+        <v>46148</v>
       </c>
       <c r="F124" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G124" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H124" s="6" t="s">
         <v>23</v>
@@ -7832,22 +7817,22 @@
         <v>23</v>
       </c>
       <c r="J124" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K124" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L124" s="6" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="M124" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>23</v>
@@ -7856,10 +7841,10 @@
         <v>35</v>
       </c>
       <c r="R124" s="6" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="S124" s="9">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="125">
@@ -7876,13 +7861,13 @@
         <v>46202</v>
       </c>
       <c r="E125" s="7">
-        <v>46170</v>
+        <v>46148</v>
       </c>
       <c r="F125" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G125" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H125" s="6" t="s">
         <v>23</v>
@@ -7891,22 +7876,22 @@
         <v>23</v>
       </c>
       <c r="J125" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K125" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L125" s="6" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="M125" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N125" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O125" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P125" s="6" t="s">
         <v>23</v>
@@ -7915,10 +7900,10 @@
         <v>35</v>
       </c>
       <c r="R125" s="6" t="s">
-        <v>36</v>
+        <v>151</v>
       </c>
       <c r="S125" s="9">
-        <v>700</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="126">
@@ -7935,13 +7920,13 @@
         <v>46202</v>
       </c>
       <c r="E126" s="7">
-        <v>46188</v>
+        <v>46160</v>
       </c>
       <c r="F126" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G126" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H126" s="6" t="s">
         <v>23</v>
@@ -7950,39 +7935,39 @@
         <v>23</v>
       </c>
       <c r="J126" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K126" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L126" s="6" t="s">
-        <v>79</v>
+        <v>156</v>
       </c>
       <c r="M126" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="Q126" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R126" s="6" t="s">
-        <v>28</v>
+        <v>151</v>
       </c>
       <c r="S126" s="9">
-        <v>700</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="s">
-        <v>106</v>
+        <v>22</v>
       </c>
       <c r="B127" s="7">
         <v>46202</v>
@@ -7994,13 +7979,13 @@
         <v>46202</v>
       </c>
       <c r="E127" s="7">
-        <v>46182</v>
+        <v>46160</v>
       </c>
       <c r="F127" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G127" s="8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H127" s="6" t="s">
         <v>23</v>
@@ -8009,293 +7994,57 @@
         <v>23</v>
       </c>
       <c r="J127" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K127" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L127" s="6" t="s">
-        <v>108</v>
+        <v>153</v>
       </c>
       <c r="M127" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N127" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="O127" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="P127" s="6" t="s">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="Q127" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R127" s="6" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="S127" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B128" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C128" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D128" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E128" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F128" s="8">
-        <v>12</v>
-      </c>
-      <c r="G128" s="8">
-        <v>12</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I128" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J128" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="K128" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L128" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="M128" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N128" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="O128" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="P128" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q128" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R128" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="S128" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B129" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C129" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D129" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E129" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F129" s="8">
-        <v>12</v>
-      </c>
-      <c r="G129" s="8">
-        <v>12</v>
-      </c>
-      <c r="H129" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I129" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J129" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="K129" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L129" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="M129" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N129" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="O129" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="P129" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q129" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R129" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="S129" s="9">
         <v>1200</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B130" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C130" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D130" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E130" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F130" s="8">
-        <v>12</v>
-      </c>
-      <c r="G130" s="8">
-        <v>12</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I130" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J130" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="K130" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L130" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="M130" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N130" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="O130" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="P130" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q130" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R130" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="S130" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B131" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C131" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D131" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E131" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F131" s="8">
-        <v>12</v>
-      </c>
-      <c r="G131" s="8">
-        <v>12</v>
-      </c>
-      <c r="H131" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I131" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J131" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="K131" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L131" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="M131" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N131" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="O131" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="P131" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q131" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R131" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="S131" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="132" ht="23" customHeight="1">
-      <c r="A132" s="10"/>
-      <c r="B132" s="11"/>
-      <c r="C132" s="11"/>
-      <c r="D132" s="11"/>
-      <c r="E132" s="11"/>
-      <c r="F132" s="12"/>
-      <c r="G132" s="12"/>
-      <c r="H132" s="10"/>
-      <c r="I132" s="10"/>
-      <c r="J132" s="10"/>
-      <c r="K132" s="10"/>
-      <c r="L132" s="10"/>
-      <c r="M132" s="10"/>
-      <c r="N132" s="10"/>
-      <c r="O132" s="10"/>
-      <c r="P132" s="10"/>
-      <c r="Q132" s="10"/>
-      <c r="R132" s="10"/>
-      <c r="S132" s="13">
-        <f>SUM(S6:S131)</f>
+    <row r="128" ht="23" customHeight="1">
+      <c r="A128" s="10"/>
+      <c r="B128" s="11"/>
+      <c r="C128" s="11"/>
+      <c r="D128" s="11"/>
+      <c r="E128" s="11"/>
+      <c r="F128" s="12"/>
+      <c r="G128" s="12"/>
+      <c r="H128" s="10"/>
+      <c r="I128" s="10"/>
+      <c r="J128" s="10"/>
+      <c r="K128" s="10"/>
+      <c r="L128" s="10"/>
+      <c r="M128" s="10"/>
+      <c r="N128" s="10"/>
+      <c r="O128" s="10"/>
+      <c r="P128" s="10"/>
+      <c r="Q128" s="10"/>
+      <c r="R128" s="10"/>
+      <c r="S128" s="13">
+        <f>SUM(S6:S127)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$128</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$126</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -169,238 +169,241 @@
     <t>ANDRE CAVALCANTI DA FE</t>
   </si>
   <si>
+    <t>FA-11568</t>
+  </si>
+  <si>
+    <t>FA-11796</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11775</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11847</t>
+  </si>
+  <si>
+    <t>FA-11814</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11693</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>ND-11801</t>
+  </si>
+  <si>
+    <t>FA-11569</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11810</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>ND-11699</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>FA-11806</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>JOAO PAULO CONSORCIOS</t>
+  </si>
+  <si>
+    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
+  </si>
+  <si>
+    <t>FA-11784</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11671</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11774</t>
+  </si>
+  <si>
+    <t>FA-11571</t>
+  </si>
+  <si>
+    <t>FA-11678</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11797</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11787</t>
+  </si>
+  <si>
+    <t>FA-11572</t>
+  </si>
+  <si>
+    <t>FA-11724</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11798</t>
+  </si>
+  <si>
+    <t>FA-11848</t>
+  </si>
+  <si>
+    <t>FA-11776</t>
+  </si>
+  <si>
+    <t>FA-11679</t>
+  </si>
+  <si>
+    <t>FA-11818</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11694</t>
+  </si>
+  <si>
+    <t>FA-11573</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11819</t>
+  </si>
+  <si>
+    <t>ND-11844</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11756</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11692</t>
+  </si>
+  <si>
+    <t>FA-11785</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11772</t>
+  </si>
+  <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>FA-11842</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
     <t>ND-11700</t>
   </si>
   <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-11568</t>
-  </si>
-  <si>
-    <t>FA-11796</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11775</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11847</t>
-  </si>
-  <si>
-    <t>FA-11814</t>
-  </si>
-  <si>
-    <t>FA-11693</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>ND-11801</t>
-  </si>
-  <si>
-    <t>FA-11569</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11810</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>ND-11699</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>FA-11806</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>JOAO PAULO CONSORCIOS</t>
-  </si>
-  <si>
-    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
-  </si>
-  <si>
-    <t>FA-11794</t>
-  </si>
-  <si>
-    <t>FA-11784</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11671</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11774</t>
-  </si>
-  <si>
-    <t>FA-11571</t>
-  </si>
-  <si>
-    <t>FA-11678</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11797</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11772</t>
-  </si>
-  <si>
-    <t>FA-11787</t>
-  </si>
-  <si>
-    <t>FA-11572</t>
-  </si>
-  <si>
-    <t>FA-11724</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11798</t>
-  </si>
-  <si>
-    <t>FA-11686</t>
+    <t>ND-11870</t>
+  </si>
+  <si>
+    <t>FA-11730</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11791</t>
+  </si>
+  <si>
+    <t>FA-11749</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11807</t>
+  </si>
+  <si>
+    <t>FA-11672</t>
+  </si>
+  <si>
+    <t>FA-11800</t>
+  </si>
+  <si>
+    <t>FA-11790</t>
+  </si>
+  <si>
+    <t>FA-11733</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11731</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11728</t>
+  </si>
+  <si>
+    <t>FA-11687</t>
   </si>
   <si>
     <t>GILVAN RODRIGUES MACHADO</t>
   </si>
   <si>
-    <t>FA-11848</t>
-  </si>
-  <si>
-    <t>FA-11776</t>
-  </si>
-  <si>
-    <t>FA-11679</t>
-  </si>
-  <si>
-    <t>FA-11818</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11819</t>
-  </si>
-  <si>
-    <t>FA-11694</t>
-  </si>
-  <si>
-    <t>FA-11573</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>ND-11844</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11756</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11692</t>
-  </si>
-  <si>
-    <t>FA-11785</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11842</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>ND-11870</t>
-  </si>
-  <si>
-    <t>FA-11730</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11791</t>
-  </si>
-  <si>
-    <t>FA-11749</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11807</t>
-  </si>
-  <si>
-    <t>FA-11672</t>
-  </si>
-  <si>
-    <t>FA-11790</t>
-  </si>
-  <si>
-    <t>FA-11733</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11731</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11728</t>
-  </si>
-  <si>
-    <t>FA-11687</t>
-  </si>
-  <si>
-    <t>FA-11800</t>
+    <t>FA-11660</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
   </si>
   <si>
     <t>FA-11799</t>
@@ -418,12 +421,6 @@
     <t>DANILO DE ALMEIDA TORRES</t>
   </si>
   <si>
-    <t>FA-11660</t>
-  </si>
-  <si>
-    <t>LUCA ZOLI</t>
-  </si>
-  <si>
     <t>FA-11850</t>
   </si>
   <si>
@@ -433,21 +430,21 @@
     <t>RAYANE ROBERTA DA SILVA</t>
   </si>
   <si>
+    <t>FA-11811</t>
+  </si>
+  <si>
+    <t>FA-11821</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11823</t>
+  </si>
+  <si>
     <t>FA-11695</t>
   </si>
   <si>
-    <t>FA-11823</t>
-  </si>
-  <si>
-    <t>FA-11811</t>
-  </si>
-  <si>
-    <t>FA-11821</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
     <t>FA-11822</t>
   </si>
   <si>
@@ -457,16 +454,19 @@
     <t>FA-11789</t>
   </si>
   <si>
+    <t>FA-11765</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
     <t>FA-11851</t>
   </si>
   <si>
     <t>MAICON LOPES SILVA</t>
   </si>
   <si>
-    <t>FA-11765</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+    <t>FA-11605</t>
   </si>
   <si>
     <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
@@ -478,9 +478,6 @@
     <t>ELIONILSON CORDEIRO BARBOSA</t>
   </si>
   <si>
-    <t>FA-11605</t>
-  </si>
-  <si>
     <t>FA-11595</t>
   </si>
   <si>
@@ -490,21 +487,21 @@
     <t>LUZ DIVINA LTDA</t>
   </si>
   <si>
+    <t>FA-11636</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
     <t>FA-11648</t>
   </si>
   <si>
     <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
   </si>
   <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-11636</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
     <t>FA-11843</t>
   </si>
   <si>
@@ -565,10 +562,10 @@
     <t>FA-11696</t>
   </si>
   <si>
+    <t>FA-11766</t>
+  </si>
+  <si>
     <t>FA-11853</t>
-  </si>
-  <si>
-    <t>FA-11766</t>
   </si>
   <si>
     <t>FA-11828</t>
@@ -726,7 +723,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S128"/>
+  <dimension ref="A1:S126"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -1826,7 +1823,7 @@
         <v>28</v>
       </c>
       <c r="S22" s="9">
-        <v>550</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23">
@@ -1837,13 +1834,13 @@
         <v>46181</v>
       </c>
       <c r="C23" s="7">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="D23" s="7">
         <v>46181</v>
       </c>
       <c r="E23" s="7">
-        <v>46167</v>
+        <v>46097</v>
       </c>
       <c r="F23" s="8">
         <v>-10</v>
@@ -1858,13 +1855,13 @@
         <v>38</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>23</v>
@@ -1882,10 +1879,10 @@
         <v>29</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S23" s="9">
-        <v>50</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="24">
@@ -1896,13 +1893,13 @@
         <v>46181</v>
       </c>
       <c r="C24" s="7">
-        <v>46082</v>
+        <v>46181</v>
       </c>
       <c r="D24" s="7">
         <v>46181</v>
       </c>
       <c r="E24" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F24" s="8">
         <v>-10</v>
@@ -1917,13 +1914,13 @@
         <v>38</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>23</v>
@@ -1938,13 +1935,13 @@
         <v>23</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S24" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="25">
@@ -1961,7 +1958,7 @@
         <v>46181</v>
       </c>
       <c r="E25" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="F25" s="8">
         <v>-10</v>
@@ -1976,13 +1973,13 @@
         <v>38</v>
       </c>
       <c r="J25" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>23</v>
@@ -2003,7 +2000,7 @@
         <v>36</v>
       </c>
       <c r="S25" s="9">
-        <v>310</v>
+        <v>630</v>
       </c>
     </row>
     <row r="26">
@@ -2044,7 +2041,7 @@
         <v>49</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>27</v>
@@ -2062,7 +2059,7 @@
         <v>36</v>
       </c>
       <c r="S26" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="27">
@@ -2079,7 +2076,7 @@
         <v>46181</v>
       </c>
       <c r="E27" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F27" s="8">
         <v>-10</v>
@@ -2100,10 +2097,10 @@
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="N27" s="6" t="s">
         <v>27</v>
@@ -2118,7 +2115,7 @@
         <v>35</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S27" s="9">
         <v>650</v>
@@ -2138,7 +2135,7 @@
         <v>46181</v>
       </c>
       <c r="E28" s="7">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="F28" s="8">
         <v>-10</v>
@@ -2153,13 +2150,13 @@
         <v>38</v>
       </c>
       <c r="J28" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>44</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>23</v>
@@ -2177,10 +2174,10 @@
         <v>35</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S28" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="29">
@@ -2197,7 +2194,7 @@
         <v>46181</v>
       </c>
       <c r="E29" s="7">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="F29" s="8">
         <v>-10</v>
@@ -2218,7 +2215,7 @@
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>23</v>
@@ -2250,13 +2247,13 @@
         <v>46181</v>
       </c>
       <c r="C30" s="7">
-        <v>46181</v>
+        <v>46143</v>
       </c>
       <c r="D30" s="7">
         <v>46181</v>
       </c>
       <c r="E30" s="7">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="F30" s="8">
         <v>-10</v>
@@ -2271,13 +2268,13 @@
         <v>38</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>23</v>
@@ -2292,13 +2289,13 @@
         <v>23</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S30" s="9">
-        <v>680</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="31">
@@ -2306,22 +2303,22 @@
         <v>22</v>
       </c>
       <c r="B31" s="7">
+        <v>46185</v>
+      </c>
+      <c r="C31" s="7">
         <v>46181</v>
-      </c>
-      <c r="C31" s="7">
-        <v>46143</v>
       </c>
       <c r="D31" s="7">
         <v>46181</v>
       </c>
-      <c r="E31" s="7">
-        <v>46170</v>
+      <c r="E31" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F31" s="8">
         <v>-10</v>
       </c>
       <c r="G31" s="8">
-        <v>-10</v>
+        <v>-6</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>38</v>
@@ -2336,10 +2333,10 @@
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>27</v>
@@ -2351,13 +2348,13 @@
         <v>23</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S31" s="9">
-        <v>2969.17</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32">
@@ -2365,22 +2362,22 @@
         <v>22</v>
       </c>
       <c r="B32" s="7">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C32" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="D32" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F32" s="8">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="G32" s="8">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>38</v>
@@ -2389,16 +2386,16 @@
         <v>38</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="N32" s="6" t="s">
         <v>27</v>
@@ -2416,7 +2413,7 @@
         <v>36</v>
       </c>
       <c r="S32" s="9">
-        <v>220</v>
+        <v>38.45</v>
       </c>
     </row>
     <row r="33">
@@ -2427,13 +2424,13 @@
         <v>46188</v>
       </c>
       <c r="C33" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D33" s="7">
         <v>46188</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>23</v>
+      <c r="E33" s="7">
+        <v>46153</v>
       </c>
       <c r="F33" s="8">
         <v>-3</v>
@@ -2448,13 +2445,13 @@
         <v>38</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>23</v>
@@ -2466,16 +2463,16 @@
         <v>27</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S33" s="9">
-        <v>38.45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
@@ -2486,13 +2483,13 @@
         <v>46188</v>
       </c>
       <c r="C34" s="7">
-        <v>46143</v>
+        <v>46188</v>
       </c>
       <c r="D34" s="7">
         <v>46188</v>
       </c>
-      <c r="E34" s="7">
-        <v>46153</v>
+      <c r="E34" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F34" s="8">
         <v>-3</v>
@@ -2507,16 +2504,16 @@
         <v>38</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>27</v>
@@ -2525,16 +2522,16 @@
         <v>27</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S34" s="9">
-        <v>50</v>
+        <v>70.07</v>
       </c>
     </row>
     <row r="35">
@@ -2566,7 +2563,7 @@
         <v>38</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
@@ -2575,7 +2572,7 @@
         <v>65</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N35" s="6" t="s">
         <v>27</v>
@@ -2590,10 +2587,10 @@
         <v>23</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="S35" s="9">
-        <v>70.07</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="36">
@@ -2604,13 +2601,13 @@
         <v>46188</v>
       </c>
       <c r="C36" s="7">
-        <v>46188</v>
+        <v>46082</v>
       </c>
       <c r="D36" s="7">
         <v>46188</v>
       </c>
-      <c r="E36" s="7" t="s">
-        <v>23</v>
+      <c r="E36" s="7">
+        <v>46097</v>
       </c>
       <c r="F36" s="8">
         <v>-3</v>
@@ -2625,16 +2622,16 @@
         <v>38</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>27</v>
@@ -2646,13 +2643,13 @@
         <v>23</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="S36" s="9">
-        <v>112.5</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="37">
@@ -2663,16 +2660,16 @@
         <v>46188</v>
       </c>
       <c r="C37" s="7">
-        <v>46082</v>
+        <v>46181</v>
       </c>
       <c r="D37" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E37" s="7">
-        <v>46097</v>
+        <v>46181</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F37" s="8">
-        <v>-3</v>
+        <v>-10</v>
       </c>
       <c r="G37" s="8">
         <v>-3</v>
@@ -2684,16 +2681,16 @@
         <v>38</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>27</v>
@@ -2705,13 +2702,13 @@
         <v>23</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S37" s="9">
-        <v>146.55</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38">
@@ -2722,16 +2719,16 @@
         <v>46188</v>
       </c>
       <c r="C38" s="7">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="D38" s="7">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-17</v>
+        <v>-3</v>
       </c>
       <c r="G38" s="8">
         <v>-3</v>
@@ -2743,13 +2740,13 @@
         <v>38</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>23</v>
@@ -2770,7 +2767,7 @@
         <v>36</v>
       </c>
       <c r="S38" s="9">
-        <v>180</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39">
@@ -2781,16 +2778,16 @@
         <v>46188</v>
       </c>
       <c r="C39" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="D39" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F39" s="8">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="G39" s="8">
         <v>-3</v>
@@ -2802,16 +2799,16 @@
         <v>38</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>27</v>
@@ -2829,7 +2826,7 @@
         <v>36</v>
       </c>
       <c r="S39" s="9">
-        <v>200</v>
+        <v>279.12</v>
       </c>
     </row>
     <row r="40">
@@ -2845,8 +2842,8 @@
       <c r="D40" s="7">
         <v>46188</v>
       </c>
-      <c r="E40" s="7" t="s">
-        <v>23</v>
+      <c r="E40" s="7">
+        <v>46141</v>
       </c>
       <c r="F40" s="8">
         <v>-3</v>
@@ -2861,13 +2858,13 @@
         <v>38</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>23</v>
@@ -2882,13 +2879,13 @@
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S40" s="9">
-        <v>230</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41">
@@ -2899,16 +2896,16 @@
         <v>46188</v>
       </c>
       <c r="C41" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D41" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F41" s="8">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="G41" s="8">
         <v>-3</v>
@@ -2926,10 +2923,10 @@
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>27</v>
@@ -2944,10 +2941,10 @@
         <v>23</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S41" s="9">
-        <v>279.12</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42">
@@ -2963,8 +2960,8 @@
       <c r="D42" s="7">
         <v>46188</v>
       </c>
-      <c r="E42" s="7">
-        <v>46141</v>
+      <c r="E42" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F42" s="8">
         <v>-3</v>
@@ -2979,13 +2976,13 @@
         <v>38</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -3000,13 +2997,13 @@
         <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S42" s="9">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="43">
@@ -3017,16 +3014,16 @@
         <v>46188</v>
       </c>
       <c r="C43" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="D43" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>23</v>
+        <v>46188</v>
+      </c>
+      <c r="E43" s="7">
+        <v>46170</v>
       </c>
       <c r="F43" s="8">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="G43" s="8">
         <v>-3</v>
@@ -3038,16 +3035,16 @@
         <v>38</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>27</v>
@@ -3059,13 +3056,13 @@
         <v>23</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S43" s="9">
-        <v>310</v>
+        <v>600</v>
       </c>
     </row>
     <row r="44">
@@ -3081,8 +3078,8 @@
       <c r="D44" s="7">
         <v>46188</v>
       </c>
-      <c r="E44" s="7" t="s">
-        <v>23</v>
+      <c r="E44" s="7">
+        <v>46141</v>
       </c>
       <c r="F44" s="8">
         <v>-3</v>
@@ -3097,16 +3094,16 @@
         <v>38</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>27</v>
@@ -3118,13 +3115,13 @@
         <v>23</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S44" s="9">
-        <v>330</v>
+        <v>620</v>
       </c>
     </row>
     <row r="45">
@@ -3135,16 +3132,16 @@
         <v>46188</v>
       </c>
       <c r="C45" s="7">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="D45" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>23</v>
+        <v>46188</v>
+      </c>
+      <c r="E45" s="7">
+        <v>46169</v>
       </c>
       <c r="F45" s="8">
-        <v>-17</v>
+        <v>-3</v>
       </c>
       <c r="G45" s="8">
         <v>-3</v>
@@ -3162,7 +3159,7 @@
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>23</v>
@@ -3177,13 +3174,13 @@
         <v>23</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S45" s="9">
-        <v>410.54</v>
+        <v>630</v>
       </c>
     </row>
     <row r="46">
@@ -3215,16 +3212,16 @@
         <v>38</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>27</v>
@@ -3242,7 +3239,7 @@
         <v>36</v>
       </c>
       <c r="S46" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="47">
@@ -3259,7 +3256,7 @@
         <v>46188</v>
       </c>
       <c r="E47" s="7">
-        <v>46141</v>
+        <v>46188</v>
       </c>
       <c r="F47" s="8">
         <v>-3</v>
@@ -3274,16 +3271,16 @@
         <v>38</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="N47" s="6" t="s">
         <v>27</v>
@@ -3298,10 +3295,10 @@
         <v>35</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S47" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="48">
@@ -3318,7 +3315,7 @@
         <v>46188</v>
       </c>
       <c r="E48" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F48" s="8">
         <v>-3</v>
@@ -3333,16 +3330,16 @@
         <v>38</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N48" s="6" t="s">
         <v>27</v>
@@ -3360,7 +3357,7 @@
         <v>36</v>
       </c>
       <c r="S48" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="49">
@@ -3377,7 +3374,7 @@
         <v>46188</v>
       </c>
       <c r="E49" s="7">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="F49" s="8">
         <v>-3</v>
@@ -3398,7 +3395,7 @@
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>23</v>
@@ -3416,10 +3413,10 @@
         <v>35</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S49" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="50">
@@ -3436,7 +3433,7 @@
         <v>46188</v>
       </c>
       <c r="E50" s="7">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="F50" s="8">
         <v>-3</v>
@@ -3478,7 +3475,7 @@
         <v>36</v>
       </c>
       <c r="S50" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="51">
@@ -3495,7 +3492,7 @@
         <v>46188</v>
       </c>
       <c r="E51" s="7">
-        <v>46188</v>
+        <v>46167</v>
       </c>
       <c r="F51" s="8">
         <v>-3</v>
@@ -3516,7 +3513,7 @@
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>23</v>
@@ -3534,10 +3531,10 @@
         <v>35</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S51" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="52">
@@ -3554,7 +3551,7 @@
         <v>46188</v>
       </c>
       <c r="E52" s="7">
-        <v>46170</v>
+        <v>46141</v>
       </c>
       <c r="F52" s="8">
         <v>-3</v>
@@ -3575,10 +3572,10 @@
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="N52" s="6" t="s">
         <v>27</v>
@@ -3593,10 +3590,10 @@
         <v>35</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S52" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="53">
@@ -3613,7 +3610,7 @@
         <v>46188</v>
       </c>
       <c r="E53" s="7">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="F53" s="8">
         <v>-3</v>
@@ -3628,13 +3625,13 @@
         <v>38</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
@@ -3652,7 +3649,7 @@
         <v>35</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S53" s="9">
         <v>680</v>
@@ -3663,22 +3660,22 @@
         <v>22</v>
       </c>
       <c r="B54" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C54" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D54" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="E54" s="7">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="F54" s="8">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G54" s="8">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>38</v>
@@ -3687,13 +3684,13 @@
         <v>38</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
@@ -3708,13 +3705,13 @@
         <v>23</v>
       </c>
       <c r="Q54" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="S54" s="9">
-        <v>680</v>
+        <v>170.96</v>
       </c>
     </row>
     <row r="55">
@@ -3722,7 +3719,7 @@
         <v>22</v>
       </c>
       <c r="B55" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C55" s="7">
         <v>46188</v>
@@ -3730,14 +3727,14 @@
       <c r="D55" s="7">
         <v>46188</v>
       </c>
-      <c r="E55" s="7">
-        <v>46182</v>
+      <c r="E55" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F55" s="8">
         <v>-3</v>
       </c>
       <c r="G55" s="8">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>38</v>
@@ -3746,13 +3743,13 @@
         <v>38</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
@@ -3767,13 +3764,13 @@
         <v>23</v>
       </c>
       <c r="Q55" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S55" s="9">
-        <v>680</v>
+        <v>134.74</v>
       </c>
     </row>
     <row r="56">
@@ -3781,22 +3778,22 @@
         <v>22</v>
       </c>
       <c r="B56" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C56" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D56" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E56" s="7">
-        <v>46167</v>
+        <v>46174</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F56" s="8">
-        <v>-3</v>
+        <v>-17</v>
       </c>
       <c r="G56" s="8">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>38</v>
@@ -3805,13 +3802,13 @@
         <v>38</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
@@ -3826,13 +3823,13 @@
         <v>23</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S56" s="9">
-        <v>680</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57">
@@ -3840,7 +3837,7 @@
         <v>22</v>
       </c>
       <c r="B57" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C57" s="7">
         <v>46188</v>
@@ -3848,14 +3845,14 @@
       <c r="D57" s="7">
         <v>46188</v>
       </c>
-      <c r="E57" s="7">
-        <v>46141</v>
+      <c r="E57" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F57" s="8">
         <v>-3</v>
       </c>
       <c r="G57" s="8">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>38</v>
@@ -3864,13 +3861,13 @@
         <v>38</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>23</v>
@@ -3882,16 +3879,16 @@
         <v>27</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S57" s="9">
-        <v>680</v>
+        <v>190</v>
       </c>
     </row>
     <row r="58">
@@ -3899,37 +3896,37 @@
         <v>22</v>
       </c>
       <c r="B58" s="7">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="C58" s="7">
         <v>46174</v>
       </c>
       <c r="D58" s="7">
-        <v>46189</v>
-      </c>
-      <c r="E58" s="7">
-        <v>46185</v>
+        <v>46174</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F58" s="8">
-        <v>-2</v>
+        <v>-17</v>
       </c>
       <c r="G58" s="8">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>38</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>23</v>
@@ -3938,19 +3935,19 @@
         <v>27</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="S58" s="9">
-        <v>170.96</v>
+        <v>310.54</v>
       </c>
     </row>
     <row r="59">
@@ -3958,58 +3955,58 @@
         <v>22</v>
       </c>
       <c r="B59" s="7">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="C59" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D59" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>23</v>
+        <v>46192</v>
+      </c>
+      <c r="E59" s="7">
+        <v>46185</v>
       </c>
       <c r="F59" s="8">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="G59" s="8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="I59" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R59" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S59" s="9">
-        <v>134.74</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="60">
@@ -4017,37 +4014,37 @@
         <v>22</v>
       </c>
       <c r="B60" s="7">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="C60" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D60" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>23</v>
+        <v>46181</v>
+      </c>
+      <c r="E60" s="7">
+        <v>46167</v>
       </c>
       <c r="F60" s="8">
-        <v>-17</v>
+        <v>-10</v>
       </c>
       <c r="G60" s="8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>38</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>23</v>
@@ -4056,19 +4053,19 @@
         <v>27</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q60" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S60" s="9">
-        <v>160</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61">
@@ -4076,58 +4073,58 @@
         <v>22</v>
       </c>
       <c r="B61" s="7">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="C61" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D61" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>23</v>
+        <v>46195</v>
+      </c>
+      <c r="E61" s="7">
+        <v>46153</v>
       </c>
       <c r="F61" s="8">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="G61" s="8">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="I61" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q61" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S61" s="9">
-        <v>190</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62">
@@ -4135,22 +4132,22 @@
         <v>22</v>
       </c>
       <c r="B62" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C62" s="7">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="D62" s="7">
-        <v>46192</v>
+        <v>46211</v>
       </c>
       <c r="E62" s="7">
-        <v>46185</v>
+        <v>46190</v>
       </c>
       <c r="F62" s="8">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G62" s="8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>23</v>
@@ -4159,34 +4156,34 @@
         <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>105</v>
+        <v>57</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S62" s="9">
-        <v>2100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63">
@@ -4203,7 +4200,7 @@
         <v>46195</v>
       </c>
       <c r="E63" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="F63" s="8">
         <v>4</v>
@@ -4218,25 +4215,25 @@
         <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="Q63" s="6" t="s">
         <v>29</v>
@@ -4245,7 +4242,7 @@
         <v>36</v>
       </c>
       <c r="S63" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64">
@@ -4256,16 +4253,16 @@
         <v>46195</v>
       </c>
       <c r="C64" s="7">
-        <v>46174</v>
+        <v>46082</v>
       </c>
       <c r="D64" s="7">
-        <v>46211</v>
+        <v>46195</v>
       </c>
       <c r="E64" s="7">
-        <v>46190</v>
+        <v>46097</v>
       </c>
       <c r="F64" s="8">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G64" s="8">
         <v>4</v>
@@ -4277,22 +4274,22 @@
         <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>107</v>
+        <v>25</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
@@ -4301,10 +4298,10 @@
         <v>29</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S64" s="9">
-        <v>50</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="65">
@@ -4315,13 +4312,13 @@
         <v>46195</v>
       </c>
       <c r="C65" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D65" s="7">
         <v>46195</v>
       </c>
       <c r="E65" s="7">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="F65" s="8">
         <v>4</v>
@@ -4336,34 +4333,34 @@
         <v>23</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>45</v>
+        <v>106</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q65" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R65" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S65" s="9">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="66">
@@ -4374,13 +4371,13 @@
         <v>46195</v>
       </c>
       <c r="C66" s="7">
-        <v>46082</v>
+        <v>46195</v>
       </c>
       <c r="D66" s="7">
         <v>46195</v>
       </c>
       <c r="E66" s="7">
-        <v>46097</v>
+        <v>46170</v>
       </c>
       <c r="F66" s="8">
         <v>4</v>
@@ -4395,34 +4392,34 @@
         <v>23</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q66" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S66" s="9">
-        <v>146.55</v>
+        <v>600</v>
       </c>
     </row>
     <row r="67">
@@ -4454,22 +4451,22 @@
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>23</v>
@@ -4498,7 +4495,7 @@
         <v>46195</v>
       </c>
       <c r="E68" s="7">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="F68" s="8">
         <v>4</v>
@@ -4513,22 +4510,22 @@
         <v>23</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
@@ -4537,10 +4534,10 @@
         <v>35</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S68" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="69">
@@ -4557,7 +4554,7 @@
         <v>46195</v>
       </c>
       <c r="E69" s="7">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="F69" s="8">
         <v>4</v>
@@ -4572,22 +4569,22 @@
         <v>23</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
@@ -4599,7 +4596,7 @@
         <v>36</v>
       </c>
       <c r="S69" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="70">
@@ -4616,7 +4613,7 @@
         <v>46195</v>
       </c>
       <c r="E70" s="7">
-        <v>46176</v>
+        <v>46170</v>
       </c>
       <c r="F70" s="8">
         <v>4</v>
@@ -4637,16 +4634,16 @@
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4655,10 +4652,10 @@
         <v>35</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S70" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="71">
@@ -4675,7 +4672,7 @@
         <v>46195</v>
       </c>
       <c r="E71" s="7">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="F71" s="8">
         <v>4</v>
@@ -4696,19 +4693,19 @@
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="Q71" s="6" t="s">
         <v>35</v>
@@ -4734,7 +4731,7 @@
         <v>46195</v>
       </c>
       <c r="E72" s="7">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="F72" s="8">
         <v>4</v>
@@ -4755,19 +4752,19 @@
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="Q72" s="6" t="s">
         <v>35</v>
@@ -4808,22 +4805,22 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4867,22 +4864,22 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4911,7 +4908,7 @@
         <v>46195</v>
       </c>
       <c r="E75" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F75" s="8">
         <v>4</v>
@@ -4932,16 +4929,16 @@
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>23</v>
@@ -4970,7 +4967,7 @@
         <v>46195</v>
       </c>
       <c r="E76" s="7">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="F76" s="8">
         <v>4</v>
@@ -4985,22 +4982,22 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -5012,7 +5009,7 @@
         <v>36</v>
       </c>
       <c r="S76" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="77">
@@ -5044,22 +5041,22 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -5071,7 +5068,7 @@
         <v>36</v>
       </c>
       <c r="S77" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="78">
@@ -5088,7 +5085,7 @@
         <v>46195</v>
       </c>
       <c r="E78" s="7">
-        <v>46170</v>
+        <v>46127</v>
       </c>
       <c r="F78" s="8">
         <v>4</v>
@@ -5103,22 +5100,22 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="M78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>23</v>
@@ -5147,7 +5144,7 @@
         <v>46195</v>
       </c>
       <c r="E79" s="7">
-        <v>46127</v>
+        <v>46153</v>
       </c>
       <c r="F79" s="8">
         <v>4</v>
@@ -5162,22 +5159,22 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
@@ -5206,7 +5203,7 @@
         <v>46195</v>
       </c>
       <c r="E80" s="7">
-        <v>46153</v>
+        <v>46188</v>
       </c>
       <c r="F80" s="8">
         <v>4</v>
@@ -5221,22 +5218,22 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
@@ -5245,7 +5242,7 @@
         <v>35</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S80" s="9">
         <v>650</v>
@@ -5265,7 +5262,7 @@
         <v>46195</v>
       </c>
       <c r="E81" s="7">
-        <v>46160</v>
+        <v>46119</v>
       </c>
       <c r="F81" s="8">
         <v>4</v>
@@ -5280,22 +5277,22 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>23</v>
@@ -5307,7 +5304,7 @@
         <v>36</v>
       </c>
       <c r="S81" s="9">
-        <v>650</v>
+        <v>670</v>
       </c>
     </row>
     <row r="82">
@@ -5324,7 +5321,7 @@
         <v>46195</v>
       </c>
       <c r="E82" s="7">
-        <v>46188</v>
+        <v>46176</v>
       </c>
       <c r="F82" s="8">
         <v>4</v>
@@ -5339,22 +5336,22 @@
         <v>23</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>23</v>
@@ -5363,10 +5360,10 @@
         <v>35</v>
       </c>
       <c r="R82" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S82" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="83">
@@ -5383,7 +5380,7 @@
         <v>46195</v>
       </c>
       <c r="E83" s="7">
-        <v>46119</v>
+        <v>46182</v>
       </c>
       <c r="F83" s="8">
         <v>4</v>
@@ -5398,22 +5395,22 @@
         <v>23</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>23</v>
@@ -5425,7 +5422,7 @@
         <v>36</v>
       </c>
       <c r="S83" s="9">
-        <v>670</v>
+        <v>680</v>
       </c>
     </row>
     <row r="84">
@@ -5442,7 +5439,7 @@
         <v>46195</v>
       </c>
       <c r="E84" s="7">
-        <v>46167</v>
+        <v>46182</v>
       </c>
       <c r="F84" s="8">
         <v>4</v>
@@ -5457,22 +5454,22 @@
         <v>23</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="M84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>23</v>
@@ -5501,7 +5498,7 @@
         <v>46195</v>
       </c>
       <c r="E85" s="7">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="F85" s="8">
         <v>4</v>
@@ -5516,22 +5513,22 @@
         <v>23</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P85" s="6" t="s">
         <v>23</v>
@@ -5560,7 +5557,7 @@
         <v>46195</v>
       </c>
       <c r="E86" s="7">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="F86" s="8">
         <v>4</v>
@@ -5575,22 +5572,22 @@
         <v>23</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>23</v>
@@ -5619,7 +5616,7 @@
         <v>46195</v>
       </c>
       <c r="E87" s="7">
-        <v>46182</v>
+        <v>46164</v>
       </c>
       <c r="F87" s="8">
         <v>4</v>
@@ -5634,22 +5631,22 @@
         <v>23</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>137</v>
+        <v>74</v>
       </c>
       <c r="M87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N87" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P87" s="6" t="s">
         <v>23</v>
@@ -5658,7 +5655,7 @@
         <v>35</v>
       </c>
       <c r="R87" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S87" s="9">
         <v>680</v>
@@ -5678,7 +5675,7 @@
         <v>46195</v>
       </c>
       <c r="E88" s="7">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="F88" s="8">
         <v>4</v>
@@ -5693,25 +5690,25 @@
         <v>23</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="M88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="Q88" s="6" t="s">
         <v>35</v>
@@ -5720,7 +5717,7 @@
         <v>36</v>
       </c>
       <c r="S88" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="89">
@@ -5737,7 +5734,7 @@
         <v>46195</v>
       </c>
       <c r="E89" s="7">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="F89" s="8">
         <v>4</v>
@@ -5752,22 +5749,22 @@
         <v>23</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>76</v>
+        <v>141</v>
       </c>
       <c r="M89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N89" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O89" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P89" s="6" t="s">
         <v>23</v>
@@ -5776,10 +5773,10 @@
         <v>35</v>
       </c>
       <c r="R89" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S89" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="90">
@@ -5796,7 +5793,7 @@
         <v>46195</v>
       </c>
       <c r="E90" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F90" s="8">
         <v>4</v>
@@ -5811,31 +5808,31 @@
         <v>23</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="M90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="Q90" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R90" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S90" s="9">
         <v>700</v>
@@ -5855,7 +5852,7 @@
         <v>46195</v>
       </c>
       <c r="E91" s="7">
-        <v>46188</v>
+        <v>46148</v>
       </c>
       <c r="F91" s="8">
         <v>4</v>
@@ -5870,22 +5867,22 @@
         <v>23</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N91" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O91" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P91" s="6" t="s">
         <v>23</v>
@@ -5894,15 +5891,15 @@
         <v>35</v>
       </c>
       <c r="R91" s="6" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="S91" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="B92" s="7">
         <v>46195</v>
@@ -5914,7 +5911,7 @@
         <v>46195</v>
       </c>
       <c r="E92" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F92" s="8">
         <v>4</v>
@@ -5929,22 +5926,22 @@
         <v>23</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="M92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>23</v>
@@ -5953,15 +5950,15 @@
         <v>35</v>
       </c>
       <c r="R92" s="6" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="S92" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="s">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="B93" s="7">
         <v>46195</v>
@@ -5973,7 +5970,7 @@
         <v>46195</v>
       </c>
       <c r="E93" s="7">
-        <v>46182</v>
+        <v>46148</v>
       </c>
       <c r="F93" s="8">
         <v>4</v>
@@ -5988,22 +5985,22 @@
         <v>23</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="K93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N93" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O93" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P93" s="6" t="s">
         <v>23</v>
@@ -6012,10 +6009,10 @@
         <v>35</v>
       </c>
       <c r="R93" s="6" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="S93" s="9">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="94">
@@ -6032,7 +6029,7 @@
         <v>46195</v>
       </c>
       <c r="E94" s="7">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="F94" s="8">
         <v>4</v>
@@ -6047,34 +6044,34 @@
         <v>23</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="M94" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>23</v>
+        <v>153</v>
       </c>
       <c r="Q94" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R94" s="6" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="S94" s="9">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="95">
@@ -6091,7 +6088,7 @@
         <v>46195</v>
       </c>
       <c r="E95" s="7">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="F95" s="8">
         <v>4</v>
@@ -6106,31 +6103,31 @@
         <v>23</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N95" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O95" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>23</v>
+        <v>153</v>
       </c>
       <c r="Q95" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R95" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="S95" s="9">
         <v>1200</v>
@@ -6141,22 +6138,22 @@
         <v>22</v>
       </c>
       <c r="B96" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="C96" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D96" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="E96" s="7">
-        <v>46160</v>
+        <v>46185</v>
       </c>
       <c r="F96" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G96" s="8">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>23</v>
@@ -6165,34 +6162,34 @@
         <v>23</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>23</v>
+        <v>158</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="Q96" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R96" s="6" t="s">
-        <v>151</v>
+        <v>36</v>
       </c>
       <c r="S96" s="9">
-        <v>1200</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="97">
@@ -6200,22 +6197,22 @@
         <v>22</v>
       </c>
       <c r="B97" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C97" s="7">
-        <v>46195</v>
+        <v>46174</v>
       </c>
       <c r="D97" s="7">
-        <v>46195</v>
+        <v>46218</v>
       </c>
       <c r="E97" s="7">
-        <v>46160</v>
+        <v>46190</v>
       </c>
       <c r="F97" s="8">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="G97" s="8">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="H97" s="6" t="s">
         <v>23</v>
@@ -6224,34 +6221,34 @@
         <v>23</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>156</v>
+        <v>57</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="N97" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O97" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="Q97" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R97" s="6" t="s">
-        <v>151</v>
+        <v>36</v>
       </c>
       <c r="S97" s="9">
-        <v>1200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="98">
@@ -6259,22 +6256,22 @@
         <v>22</v>
       </c>
       <c r="B98" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="C98" s="7">
         <v>46143</v>
       </c>
       <c r="D98" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="E98" s="7">
-        <v>46185</v>
+        <v>46153</v>
       </c>
       <c r="F98" s="8">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G98" s="8">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>23</v>
@@ -6283,34 +6280,34 @@
         <v>23</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>157</v>
+        <v>60</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>158</v>
+        <v>61</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>159</v>
+        <v>23</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="Q98" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S98" s="9">
-        <v>4400</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99">
@@ -6321,16 +6318,16 @@
         <v>46202</v>
       </c>
       <c r="C99" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D99" s="7">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="E99" s="7">
-        <v>46190</v>
+        <v>46167</v>
       </c>
       <c r="F99" s="8">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G99" s="8">
         <v>11</v>
@@ -6342,22 +6339,22 @@
         <v>23</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="N99" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O99" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P99" s="6" t="s">
         <v>23</v>
@@ -6369,7 +6366,7 @@
         <v>36</v>
       </c>
       <c r="S99" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100">
@@ -6383,43 +6380,43 @@
         <v>46143</v>
       </c>
       <c r="D100" s="7">
-        <v>46202</v>
+        <v>46188</v>
       </c>
       <c r="E100" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="F100" s="8">
-        <v>11</v>
+        <v>-3</v>
       </c>
       <c r="G100" s="8">
         <v>11</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="M100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>106</v>
+        <v>27</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="Q100" s="6" t="s">
         <v>29</v>
@@ -6428,7 +6425,7 @@
         <v>36</v>
       </c>
       <c r="S100" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101">
@@ -6439,13 +6436,13 @@
         <v>46202</v>
       </c>
       <c r="C101" s="7">
-        <v>46143</v>
+        <v>46188</v>
       </c>
       <c r="D101" s="7">
         <v>46202</v>
       </c>
       <c r="E101" s="7">
-        <v>46167</v>
+        <v>46188</v>
       </c>
       <c r="F101" s="8">
         <v>11</v>
@@ -6460,34 +6457,34 @@
         <v>23</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>45</v>
+        <v>159</v>
       </c>
       <c r="K101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="M101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N101" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O101" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q101" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R101" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S101" s="9">
-        <v>100</v>
+        <v>116.66</v>
       </c>
     </row>
     <row r="102">
@@ -6498,43 +6495,43 @@
         <v>46202</v>
       </c>
       <c r="C102" s="7">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="D102" s="7">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="E102" s="7">
-        <v>46167</v>
+        <v>46097</v>
       </c>
       <c r="F102" s="8">
-        <v>-3</v>
+        <v>11</v>
       </c>
       <c r="G102" s="8">
         <v>11</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="I102" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="K102" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="M102" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>23</v>
@@ -6543,10 +6540,10 @@
         <v>29</v>
       </c>
       <c r="R102" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S102" s="9">
-        <v>100</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="103">
@@ -6557,13 +6554,13 @@
         <v>46202</v>
       </c>
       <c r="C103" s="7">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="D103" s="7">
         <v>46202</v>
       </c>
       <c r="E103" s="7">
-        <v>46188</v>
+        <v>46169</v>
       </c>
       <c r="F103" s="8">
         <v>11</v>
@@ -6584,16 +6581,16 @@
         <v>23</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="M103" s="6" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="N103" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O103" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P103" s="6" t="s">
         <v>23</v>
@@ -6602,10 +6599,10 @@
         <v>35</v>
       </c>
       <c r="R103" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S103" s="9">
-        <v>116.66</v>
+        <v>600</v>
       </c>
     </row>
     <row r="104">
@@ -6616,13 +6613,13 @@
         <v>46202</v>
       </c>
       <c r="C104" s="7">
-        <v>46082</v>
+        <v>46202</v>
       </c>
       <c r="D104" s="7">
         <v>46202</v>
       </c>
       <c r="E104" s="7">
-        <v>46097</v>
+        <v>46169</v>
       </c>
       <c r="F104" s="8">
         <v>11</v>
@@ -6637,34 +6634,34 @@
         <v>23</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>25</v>
+        <v>161</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>26</v>
+        <v>110</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q104" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R104" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S104" s="9">
-        <v>146.55</v>
+        <v>600</v>
       </c>
     </row>
     <row r="105">
@@ -6681,7 +6678,7 @@
         <v>46202</v>
       </c>
       <c r="E105" s="7">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="F105" s="8">
         <v>11</v>
@@ -6696,22 +6693,22 @@
         <v>23</v>
       </c>
       <c r="J105" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K105" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="N105" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O105" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P105" s="6" t="s">
         <v>23</v>
@@ -6723,7 +6720,7 @@
         <v>36</v>
       </c>
       <c r="S105" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="106">
@@ -6755,22 +6752,22 @@
         <v>23</v>
       </c>
       <c r="J106" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K106" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>112</v>
+        <v>23</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>23</v>
@@ -6782,7 +6779,7 @@
         <v>36</v>
       </c>
       <c r="S106" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="107">
@@ -6799,7 +6796,7 @@
         <v>46202</v>
       </c>
       <c r="E107" s="7">
-        <v>46163</v>
+        <v>46169</v>
       </c>
       <c r="F107" s="8">
         <v>11</v>
@@ -6814,22 +6811,22 @@
         <v>23</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="M107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N107" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O107" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P107" s="6" t="s">
         <v>23</v>
@@ -6873,22 +6870,22 @@
         <v>23</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="M108" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>23</v>
@@ -6917,7 +6914,7 @@
         <v>46202</v>
       </c>
       <c r="E109" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F109" s="8">
         <v>11</v>
@@ -6932,22 +6929,22 @@
         <v>23</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K109" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M109" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N109" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O109" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P109" s="6" t="s">
         <v>23</v>
@@ -6976,7 +6973,7 @@
         <v>46202</v>
       </c>
       <c r="E110" s="7">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="F110" s="8">
         <v>11</v>
@@ -6991,22 +6988,22 @@
         <v>23</v>
       </c>
       <c r="J110" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K110" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="M110" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>23</v>
@@ -7018,7 +7015,7 @@
         <v>36</v>
       </c>
       <c r="S110" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="111">
@@ -7035,7 +7032,7 @@
         <v>46202</v>
       </c>
       <c r="E111" s="7">
-        <v>46164</v>
+        <v>46153</v>
       </c>
       <c r="F111" s="8">
         <v>11</v>
@@ -7050,22 +7047,22 @@
         <v>23</v>
       </c>
       <c r="J111" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K111" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="M111" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N111" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O111" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P111" s="6" t="s">
         <v>23</v>
@@ -7077,7 +7074,7 @@
         <v>36</v>
       </c>
       <c r="S111" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="112">
@@ -7094,7 +7091,7 @@
         <v>46202</v>
       </c>
       <c r="E112" s="7">
-        <v>46160</v>
+        <v>46127</v>
       </c>
       <c r="F112" s="8">
         <v>11</v>
@@ -7109,22 +7106,22 @@
         <v>23</v>
       </c>
       <c r="J112" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K112" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L112" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="M112" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>23</v>
@@ -7153,7 +7150,7 @@
         <v>46202</v>
       </c>
       <c r="E113" s="7">
-        <v>46153</v>
+        <v>46188</v>
       </c>
       <c r="F113" s="8">
         <v>11</v>
@@ -7168,22 +7165,22 @@
         <v>23</v>
       </c>
       <c r="J113" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K113" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="M113" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N113" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O113" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P113" s="6" t="s">
         <v>23</v>
@@ -7192,7 +7189,7 @@
         <v>35</v>
       </c>
       <c r="R113" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S113" s="9">
         <v>650</v>
@@ -7212,7 +7209,7 @@
         <v>46202</v>
       </c>
       <c r="E114" s="7">
-        <v>46127</v>
+        <v>46164</v>
       </c>
       <c r="F114" s="8">
         <v>11</v>
@@ -7227,22 +7224,22 @@
         <v>23</v>
       </c>
       <c r="J114" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K114" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="M114" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>23</v>
@@ -7251,10 +7248,10 @@
         <v>35</v>
       </c>
       <c r="R114" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S114" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="115">
@@ -7271,7 +7268,7 @@
         <v>46202</v>
       </c>
       <c r="E115" s="7">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="F115" s="8">
         <v>11</v>
@@ -7286,22 +7283,22 @@
         <v>23</v>
       </c>
       <c r="J115" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K115" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="M115" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N115" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O115" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P115" s="6" t="s">
         <v>23</v>
@@ -7310,10 +7307,10 @@
         <v>35</v>
       </c>
       <c r="R115" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S115" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="116">
@@ -7330,7 +7327,7 @@
         <v>46202</v>
       </c>
       <c r="E116" s="7">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="F116" s="8">
         <v>11</v>
@@ -7345,22 +7342,22 @@
         <v>23</v>
       </c>
       <c r="J116" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K116" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L116" s="6" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="M116" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>23</v>
@@ -7369,7 +7366,7 @@
         <v>35</v>
       </c>
       <c r="R116" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S116" s="9">
         <v>680</v>
@@ -7404,22 +7401,22 @@
         <v>23</v>
       </c>
       <c r="J117" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K117" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L117" s="6" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="M117" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N117" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O117" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P117" s="6" t="s">
         <v>23</v>
@@ -7448,7 +7445,7 @@
         <v>46202</v>
       </c>
       <c r="E118" s="7">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="F118" s="8">
         <v>11</v>
@@ -7463,22 +7460,22 @@
         <v>23</v>
       </c>
       <c r="J118" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K118" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L118" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="M118" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>23</v>
@@ -7507,7 +7504,7 @@
         <v>46202</v>
       </c>
       <c r="E119" s="7">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="F119" s="8">
         <v>11</v>
@@ -7522,22 +7519,22 @@
         <v>23</v>
       </c>
       <c r="J119" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K119" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L119" s="6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="M119" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N119" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O119" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P119" s="6" t="s">
         <v>23</v>
@@ -7549,7 +7546,7 @@
         <v>36</v>
       </c>
       <c r="S119" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="120">
@@ -7566,7 +7563,7 @@
         <v>46202</v>
       </c>
       <c r="E120" s="7">
-        <v>46167</v>
+        <v>46188</v>
       </c>
       <c r="F120" s="8">
         <v>11</v>
@@ -7581,22 +7578,22 @@
         <v>23</v>
       </c>
       <c r="J120" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K120" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L120" s="6" t="s">
-        <v>55</v>
+        <v>143</v>
       </c>
       <c r="M120" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>23</v>
@@ -7605,15 +7602,15 @@
         <v>35</v>
       </c>
       <c r="R120" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S120" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="s">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="B121" s="7">
         <v>46202</v>
@@ -7625,7 +7622,7 @@
         <v>46202</v>
       </c>
       <c r="E121" s="7">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="F121" s="8">
         <v>11</v>
@@ -7640,22 +7637,22 @@
         <v>23</v>
       </c>
       <c r="J121" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K121" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L121" s="6" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="M121" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N121" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O121" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P121" s="6" t="s">
         <v>23</v>
@@ -7664,10 +7661,10 @@
         <v>35</v>
       </c>
       <c r="R121" s="6" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="S121" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="122">
@@ -7684,7 +7681,7 @@
         <v>46202</v>
       </c>
       <c r="E122" s="7">
-        <v>46170</v>
+        <v>46148</v>
       </c>
       <c r="F122" s="8">
         <v>11</v>
@@ -7699,22 +7696,22 @@
         <v>23</v>
       </c>
       <c r="J122" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K122" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L122" s="6" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="M122" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>23</v>
@@ -7723,15 +7720,15 @@
         <v>35</v>
       </c>
       <c r="R122" s="6" t="s">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="S122" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="s">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="B123" s="7">
         <v>46202</v>
@@ -7743,7 +7740,7 @@
         <v>46202</v>
       </c>
       <c r="E123" s="7">
-        <v>46182</v>
+        <v>46148</v>
       </c>
       <c r="F123" s="8">
         <v>11</v>
@@ -7758,22 +7755,22 @@
         <v>23</v>
       </c>
       <c r="J123" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K123" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L123" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M123" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N123" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O123" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P123" s="6" t="s">
         <v>23</v>
@@ -7782,10 +7779,10 @@
         <v>35</v>
       </c>
       <c r="R123" s="6" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="S123" s="9">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="124">
@@ -7802,7 +7799,7 @@
         <v>46202</v>
       </c>
       <c r="E124" s="7">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="F124" s="8">
         <v>11</v>
@@ -7817,34 +7814,34 @@
         <v>23</v>
       </c>
       <c r="J124" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K124" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L124" s="6" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="M124" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>23</v>
+        <v>153</v>
       </c>
       <c r="Q124" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R124" s="6" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="S124" s="9">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="125">
@@ -7861,7 +7858,7 @@
         <v>46202</v>
       </c>
       <c r="E125" s="7">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="F125" s="8">
         <v>11</v>
@@ -7876,175 +7873,57 @@
         <v>23</v>
       </c>
       <c r="J125" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K125" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L125" s="6" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M125" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N125" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="O125" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P125" s="6" t="s">
-        <v>23</v>
+        <v>153</v>
       </c>
       <c r="Q125" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R125" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="S125" s="9">
         <v>1200</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B126" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C126" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D126" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E126" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F126" s="8">
-        <v>11</v>
-      </c>
-      <c r="G126" s="8">
-        <v>11</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I126" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J126" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="K126" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L126" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="M126" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N126" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="O126" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="P126" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q126" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R126" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="S126" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B127" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C127" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D127" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E127" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F127" s="8">
-        <v>11</v>
-      </c>
-      <c r="G127" s="8">
-        <v>11</v>
-      </c>
-      <c r="H127" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I127" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J127" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="K127" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L127" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="M127" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N127" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="O127" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="P127" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q127" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R127" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="S127" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="128" ht="23" customHeight="1">
-      <c r="A128" s="10"/>
-      <c r="B128" s="11"/>
-      <c r="C128" s="11"/>
-      <c r="D128" s="11"/>
-      <c r="E128" s="11"/>
-      <c r="F128" s="12"/>
-      <c r="G128" s="12"/>
-      <c r="H128" s="10"/>
-      <c r="I128" s="10"/>
-      <c r="J128" s="10"/>
-      <c r="K128" s="10"/>
-      <c r="L128" s="10"/>
-      <c r="M128" s="10"/>
-      <c r="N128" s="10"/>
-      <c r="O128" s="10"/>
-      <c r="P128" s="10"/>
-      <c r="Q128" s="10"/>
-      <c r="R128" s="10"/>
-      <c r="S128" s="13">
-        <f>SUM(S6:S127)</f>
+    <row r="126" ht="23" customHeight="1">
+      <c r="A126" s="10"/>
+      <c r="B126" s="11"/>
+      <c r="C126" s="11"/>
+      <c r="D126" s="11"/>
+      <c r="E126" s="11"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="12"/>
+      <c r="H126" s="10"/>
+      <c r="I126" s="10"/>
+      <c r="J126" s="10"/>
+      <c r="K126" s="10"/>
+      <c r="L126" s="10"/>
+      <c r="M126" s="10"/>
+      <c r="N126" s="10"/>
+      <c r="O126" s="10"/>
+      <c r="P126" s="10"/>
+      <c r="Q126" s="10"/>
+      <c r="R126" s="10"/>
+      <c r="S126" s="13">
+        <f>SUM(S6:S125)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$126</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$124</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quinta-feira, 18 de junho de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em segunda-feira, 22 de junho de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -148,12 +148,12 @@
     <t>FA-11559</t>
   </si>
   <si>
+    <t>FA-11553</t>
+  </si>
+  <si>
     <t>VENCIDO ATÉ 30 DIAS</t>
   </si>
   <si>
-    <t>FA-11553</t>
-  </si>
-  <si>
     <t>FA-11562</t>
   </si>
   <si>
@@ -187,171 +187,165 @@
     <t>FA-11847</t>
   </si>
   <si>
-    <t>FA-11814</t>
+    <t>FA-11693</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>ND-11801</t>
+  </si>
+  <si>
+    <t>FA-11569</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11810</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>ND-11699</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>FA-11806</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>JOAO PAULO CONSORCIOS</t>
+  </si>
+  <si>
+    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
+  </si>
+  <si>
+    <t>FA-11784</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11671</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11774</t>
+  </si>
+  <si>
+    <t>FA-11571</t>
+  </si>
+  <si>
+    <t>FA-11678</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11797</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11787</t>
+  </si>
+  <si>
+    <t>FA-11572</t>
+  </si>
+  <si>
+    <t>FA-11724</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11798</t>
+  </si>
+  <si>
+    <t>FA-11848</t>
+  </si>
+  <si>
+    <t>FA-11776</t>
+  </si>
+  <si>
+    <t>FA-11818</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11679</t>
+  </si>
+  <si>
+    <t>FA-11694</t>
+  </si>
+  <si>
+    <t>FA-11573</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>ND-11844</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11756</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11692</t>
+  </si>
+  <si>
+    <t>FA-11785</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11772</t>
   </si>
   <si>
     <t>OLIZIEL DA SILVA CARDOSO</t>
   </si>
   <si>
-    <t>FA-11693</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>ND-11801</t>
-  </si>
-  <si>
-    <t>FA-11569</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11810</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>ND-11699</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>FA-11806</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>JOAO PAULO CONSORCIOS</t>
-  </si>
-  <si>
-    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
-  </si>
-  <si>
-    <t>FA-11784</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11671</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11774</t>
-  </si>
-  <si>
-    <t>FA-11571</t>
-  </si>
-  <si>
-    <t>FA-11678</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11797</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11787</t>
-  </si>
-  <si>
-    <t>FA-11572</t>
-  </si>
-  <si>
-    <t>FA-11724</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11798</t>
-  </si>
-  <si>
-    <t>FA-11848</t>
-  </si>
-  <si>
-    <t>FA-11776</t>
-  </si>
-  <si>
-    <t>FA-11679</t>
-  </si>
-  <si>
-    <t>FA-11818</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11694</t>
-  </si>
-  <si>
-    <t>FA-11573</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11819</t>
-  </si>
-  <si>
-    <t>ND-11844</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11756</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11692</t>
-  </si>
-  <si>
-    <t>FA-11785</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11772</t>
+    <t>FA-11842</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
+  </si>
+  <si>
+    <t>ND-11700</t>
   </si>
   <si>
     <t>HOJE</t>
   </si>
   <si>
-    <t>FA-11842</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
+    <t>ND-11870</t>
   </si>
   <si>
     <t>A VENCER</t>
   </si>
   <si>
-    <t>ND-11700</t>
-  </si>
-  <si>
-    <t>ND-11870</t>
-  </si>
-  <si>
     <t>FA-11730</t>
   </si>
   <si>
@@ -373,12 +367,12 @@
     <t>FA-11672</t>
   </si>
   <si>
+    <t>FA-11790</t>
+  </si>
+  <si>
     <t>FA-11800</t>
   </si>
   <si>
-    <t>FA-11790</t>
-  </si>
-  <si>
     <t>FA-11733</t>
   </si>
   <si>
@@ -400,27 +394,27 @@
     <t>GILVAN RODRIGUES MACHADO</t>
   </si>
   <si>
+    <t>FA-11799</t>
+  </si>
+  <si>
+    <t>FA-11508</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11625</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
     <t>FA-11660</t>
   </si>
   <si>
     <t>LUCA ZOLI</t>
   </si>
   <si>
-    <t>FA-11799</t>
-  </si>
-  <si>
-    <t>FA-11508</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11625</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
     <t>FA-11850</t>
   </si>
   <si>
@@ -439,15 +433,15 @@
     <t>ANDERSON QUEIROZ PINHEIRO</t>
   </si>
   <si>
+    <t>FA-11695</t>
+  </si>
+  <si>
+    <t>FA-11822</t>
+  </si>
+  <si>
     <t>FA-11823</t>
   </si>
   <si>
-    <t>FA-11695</t>
-  </si>
-  <si>
-    <t>FA-11822</t>
-  </si>
-  <si>
     <t>FA-11680</t>
   </si>
   <si>
@@ -466,18 +460,18 @@
     <t>MAICON LOPES SILVA</t>
   </si>
   <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>FA-11824</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
     <t>FA-11605</t>
   </si>
   <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>FA-11824</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
     <t>FA-11595</t>
   </si>
   <si>
@@ -487,21 +481,21 @@
     <t>LUZ DIVINA LTDA</t>
   </si>
   <si>
+    <t>FA-11648</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
     <t>FA-11636</t>
   </si>
   <si>
     <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
   </si>
   <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-11648</t>
-  </si>
-  <si>
-    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
-  </si>
-  <si>
     <t>FA-11843</t>
   </si>
   <si>
@@ -535,25 +529,25 @@
     <t>FA-11688</t>
   </si>
   <si>
+    <t>FA-11626</t>
+  </si>
+  <si>
+    <t>FA-11509</t>
+  </si>
+  <si>
     <t>FA-11661</t>
   </si>
   <si>
-    <t>FA-11626</t>
-  </si>
-  <si>
-    <t>FA-11509</t>
-  </si>
-  <si>
     <t>FA-11852</t>
   </si>
   <si>
+    <t>FA-11827</t>
+  </si>
+  <si>
     <t>FA-11681</t>
   </si>
   <si>
     <t>FA-11826</t>
-  </si>
-  <si>
-    <t>FA-11827</t>
   </si>
   <si>
     <t>FA-11825</t>
@@ -723,7 +717,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S126"/>
+  <dimension ref="A1:S124"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -840,10 +834,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-66</v>
+        <v>-70</v>
       </c>
       <c r="G6" s="8">
-        <v>-57</v>
+        <v>-61</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -899,10 +893,10 @@
         <v>46097</v>
       </c>
       <c r="F7" s="8">
-        <v>-52</v>
+        <v>-56</v>
       </c>
       <c r="G7" s="8">
-        <v>-52</v>
+        <v>-56</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>24</v>
@@ -958,10 +952,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-59</v>
+        <v>-63</v>
       </c>
       <c r="G8" s="8">
-        <v>-51</v>
+        <v>-55</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -1017,10 +1011,10 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-80</v>
+        <v>-84</v>
       </c>
       <c r="G9" s="8">
-        <v>-51</v>
+        <v>-55</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>24</v>
@@ -1076,10 +1070,10 @@
         <v>23</v>
       </c>
       <c r="F10" s="8">
-        <v>-66</v>
+        <v>-70</v>
       </c>
       <c r="G10" s="8">
-        <v>-51</v>
+        <v>-55</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>24</v>
@@ -1135,10 +1129,10 @@
         <v>46097</v>
       </c>
       <c r="F11" s="8">
-        <v>-45</v>
+        <v>-49</v>
       </c>
       <c r="G11" s="8">
-        <v>-45</v>
+        <v>-49</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>24</v>
@@ -1194,10 +1188,10 @@
         <v>46097</v>
       </c>
       <c r="F12" s="8">
-        <v>-38</v>
+        <v>-42</v>
       </c>
       <c r="G12" s="8">
-        <v>-38</v>
+        <v>-42</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>24</v>
@@ -1253,10 +1247,10 @@
         <v>46141</v>
       </c>
       <c r="F13" s="8">
-        <v>-38</v>
+        <v>-42</v>
       </c>
       <c r="G13" s="8">
-        <v>-38</v>
+        <v>-42</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>24</v>
@@ -1312,10 +1306,10 @@
         <v>46097</v>
       </c>
       <c r="F14" s="8">
-        <v>-31</v>
+        <v>-35</v>
       </c>
       <c r="G14" s="8">
-        <v>-31</v>
+        <v>-35</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>24</v>
@@ -1371,10 +1365,10 @@
         <v>46141</v>
       </c>
       <c r="F15" s="8">
-        <v>-31</v>
+        <v>-35</v>
       </c>
       <c r="G15" s="8">
-        <v>-31</v>
+        <v>-35</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>24</v>
@@ -1430,19 +1424,19 @@
         <v>23</v>
       </c>
       <c r="F16" s="8">
-        <v>-45</v>
+        <v>-49</v>
       </c>
       <c r="G16" s="8">
-        <v>-27</v>
+        <v>-31</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>24</v>
       </c>
       <c r="I16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>23</v>
@@ -1489,16 +1483,16 @@
         <v>46097</v>
       </c>
       <c r="F17" s="8">
-        <v>-24</v>
+        <v>-28</v>
       </c>
       <c r="G17" s="8">
-        <v>-24</v>
+        <v>-28</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J17" s="6" t="s">
         <v>25</v>
@@ -1548,16 +1542,16 @@
         <v>46141</v>
       </c>
       <c r="F18" s="8">
-        <v>-24</v>
+        <v>-28</v>
       </c>
       <c r="G18" s="8">
-        <v>-24</v>
+        <v>-28</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>40</v>
@@ -1607,16 +1601,16 @@
         <v>23</v>
       </c>
       <c r="F19" s="8">
-        <v>-19</v>
+        <v>-23</v>
       </c>
       <c r="G19" s="8">
-        <v>-19</v>
+        <v>-23</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>23</v>
@@ -1666,16 +1660,16 @@
         <v>46097</v>
       </c>
       <c r="F20" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="G20" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>25</v>
@@ -1725,16 +1719,16 @@
         <v>46141</v>
       </c>
       <c r="F21" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="G21" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>42</v>
@@ -1784,16 +1778,16 @@
         <v>23</v>
       </c>
       <c r="F22" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="G22" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>43</v>
@@ -1843,16 +1837,16 @@
         <v>46097</v>
       </c>
       <c r="F23" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G23" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>25</v>
@@ -1902,16 +1896,16 @@
         <v>46141</v>
       </c>
       <c r="F24" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G24" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>45</v>
@@ -1961,16 +1955,16 @@
         <v>46170</v>
       </c>
       <c r="F25" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G25" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>46</v>
@@ -2020,16 +2014,16 @@
         <v>46170</v>
       </c>
       <c r="F26" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G26" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>48</v>
@@ -2079,16 +2073,16 @@
         <v>46188</v>
       </c>
       <c r="F27" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G27" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>50</v>
@@ -2135,19 +2129,19 @@
         <v>46181</v>
       </c>
       <c r="E28" s="7">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="F28" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G28" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>51</v>
@@ -2188,25 +2182,25 @@
         <v>46181</v>
       </c>
       <c r="C29" s="7">
-        <v>46181</v>
+        <v>46143</v>
       </c>
       <c r="D29" s="7">
         <v>46181</v>
       </c>
       <c r="E29" s="7">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="F29" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G29" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>53</v>
@@ -2215,7 +2209,7 @@
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>23</v>
@@ -2230,13 +2224,13 @@
         <v>23</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S29" s="9">
-        <v>680</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="30">
@@ -2244,40 +2238,40 @@
         <v>22</v>
       </c>
       <c r="B30" s="7">
+        <v>46185</v>
+      </c>
+      <c r="C30" s="7">
         <v>46181</v>
-      </c>
-      <c r="C30" s="7">
-        <v>46143</v>
       </c>
       <c r="D30" s="7">
         <v>46181</v>
       </c>
-      <c r="E30" s="7">
-        <v>46170</v>
+      <c r="E30" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F30" s="8">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="G30" s="8">
         <v>-10</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J30" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>26</v>
-      </c>
       <c r="M30" s="6" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -2289,13 +2283,13 @@
         <v>23</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S30" s="9">
-        <v>2969.17</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31">
@@ -2303,28 +2297,28 @@
         <v>22</v>
       </c>
       <c r="B31" s="7">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C31" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="D31" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F31" s="8">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="G31" s="8">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>56</v>
@@ -2336,7 +2330,7 @@
         <v>57</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>27</v>
@@ -2354,7 +2348,7 @@
         <v>36</v>
       </c>
       <c r="S31" s="9">
-        <v>220</v>
+        <v>38.45</v>
       </c>
     </row>
     <row r="32">
@@ -2365,25 +2359,25 @@
         <v>46188</v>
       </c>
       <c r="C32" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D32" s="7">
         <v>46188</v>
       </c>
-      <c r="E32" s="7" t="s">
-        <v>23</v>
+      <c r="E32" s="7">
+        <v>46153</v>
       </c>
       <c r="F32" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G32" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>58</v>
@@ -2404,16 +2398,16 @@
         <v>27</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S32" s="9">
-        <v>38.45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
@@ -2424,37 +2418,37 @@
         <v>46188</v>
       </c>
       <c r="C33" s="7">
-        <v>46143</v>
+        <v>46188</v>
       </c>
       <c r="D33" s="7">
         <v>46188</v>
       </c>
-      <c r="E33" s="7">
-        <v>46153</v>
+      <c r="E33" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F33" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G33" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>27</v>
@@ -2463,16 +2457,16 @@
         <v>27</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S33" s="9">
-        <v>50</v>
+        <v>70.07</v>
       </c>
     </row>
     <row r="34">
@@ -2492,25 +2486,25 @@
         <v>23</v>
       </c>
       <c r="F34" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G34" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>64</v>
@@ -2528,10 +2522,10 @@
         <v>23</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="S34" s="9">
-        <v>70.07</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="35">
@@ -2542,37 +2536,37 @@
         <v>46188</v>
       </c>
       <c r="C35" s="7">
-        <v>46188</v>
+        <v>46082</v>
       </c>
       <c r="D35" s="7">
         <v>46188</v>
       </c>
-      <c r="E35" s="7" t="s">
-        <v>23</v>
+      <c r="E35" s="7">
+        <v>46097</v>
       </c>
       <c r="F35" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G35" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N35" s="6" t="s">
         <v>27</v>
@@ -2584,13 +2578,13 @@
         <v>23</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="S35" s="9">
-        <v>112.5</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="36">
@@ -2601,37 +2595,37 @@
         <v>46188</v>
       </c>
       <c r="C36" s="7">
-        <v>46082</v>
+        <v>46181</v>
       </c>
       <c r="D36" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E36" s="7">
-        <v>46097</v>
+        <v>46181</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F36" s="8">
-        <v>-3</v>
+        <v>-14</v>
       </c>
       <c r="G36" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>27</v>
@@ -2643,13 +2637,13 @@
         <v>23</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S36" s="9">
-        <v>146.55</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37">
@@ -2660,25 +2654,25 @@
         <v>46188</v>
       </c>
       <c r="C37" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="D37" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F37" s="8">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="G37" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>67</v>
@@ -2690,7 +2684,7 @@
         <v>68</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>27</v>
@@ -2708,7 +2702,7 @@
         <v>36</v>
       </c>
       <c r="S37" s="9">
-        <v>200</v>
+        <v>230</v>
       </c>
     </row>
     <row r="38">
@@ -2719,25 +2713,25 @@
         <v>46188</v>
       </c>
       <c r="C38" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D38" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-3</v>
+        <v>-21</v>
       </c>
       <c r="G38" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J38" s="6" t="s">
         <v>69</v>
@@ -2746,10 +2740,10 @@
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>27</v>
@@ -2767,7 +2761,7 @@
         <v>36</v>
       </c>
       <c r="S38" s="9">
-        <v>230</v>
+        <v>279.12</v>
       </c>
     </row>
     <row r="39">
@@ -2778,37 +2772,37 @@
         <v>46188</v>
       </c>
       <c r="C39" s="7">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="D39" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>23</v>
+        <v>46188</v>
+      </c>
+      <c r="E39" s="7">
+        <v>46141</v>
       </c>
       <c r="F39" s="8">
-        <v>-17</v>
+        <v>-7</v>
       </c>
       <c r="G39" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>27</v>
@@ -2820,13 +2814,13 @@
         <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S39" s="9">
-        <v>279.12</v>
+        <v>310</v>
       </c>
     </row>
     <row r="40">
@@ -2837,35 +2831,35 @@
         <v>46188</v>
       </c>
       <c r="C40" s="7">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="D40" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E40" s="7">
-        <v>46141</v>
+        <v>46181</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F40" s="8">
-        <v>-3</v>
+        <v>-14</v>
       </c>
       <c r="G40" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J40" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="K40" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L40" s="6" t="s">
-        <v>34</v>
-      </c>
       <c r="M40" s="6" t="s">
         <v>23</v>
       </c>
@@ -2879,10 +2873,10 @@
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S40" s="9">
         <v>310</v>
@@ -2896,25 +2890,25 @@
         <v>46188</v>
       </c>
       <c r="C41" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="D41" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F41" s="8">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="G41" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>73</v>
@@ -2941,10 +2935,10 @@
         <v>23</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S41" s="9">
-        <v>310</v>
+        <v>330</v>
       </c>
     </row>
     <row r="42">
@@ -2960,20 +2954,20 @@
       <c r="D42" s="7">
         <v>46188</v>
       </c>
-      <c r="E42" s="7" t="s">
-        <v>23</v>
+      <c r="E42" s="7">
+        <v>46170</v>
       </c>
       <c r="F42" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G42" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J42" s="6" t="s">
         <v>75</v>
@@ -2982,10 +2976,10 @@
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="N42" s="6" t="s">
         <v>27</v>
@@ -2997,13 +2991,13 @@
         <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S42" s="9">
-        <v>330</v>
+        <v>600</v>
       </c>
     </row>
     <row r="43">
@@ -3020,31 +3014,31 @@
         <v>46188</v>
       </c>
       <c r="E43" s="7">
-        <v>46170</v>
+        <v>46141</v>
       </c>
       <c r="F43" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G43" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>27</v>
@@ -3062,7 +3056,7 @@
         <v>36</v>
       </c>
       <c r="S43" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="44">
@@ -3079,31 +3073,31 @@
         <v>46188</v>
       </c>
       <c r="E44" s="7">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="F44" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G44" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J44" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="K44" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>57</v>
-      </c>
       <c r="M44" s="6" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>27</v>
@@ -3121,7 +3115,7 @@
         <v>36</v>
       </c>
       <c r="S44" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="45">
@@ -3138,19 +3132,19 @@
         <v>46188</v>
       </c>
       <c r="E45" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F45" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G45" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J45" s="6" t="s">
         <v>79</v>
@@ -3159,7 +3153,7 @@
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>23</v>
@@ -3197,28 +3191,28 @@
         <v>46188</v>
       </c>
       <c r="E46" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F46" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G46" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>23</v>
@@ -3236,10 +3230,10 @@
         <v>35</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S46" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="47">
@@ -3256,31 +3250,31 @@
         <v>46188</v>
       </c>
       <c r="E47" s="7">
-        <v>46188</v>
+        <v>46170</v>
       </c>
       <c r="F47" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G47" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N47" s="6" t="s">
         <v>27</v>
@@ -3295,7 +3289,7 @@
         <v>35</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S47" s="9">
         <v>650</v>
@@ -3315,31 +3309,31 @@
         <v>46188</v>
       </c>
       <c r="E48" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F48" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G48" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J48" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="K48" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>49</v>
-      </c>
       <c r="M48" s="6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="N48" s="6" t="s">
         <v>27</v>
@@ -3357,7 +3351,7 @@
         <v>36</v>
       </c>
       <c r="S48" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="49">
@@ -3377,16 +3371,16 @@
         <v>46164</v>
       </c>
       <c r="F49" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G49" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J49" s="6" t="s">
         <v>84</v>
@@ -3395,7 +3389,7 @@
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>23</v>
@@ -3433,19 +3427,19 @@
         <v>46188</v>
       </c>
       <c r="E50" s="7">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="F50" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G50" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J50" s="6" t="s">
         <v>85</v>
@@ -3454,7 +3448,7 @@
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>23</v>
@@ -3492,28 +3486,28 @@
         <v>46188</v>
       </c>
       <c r="E51" s="7">
-        <v>46167</v>
+        <v>46141</v>
       </c>
       <c r="F51" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G51" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J51" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="K51" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L51" s="6" t="s">
-        <v>54</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>23</v>
@@ -3531,7 +3525,7 @@
         <v>35</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S51" s="9">
         <v>680</v>
@@ -3542,28 +3536,28 @@
         <v>22</v>
       </c>
       <c r="B52" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C52" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D52" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="E52" s="7">
-        <v>46141</v>
+        <v>46185</v>
       </c>
       <c r="F52" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G52" s="8">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>88</v>
@@ -3587,13 +3581,13 @@
         <v>23</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="S52" s="9">
-        <v>680</v>
+        <v>170.96</v>
       </c>
     </row>
     <row r="53">
@@ -3601,7 +3595,7 @@
         <v>22</v>
       </c>
       <c r="B53" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C53" s="7">
         <v>46188</v>
@@ -3609,29 +3603,29 @@
       <c r="D53" s="7">
         <v>46188</v>
       </c>
-      <c r="E53" s="7">
-        <v>46182</v>
+      <c r="E53" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F53" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G53" s="8">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>23</v>
@@ -3646,13 +3640,13 @@
         <v>23</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S53" s="9">
-        <v>680</v>
+        <v>134.74</v>
       </c>
     </row>
     <row r="54">
@@ -3660,37 +3654,37 @@
         <v>22</v>
       </c>
       <c r="B54" s="7">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="C54" s="7">
         <v>46174</v>
       </c>
       <c r="D54" s="7">
-        <v>46189</v>
-      </c>
-      <c r="E54" s="7">
-        <v>46185</v>
+        <v>46174</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F54" s="8">
-        <v>-2</v>
+        <v>-21</v>
       </c>
       <c r="G54" s="8">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
@@ -3705,13 +3699,13 @@
         <v>23</v>
       </c>
       <c r="Q54" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>93</v>
+        <v>36</v>
       </c>
       <c r="S54" s="9">
-        <v>170.96</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55">
@@ -3731,16 +3725,16 @@
         <v>23</v>
       </c>
       <c r="F55" s="8">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="G55" s="8">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J55" s="6" t="s">
         <v>94</v>
@@ -3761,7 +3755,7 @@
         <v>27</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q55" s="6" t="s">
         <v>23</v>
@@ -3770,7 +3764,7 @@
         <v>36</v>
       </c>
       <c r="S55" s="9">
-        <v>134.74</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56">
@@ -3778,7 +3772,7 @@
         <v>22</v>
       </c>
       <c r="B56" s="7">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="C56" s="7">
         <v>46174</v>
@@ -3790,16 +3784,16 @@
         <v>23</v>
       </c>
       <c r="F56" s="8">
-        <v>-17</v>
+        <v>-21</v>
       </c>
       <c r="G56" s="8">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J56" s="6" t="s">
         <v>96</v>
@@ -3808,7 +3802,7 @@
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
@@ -3829,7 +3823,7 @@
         <v>36</v>
       </c>
       <c r="S56" s="9">
-        <v>160</v>
+        <v>310.54</v>
       </c>
     </row>
     <row r="57">
@@ -3837,40 +3831,40 @@
         <v>22</v>
       </c>
       <c r="B57" s="7">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="C57" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D57" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>23</v>
+        <v>46192</v>
+      </c>
+      <c r="E57" s="7">
+        <v>46185</v>
       </c>
       <c r="F57" s="8">
         <v>-3</v>
       </c>
       <c r="G57" s="8">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="N57" s="6" t="s">
         <v>27</v>
@@ -3879,16 +3873,16 @@
         <v>27</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S57" s="9">
-        <v>190</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="58">
@@ -3896,37 +3890,37 @@
         <v>22</v>
       </c>
       <c r="B58" s="7">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="C58" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D58" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>23</v>
+        <v>46181</v>
+      </c>
+      <c r="E58" s="7">
+        <v>46167</v>
       </c>
       <c r="F58" s="8">
-        <v>-17</v>
+        <v>-14</v>
       </c>
       <c r="G58" s="8">
         <v>0</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>23</v>
@@ -3935,19 +3929,19 @@
         <v>27</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R58" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S58" s="9">
-        <v>310.54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
@@ -3955,22 +3949,22 @@
         <v>22</v>
       </c>
       <c r="B59" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C59" s="7">
         <v>46143</v>
       </c>
       <c r="D59" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="E59" s="7">
-        <v>46185</v>
+        <v>46153</v>
       </c>
       <c r="F59" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>23</v>
@@ -3979,34 +3973,34 @@
         <v>23</v>
       </c>
       <c r="J59" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N59" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="K59" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L59" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="M59" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="N59" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="O59" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R59" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S59" s="9">
-        <v>2100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60">
@@ -4017,43 +4011,43 @@
         <v>46195</v>
       </c>
       <c r="C60" s="7">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="D60" s="7">
-        <v>46181</v>
+        <v>46211</v>
       </c>
       <c r="E60" s="7">
-        <v>46167</v>
+        <v>46190</v>
       </c>
       <c r="F60" s="8">
-        <v>-10</v>
+        <v>16</v>
       </c>
       <c r="G60" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>23</v>
@@ -4082,13 +4076,13 @@
         <v>46195</v>
       </c>
       <c r="E61" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="F61" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G61" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>23</v>
@@ -4097,25 +4091,25 @@
         <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="Q61" s="6" t="s">
         <v>29</v>
@@ -4124,7 +4118,7 @@
         <v>36</v>
       </c>
       <c r="S61" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62">
@@ -4135,19 +4129,19 @@
         <v>46195</v>
       </c>
       <c r="C62" s="7">
-        <v>46174</v>
+        <v>46082</v>
       </c>
       <c r="D62" s="7">
-        <v>46211</v>
+        <v>46195</v>
       </c>
       <c r="E62" s="7">
-        <v>46190</v>
+        <v>46097</v>
       </c>
       <c r="F62" s="8">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G62" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>23</v>
@@ -4156,22 +4150,22 @@
         <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>23</v>
@@ -4180,10 +4174,10 @@
         <v>29</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S62" s="9">
-        <v>50</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="63">
@@ -4194,19 +4188,19 @@
         <v>46195</v>
       </c>
       <c r="C63" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D63" s="7">
         <v>46195</v>
       </c>
       <c r="E63" s="7">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="F63" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G63" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>23</v>
@@ -4221,28 +4215,28 @@
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>23</v>
+        <v>105</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q63" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S63" s="9">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="64">
@@ -4253,19 +4247,19 @@
         <v>46195</v>
       </c>
       <c r="C64" s="7">
-        <v>46082</v>
+        <v>46195</v>
       </c>
       <c r="D64" s="7">
         <v>46195</v>
       </c>
       <c r="E64" s="7">
-        <v>46097</v>
+        <v>46170</v>
       </c>
       <c r="F64" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G64" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>23</v>
@@ -4274,34 +4268,34 @@
         <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q64" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S64" s="9">
-        <v>146.55</v>
+        <v>600</v>
       </c>
     </row>
     <row r="65">
@@ -4321,10 +4315,10 @@
         <v>46169</v>
       </c>
       <c r="F65" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G65" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>23</v>
@@ -4333,22 +4327,22 @@
         <v>23</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
@@ -4377,13 +4371,13 @@
         <v>46195</v>
       </c>
       <c r="E66" s="7">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="F66" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G66" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>23</v>
@@ -4392,22 +4386,22 @@
         <v>23</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
@@ -4416,10 +4410,10 @@
         <v>35</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S66" s="9">
-        <v>600</v>
+        <v>620</v>
       </c>
     </row>
     <row r="67">
@@ -4436,13 +4430,13 @@
         <v>46195</v>
       </c>
       <c r="E67" s="7">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="F67" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G67" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>23</v>
@@ -4451,22 +4445,22 @@
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>23</v>
@@ -4478,7 +4472,7 @@
         <v>36</v>
       </c>
       <c r="S67" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="68">
@@ -4495,13 +4489,13 @@
         <v>46195</v>
       </c>
       <c r="E68" s="7">
-        <v>46176</v>
+        <v>46170</v>
       </c>
       <c r="F68" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G68" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>23</v>
@@ -4516,28 +4510,28 @@
         <v>23</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q68" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S68" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="69">
@@ -4554,13 +4548,13 @@
         <v>46195</v>
       </c>
       <c r="E69" s="7">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="F69" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G69" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>23</v>
@@ -4575,16 +4569,16 @@
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="M69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
@@ -4613,13 +4607,13 @@
         <v>46195</v>
       </c>
       <c r="E70" s="7">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="F70" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G70" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>23</v>
@@ -4634,16 +4628,16 @@
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4672,13 +4666,13 @@
         <v>46195</v>
       </c>
       <c r="E71" s="7">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="F71" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G71" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4687,25 +4681,25 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="Q71" s="6" t="s">
         <v>35</v>
@@ -4734,10 +4728,10 @@
         <v>46169</v>
       </c>
       <c r="F72" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G72" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4746,22 +4740,22 @@
         <v>23</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>23</v>
@@ -4790,13 +4784,13 @@
         <v>46195</v>
       </c>
       <c r="E73" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F73" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G73" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4805,22 +4799,22 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4849,13 +4843,13 @@
         <v>46195</v>
       </c>
       <c r="E74" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F74" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G74" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4864,22 +4858,22 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4891,7 +4885,7 @@
         <v>36</v>
       </c>
       <c r="S74" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="75">
@@ -4908,13 +4902,13 @@
         <v>46195</v>
       </c>
       <c r="E75" s="7">
-        <v>46164</v>
+        <v>46127</v>
       </c>
       <c r="F75" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G75" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>23</v>
@@ -4923,22 +4917,22 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>23</v>
@@ -4950,7 +4944,7 @@
         <v>36</v>
       </c>
       <c r="S75" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="76">
@@ -4967,13 +4961,13 @@
         <v>46195</v>
       </c>
       <c r="E76" s="7">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="F76" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G76" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -4982,22 +4976,22 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -5026,13 +5020,13 @@
         <v>46195</v>
       </c>
       <c r="E77" s="7">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="F77" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G77" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -5041,22 +5035,22 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -5085,13 +5079,13 @@
         <v>46195</v>
       </c>
       <c r="E78" s="7">
-        <v>46127</v>
+        <v>46188</v>
       </c>
       <c r="F78" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G78" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -5100,22 +5094,22 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>126</v>
+        <v>44</v>
       </c>
       <c r="M78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>23</v>
@@ -5124,7 +5118,7 @@
         <v>35</v>
       </c>
       <c r="R78" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S78" s="9">
         <v>650</v>
@@ -5144,13 +5138,13 @@
         <v>46195</v>
       </c>
       <c r="E79" s="7">
-        <v>46153</v>
+        <v>46119</v>
       </c>
       <c r="F79" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G79" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>23</v>
@@ -5159,22 +5153,22 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
@@ -5186,7 +5180,7 @@
         <v>36</v>
       </c>
       <c r="S79" s="9">
-        <v>650</v>
+        <v>670</v>
       </c>
     </row>
     <row r="80">
@@ -5203,13 +5197,13 @@
         <v>46195</v>
       </c>
       <c r="E80" s="7">
-        <v>46188</v>
+        <v>46176</v>
       </c>
       <c r="F80" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G80" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>23</v>
@@ -5218,22 +5212,22 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
@@ -5242,10 +5236,10 @@
         <v>35</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S80" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="81">
@@ -5262,13 +5256,13 @@
         <v>46195</v>
       </c>
       <c r="E81" s="7">
-        <v>46119</v>
+        <v>46182</v>
       </c>
       <c r="F81" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G81" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>23</v>
@@ -5277,22 +5271,22 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>23</v>
@@ -5304,7 +5298,7 @@
         <v>36</v>
       </c>
       <c r="S81" s="9">
-        <v>670</v>
+        <v>680</v>
       </c>
     </row>
     <row r="82">
@@ -5321,13 +5315,13 @@
         <v>46195</v>
       </c>
       <c r="E82" s="7">
-        <v>46176</v>
+        <v>46167</v>
       </c>
       <c r="F82" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G82" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>23</v>
@@ -5336,22 +5330,22 @@
         <v>23</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>23</v>
@@ -5383,10 +5377,10 @@
         <v>46182</v>
       </c>
       <c r="F83" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G83" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>23</v>
@@ -5395,22 +5389,22 @@
         <v>23</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>134</v>
+        <v>83</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>23</v>
@@ -5442,10 +5436,10 @@
         <v>46182</v>
       </c>
       <c r="F84" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G84" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>23</v>
@@ -5460,16 +5454,16 @@
         <v>23</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>52</v>
+        <v>97</v>
       </c>
       <c r="M84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>23</v>
@@ -5498,13 +5492,13 @@
         <v>46195</v>
       </c>
       <c r="E85" s="7">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="F85" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G85" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>23</v>
@@ -5519,16 +5513,16 @@
         <v>23</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="M85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P85" s="6" t="s">
         <v>23</v>
@@ -5537,7 +5531,7 @@
         <v>35</v>
       </c>
       <c r="R85" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S85" s="9">
         <v>680</v>
@@ -5557,13 +5551,13 @@
         <v>46195</v>
       </c>
       <c r="E86" s="7">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="F86" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G86" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>23</v>
@@ -5578,19 +5572,19 @@
         <v>23</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q86" s="6" t="s">
         <v>35</v>
@@ -5599,7 +5593,7 @@
         <v>36</v>
       </c>
       <c r="S86" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="87">
@@ -5616,13 +5610,13 @@
         <v>46195</v>
       </c>
       <c r="E87" s="7">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="F87" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G87" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H87" s="6" t="s">
         <v>23</v>
@@ -5637,16 +5631,16 @@
         <v>23</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>74</v>
+        <v>139</v>
       </c>
       <c r="M87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N87" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P87" s="6" t="s">
         <v>23</v>
@@ -5655,10 +5649,10 @@
         <v>35</v>
       </c>
       <c r="R87" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S87" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="88">
@@ -5675,13 +5669,13 @@
         <v>46195</v>
       </c>
       <c r="E88" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F88" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G88" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>23</v>
@@ -5690,31 +5684,31 @@
         <v>23</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="M88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="Q88" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R88" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S88" s="9">
         <v>700</v>
@@ -5722,7 +5716,7 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>22</v>
+        <v>142</v>
       </c>
       <c r="B89" s="7">
         <v>46195</v>
@@ -5734,13 +5728,13 @@
         <v>46195</v>
       </c>
       <c r="E89" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F89" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G89" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>23</v>
@@ -5749,22 +5743,22 @@
         <v>23</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N89" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O89" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P89" s="6" t="s">
         <v>23</v>
@@ -5773,10 +5767,10 @@
         <v>35</v>
       </c>
       <c r="R89" s="6" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="S89" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="90">
@@ -5793,13 +5787,13 @@
         <v>46195</v>
       </c>
       <c r="E90" s="7">
-        <v>46188</v>
+        <v>46148</v>
       </c>
       <c r="F90" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G90" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>23</v>
@@ -5808,22 +5802,22 @@
         <v>23</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>143</v>
+        <v>89</v>
       </c>
       <c r="M90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>23</v>
@@ -5832,10 +5826,10 @@
         <v>35</v>
       </c>
       <c r="R90" s="6" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="S90" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="91">
@@ -5855,10 +5849,10 @@
         <v>46148</v>
       </c>
       <c r="F91" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G91" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>23</v>
@@ -5867,22 +5861,22 @@
         <v>23</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N91" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O91" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P91" s="6" t="s">
         <v>23</v>
@@ -5891,15 +5885,15 @@
         <v>35</v>
       </c>
       <c r="R91" s="6" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="S91" s="9">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="B92" s="7">
         <v>46195</v>
@@ -5911,13 +5905,13 @@
         <v>46195</v>
       </c>
       <c r="E92" s="7">
-        <v>46182</v>
+        <v>46160</v>
       </c>
       <c r="F92" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G92" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>23</v>
@@ -5926,34 +5920,34 @@
         <v>23</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="Q92" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R92" s="6" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="S92" s="9">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="93">
@@ -5970,13 +5964,13 @@
         <v>46195</v>
       </c>
       <c r="E93" s="7">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="F93" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G93" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>23</v>
@@ -5985,31 +5979,31 @@
         <v>23</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="M93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N93" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O93" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="Q93" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R93" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="S93" s="9">
         <v>1200</v>
@@ -6020,22 +6014,22 @@
         <v>22</v>
       </c>
       <c r="B94" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="C94" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D94" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="E94" s="7">
-        <v>46160</v>
+        <v>46185</v>
       </c>
       <c r="F94" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G94" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>23</v>
@@ -6044,16 +6038,16 @@
         <v>23</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>23</v>
+        <v>156</v>
       </c>
       <c r="N94" s="6" t="s">
         <v>103</v>
@@ -6062,16 +6056,16 @@
         <v>103</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="Q94" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R94" s="6" t="s">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="S94" s="9">
-        <v>1200</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="95">
@@ -6079,22 +6073,22 @@
         <v>22</v>
       </c>
       <c r="B95" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C95" s="7">
-        <v>46195</v>
+        <v>46174</v>
       </c>
       <c r="D95" s="7">
-        <v>46195</v>
+        <v>46218</v>
       </c>
       <c r="E95" s="7">
-        <v>46160</v>
+        <v>46190</v>
       </c>
       <c r="F95" s="8">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G95" s="8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>23</v>
@@ -6103,16 +6097,16 @@
         <v>23</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>155</v>
+        <v>55</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="N95" s="6" t="s">
         <v>103</v>
@@ -6121,16 +6115,16 @@
         <v>103</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="Q95" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R95" s="6" t="s">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="S95" s="9">
-        <v>1200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="96">
@@ -6138,22 +6132,22 @@
         <v>22</v>
       </c>
       <c r="B96" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="C96" s="7">
         <v>46143</v>
       </c>
       <c r="D96" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="E96" s="7">
-        <v>46185</v>
+        <v>46153</v>
       </c>
       <c r="F96" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G96" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H96" s="6" t="s">
         <v>23</v>
@@ -6162,16 +6156,16 @@
         <v>23</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>156</v>
+        <v>58</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>157</v>
+        <v>59</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>158</v>
+        <v>23</v>
       </c>
       <c r="N96" s="6" t="s">
         <v>103</v>
@@ -6180,16 +6174,16 @@
         <v>103</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Q96" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S96" s="9">
-        <v>4400</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97">
@@ -6200,40 +6194,40 @@
         <v>46202</v>
       </c>
       <c r="C97" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D97" s="7">
-        <v>46218</v>
+        <v>46188</v>
       </c>
       <c r="E97" s="7">
-        <v>46190</v>
+        <v>46167</v>
       </c>
       <c r="F97" s="8">
-        <v>27</v>
+        <v>-7</v>
       </c>
       <c r="G97" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>57</v>
+        <v>97</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="N97" s="6" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>103</v>
@@ -6248,7 +6242,7 @@
         <v>36</v>
       </c>
       <c r="S97" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="98">
@@ -6265,13 +6259,13 @@
         <v>46202</v>
       </c>
       <c r="E98" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="F98" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G98" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>23</v>
@@ -6280,13 +6274,13 @@
         <v>23</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="M98" s="6" t="s">
         <v>23</v>
@@ -6298,7 +6292,7 @@
         <v>103</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="Q98" s="6" t="s">
         <v>29</v>
@@ -6307,7 +6301,7 @@
         <v>36</v>
       </c>
       <c r="S98" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99">
@@ -6318,19 +6312,19 @@
         <v>46202</v>
       </c>
       <c r="C99" s="7">
-        <v>46143</v>
+        <v>46188</v>
       </c>
       <c r="D99" s="7">
         <v>46202</v>
       </c>
       <c r="E99" s="7">
-        <v>46167</v>
+        <v>46188</v>
       </c>
       <c r="F99" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G99" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>23</v>
@@ -6339,13 +6333,13 @@
         <v>23</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>104</v>
+        <v>157</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="M99" s="6" t="s">
         <v>23</v>
@@ -6360,13 +6354,13 @@
         <v>23</v>
       </c>
       <c r="Q99" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R99" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S99" s="9">
-        <v>100</v>
+        <v>116.66</v>
       </c>
     </row>
     <row r="100">
@@ -6377,40 +6371,40 @@
         <v>46202</v>
       </c>
       <c r="C100" s="7">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="D100" s="7">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="E100" s="7">
-        <v>46167</v>
+        <v>46097</v>
       </c>
       <c r="F100" s="8">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="G100" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="I100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>104</v>
+        <v>25</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="M100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>103</v>
@@ -6422,10 +6416,10 @@
         <v>29</v>
       </c>
       <c r="R100" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S100" s="9">
-        <v>100</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="101">
@@ -6436,19 +6430,19 @@
         <v>46202</v>
       </c>
       <c r="C101" s="7">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="D101" s="7">
         <v>46202</v>
       </c>
       <c r="E101" s="7">
-        <v>46188</v>
+        <v>46169</v>
       </c>
       <c r="F101" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G101" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H101" s="6" t="s">
         <v>23</v>
@@ -6457,16 +6451,16 @@
         <v>23</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="M101" s="6" t="s">
-        <v>23</v>
+        <v>105</v>
       </c>
       <c r="N101" s="6" t="s">
         <v>103</v>
@@ -6481,10 +6475,10 @@
         <v>35</v>
       </c>
       <c r="R101" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S101" s="9">
-        <v>116.66</v>
+        <v>600</v>
       </c>
     </row>
     <row r="102">
@@ -6495,19 +6489,19 @@
         <v>46202</v>
       </c>
       <c r="C102" s="7">
-        <v>46082</v>
+        <v>46202</v>
       </c>
       <c r="D102" s="7">
         <v>46202</v>
       </c>
       <c r="E102" s="7">
-        <v>46097</v>
+        <v>46169</v>
       </c>
       <c r="F102" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G102" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H102" s="6" t="s">
         <v>23</v>
@@ -6516,16 +6510,16 @@
         <v>23</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>25</v>
+        <v>159</v>
       </c>
       <c r="K102" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="N102" s="6" t="s">
         <v>103</v>
@@ -6537,13 +6531,13 @@
         <v>23</v>
       </c>
       <c r="Q102" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R102" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S102" s="9">
-        <v>146.55</v>
+        <v>600</v>
       </c>
     </row>
     <row r="103">
@@ -6560,13 +6554,13 @@
         <v>46202</v>
       </c>
       <c r="E103" s="7">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="F103" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G103" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H103" s="6" t="s">
         <v>23</v>
@@ -6581,10 +6575,10 @@
         <v>23</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="M103" s="6" t="s">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="N103" s="6" t="s">
         <v>103</v>
@@ -6602,7 +6596,7 @@
         <v>36</v>
       </c>
       <c r="S103" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="104">
@@ -6622,10 +6616,10 @@
         <v>46169</v>
       </c>
       <c r="F104" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G104" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>23</v>
@@ -6640,10 +6634,10 @@
         <v>23</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="N104" s="6" t="s">
         <v>103</v>
@@ -6661,7 +6655,7 @@
         <v>36</v>
       </c>
       <c r="S104" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="105">
@@ -6678,13 +6672,13 @@
         <v>46202</v>
       </c>
       <c r="E105" s="7">
-        <v>46163</v>
+        <v>46169</v>
       </c>
       <c r="F105" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G105" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>23</v>
@@ -6699,7 +6693,7 @@
         <v>23</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="M105" s="6" t="s">
         <v>23</v>
@@ -6740,10 +6734,10 @@
         <v>46169</v>
       </c>
       <c r="F106" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G106" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>23</v>
@@ -6758,7 +6752,7 @@
         <v>23</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="M106" s="6" t="s">
         <v>23</v>
@@ -6796,13 +6790,13 @@
         <v>46202</v>
       </c>
       <c r="E107" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F107" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G107" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H107" s="6" t="s">
         <v>23</v>
@@ -6817,7 +6811,7 @@
         <v>23</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M107" s="6" t="s">
         <v>23</v>
@@ -6855,13 +6849,13 @@
         <v>46202</v>
       </c>
       <c r="E108" s="7">
-        <v>46169</v>
+        <v>46153</v>
       </c>
       <c r="F108" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G108" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H108" s="6" t="s">
         <v>23</v>
@@ -6876,7 +6870,7 @@
         <v>23</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="M108" s="6" t="s">
         <v>23</v>
@@ -6897,7 +6891,7 @@
         <v>36</v>
       </c>
       <c r="S108" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="109">
@@ -6914,13 +6908,13 @@
         <v>46202</v>
       </c>
       <c r="E109" s="7">
-        <v>46164</v>
+        <v>46127</v>
       </c>
       <c r="F109" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G109" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>23</v>
@@ -6935,7 +6929,7 @@
         <v>23</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M109" s="6" t="s">
         <v>23</v>
@@ -6956,7 +6950,7 @@
         <v>36</v>
       </c>
       <c r="S109" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="110">
@@ -6976,10 +6970,10 @@
         <v>46160</v>
       </c>
       <c r="F110" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G110" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>23</v>
@@ -6994,7 +6988,7 @@
         <v>23</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M110" s="6" t="s">
         <v>23</v>
@@ -7032,13 +7026,13 @@
         <v>46202</v>
       </c>
       <c r="E111" s="7">
-        <v>46153</v>
+        <v>46188</v>
       </c>
       <c r="F111" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G111" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>23</v>
@@ -7053,7 +7047,7 @@
         <v>23</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="M111" s="6" t="s">
         <v>23</v>
@@ -7071,7 +7065,7 @@
         <v>35</v>
       </c>
       <c r="R111" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S111" s="9">
         <v>650</v>
@@ -7091,13 +7085,13 @@
         <v>46202</v>
       </c>
       <c r="E112" s="7">
-        <v>46127</v>
+        <v>46182</v>
       </c>
       <c r="F112" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G112" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H112" s="6" t="s">
         <v>23</v>
@@ -7112,7 +7106,7 @@
         <v>23</v>
       </c>
       <c r="L112" s="6" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="M112" s="6" t="s">
         <v>23</v>
@@ -7133,7 +7127,7 @@
         <v>36</v>
       </c>
       <c r="S112" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="113">
@@ -7150,13 +7144,13 @@
         <v>46202</v>
       </c>
       <c r="E113" s="7">
-        <v>46188</v>
+        <v>46164</v>
       </c>
       <c r="F113" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G113" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>23</v>
@@ -7171,7 +7165,7 @@
         <v>23</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="M113" s="6" t="s">
         <v>23</v>
@@ -7192,7 +7186,7 @@
         <v>28</v>
       </c>
       <c r="S113" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="114">
@@ -7209,13 +7203,13 @@
         <v>46202</v>
       </c>
       <c r="E114" s="7">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="F114" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G114" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H114" s="6" t="s">
         <v>23</v>
@@ -7230,7 +7224,7 @@
         <v>23</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="M114" s="6" t="s">
         <v>23</v>
@@ -7248,7 +7242,7 @@
         <v>35</v>
       </c>
       <c r="R114" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S114" s="9">
         <v>680</v>
@@ -7271,10 +7265,10 @@
         <v>46182</v>
       </c>
       <c r="F115" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G115" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H115" s="6" t="s">
         <v>23</v>
@@ -7289,7 +7283,7 @@
         <v>23</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="M115" s="6" t="s">
         <v>23</v>
@@ -7327,13 +7321,13 @@
         <v>46202</v>
       </c>
       <c r="E116" s="7">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="F116" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G116" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H116" s="6" t="s">
         <v>23</v>
@@ -7386,13 +7380,13 @@
         <v>46202</v>
       </c>
       <c r="E117" s="7">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="F117" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G117" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H117" s="6" t="s">
         <v>23</v>
@@ -7407,7 +7401,7 @@
         <v>23</v>
       </c>
       <c r="L117" s="6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="M117" s="6" t="s">
         <v>23</v>
@@ -7428,7 +7422,7 @@
         <v>36</v>
       </c>
       <c r="S117" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="118">
@@ -7445,13 +7439,13 @@
         <v>46202</v>
       </c>
       <c r="E118" s="7">
-        <v>46167</v>
+        <v>46188</v>
       </c>
       <c r="F118" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G118" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H118" s="6" t="s">
         <v>23</v>
@@ -7466,7 +7460,7 @@
         <v>23</v>
       </c>
       <c r="L118" s="6" t="s">
-        <v>54</v>
+        <v>141</v>
       </c>
       <c r="M118" s="6" t="s">
         <v>23</v>
@@ -7484,15 +7478,15 @@
         <v>35</v>
       </c>
       <c r="R118" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S118" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="s">
-        <v>22</v>
+        <v>142</v>
       </c>
       <c r="B119" s="7">
         <v>46202</v>
@@ -7504,13 +7498,13 @@
         <v>46202</v>
       </c>
       <c r="E119" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F119" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G119" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H119" s="6" t="s">
         <v>23</v>
@@ -7525,7 +7519,7 @@
         <v>23</v>
       </c>
       <c r="L119" s="6" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="M119" s="6" t="s">
         <v>23</v>
@@ -7543,10 +7537,10 @@
         <v>35</v>
       </c>
       <c r="R119" s="6" t="s">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="S119" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="120">
@@ -7563,13 +7557,13 @@
         <v>46202</v>
       </c>
       <c r="E120" s="7">
-        <v>46188</v>
+        <v>46148</v>
       </c>
       <c r="F120" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G120" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H120" s="6" t="s">
         <v>23</v>
@@ -7584,7 +7578,7 @@
         <v>23</v>
       </c>
       <c r="L120" s="6" t="s">
-        <v>143</v>
+        <v>89</v>
       </c>
       <c r="M120" s="6" t="s">
         <v>23</v>
@@ -7602,15 +7596,15 @@
         <v>35</v>
       </c>
       <c r="R120" s="6" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="S120" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="s">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="B121" s="7">
         <v>46202</v>
@@ -7622,13 +7616,13 @@
         <v>46202</v>
       </c>
       <c r="E121" s="7">
-        <v>46182</v>
+        <v>46148</v>
       </c>
       <c r="F121" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G121" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H121" s="6" t="s">
         <v>23</v>
@@ -7661,10 +7655,10 @@
         <v>35</v>
       </c>
       <c r="R121" s="6" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="S121" s="9">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="122">
@@ -7681,13 +7675,13 @@
         <v>46202</v>
       </c>
       <c r="E122" s="7">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="F122" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G122" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H122" s="6" t="s">
         <v>23</v>
@@ -7702,7 +7696,7 @@
         <v>23</v>
       </c>
       <c r="L122" s="6" t="s">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="M122" s="6" t="s">
         <v>23</v>
@@ -7714,16 +7708,16 @@
         <v>103</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="Q122" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R122" s="6" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="S122" s="9">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="123">
@@ -7740,13 +7734,13 @@
         <v>46202</v>
       </c>
       <c r="E123" s="7">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="F123" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G123" s="8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H123" s="6" t="s">
         <v>23</v>
@@ -7761,7 +7755,7 @@
         <v>23</v>
       </c>
       <c r="L123" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M123" s="6" t="s">
         <v>23</v>
@@ -7773,157 +7767,39 @@
         <v>103</v>
       </c>
       <c r="P123" s="6" t="s">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="Q123" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R123" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="S123" s="9">
         <v>1200</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B124" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C124" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D124" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E124" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F124" s="8">
-        <v>11</v>
-      </c>
-      <c r="G124" s="8">
-        <v>11</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I124" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J124" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="K124" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L124" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="M124" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N124" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O124" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P124" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q124" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R124" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="S124" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B125" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C125" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D125" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E125" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F125" s="8">
-        <v>11</v>
-      </c>
-      <c r="G125" s="8">
-        <v>11</v>
-      </c>
-      <c r="H125" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I125" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J125" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="K125" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L125" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="M125" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N125" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O125" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P125" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q125" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R125" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="S125" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="126" ht="23" customHeight="1">
-      <c r="A126" s="10"/>
-      <c r="B126" s="11"/>
-      <c r="C126" s="11"/>
-      <c r="D126" s="11"/>
-      <c r="E126" s="11"/>
-      <c r="F126" s="12"/>
-      <c r="G126" s="12"/>
-      <c r="H126" s="10"/>
-      <c r="I126" s="10"/>
-      <c r="J126" s="10"/>
-      <c r="K126" s="10"/>
-      <c r="L126" s="10"/>
-      <c r="M126" s="10"/>
-      <c r="N126" s="10"/>
-      <c r="O126" s="10"/>
-      <c r="P126" s="10"/>
-      <c r="Q126" s="10"/>
-      <c r="R126" s="10"/>
-      <c r="S126" s="13">
-        <f>SUM(S6:S125)</f>
+    <row r="124" ht="23" customHeight="1">
+      <c r="A124" s="10"/>
+      <c r="B124" s="11"/>
+      <c r="C124" s="11"/>
+      <c r="D124" s="11"/>
+      <c r="E124" s="11"/>
+      <c r="F124" s="12"/>
+      <c r="G124" s="12"/>
+      <c r="H124" s="10"/>
+      <c r="I124" s="10"/>
+      <c r="J124" s="10"/>
+      <c r="K124" s="10"/>
+      <c r="L124" s="10"/>
+      <c r="M124" s="10"/>
+      <c r="N124" s="10"/>
+      <c r="O124" s="10"/>
+      <c r="P124" s="10"/>
+      <c r="Q124" s="10"/>
+      <c r="R124" s="10"/>
+      <c r="S124" s="13">
+        <f>SUM(S6:S123)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$124</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$110</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -163,418 +163,370 @@
     <t>FA-11565</t>
   </si>
   <si>
-    <t>FA-11711</t>
+    <t>FA-11568</t>
+  </si>
+  <si>
+    <t>FA-11796</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11847</t>
   </si>
   <si>
     <t>ANDRE CAVALCANTI DA FE</t>
   </si>
   <si>
-    <t>FA-11568</t>
-  </si>
-  <si>
-    <t>FA-11796</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+    <t>ND-11801</t>
+  </si>
+  <si>
+    <t>ND-11699</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>FA-11806</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11571</t>
+  </si>
+  <si>
+    <t>FA-11797</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11724</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11572</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11798</t>
+  </si>
+  <si>
+    <t>FA-11848</t>
+  </si>
+  <si>
+    <t>FA-11776</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11679</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11818</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11694</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>ND-11844</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11756</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11785</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11772</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11842</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
+  </si>
+  <si>
+    <t>ND-11700</t>
+  </si>
+  <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>ND-11870</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
   </si>
   <si>
     <t>FA-11775</t>
   </si>
   <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11847</t>
+    <t>FA-11787</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
   </si>
   <si>
     <t>FA-11693</t>
   </si>
   <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>ND-11801</t>
-  </si>
-  <si>
-    <t>FA-11569</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11810</t>
+    <t>FA-11791</t>
+  </si>
+  <si>
+    <t>FA-11730</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11807</t>
+  </si>
+  <si>
+    <t>FA-11731</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11728</t>
+  </si>
+  <si>
+    <t>FA-11790</t>
+  </si>
+  <si>
+    <t>FA-11800</t>
+  </si>
+  <si>
+    <t>FA-11672</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11687</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
+    <t>FA-11850</t>
+  </si>
+  <si>
+    <t>FA-11799</t>
+  </si>
+  <si>
+    <t>FA-11508</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11625</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11438</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11695</t>
+  </si>
+  <si>
+    <t>FA-11811</t>
   </si>
   <si>
     <t>LUCAS NAJA MOURA RODRIGUES</t>
   </si>
   <si>
-    <t>ND-11699</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>FA-11806</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>JOAO PAULO CONSORCIOS</t>
-  </si>
-  <si>
-    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
-  </si>
-  <si>
-    <t>FA-11784</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11671</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11774</t>
-  </si>
-  <si>
-    <t>FA-11571</t>
-  </si>
-  <si>
-    <t>FA-11678</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11797</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11787</t>
-  </si>
-  <si>
-    <t>FA-11572</t>
-  </si>
-  <si>
-    <t>FA-11724</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11798</t>
-  </si>
-  <si>
-    <t>FA-11848</t>
-  </si>
-  <si>
-    <t>FA-11776</t>
-  </si>
-  <si>
-    <t>FA-11818</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11679</t>
-  </si>
-  <si>
-    <t>FA-11694</t>
-  </si>
-  <si>
-    <t>FA-11573</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>ND-11844</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11756</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11692</t>
-  </si>
-  <si>
-    <t>FA-11785</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11772</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-11842</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
-    <t>ND-11700</t>
-  </si>
-  <si>
-    <t>HOJE</t>
-  </si>
-  <si>
-    <t>ND-11870</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>FA-11730</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11791</t>
-  </si>
-  <si>
-    <t>FA-11749</t>
+    <t>FA-11822</t>
+  </si>
+  <si>
+    <t>FA-11823</t>
+  </si>
+  <si>
+    <t>FA-11680</t>
+  </si>
+  <si>
+    <t>FA-11789</t>
+  </si>
+  <si>
+    <t>FA-11765</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11851</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-11605</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>FA-11824</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>FA-11636</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11595</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>FA-11821</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11843</t>
+  </si>
+  <si>
+    <t>SEGCOMP</t>
+  </si>
+  <si>
+    <t>SEGCOMP TECNOLOGIA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11849</t>
+  </si>
+  <si>
+    <t>FA-11735</t>
+  </si>
+  <si>
+    <t>FA-11750</t>
   </si>
   <si>
     <t>ROBERTO MURATORI</t>
   </si>
   <si>
-    <t>FA-11807</t>
-  </si>
-  <si>
-    <t>FA-11672</t>
-  </si>
-  <si>
-    <t>FA-11790</t>
-  </si>
-  <si>
-    <t>FA-11800</t>
-  </si>
-  <si>
-    <t>FA-11733</t>
+    <t>FA-11673</t>
+  </si>
+  <si>
+    <t>FA-11688</t>
+  </si>
+  <si>
+    <t>FA-11737</t>
   </si>
   <si>
     <t>JONILSON JOSEMAR DO NASCIMENTO</t>
   </si>
   <si>
-    <t>FA-11731</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11728</t>
-  </si>
-  <si>
-    <t>FA-11687</t>
-  </si>
-  <si>
-    <t>GILVAN RODRIGUES MACHADO</t>
-  </si>
-  <si>
-    <t>FA-11799</t>
-  </si>
-  <si>
-    <t>FA-11508</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11625</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>FA-11660</t>
+    <t>FA-11732</t>
+  </si>
+  <si>
+    <t>FA-11734</t>
+  </si>
+  <si>
+    <t>FA-11852</t>
+  </si>
+  <si>
+    <t>FA-11509</t>
+  </si>
+  <si>
+    <t>FA-11626</t>
+  </si>
+  <si>
+    <t>FA-11661</t>
   </si>
   <si>
     <t>LUCA ZOLI</t>
   </si>
   <si>
-    <t>FA-11850</t>
-  </si>
-  <si>
-    <t>FA-11438</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11811</t>
-  </si>
-  <si>
-    <t>FA-11821</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11695</t>
-  </si>
-  <si>
-    <t>FA-11822</t>
-  </si>
-  <si>
-    <t>FA-11823</t>
-  </si>
-  <si>
-    <t>FA-11680</t>
-  </si>
-  <si>
-    <t>FA-11789</t>
-  </si>
-  <si>
-    <t>FA-11765</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11851</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>FA-11824</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t>FA-11605</t>
-  </si>
-  <si>
-    <t>FA-11595</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11648</t>
+    <t>FA-11696</t>
+  </si>
+  <si>
+    <t>FA-11827</t>
+  </si>
+  <si>
+    <t>FA-11825</t>
+  </si>
+  <si>
+    <t>FA-11681</t>
+  </si>
+  <si>
+    <t>FA-11826</t>
+  </si>
+  <si>
+    <t>FA-11766</t>
+  </si>
+  <si>
+    <t>FA-11853</t>
+  </si>
+  <si>
+    <t>FA-11828</t>
+  </si>
+  <si>
+    <t>FA-11606</t>
+  </si>
+  <si>
+    <t>FA-11649</t>
   </si>
   <si>
     <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
   </si>
   <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-11636</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11843</t>
-  </si>
-  <si>
-    <t>SEGCOMP</t>
-  </si>
-  <si>
-    <t>SEGCOMP TECNOLOGIA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11849</t>
-  </si>
-  <si>
-    <t>FA-11735</t>
-  </si>
-  <si>
-    <t>FA-11750</t>
-  </si>
-  <si>
-    <t>FA-11673</t>
-  </si>
-  <si>
-    <t>FA-11737</t>
-  </si>
-  <si>
-    <t>FA-11734</t>
-  </si>
-  <si>
-    <t>FA-11732</t>
-  </si>
-  <si>
-    <t>FA-11688</t>
-  </si>
-  <si>
-    <t>FA-11626</t>
-  </si>
-  <si>
-    <t>FA-11509</t>
-  </si>
-  <si>
-    <t>FA-11661</t>
-  </si>
-  <si>
-    <t>FA-11852</t>
-  </si>
-  <si>
-    <t>FA-11827</t>
-  </si>
-  <si>
-    <t>FA-11681</t>
-  </si>
-  <si>
-    <t>FA-11826</t>
-  </si>
-  <si>
-    <t>FA-11825</t>
-  </si>
-  <si>
-    <t>FA-11696</t>
-  </si>
-  <si>
-    <t>FA-11766</t>
-  </si>
-  <si>
-    <t>FA-11853</t>
-  </si>
-  <si>
-    <t>FA-11828</t>
-  </si>
-  <si>
-    <t>FA-11606</t>
+    <t>FA-11637</t>
   </si>
   <si>
     <t>FA-11596</t>
-  </si>
-  <si>
-    <t>FA-11637</t>
-  </si>
-  <si>
-    <t>FA-11649</t>
   </si>
 </sst>
 </file>
@@ -717,7 +669,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S124"/>
+  <dimension ref="A1:S110"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -732,7 +684,7 @@
     <col min="10" max="10" width="21" customWidth="1" style="1"/>
     <col min="11" max="11" width="13" customWidth="1" style="1"/>
     <col min="12" max="12" width="39" customWidth="1" style="1"/>
-    <col min="13" max="13" width="55" customWidth="1" style="1"/>
+    <col min="13" max="13" width="35" customWidth="1" style="1"/>
     <col min="14" max="14" width="31" customWidth="1" style="1"/>
     <col min="15" max="15" width="26" customWidth="1" style="1"/>
     <col min="16" max="16" width="14" customWidth="1" style="1"/>
@@ -1766,22 +1718,22 @@
         <v>22</v>
       </c>
       <c r="B22" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C22" s="7">
-        <v>46174</v>
+        <v>46082</v>
       </c>
       <c r="D22" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>23</v>
+        <v>46181</v>
+      </c>
+      <c r="E22" s="7">
+        <v>46097</v>
       </c>
       <c r="F22" s="8">
-        <v>-21</v>
+        <v>-14</v>
       </c>
       <c r="G22" s="8">
-        <v>-21</v>
+        <v>-14</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>39</v>
@@ -1790,13 +1742,13 @@
         <v>39</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>23</v>
@@ -1811,13 +1763,13 @@
         <v>23</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="S22" s="9">
-        <v>400</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="23">
@@ -1828,13 +1780,13 @@
         <v>46181</v>
       </c>
       <c r="C23" s="7">
-        <v>46082</v>
+        <v>46181</v>
       </c>
       <c r="D23" s="7">
         <v>46181</v>
       </c>
       <c r="E23" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F23" s="8">
         <v>-14</v>
@@ -1849,13 +1801,13 @@
         <v>39</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>23</v>
@@ -1870,13 +1822,13 @@
         <v>23</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S23" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24">
@@ -1893,7 +1845,7 @@
         <v>46181</v>
       </c>
       <c r="E24" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="F24" s="8">
         <v>-14</v>
@@ -1908,13 +1860,13 @@
         <v>39</v>
       </c>
       <c r="J24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>23</v>
@@ -1935,7 +1887,7 @@
         <v>36</v>
       </c>
       <c r="S24" s="9">
-        <v>310</v>
+        <v>630</v>
       </c>
     </row>
     <row r="25">
@@ -1952,7 +1904,7 @@
         <v>46181</v>
       </c>
       <c r="E25" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F25" s="8">
         <v>-14</v>
@@ -1991,10 +1943,10 @@
         <v>35</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S25" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="26">
@@ -2005,7 +1957,7 @@
         <v>46181</v>
       </c>
       <c r="C26" s="7">
-        <v>46181</v>
+        <v>46143</v>
       </c>
       <c r="D26" s="7">
         <v>46181</v>
@@ -2032,10 +1984,10 @@
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>27</v>
@@ -2047,13 +1999,13 @@
         <v>23</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S26" s="9">
-        <v>650</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="27">
@@ -2061,22 +2013,22 @@
         <v>22</v>
       </c>
       <c r="B27" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="C27" s="7">
-        <v>46181</v>
+        <v>46143</v>
       </c>
       <c r="D27" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="E27" s="7">
-        <v>46188</v>
+        <v>46153</v>
       </c>
       <c r="F27" s="8">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="G27" s="8">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>39</v>
@@ -2085,14 +2037,14 @@
         <v>39</v>
       </c>
       <c r="J27" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="K27" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
       </c>
@@ -2103,16 +2055,16 @@
         <v>27</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S27" s="9">
-        <v>650</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
@@ -2120,22 +2072,22 @@
         <v>22</v>
       </c>
       <c r="B28" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="C28" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="D28" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E28" s="7">
-        <v>46167</v>
+        <v>46188</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F28" s="8">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="G28" s="8">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>39</v>
@@ -2144,16 +2096,16 @@
         <v>39</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>27</v>
@@ -2165,13 +2117,13 @@
         <v>23</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S28" s="9">
-        <v>680</v>
+        <v>70.07</v>
       </c>
     </row>
     <row r="29">
@@ -2179,22 +2131,22 @@
         <v>22</v>
       </c>
       <c r="B29" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="C29" s="7">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="D29" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="E29" s="7">
-        <v>46170</v>
+        <v>46097</v>
       </c>
       <c r="F29" s="8">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="G29" s="8">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>39</v>
@@ -2203,7 +2155,7 @@
         <v>39</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>23</v>
@@ -2230,7 +2182,7 @@
         <v>28</v>
       </c>
       <c r="S29" s="9">
-        <v>2969.17</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="30">
@@ -2238,22 +2190,22 @@
         <v>22</v>
       </c>
       <c r="B30" s="7">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="C30" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="D30" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>23</v>
+        <v>46188</v>
+      </c>
+      <c r="E30" s="7">
+        <v>46141</v>
       </c>
       <c r="F30" s="8">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="G30" s="8">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>39</v>
@@ -2268,10 +2220,10 @@
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -2283,13 +2235,13 @@
         <v>23</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S30" s="9">
-        <v>220</v>
+        <v>310</v>
       </c>
     </row>
     <row r="31">
@@ -2321,13 +2273,13 @@
         <v>39</v>
       </c>
       <c r="J31" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="K31" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>23</v>
@@ -2348,7 +2300,7 @@
         <v>36</v>
       </c>
       <c r="S31" s="9">
-        <v>38.45</v>
+        <v>330</v>
       </c>
     </row>
     <row r="32">
@@ -2359,13 +2311,13 @@
         <v>46188</v>
       </c>
       <c r="C32" s="7">
-        <v>46143</v>
+        <v>46188</v>
       </c>
       <c r="D32" s="7">
         <v>46188</v>
       </c>
       <c r="E32" s="7">
-        <v>46153</v>
+        <v>46169</v>
       </c>
       <c r="F32" s="8">
         <v>-7</v>
@@ -2380,14 +2332,14 @@
         <v>39</v>
       </c>
       <c r="J32" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="K32" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>59</v>
-      </c>
       <c r="M32" s="6" t="s">
         <v>23</v>
       </c>
@@ -2398,16 +2350,16 @@
         <v>27</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S32" s="9">
-        <v>50</v>
+        <v>540</v>
       </c>
     </row>
     <row r="33">
@@ -2423,8 +2375,8 @@
       <c r="D33" s="7">
         <v>46188</v>
       </c>
-      <c r="E33" s="7" t="s">
-        <v>23</v>
+      <c r="E33" s="7">
+        <v>46141</v>
       </c>
       <c r="F33" s="8">
         <v>-7</v>
@@ -2439,16 +2391,16 @@
         <v>39</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>27</v>
@@ -2460,13 +2412,13 @@
         <v>23</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S33" s="9">
-        <v>70.07</v>
+        <v>620</v>
       </c>
     </row>
     <row r="34">
@@ -2482,8 +2434,8 @@
       <c r="D34" s="7">
         <v>46188</v>
       </c>
-      <c r="E34" s="7" t="s">
-        <v>23</v>
+      <c r="E34" s="7">
+        <v>46170</v>
       </c>
       <c r="F34" s="8">
         <v>-7</v>
@@ -2498,16 +2450,16 @@
         <v>39</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>27</v>
@@ -2519,13 +2471,13 @@
         <v>23</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="S34" s="9">
-        <v>112.5</v>
+        <v>630</v>
       </c>
     </row>
     <row r="35">
@@ -2536,13 +2488,13 @@
         <v>46188</v>
       </c>
       <c r="C35" s="7">
-        <v>46082</v>
+        <v>46188</v>
       </c>
       <c r="D35" s="7">
         <v>46188</v>
       </c>
       <c r="E35" s="7">
-        <v>46097</v>
+        <v>46188</v>
       </c>
       <c r="F35" s="8">
         <v>-7</v>
@@ -2557,13 +2509,13 @@
         <v>39</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2578,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="S35" s="9">
-        <v>146.55</v>
+        <v>650</v>
       </c>
     </row>
     <row r="36">
@@ -2595,16 +2547,16 @@
         <v>46188</v>
       </c>
       <c r="C36" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="D36" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>23</v>
+        <v>46188</v>
+      </c>
+      <c r="E36" s="7">
+        <v>46170</v>
       </c>
       <c r="F36" s="8">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="G36" s="8">
         <v>-7</v>
@@ -2616,16 +2568,16 @@
         <v>39</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>27</v>
@@ -2637,13 +2589,13 @@
         <v>23</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S36" s="9">
-        <v>200</v>
+        <v>650</v>
       </c>
     </row>
     <row r="37">
@@ -2659,8 +2611,8 @@
       <c r="D37" s="7">
         <v>46188</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>23</v>
+      <c r="E37" s="7">
+        <v>46164</v>
       </c>
       <c r="F37" s="8">
         <v>-7</v>
@@ -2675,13 +2627,13 @@
         <v>39</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>23</v>
@@ -2696,13 +2648,13 @@
         <v>23</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S37" s="9">
-        <v>230</v>
+        <v>680</v>
       </c>
     </row>
     <row r="38">
@@ -2713,16 +2665,16 @@
         <v>46188</v>
       </c>
       <c r="C38" s="7">
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="D38" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>23</v>
+        <v>46188</v>
+      </c>
+      <c r="E38" s="7">
+        <v>46182</v>
       </c>
       <c r="F38" s="8">
-        <v>-21</v>
+        <v>-7</v>
       </c>
       <c r="G38" s="8">
         <v>-7</v>
@@ -2734,16 +2686,16 @@
         <v>39</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>27</v>
@@ -2755,13 +2707,13 @@
         <v>23</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S38" s="9">
-        <v>279.12</v>
+        <v>680</v>
       </c>
     </row>
     <row r="39">
@@ -2778,7 +2730,7 @@
         <v>46188</v>
       </c>
       <c r="E39" s="7">
-        <v>46141</v>
+        <v>46167</v>
       </c>
       <c r="F39" s="8">
         <v>-7</v>
@@ -2793,13 +2745,13 @@
         <v>39</v>
       </c>
       <c r="J39" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="K39" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L39" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>23</v>
@@ -2820,7 +2772,7 @@
         <v>36</v>
       </c>
       <c r="S39" s="9">
-        <v>310</v>
+        <v>680</v>
       </c>
     </row>
     <row r="40">
@@ -2828,22 +2780,22 @@
         <v>22</v>
       </c>
       <c r="B40" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C40" s="7">
-        <v>46181</v>
+        <v>46174</v>
       </c>
       <c r="D40" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>23</v>
+        <v>46189</v>
+      </c>
+      <c r="E40" s="7">
+        <v>46185</v>
       </c>
       <c r="F40" s="8">
-        <v>-14</v>
+        <v>-6</v>
       </c>
       <c r="G40" s="8">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>39</v>
@@ -2873,13 +2825,13 @@
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="S40" s="9">
-        <v>310</v>
+        <v>170.96</v>
       </c>
     </row>
     <row r="41">
@@ -2887,7 +2839,7 @@
         <v>22</v>
       </c>
       <c r="B41" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C41" s="7">
         <v>46188</v>
@@ -2902,7 +2854,7 @@
         <v>-7</v>
       </c>
       <c r="G41" s="8">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>39</v>
@@ -2911,13 +2863,13 @@
         <v>39</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>23</v>
@@ -2938,7 +2890,7 @@
         <v>36</v>
       </c>
       <c r="S41" s="9">
-        <v>330</v>
+        <v>134.74</v>
       </c>
     </row>
     <row r="42">
@@ -2946,7 +2898,7 @@
         <v>22</v>
       </c>
       <c r="B42" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C42" s="7">
         <v>46188</v>
@@ -2954,14 +2906,14 @@
       <c r="D42" s="7">
         <v>46188</v>
       </c>
-      <c r="E42" s="7">
-        <v>46170</v>
+      <c r="E42" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F42" s="8">
         <v>-7</v>
       </c>
       <c r="G42" s="8">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>39</v>
@@ -2970,16 +2922,16 @@
         <v>39</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N42" s="6" t="s">
         <v>27</v>
@@ -2988,16 +2940,16 @@
         <v>27</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S42" s="9">
-        <v>600</v>
+        <v>190</v>
       </c>
     </row>
     <row r="43">
@@ -3005,22 +2957,22 @@
         <v>22</v>
       </c>
       <c r="B43" s="7">
-        <v>46188</v>
+        <v>46192</v>
       </c>
       <c r="C43" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D43" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E43" s="7">
-        <v>46141</v>
+        <v>46174</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F43" s="8">
-        <v>-7</v>
+        <v>-21</v>
       </c>
       <c r="G43" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>39</v>
@@ -3029,16 +2981,16 @@
         <v>39</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="M43" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N43" s="6" t="s">
         <v>27</v>
@@ -3050,13 +3002,13 @@
         <v>23</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S43" s="9">
-        <v>620</v>
+        <v>160.54</v>
       </c>
     </row>
     <row r="44">
@@ -3064,22 +3016,22 @@
         <v>22</v>
       </c>
       <c r="B44" s="7">
-        <v>46188</v>
+        <v>46192</v>
       </c>
       <c r="C44" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D44" s="7">
-        <v>46188</v>
+        <v>46192</v>
       </c>
       <c r="E44" s="7">
-        <v>46169</v>
+        <v>46185</v>
       </c>
       <c r="F44" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="G44" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>39</v>
@@ -3088,16 +3040,16 @@
         <v>39</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>27</v>
@@ -3115,7 +3067,7 @@
         <v>36</v>
       </c>
       <c r="S44" s="9">
-        <v>630</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="45">
@@ -3123,38 +3075,38 @@
         <v>22</v>
       </c>
       <c r="B45" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C45" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D45" s="7">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="E45" s="7">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="F45" s="8">
-        <v>-7</v>
+        <v>-14</v>
       </c>
       <c r="G45" s="8">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>39</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J45" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="K45" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L45" s="6" t="s">
-        <v>47</v>
-      </c>
       <c r="M45" s="6" t="s">
         <v>23</v>
       </c>
@@ -3162,19 +3114,19 @@
         <v>27</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S45" s="9">
-        <v>630</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46">
@@ -3182,58 +3134,58 @@
         <v>22</v>
       </c>
       <c r="B46" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C46" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D46" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E46" s="7">
-        <v>46188</v>
+        <v>46153</v>
       </c>
       <c r="F46" s="8">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="G46" s="8">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S46" s="9">
-        <v>650</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47">
@@ -3241,58 +3193,58 @@
         <v>22</v>
       </c>
       <c r="B47" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C47" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D47" s="7">
-        <v>46188</v>
+        <v>46211</v>
       </c>
       <c r="E47" s="7">
-        <v>46170</v>
+        <v>46190</v>
       </c>
       <c r="F47" s="8">
-        <v>-7</v>
+        <v>16</v>
       </c>
       <c r="G47" s="8">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S47" s="9">
-        <v>650</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48">
@@ -3300,28 +3252,28 @@
         <v>22</v>
       </c>
       <c r="B48" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C48" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D48" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E48" s="7">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="F48" s="8">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="G48" s="8">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>82</v>
@@ -3330,28 +3282,28 @@
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N48" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="M48" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="O48" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S48" s="9">
-        <v>680</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49">
@@ -3359,58 +3311,58 @@
         <v>22</v>
       </c>
       <c r="B49" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C49" s="7">
-        <v>46188</v>
+        <v>46082</v>
       </c>
       <c r="D49" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E49" s="7">
-        <v>46164</v>
+        <v>46097</v>
       </c>
       <c r="F49" s="8">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="G49" s="8">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="S49" s="9">
-        <v>680</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="50">
@@ -3418,58 +3370,58 @@
         <v>22</v>
       </c>
       <c r="B50" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C50" s="7">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="D50" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E50" s="7">
-        <v>46167</v>
+        <v>46181</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F50" s="8">
-        <v>-7</v>
+        <v>-14</v>
       </c>
       <c r="G50" s="8">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>39</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="N50" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S50" s="9">
-        <v>680</v>
+        <v>500</v>
       </c>
     </row>
     <row r="51">
@@ -3477,7 +3429,7 @@
         <v>22</v>
       </c>
       <c r="B51" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C51" s="7">
         <v>46188</v>
@@ -3485,50 +3437,50 @@
       <c r="D51" s="7">
         <v>46188</v>
       </c>
-      <c r="E51" s="7">
-        <v>46141</v>
+      <c r="E51" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F51" s="8">
         <v>-7</v>
       </c>
       <c r="G51" s="8">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>39</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="N51" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S51" s="9">
-        <v>680</v>
+        <v>500</v>
       </c>
     </row>
     <row r="52">
@@ -3536,37 +3488,37 @@
         <v>22</v>
       </c>
       <c r="B52" s="7">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="C52" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D52" s="7">
-        <v>46189</v>
-      </c>
-      <c r="E52" s="7">
-        <v>46185</v>
+        <v>46181</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F52" s="8">
-        <v>-6</v>
+        <v>-14</v>
       </c>
       <c r="G52" s="8">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>39</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="M52" s="6" t="s">
         <v>23</v>
@@ -3575,19 +3527,19 @@
         <v>27</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="S52" s="9">
-        <v>170.96</v>
+        <v>540</v>
       </c>
     </row>
     <row r="53">
@@ -3595,58 +3547,58 @@
         <v>22</v>
       </c>
       <c r="B53" s="7">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="C53" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="D53" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>23</v>
+        <v>46195</v>
+      </c>
+      <c r="E53" s="7">
+        <v>46170</v>
       </c>
       <c r="F53" s="8">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="G53" s="8">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S53" s="9">
-        <v>134.74</v>
+        <v>600</v>
       </c>
     </row>
     <row r="54">
@@ -3654,58 +3606,58 @@
         <v>22</v>
       </c>
       <c r="B54" s="7">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="C54" s="7">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="D54" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>23</v>
+        <v>46195</v>
+      </c>
+      <c r="E54" s="7">
+        <v>46169</v>
       </c>
       <c r="F54" s="8">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="G54" s="8">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q54" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S54" s="9">
-        <v>160</v>
+        <v>600</v>
       </c>
     </row>
     <row r="55">
@@ -3713,58 +3665,58 @@
         <v>22</v>
       </c>
       <c r="B55" s="7">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="C55" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="D55" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>23</v>
+        <v>46195</v>
+      </c>
+      <c r="E55" s="7">
+        <v>46176</v>
       </c>
       <c r="F55" s="8">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="G55" s="8">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q55" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S55" s="9">
-        <v>190</v>
+        <v>620</v>
       </c>
     </row>
     <row r="56">
@@ -3772,58 +3724,58 @@
         <v>22</v>
       </c>
       <c r="B56" s="7">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="C56" s="7">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="D56" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>23</v>
+        <v>46195</v>
+      </c>
+      <c r="E56" s="7">
+        <v>46169</v>
       </c>
       <c r="F56" s="8">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="G56" s="8">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S56" s="9">
-        <v>310.54</v>
+        <v>630</v>
       </c>
     </row>
     <row r="57">
@@ -3831,46 +3783,46 @@
         <v>22</v>
       </c>
       <c r="B57" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C57" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D57" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="E57" s="7">
-        <v>46185</v>
+        <v>46169</v>
       </c>
       <c r="F57" s="8">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="G57" s="8">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>23</v>
@@ -3882,7 +3834,7 @@
         <v>36</v>
       </c>
       <c r="S57" s="9">
-        <v>2100</v>
+        <v>630</v>
       </c>
     </row>
     <row r="58">
@@ -3893,55 +3845,55 @@
         <v>46195</v>
       </c>
       <c r="C58" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D58" s="7">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="E58" s="7">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="F58" s="8">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="G58" s="8">
         <v>0</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R58" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S58" s="9">
-        <v>50</v>
+        <v>630</v>
       </c>
     </row>
     <row r="59">
@@ -3952,13 +3904,13 @@
         <v>46195</v>
       </c>
       <c r="C59" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D59" s="7">
         <v>46195</v>
       </c>
       <c r="E59" s="7">
-        <v>46153</v>
+        <v>46170</v>
       </c>
       <c r="F59" s="8">
         <v>0</v>
@@ -3973,34 +3925,34 @@
         <v>23</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R59" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S59" s="9">
-        <v>50</v>
+        <v>630</v>
       </c>
     </row>
     <row r="60">
@@ -4011,16 +3963,16 @@
         <v>46195</v>
       </c>
       <c r="C60" s="7">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="D60" s="7">
-        <v>46211</v>
+        <v>46195</v>
       </c>
       <c r="E60" s="7">
-        <v>46190</v>
+        <v>46163</v>
       </c>
       <c r="F60" s="8">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G60" s="8">
         <v>0</v>
@@ -4032,34 +3984,34 @@
         <v>23</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q60" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S60" s="9">
-        <v>50</v>
+        <v>630</v>
       </c>
     </row>
     <row r="61">
@@ -4070,13 +4022,13 @@
         <v>46195</v>
       </c>
       <c r="C61" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D61" s="7">
         <v>46195</v>
       </c>
       <c r="E61" s="7">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="F61" s="8">
         <v>0</v>
@@ -4091,34 +4043,34 @@
         <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q61" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S61" s="9">
-        <v>100</v>
+        <v>630</v>
       </c>
     </row>
     <row r="62">
@@ -4129,13 +4081,13 @@
         <v>46195</v>
       </c>
       <c r="C62" s="7">
-        <v>46082</v>
+        <v>46195</v>
       </c>
       <c r="D62" s="7">
         <v>46195</v>
       </c>
       <c r="E62" s="7">
-        <v>46097</v>
+        <v>46188</v>
       </c>
       <c r="F62" s="8">
         <v>0</v>
@@ -4150,34 +4102,34 @@
         <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="S62" s="9">
-        <v>146.55</v>
+        <v>650</v>
       </c>
     </row>
     <row r="63">
@@ -4194,7 +4146,7 @@
         <v>46195</v>
       </c>
       <c r="E63" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F63" s="8">
         <v>0</v>
@@ -4215,16 +4167,16 @@
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
@@ -4236,7 +4188,7 @@
         <v>36</v>
       </c>
       <c r="S63" s="9">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row r="64">
@@ -4253,7 +4205,7 @@
         <v>46195</v>
       </c>
       <c r="E64" s="7">
-        <v>46170</v>
+        <v>46127</v>
       </c>
       <c r="F64" s="8">
         <v>0</v>
@@ -4268,22 +4220,22 @@
         <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="K64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L64" s="6" t="s">
-        <v>66</v>
-      </c>
       <c r="M64" s="6" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
@@ -4295,7 +4247,7 @@
         <v>36</v>
       </c>
       <c r="S64" s="9">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row r="65">
@@ -4312,7 +4264,7 @@
         <v>46195</v>
       </c>
       <c r="E65" s="7">
-        <v>46169</v>
+        <v>46153</v>
       </c>
       <c r="F65" s="8">
         <v>0</v>
@@ -4336,13 +4288,13 @@
         <v>108</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
@@ -4354,7 +4306,7 @@
         <v>36</v>
       </c>
       <c r="S65" s="9">
-        <v>600</v>
+        <v>650</v>
       </c>
     </row>
     <row r="66">
@@ -4371,7 +4323,7 @@
         <v>46195</v>
       </c>
       <c r="E66" s="7">
-        <v>46176</v>
+        <v>46119</v>
       </c>
       <c r="F66" s="8">
         <v>0</v>
@@ -4392,16 +4344,16 @@
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>62</v>
+        <v>110</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
@@ -4410,10 +4362,10 @@
         <v>35</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S66" s="9">
-        <v>620</v>
+        <v>670</v>
       </c>
     </row>
     <row r="67">
@@ -4430,7 +4382,7 @@
         <v>46195</v>
       </c>
       <c r="E67" s="7">
-        <v>46163</v>
+        <v>46167</v>
       </c>
       <c r="F67" s="8">
         <v>0</v>
@@ -4445,22 +4397,22 @@
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>23</v>
@@ -4472,7 +4424,7 @@
         <v>36</v>
       </c>
       <c r="S67" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="68">
@@ -4489,7 +4441,7 @@
         <v>46195</v>
       </c>
       <c r="E68" s="7">
-        <v>46170</v>
+        <v>46176</v>
       </c>
       <c r="F68" s="8">
         <v>0</v>
@@ -4504,25 +4456,25 @@
         <v>23</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="M68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q68" s="6" t="s">
         <v>35</v>
@@ -4531,7 +4483,7 @@
         <v>36</v>
       </c>
       <c r="S68" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="69">
@@ -4548,7 +4500,7 @@
         <v>46195</v>
       </c>
       <c r="E69" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F69" s="8">
         <v>0</v>
@@ -4563,22 +4515,22 @@
         <v>23</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="M69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
@@ -4590,7 +4542,7 @@
         <v>36</v>
       </c>
       <c r="S69" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="70">
@@ -4607,7 +4559,7 @@
         <v>46195</v>
       </c>
       <c r="E70" s="7">
-        <v>46169</v>
+        <v>46182</v>
       </c>
       <c r="F70" s="8">
         <v>0</v>
@@ -4622,22 +4574,22 @@
         <v>23</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>114</v>
+        <v>79</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4649,7 +4601,7 @@
         <v>36</v>
       </c>
       <c r="S70" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="71">
@@ -4666,7 +4618,7 @@
         <v>46195</v>
       </c>
       <c r="E71" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F71" s="8">
         <v>0</v>
@@ -4681,22 +4633,22 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
@@ -4705,10 +4657,10 @@
         <v>35</v>
       </c>
       <c r="R71" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S71" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="72">
@@ -4725,7 +4677,7 @@
         <v>46195</v>
       </c>
       <c r="E72" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F72" s="8">
         <v>0</v>
@@ -4746,19 +4698,19 @@
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="Q72" s="6" t="s">
         <v>35</v>
@@ -4767,7 +4719,7 @@
         <v>36</v>
       </c>
       <c r="S72" s="9">
-        <v>630</v>
+        <v>700</v>
       </c>
     </row>
     <row r="73">
@@ -4784,7 +4736,7 @@
         <v>46195</v>
       </c>
       <c r="E73" s="7">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="F73" s="8">
         <v>0</v>
@@ -4811,10 +4763,10 @@
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4826,7 +4778,7 @@
         <v>36</v>
       </c>
       <c r="S73" s="9">
-        <v>630</v>
+        <v>700</v>
       </c>
     </row>
     <row r="74">
@@ -4843,7 +4795,7 @@
         <v>46195</v>
       </c>
       <c r="E74" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F74" s="8">
         <v>0</v>
@@ -4864,16 +4816,16 @@
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4882,10 +4834,10 @@
         <v>35</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S74" s="9">
-        <v>650</v>
+        <v>700</v>
       </c>
     </row>
     <row r="75">
@@ -4902,7 +4854,7 @@
         <v>46195</v>
       </c>
       <c r="E75" s="7">
-        <v>46127</v>
+        <v>46148</v>
       </c>
       <c r="F75" s="8">
         <v>0</v>
@@ -4917,22 +4869,22 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>23</v>
@@ -4941,15 +4893,15 @@
         <v>35</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="S75" s="9">
-        <v>650</v>
+        <v>800</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="B76" s="7">
         <v>46195</v>
@@ -4961,7 +4913,7 @@
         <v>46195</v>
       </c>
       <c r="E76" s="7">
-        <v>46153</v>
+        <v>46182</v>
       </c>
       <c r="F76" s="8">
         <v>0</v>
@@ -4976,22 +4928,22 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -5000,10 +4952,10 @@
         <v>35</v>
       </c>
       <c r="R76" s="6" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="S76" s="9">
-        <v>650</v>
+        <v>800</v>
       </c>
     </row>
     <row r="77">
@@ -5035,34 +4987,34 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="Q77" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R77" s="6" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="S77" s="9">
-        <v>650</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="78">
@@ -5079,7 +5031,7 @@
         <v>46195</v>
       </c>
       <c r="E78" s="7">
-        <v>46188</v>
+        <v>46148</v>
       </c>
       <c r="F78" s="8">
         <v>0</v>
@@ -5094,22 +5046,22 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>44</v>
+        <v>131</v>
       </c>
       <c r="M78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>23</v>
@@ -5118,10 +5070,10 @@
         <v>35</v>
       </c>
       <c r="R78" s="6" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="S78" s="9">
-        <v>650</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="79">
@@ -5129,7 +5081,7 @@
         <v>22</v>
       </c>
       <c r="B79" s="7">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C79" s="7">
         <v>46195</v>
@@ -5137,14 +5089,14 @@
       <c r="D79" s="7">
         <v>46195</v>
       </c>
-      <c r="E79" s="7">
-        <v>46119</v>
+      <c r="E79" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F79" s="8">
         <v>0</v>
       </c>
       <c r="G79" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>23</v>
@@ -5153,34 +5105,34 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q79" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S79" s="9">
-        <v>670</v>
+        <v>80.46</v>
       </c>
     </row>
     <row r="80">
@@ -5188,22 +5140,22 @@
         <v>22</v>
       </c>
       <c r="B80" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="C80" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D80" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="E80" s="7">
-        <v>46176</v>
+        <v>46185</v>
       </c>
       <c r="F80" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G80" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>23</v>
@@ -5212,22 +5164,22 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
@@ -5239,7 +5191,7 @@
         <v>36</v>
       </c>
       <c r="S80" s="9">
-        <v>680</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="81">
@@ -5247,22 +5199,22 @@
         <v>22</v>
       </c>
       <c r="B81" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C81" s="7">
-        <v>46195</v>
+        <v>46174</v>
       </c>
       <c r="D81" s="7">
-        <v>46195</v>
+        <v>46218</v>
       </c>
       <c r="E81" s="7">
-        <v>46182</v>
+        <v>46190</v>
       </c>
       <c r="F81" s="8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G81" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>23</v>
@@ -5271,34 +5223,34 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q81" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S81" s="9">
-        <v>680</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82">
@@ -5306,22 +5258,22 @@
         <v>22</v>
       </c>
       <c r="B82" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C82" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D82" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E82" s="7">
-        <v>46167</v>
+        <v>46153</v>
       </c>
       <c r="F82" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G82" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>23</v>
@@ -5330,34 +5282,34 @@
         <v>23</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>133</v>
+        <v>49</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="Q82" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S82" s="9">
-        <v>680</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83">
@@ -5365,58 +5317,58 @@
         <v>22</v>
       </c>
       <c r="B83" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C83" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D83" s="7">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="E83" s="7">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="F83" s="8">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="G83" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q83" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S83" s="9">
-        <v>680</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84">
@@ -5424,22 +5376,22 @@
         <v>22</v>
       </c>
       <c r="B84" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C84" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D84" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E84" s="7">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="F84" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G84" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>23</v>
@@ -5448,34 +5400,34 @@
         <v>23</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="M84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q84" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S84" s="9">
-        <v>680</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85">
@@ -5483,22 +5435,22 @@
         <v>22</v>
       </c>
       <c r="B85" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C85" s="7">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="D85" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E85" s="7">
-        <v>46164</v>
+        <v>46188</v>
       </c>
       <c r="F85" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G85" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>23</v>
@@ -5507,22 +5459,22 @@
         <v>23</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>72</v>
+        <v>121</v>
       </c>
       <c r="M85" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P85" s="6" t="s">
         <v>23</v>
@@ -5534,7 +5486,7 @@
         <v>28</v>
       </c>
       <c r="S85" s="9">
-        <v>680</v>
+        <v>116.66</v>
       </c>
     </row>
     <row r="86">
@@ -5542,22 +5494,22 @@
         <v>22</v>
       </c>
       <c r="B86" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C86" s="7">
-        <v>46195</v>
+        <v>46082</v>
       </c>
       <c r="D86" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E86" s="7">
-        <v>46170</v>
+        <v>46097</v>
       </c>
       <c r="F86" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G86" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>23</v>
@@ -5566,34 +5518,34 @@
         <v>23</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>95</v>
+        <v>26</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q86" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R86" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S86" s="9">
-        <v>700</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="87">
@@ -5601,22 +5553,22 @@
         <v>22</v>
       </c>
       <c r="B87" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C87" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D87" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E87" s="7">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="F87" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G87" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H87" s="6" t="s">
         <v>23</v>
@@ -5631,16 +5583,16 @@
         <v>23</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>139</v>
+        <v>92</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>23</v>
+        <v>92</v>
       </c>
       <c r="N87" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P87" s="6" t="s">
         <v>23</v>
@@ -5652,7 +5604,7 @@
         <v>36</v>
       </c>
       <c r="S87" s="9">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="88">
@@ -5660,22 +5612,22 @@
         <v>22</v>
       </c>
       <c r="B88" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C88" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D88" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E88" s="7">
-        <v>46188</v>
+        <v>46169</v>
       </c>
       <c r="F88" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G88" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>23</v>
@@ -5684,22 +5636,22 @@
         <v>23</v>
       </c>
       <c r="J88" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="K88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="M88" s="6" t="s">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>23</v>
@@ -5708,33 +5660,33 @@
         <v>35</v>
       </c>
       <c r="R88" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S88" s="9">
-        <v>700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>142</v>
+        <v>22</v>
       </c>
       <c r="B89" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C89" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D89" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E89" s="7">
-        <v>46182</v>
+        <v>46163</v>
       </c>
       <c r="F89" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G89" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>23</v>
@@ -5743,22 +5695,22 @@
         <v>23</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="M89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N89" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="O89" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P89" s="6" t="s">
         <v>23</v>
@@ -5767,10 +5719,10 @@
         <v>35</v>
       </c>
       <c r="R89" s="6" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="S89" s="9">
-        <v>800</v>
+        <v>630</v>
       </c>
     </row>
     <row r="90">
@@ -5778,22 +5730,22 @@
         <v>22</v>
       </c>
       <c r="B90" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C90" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D90" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E90" s="7">
-        <v>46148</v>
+        <v>46164</v>
       </c>
       <c r="F90" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G90" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H90" s="6" t="s">
         <v>23</v>
@@ -5802,22 +5754,22 @@
         <v>23</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="M90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>23</v>
@@ -5826,10 +5778,10 @@
         <v>35</v>
       </c>
       <c r="R90" s="6" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="S90" s="9">
-        <v>800</v>
+        <v>630</v>
       </c>
     </row>
     <row r="91">
@@ -5837,22 +5789,22 @@
         <v>22</v>
       </c>
       <c r="B91" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C91" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D91" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E91" s="7">
-        <v>46148</v>
+        <v>46169</v>
       </c>
       <c r="F91" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G91" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>23</v>
@@ -5861,22 +5813,22 @@
         <v>23</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N91" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="O91" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P91" s="6" t="s">
         <v>23</v>
@@ -5885,10 +5837,10 @@
         <v>35</v>
       </c>
       <c r="R91" s="6" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="S91" s="9">
-        <v>1200</v>
+        <v>630</v>
       </c>
     </row>
     <row r="92">
@@ -5896,22 +5848,22 @@
         <v>22</v>
       </c>
       <c r="B92" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C92" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D92" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E92" s="7">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="F92" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G92" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H92" s="6" t="s">
         <v>23</v>
@@ -5920,34 +5872,34 @@
         <v>23</v>
       </c>
       <c r="J92" s="6" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="K92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="M92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="Q92" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R92" s="6" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="S92" s="9">
-        <v>1200</v>
+        <v>630</v>
       </c>
     </row>
     <row r="93">
@@ -5955,22 +5907,22 @@
         <v>22</v>
       </c>
       <c r="B93" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C93" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D93" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E93" s="7">
-        <v>46160</v>
+        <v>46169</v>
       </c>
       <c r="F93" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G93" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>23</v>
@@ -5979,34 +5931,34 @@
         <v>23</v>
       </c>
       <c r="J93" s="6" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="K93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>153</v>
+        <v>95</v>
       </c>
       <c r="M93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N93" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="O93" s="6" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>151</v>
+        <v>23</v>
       </c>
       <c r="Q93" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R93" s="6" t="s">
-        <v>148</v>
+        <v>36</v>
       </c>
       <c r="S93" s="9">
-        <v>1200</v>
+        <v>630</v>
       </c>
     </row>
     <row r="94">
@@ -6014,22 +5966,22 @@
         <v>22</v>
       </c>
       <c r="B94" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="C94" s="7">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D94" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="E94" s="7">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="F94" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G94" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>23</v>
@@ -6038,22 +5990,22 @@
         <v>23</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>155</v>
+        <v>47</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>23</v>
@@ -6062,10 +6014,10 @@
         <v>35</v>
       </c>
       <c r="R94" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S94" s="9">
-        <v>4400</v>
+        <v>650</v>
       </c>
     </row>
     <row r="95">
@@ -6076,16 +6028,16 @@
         <v>46202</v>
       </c>
       <c r="C95" s="7">
-        <v>46174</v>
+        <v>46202</v>
       </c>
       <c r="D95" s="7">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="E95" s="7">
-        <v>46190</v>
+        <v>46127</v>
       </c>
       <c r="F95" s="8">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G95" s="8">
         <v>7</v>
@@ -6097,34 +6049,34 @@
         <v>23</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="N95" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="O95" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q95" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S95" s="9">
-        <v>50</v>
+        <v>650</v>
       </c>
     </row>
     <row r="96">
@@ -6135,7 +6087,7 @@
         <v>46202</v>
       </c>
       <c r="C96" s="7">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D96" s="7">
         <v>46202</v>
@@ -6156,34 +6108,34 @@
         <v>23</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>58</v>
+        <v>149</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>59</v>
+        <v>108</v>
       </c>
       <c r="M96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="Q96" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S96" s="9">
-        <v>50</v>
+        <v>650</v>
       </c>
     </row>
     <row r="97">
@@ -6194,55 +6146,55 @@
         <v>46202</v>
       </c>
       <c r="C97" s="7">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D97" s="7">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="E97" s="7">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="F97" s="8">
-        <v>-7</v>
+        <v>7</v>
       </c>
       <c r="G97" s="8">
         <v>7</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="M97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N97" s="6" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="O97" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q97" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S97" s="9">
-        <v>100</v>
+        <v>650</v>
       </c>
     </row>
     <row r="98">
@@ -6253,7 +6205,7 @@
         <v>46202</v>
       </c>
       <c r="C98" s="7">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D98" s="7">
         <v>46202</v>
@@ -6274,34 +6226,34 @@
         <v>23</v>
       </c>
       <c r="J98" s="6" t="s">
-        <v>100</v>
+        <v>152</v>
       </c>
       <c r="K98" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="M98" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q98" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S98" s="9">
-        <v>100</v>
+        <v>680</v>
       </c>
     </row>
     <row r="99">
@@ -6312,13 +6264,13 @@
         <v>46202</v>
       </c>
       <c r="C99" s="7">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="D99" s="7">
         <v>46202</v>
       </c>
       <c r="E99" s="7">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="F99" s="8">
         <v>7</v>
@@ -6333,22 +6285,22 @@
         <v>23</v>
       </c>
       <c r="J99" s="6" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="M99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N99" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="O99" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P99" s="6" t="s">
         <v>23</v>
@@ -6357,10 +6309,10 @@
         <v>35</v>
       </c>
       <c r="R99" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S99" s="9">
-        <v>116.66</v>
+        <v>680</v>
       </c>
     </row>
     <row r="100">
@@ -6371,13 +6323,13 @@
         <v>46202</v>
       </c>
       <c r="C100" s="7">
-        <v>46082</v>
+        <v>46202</v>
       </c>
       <c r="D100" s="7">
         <v>46202</v>
       </c>
       <c r="E100" s="7">
-        <v>46097</v>
+        <v>46182</v>
       </c>
       <c r="F100" s="8">
         <v>7</v>
@@ -6392,34 +6344,34 @@
         <v>23</v>
       </c>
       <c r="J100" s="6" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="K100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>26</v>
+        <v>133</v>
       </c>
       <c r="M100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q100" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R100" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S100" s="9">
-        <v>146.55</v>
+        <v>680</v>
       </c>
     </row>
     <row r="101">
@@ -6436,7 +6388,7 @@
         <v>46202</v>
       </c>
       <c r="E101" s="7">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="F101" s="8">
         <v>7</v>
@@ -6451,22 +6403,22 @@
         <v>23</v>
       </c>
       <c r="J101" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="K101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="M101" s="6" t="s">
-        <v>105</v>
+        <v>23</v>
       </c>
       <c r="N101" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="O101" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P101" s="6" t="s">
         <v>23</v>
@@ -6475,10 +6427,10 @@
         <v>35</v>
       </c>
       <c r="R101" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S101" s="9">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="102">
@@ -6495,7 +6447,7 @@
         <v>46202</v>
       </c>
       <c r="E102" s="7">
-        <v>46169</v>
+        <v>46182</v>
       </c>
       <c r="F102" s="8">
         <v>7</v>
@@ -6510,22 +6462,22 @@
         <v>23</v>
       </c>
       <c r="J102" s="6" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="K102" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>23</v>
@@ -6537,7 +6489,7 @@
         <v>36</v>
       </c>
       <c r="S102" s="9">
-        <v>600</v>
+        <v>680</v>
       </c>
     </row>
     <row r="103">
@@ -6554,7 +6506,7 @@
         <v>46202</v>
       </c>
       <c r="E103" s="7">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="F103" s="8">
         <v>7</v>
@@ -6569,22 +6521,22 @@
         <v>23</v>
       </c>
       <c r="J103" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K103" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="M103" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N103" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="O103" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P103" s="6" t="s">
         <v>23</v>
@@ -6596,7 +6548,7 @@
         <v>36</v>
       </c>
       <c r="S103" s="9">
-        <v>630</v>
+        <v>700</v>
       </c>
     </row>
     <row r="104">
@@ -6613,7 +6565,7 @@
         <v>46202</v>
       </c>
       <c r="E104" s="7">
-        <v>46169</v>
+        <v>46188</v>
       </c>
       <c r="F104" s="8">
         <v>7</v>
@@ -6628,22 +6580,22 @@
         <v>23</v>
       </c>
       <c r="J104" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="M104" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>23</v>
@@ -6652,15 +6604,15 @@
         <v>35</v>
       </c>
       <c r="R104" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S104" s="9">
-        <v>630</v>
+        <v>700</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="s">
-        <v>22</v>
+        <v>123</v>
       </c>
       <c r="B105" s="7">
         <v>46202</v>
@@ -6672,7 +6624,7 @@
         <v>46202</v>
       </c>
       <c r="E105" s="7">
-        <v>46169</v>
+        <v>46182</v>
       </c>
       <c r="F105" s="8">
         <v>7</v>
@@ -6687,22 +6639,22 @@
         <v>23</v>
       </c>
       <c r="J105" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K105" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="M105" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N105" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="O105" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P105" s="6" t="s">
         <v>23</v>
@@ -6711,10 +6663,10 @@
         <v>35</v>
       </c>
       <c r="R105" s="6" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="S105" s="9">
-        <v>630</v>
+        <v>800</v>
       </c>
     </row>
     <row r="106">
@@ -6731,7 +6683,7 @@
         <v>46202</v>
       </c>
       <c r="E106" s="7">
-        <v>46169</v>
+        <v>46148</v>
       </c>
       <c r="F106" s="8">
         <v>7</v>
@@ -6746,22 +6698,22 @@
         <v>23</v>
       </c>
       <c r="J106" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K106" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="M106" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>23</v>
@@ -6770,10 +6722,10 @@
         <v>35</v>
       </c>
       <c r="R106" s="6" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="S106" s="9">
-        <v>630</v>
+        <v>800</v>
       </c>
     </row>
     <row r="107">
@@ -6790,7 +6742,7 @@
         <v>46202</v>
       </c>
       <c r="E107" s="7">
-        <v>46164</v>
+        <v>46160</v>
       </c>
       <c r="F107" s="8">
         <v>7</v>
@@ -6805,34 +6757,34 @@
         <v>23</v>
       </c>
       <c r="J107" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="K107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="M107" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N107" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="O107" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P107" s="6" t="s">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="Q107" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R107" s="6" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="S107" s="9">
-        <v>630</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="108">
@@ -6849,7 +6801,7 @@
         <v>46202</v>
       </c>
       <c r="E108" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="F108" s="8">
         <v>7</v>
@@ -6864,34 +6816,34 @@
         <v>23</v>
       </c>
       <c r="J108" s="6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M108" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="Q108" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R108" s="6" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="S108" s="9">
-        <v>650</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="109">
@@ -6908,7 +6860,7 @@
         <v>46202</v>
       </c>
       <c r="E109" s="7">
-        <v>46127</v>
+        <v>46148</v>
       </c>
       <c r="F109" s="8">
         <v>7</v>
@@ -6923,22 +6875,22 @@
         <v>23</v>
       </c>
       <c r="J109" s="6" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K109" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="M109" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N109" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="O109" s="6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="P109" s="6" t="s">
         <v>23</v>
@@ -6947,859 +6899,33 @@
         <v>35</v>
       </c>
       <c r="R109" s="6" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="S109" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B110" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C110" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D110" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E110" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F110" s="8">
-        <v>7</v>
-      </c>
-      <c r="G110" s="8">
-        <v>7</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I110" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J110" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="K110" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L110" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="M110" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N110" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O110" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P110" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q110" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R110" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S110" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B111" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C111" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D111" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E111" s="7">
-        <v>46188</v>
-      </c>
-      <c r="F111" s="8">
-        <v>7</v>
-      </c>
-      <c r="G111" s="8">
-        <v>7</v>
-      </c>
-      <c r="H111" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I111" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J111" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="K111" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L111" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="M111" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N111" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O111" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P111" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q111" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R111" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S111" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B112" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C112" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D112" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E112" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F112" s="8">
-        <v>7</v>
-      </c>
-      <c r="G112" s="8">
-        <v>7</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I112" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J112" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="K112" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L112" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="M112" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N112" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O112" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P112" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q112" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R112" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S112" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B113" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C113" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D113" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E113" s="7">
-        <v>46164</v>
-      </c>
-      <c r="F113" s="8">
-        <v>7</v>
-      </c>
-      <c r="G113" s="8">
-        <v>7</v>
-      </c>
-      <c r="H113" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I113" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J113" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="K113" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L113" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="M113" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N113" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O113" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P113" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q113" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R113" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S113" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B114" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C114" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D114" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E114" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F114" s="8">
-        <v>7</v>
-      </c>
-      <c r="G114" s="8">
-        <v>7</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J114" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="K114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L114" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="M114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N114" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O114" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P114" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q114" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R114" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S114" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B115" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C115" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D115" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E115" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F115" s="8">
-        <v>7</v>
-      </c>
-      <c r="G115" s="8">
-        <v>7</v>
-      </c>
-      <c r="H115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J115" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="K115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L115" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="M115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N115" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O115" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P115" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q115" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R115" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S115" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B116" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C116" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D116" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E116" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F116" s="8">
-        <v>7</v>
-      </c>
-      <c r="G116" s="8">
-        <v>7</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I116" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J116" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="K116" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L116" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="M116" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N116" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O116" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P116" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q116" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R116" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S116" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B117" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C117" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D117" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E117" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F117" s="8">
-        <v>7</v>
-      </c>
-      <c r="G117" s="8">
-        <v>7</v>
-      </c>
-      <c r="H117" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I117" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J117" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="K117" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L117" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="M117" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N117" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O117" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P117" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q117" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R117" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S117" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B118" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C118" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D118" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E118" s="7">
-        <v>46188</v>
-      </c>
-      <c r="F118" s="8">
-        <v>7</v>
-      </c>
-      <c r="G118" s="8">
-        <v>7</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I118" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J118" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="K118" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L118" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="M118" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N118" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O118" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P118" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q118" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R118" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S118" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B119" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C119" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D119" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E119" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F119" s="8">
-        <v>7</v>
-      </c>
-      <c r="G119" s="8">
-        <v>7</v>
-      </c>
-      <c r="H119" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I119" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J119" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="K119" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L119" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="M119" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N119" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O119" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P119" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q119" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R119" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="S119" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B120" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C120" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D120" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E120" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F120" s="8">
-        <v>7</v>
-      </c>
-      <c r="G120" s="8">
-        <v>7</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I120" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J120" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="K120" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L120" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="M120" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N120" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O120" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P120" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q120" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R120" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="S120" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B121" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C121" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D121" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E121" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F121" s="8">
-        <v>7</v>
-      </c>
-      <c r="G121" s="8">
-        <v>7</v>
-      </c>
-      <c r="H121" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I121" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J121" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="K121" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L121" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="M121" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N121" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O121" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P121" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q121" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R121" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="S121" s="9">
         <v>1200</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B122" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C122" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D122" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E122" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F122" s="8">
-        <v>7</v>
-      </c>
-      <c r="G122" s="8">
-        <v>7</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I122" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J122" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="K122" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L122" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="M122" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N122" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O122" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P122" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q122" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R122" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="S122" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B123" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C123" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D123" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E123" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F123" s="8">
-        <v>7</v>
-      </c>
-      <c r="G123" s="8">
-        <v>7</v>
-      </c>
-      <c r="H123" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I123" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J123" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="K123" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L123" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="M123" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N123" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="O123" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="P123" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="Q123" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R123" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="S123" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="124" ht="23" customHeight="1">
-      <c r="A124" s="10"/>
-      <c r="B124" s="11"/>
-      <c r="C124" s="11"/>
-      <c r="D124" s="11"/>
-      <c r="E124" s="11"/>
-      <c r="F124" s="12"/>
-      <c r="G124" s="12"/>
-      <c r="H124" s="10"/>
-      <c r="I124" s="10"/>
-      <c r="J124" s="10"/>
-      <c r="K124" s="10"/>
-      <c r="L124" s="10"/>
-      <c r="M124" s="10"/>
-      <c r="N124" s="10"/>
-      <c r="O124" s="10"/>
-      <c r="P124" s="10"/>
-      <c r="Q124" s="10"/>
-      <c r="R124" s="10"/>
-      <c r="S124" s="13">
-        <f>SUM(S6:S123)</f>
+    <row r="110" ht="23" customHeight="1">
+      <c r="A110" s="10"/>
+      <c r="B110" s="11"/>
+      <c r="C110" s="11"/>
+      <c r="D110" s="11"/>
+      <c r="E110" s="11"/>
+      <c r="F110" s="12"/>
+      <c r="G110" s="12"/>
+      <c r="H110" s="10"/>
+      <c r="I110" s="10"/>
+      <c r="J110" s="10"/>
+      <c r="K110" s="10"/>
+      <c r="L110" s="10"/>
+      <c r="M110" s="10"/>
+      <c r="N110" s="10"/>
+      <c r="O110" s="10"/>
+      <c r="P110" s="10"/>
+      <c r="Q110" s="10"/>
+      <c r="R110" s="10"/>
+      <c r="S110" s="13">
+        <f>SUM(S6:S109)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$110</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$107</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -166,69 +166,63 @@
     <t>FA-11568</t>
   </si>
   <si>
-    <t>FA-11796</t>
+    <t>ND-11801</t>
+  </si>
+  <si>
+    <t>ND-11699</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>FA-11806</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11571</t>
+  </si>
+  <si>
+    <t>FA-11797</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11724</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11572</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11798</t>
   </si>
   <si>
     <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
   </si>
   <si>
-    <t>FA-11847</t>
+    <t>FA-11776</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11848</t>
   </si>
   <si>
     <t>ANDRE CAVALCANTI DA FE</t>
   </si>
   <si>
-    <t>ND-11801</t>
-  </si>
-  <si>
-    <t>ND-11699</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>FA-11806</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11571</t>
-  </si>
-  <si>
-    <t>FA-11797</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11724</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11572</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11798</t>
-  </si>
-  <si>
-    <t>FA-11848</t>
-  </si>
-  <si>
-    <t>FA-11776</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
     <t>FA-11679</t>
   </si>
   <si>
@@ -241,69 +235,66 @@
     <t>LEONARDO GOMES DO NASCIMENTO</t>
   </si>
   <si>
-    <t>FA-11694</t>
+    <t>ND-11844</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11756</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11785</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11772</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11842</t>
+  </si>
+  <si>
+    <t>M&amp;S DO TRABALHO</t>
+  </si>
+  <si>
+    <t>ND-11700</t>
+  </si>
+  <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>ND-11870</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-11775</t>
+  </si>
+  <si>
+    <t>FA-11787</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11693</t>
   </si>
   <si>
     <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
   </si>
   <si>
-    <t>ND-11844</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11756</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11785</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11772</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-11842</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
-  </si>
-  <si>
-    <t>ND-11700</t>
-  </si>
-  <si>
-    <t>HOJE</t>
-  </si>
-  <si>
-    <t>ND-11870</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>FA-11775</t>
-  </si>
-  <si>
-    <t>FA-11787</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11693</t>
-  </si>
-  <si>
     <t>FA-11791</t>
   </si>
   <si>
@@ -316,6 +307,12 @@
     <t>FA-11807</t>
   </si>
   <si>
+    <t>FA-11672</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
     <t>FA-11731</t>
   </si>
   <si>
@@ -331,12 +328,6 @@
     <t>FA-11800</t>
   </si>
   <si>
-    <t>FA-11672</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
     <t>FA-11687</t>
   </si>
   <si>
@@ -376,12 +367,12 @@
     <t>LUCAS NAJA MOURA RODRIGUES</t>
   </si>
   <si>
+    <t>FA-11823</t>
+  </si>
+  <si>
     <t>FA-11822</t>
   </si>
   <si>
-    <t>FA-11823</t>
-  </si>
-  <si>
     <t>FA-11680</t>
   </si>
   <si>
@@ -400,16 +391,25 @@
     <t>MAICON LOPES SILVA</t>
   </si>
   <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>FA-11824</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
     <t>FA-11605</t>
   </si>
   <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>FA-11824</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
+    <t>FA-11595</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
   </si>
   <si>
     <t>FA-11636</t>
@@ -421,15 +421,6 @@
     <t>PÚBLICO</t>
   </si>
   <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11595</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
     <t>FA-11821</t>
   </si>
   <si>
@@ -457,64 +448,67 @@
     <t>ROBERTO MURATORI</t>
   </si>
   <si>
+    <t>FA-11688</t>
+  </si>
+  <si>
+    <t>FA-11737</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11732</t>
+  </si>
+  <si>
+    <t>FA-11734</t>
+  </si>
+  <si>
     <t>FA-11673</t>
   </si>
   <si>
-    <t>FA-11688</t>
-  </si>
-  <si>
-    <t>FA-11737</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11732</t>
-  </si>
-  <si>
-    <t>FA-11734</t>
-  </si>
-  <si>
     <t>FA-11852</t>
   </si>
   <si>
     <t>FA-11509</t>
   </si>
   <si>
+    <t>FA-11661</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
     <t>FA-11626</t>
   </si>
   <si>
-    <t>FA-11661</t>
-  </si>
-  <si>
-    <t>LUCA ZOLI</t>
-  </si>
-  <si>
     <t>FA-11696</t>
   </si>
   <si>
+    <t>FA-11825</t>
+  </si>
+  <si>
+    <t>FA-11826</t>
+  </si>
+  <si>
     <t>FA-11827</t>
   </si>
   <si>
-    <t>FA-11825</t>
-  </si>
-  <si>
     <t>FA-11681</t>
   </si>
   <si>
-    <t>FA-11826</t>
-  </si>
-  <si>
     <t>FA-11766</t>
   </si>
   <si>
     <t>FA-11853</t>
   </si>
   <si>
+    <t>FA-11606</t>
+  </si>
+  <si>
     <t>FA-11828</t>
   </si>
   <si>
-    <t>FA-11606</t>
+    <t>FA-11596</t>
   </si>
   <si>
     <t>FA-11649</t>
@@ -524,9 +518,6 @@
   </si>
   <si>
     <t>FA-11637</t>
-  </si>
-  <si>
-    <t>FA-11596</t>
   </si>
 </sst>
 </file>
@@ -669,7 +660,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S110"/>
+  <dimension ref="A1:S107"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -1839,7 +1830,7 @@
         <v>46181</v>
       </c>
       <c r="C24" s="7">
-        <v>46181</v>
+        <v>46143</v>
       </c>
       <c r="D24" s="7">
         <v>46181</v>
@@ -1866,7 +1857,7 @@
         <v>23</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>23</v>
@@ -1881,13 +1872,13 @@
         <v>23</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S24" s="9">
-        <v>630</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="25">
@@ -1895,22 +1886,22 @@
         <v>22</v>
       </c>
       <c r="B25" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="C25" s="7">
-        <v>46181</v>
+        <v>46143</v>
       </c>
       <c r="D25" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="E25" s="7">
-        <v>46188</v>
+        <v>46153</v>
       </c>
       <c r="F25" s="8">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="G25" s="8">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>39</v>
@@ -1919,34 +1910,34 @@
         <v>39</v>
       </c>
       <c r="J25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="K25" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L25" s="6" t="s">
+      <c r="M25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N25" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P25" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="M25" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N25" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O25" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P25" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="Q25" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S25" s="9">
-        <v>650</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
@@ -1954,22 +1945,22 @@
         <v>22</v>
       </c>
       <c r="B26" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="C26" s="7">
-        <v>46143</v>
+        <v>46188</v>
       </c>
       <c r="D26" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E26" s="7">
-        <v>46170</v>
+        <v>46188</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F26" s="8">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="G26" s="8">
-        <v>-14</v>
+        <v>-7</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>39</v>
@@ -1984,10 +1975,10 @@
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>27</v>
@@ -1999,13 +1990,13 @@
         <v>23</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="S26" s="9">
-        <v>2969.17</v>
+        <v>70.07</v>
       </c>
     </row>
     <row r="27">
@@ -2016,13 +2007,13 @@
         <v>46188</v>
       </c>
       <c r="C27" s="7">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="D27" s="7">
         <v>46188</v>
       </c>
       <c r="E27" s="7">
-        <v>46153</v>
+        <v>46097</v>
       </c>
       <c r="F27" s="8">
         <v>-7</v>
@@ -2037,13 +2028,13 @@
         <v>39</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -2055,16 +2046,16 @@
         <v>27</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="Q27" s="6" t="s">
         <v>29</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S27" s="9">
-        <v>50</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="28">
@@ -2080,8 +2071,8 @@
       <c r="D28" s="7">
         <v>46188</v>
       </c>
-      <c r="E28" s="7" t="s">
-        <v>23</v>
+      <c r="E28" s="7">
+        <v>46141</v>
       </c>
       <c r="F28" s="8">
         <v>-7</v>
@@ -2096,16 +2087,16 @@
         <v>39</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>27</v>
@@ -2117,13 +2108,13 @@
         <v>23</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S28" s="9">
-        <v>70.07</v>
+        <v>310</v>
       </c>
     </row>
     <row r="29">
@@ -2134,13 +2125,13 @@
         <v>46188</v>
       </c>
       <c r="C29" s="7">
-        <v>46082</v>
+        <v>46188</v>
       </c>
       <c r="D29" s="7">
         <v>46188</v>
       </c>
-      <c r="E29" s="7">
-        <v>46097</v>
+      <c r="E29" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F29" s="8">
         <v>-7</v>
@@ -2155,13 +2146,13 @@
         <v>39</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>23</v>
@@ -2176,13 +2167,13 @@
         <v>23</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S29" s="9">
-        <v>146.55</v>
+        <v>330</v>
       </c>
     </row>
     <row r="30">
@@ -2199,7 +2190,7 @@
         <v>46188</v>
       </c>
       <c r="E30" s="7">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="F30" s="8">
         <v>-7</v>
@@ -2214,13 +2205,13 @@
         <v>39</v>
       </c>
       <c r="J30" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>23</v>
@@ -2241,7 +2232,7 @@
         <v>36</v>
       </c>
       <c r="S30" s="9">
-        <v>310</v>
+        <v>540</v>
       </c>
     </row>
     <row r="31">
@@ -2257,8 +2248,8 @@
       <c r="D31" s="7">
         <v>46188</v>
       </c>
-      <c r="E31" s="7" t="s">
-        <v>23</v>
+      <c r="E31" s="7">
+        <v>46141</v>
       </c>
       <c r="F31" s="8">
         <v>-7</v>
@@ -2282,7 +2273,7 @@
         <v>56</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>27</v>
@@ -2294,13 +2285,13 @@
         <v>23</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S31" s="9">
-        <v>330</v>
+        <v>620</v>
       </c>
     </row>
     <row r="32">
@@ -2317,7 +2308,7 @@
         <v>46188</v>
       </c>
       <c r="E32" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F32" s="8">
         <v>-7</v>
@@ -2359,7 +2350,7 @@
         <v>36</v>
       </c>
       <c r="S32" s="9">
-        <v>540</v>
+        <v>630</v>
       </c>
     </row>
     <row r="33">
@@ -2376,7 +2367,7 @@
         <v>46188</v>
       </c>
       <c r="E33" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="F33" s="8">
         <v>-7</v>
@@ -2418,7 +2409,7 @@
         <v>36</v>
       </c>
       <c r="S33" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="34">
@@ -2435,7 +2426,7 @@
         <v>46188</v>
       </c>
       <c r="E34" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F34" s="8">
         <v>-7</v>
@@ -2456,7 +2447,7 @@
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>23</v>
@@ -2474,10 +2465,10 @@
         <v>35</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S34" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="35">
@@ -2494,7 +2485,7 @@
         <v>46188</v>
       </c>
       <c r="E35" s="7">
-        <v>46188</v>
+        <v>46164</v>
       </c>
       <c r="F35" s="8">
         <v>-7</v>
@@ -2509,13 +2500,13 @@
         <v>39</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2536,7 +2527,7 @@
         <v>28</v>
       </c>
       <c r="S35" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="36">
@@ -2553,7 +2544,7 @@
         <v>46188</v>
       </c>
       <c r="E36" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F36" s="8">
         <v>-7</v>
@@ -2568,16 +2559,16 @@
         <v>39</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>64</v>
+        <v>23</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>27</v>
@@ -2595,7 +2586,7 @@
         <v>36</v>
       </c>
       <c r="S36" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="37">
@@ -2603,22 +2594,22 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="C37" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D37" s="7">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="E37" s="7">
-        <v>46164</v>
+        <v>46185</v>
       </c>
       <c r="F37" s="8">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="G37" s="8">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>39</v>
@@ -2627,13 +2618,13 @@
         <v>39</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>23</v>
@@ -2648,13 +2639,13 @@
         <v>23</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="S37" s="9">
-        <v>680</v>
+        <v>170.96</v>
       </c>
     </row>
     <row r="38">
@@ -2662,7 +2653,7 @@
         <v>22</v>
       </c>
       <c r="B38" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C38" s="7">
         <v>46188</v>
@@ -2670,14 +2661,14 @@
       <c r="D38" s="7">
         <v>46188</v>
       </c>
-      <c r="E38" s="7">
-        <v>46182</v>
+      <c r="E38" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F38" s="8">
         <v>-7</v>
       </c>
       <c r="G38" s="8">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>39</v>
@@ -2686,13 +2677,13 @@
         <v>39</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>23</v>
@@ -2707,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S38" s="9">
-        <v>680</v>
+        <v>134.74</v>
       </c>
     </row>
     <row r="39">
@@ -2721,7 +2712,7 @@
         <v>22</v>
       </c>
       <c r="B39" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C39" s="7">
         <v>46188</v>
@@ -2729,14 +2720,14 @@
       <c r="D39" s="7">
         <v>46188</v>
       </c>
-      <c r="E39" s="7">
-        <v>46167</v>
+      <c r="E39" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F39" s="8">
         <v>-7</v>
       </c>
       <c r="G39" s="8">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>39</v>
@@ -2745,13 +2736,13 @@
         <v>39</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>23</v>
@@ -2763,16 +2754,16 @@
         <v>27</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S39" s="9">
-        <v>680</v>
+        <v>190</v>
       </c>
     </row>
     <row r="40">
@@ -2780,22 +2771,22 @@
         <v>22</v>
       </c>
       <c r="B40" s="7">
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="C40" s="7">
         <v>46174</v>
       </c>
       <c r="D40" s="7">
-        <v>46189</v>
-      </c>
-      <c r="E40" s="7">
-        <v>46185</v>
+        <v>46174</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F40" s="8">
-        <v>-6</v>
+        <v>-21</v>
       </c>
       <c r="G40" s="8">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>39</v>
@@ -2804,13 +2795,13 @@
         <v>39</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>23</v>
@@ -2825,13 +2816,13 @@
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="S40" s="9">
-        <v>170.96</v>
+        <v>160.54</v>
       </c>
     </row>
     <row r="41">
@@ -2839,22 +2830,22 @@
         <v>22</v>
       </c>
       <c r="B41" s="7">
-        <v>46190</v>
+        <v>46192</v>
       </c>
       <c r="C41" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D41" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>23</v>
+        <v>46192</v>
+      </c>
+      <c r="E41" s="7">
+        <v>46185</v>
       </c>
       <c r="F41" s="8">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="G41" s="8">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>39</v>
@@ -2863,16 +2854,16 @@
         <v>39</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>27</v>
@@ -2884,13 +2875,13 @@
         <v>23</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S41" s="9">
-        <v>134.74</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="42">
@@ -2898,37 +2889,37 @@
         <v>22</v>
       </c>
       <c r="B42" s="7">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="C42" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D42" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>23</v>
+        <v>46181</v>
+      </c>
+      <c r="E42" s="7">
+        <v>46167</v>
       </c>
       <c r="F42" s="8">
-        <v>-7</v>
+        <v>-14</v>
       </c>
       <c r="G42" s="8">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>39</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -2937,19 +2928,19 @@
         <v>27</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S42" s="9">
-        <v>190</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43">
@@ -2957,58 +2948,58 @@
         <v>22</v>
       </c>
       <c r="B43" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C43" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D43" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>23</v>
+        <v>46195</v>
+      </c>
+      <c r="E43" s="7">
+        <v>46153</v>
       </c>
       <c r="F43" s="8">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="G43" s="8">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N43" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="M43" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N43" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="O43" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S43" s="9">
-        <v>160.54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44">
@@ -3016,28 +3007,28 @@
         <v>22</v>
       </c>
       <c r="B44" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C44" s="7">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="D44" s="7">
-        <v>46192</v>
+        <v>46211</v>
       </c>
       <c r="E44" s="7">
-        <v>46185</v>
+        <v>46190</v>
       </c>
       <c r="F44" s="8">
-        <v>-3</v>
+        <v>16</v>
       </c>
       <c r="G44" s="8">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="J44" s="6" t="s">
         <v>80</v>
@@ -3046,28 +3037,28 @@
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="N44" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="M44" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="N44" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="O44" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S44" s="9">
-        <v>2100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45">
@@ -3081,40 +3072,40 @@
         <v>46143</v>
       </c>
       <c r="D45" s="7">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="E45" s="7">
         <v>46167</v>
       </c>
       <c r="F45" s="8">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="G45" s="8">
         <v>0</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N45" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="M45" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N45" s="6" t="s">
-        <v>27</v>
-      </c>
       <c r="O45" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>23</v>
@@ -3126,7 +3117,7 @@
         <v>36</v>
       </c>
       <c r="S45" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
@@ -3137,13 +3128,13 @@
         <v>46195</v>
       </c>
       <c r="C46" s="7">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="D46" s="7">
         <v>46195</v>
       </c>
       <c r="E46" s="7">
-        <v>46153</v>
+        <v>46097</v>
       </c>
       <c r="F46" s="8">
         <v>0</v>
@@ -3158,34 +3149,34 @@
         <v>23</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="Q46" s="6" t="s">
         <v>29</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S46" s="9">
-        <v>50</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="47">
@@ -3196,28 +3187,28 @@
         <v>46195</v>
       </c>
       <c r="C47" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D47" s="7">
-        <v>46211</v>
-      </c>
-      <c r="E47" s="7">
-        <v>46190</v>
+        <v>46181</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F47" s="8">
-        <v>16</v>
+        <v>-14</v>
       </c>
       <c r="G47" s="8">
         <v>0</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
@@ -3229,22 +3220,22 @@
         <v>60</v>
       </c>
       <c r="N47" s="6" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S47" s="9">
-        <v>50</v>
+        <v>500</v>
       </c>
     </row>
     <row r="48">
@@ -3255,55 +3246,55 @@
         <v>46195</v>
       </c>
       <c r="C48" s="7">
-        <v>46143</v>
+        <v>46188</v>
       </c>
       <c r="D48" s="7">
-        <v>46195</v>
-      </c>
-      <c r="E48" s="7">
-        <v>46167</v>
+        <v>46188</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F48" s="8">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="G48" s="8">
         <v>0</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O48" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="M48" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="P48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S48" s="9">
-        <v>100</v>
+        <v>500</v>
       </c>
     </row>
     <row r="49">
@@ -3314,55 +3305,55 @@
         <v>46195</v>
       </c>
       <c r="C49" s="7">
-        <v>46082</v>
+        <v>46181</v>
       </c>
       <c r="D49" s="7">
-        <v>46195</v>
-      </c>
-      <c r="E49" s="7">
-        <v>46097</v>
+        <v>46181</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F49" s="8">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="G49" s="8">
         <v>0</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N49" s="6" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S49" s="9">
-        <v>146.55</v>
+        <v>540</v>
       </c>
     </row>
     <row r="50">
@@ -3373,55 +3364,55 @@
         <v>46195</v>
       </c>
       <c r="C50" s="7">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="D50" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>23</v>
+        <v>46195</v>
+      </c>
+      <c r="E50" s="7">
+        <v>46170</v>
       </c>
       <c r="F50" s="8">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="G50" s="8">
         <v>0</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q50" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S50" s="9">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="51">
@@ -3432,55 +3423,55 @@
         <v>46195</v>
       </c>
       <c r="C51" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="D51" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>23</v>
+        <v>46195</v>
+      </c>
+      <c r="E51" s="7">
+        <v>46169</v>
       </c>
       <c r="F51" s="8">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="G51" s="8">
         <v>0</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q51" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S51" s="9">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="52">
@@ -3491,55 +3482,55 @@
         <v>46195</v>
       </c>
       <c r="C52" s="7">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="D52" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>23</v>
+        <v>46195</v>
+      </c>
+      <c r="E52" s="7">
+        <v>46176</v>
       </c>
       <c r="F52" s="8">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="G52" s="8">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J52" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S52" s="9">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="53">
@@ -3556,7 +3547,7 @@
         <v>46195</v>
       </c>
       <c r="E53" s="7">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="F53" s="8">
         <v>0</v>
@@ -3571,22 +3562,22 @@
         <v>23</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>23</v>
@@ -3598,7 +3589,7 @@
         <v>36</v>
       </c>
       <c r="S53" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="54">
@@ -3630,22 +3621,22 @@
         <v>23</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>23</v>
@@ -3657,7 +3648,7 @@
         <v>36</v>
       </c>
       <c r="S54" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="55">
@@ -3674,7 +3665,7 @@
         <v>46195</v>
       </c>
       <c r="E55" s="7">
-        <v>46176</v>
+        <v>46169</v>
       </c>
       <c r="F55" s="8">
         <v>0</v>
@@ -3689,22 +3680,22 @@
         <v>23</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>23</v>
@@ -3713,10 +3704,10 @@
         <v>35</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S55" s="9">
-        <v>620</v>
+        <v>630</v>
       </c>
     </row>
     <row r="56">
@@ -3733,7 +3724,7 @@
         <v>46195</v>
       </c>
       <c r="E56" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F56" s="8">
         <v>0</v>
@@ -3748,25 +3739,25 @@
         <v>23</v>
       </c>
       <c r="J56" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="Q56" s="6" t="s">
         <v>35</v>
@@ -3792,7 +3783,7 @@
         <v>46195</v>
       </c>
       <c r="E57" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F57" s="8">
         <v>0</v>
@@ -3807,7 +3798,7 @@
         <v>23</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
@@ -3819,10 +3810,10 @@
         <v>23</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>23</v>
@@ -3851,7 +3842,7 @@
         <v>46195</v>
       </c>
       <c r="E58" s="7">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="F58" s="8">
         <v>0</v>
@@ -3866,25 +3857,25 @@
         <v>23</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="Q58" s="6" t="s">
         <v>35</v>
@@ -3910,7 +3901,7 @@
         <v>46195</v>
       </c>
       <c r="E59" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F59" s="8">
         <v>0</v>
@@ -3925,22 +3916,22 @@
         <v>23</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>23</v>
@@ -3949,10 +3940,10 @@
         <v>35</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S59" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="60">
@@ -3969,7 +3960,7 @@
         <v>46195</v>
       </c>
       <c r="E60" s="7">
-        <v>46163</v>
+        <v>46170</v>
       </c>
       <c r="F60" s="8">
         <v>0</v>
@@ -3984,22 +3975,22 @@
         <v>23</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>23</v>
@@ -4011,7 +4002,7 @@
         <v>36</v>
       </c>
       <c r="S60" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="61">
@@ -4028,7 +4019,7 @@
         <v>46195</v>
       </c>
       <c r="E61" s="7">
-        <v>46164</v>
+        <v>46127</v>
       </c>
       <c r="F61" s="8">
         <v>0</v>
@@ -4043,22 +4034,22 @@
         <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
@@ -4070,7 +4061,7 @@
         <v>36</v>
       </c>
       <c r="S61" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="62">
@@ -4087,7 +4078,7 @@
         <v>46195</v>
       </c>
       <c r="E62" s="7">
-        <v>46188</v>
+        <v>46153</v>
       </c>
       <c r="F62" s="8">
         <v>0</v>
@@ -4102,22 +4093,22 @@
         <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>23</v>
@@ -4126,7 +4117,7 @@
         <v>35</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S62" s="9">
         <v>650</v>
@@ -4146,7 +4137,7 @@
         <v>46195</v>
       </c>
       <c r="E63" s="7">
-        <v>46170</v>
+        <v>46119</v>
       </c>
       <c r="F63" s="8">
         <v>0</v>
@@ -4161,22 +4152,22 @@
         <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
@@ -4188,7 +4179,7 @@
         <v>36</v>
       </c>
       <c r="S63" s="9">
-        <v>650</v>
+        <v>670</v>
       </c>
     </row>
     <row r="64">
@@ -4205,7 +4196,7 @@
         <v>46195</v>
       </c>
       <c r="E64" s="7">
-        <v>46127</v>
+        <v>46167</v>
       </c>
       <c r="F64" s="8">
         <v>0</v>
@@ -4220,22 +4211,22 @@
         <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
@@ -4247,7 +4238,7 @@
         <v>36</v>
       </c>
       <c r="S64" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="65">
@@ -4264,7 +4255,7 @@
         <v>46195</v>
       </c>
       <c r="E65" s="7">
-        <v>46153</v>
+        <v>46176</v>
       </c>
       <c r="F65" s="8">
         <v>0</v>
@@ -4279,22 +4270,22 @@
         <v>23</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
@@ -4306,7 +4297,7 @@
         <v>36</v>
       </c>
       <c r="S65" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="66">
@@ -4323,7 +4314,7 @@
         <v>46195</v>
       </c>
       <c r="E66" s="7">
-        <v>46119</v>
+        <v>46182</v>
       </c>
       <c r="F66" s="8">
         <v>0</v>
@@ -4338,22 +4329,22 @@
         <v>23</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="M66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
@@ -4365,7 +4356,7 @@
         <v>36</v>
       </c>
       <c r="S66" s="9">
-        <v>670</v>
+        <v>680</v>
       </c>
     </row>
     <row r="67">
@@ -4382,7 +4373,7 @@
         <v>46195</v>
       </c>
       <c r="E67" s="7">
-        <v>46167</v>
+        <v>46182</v>
       </c>
       <c r="F67" s="8">
         <v>0</v>
@@ -4397,22 +4388,22 @@
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="M67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>23</v>
@@ -4441,7 +4432,7 @@
         <v>46195</v>
       </c>
       <c r="E68" s="7">
-        <v>46176</v>
+        <v>46164</v>
       </c>
       <c r="F68" s="8">
         <v>0</v>
@@ -4456,22 +4447,22 @@
         <v>23</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="M68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
@@ -4480,7 +4471,7 @@
         <v>35</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S68" s="9">
         <v>680</v>
@@ -4500,7 +4491,7 @@
         <v>46195</v>
       </c>
       <c r="E69" s="7">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="F69" s="8">
         <v>0</v>
@@ -4521,19 +4512,19 @@
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="M69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="Q69" s="6" t="s">
         <v>35</v>
@@ -4542,7 +4533,7 @@
         <v>36</v>
       </c>
       <c r="S69" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="70">
@@ -4559,7 +4550,7 @@
         <v>46195</v>
       </c>
       <c r="E70" s="7">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="F70" s="8">
         <v>0</v>
@@ -4580,16 +4571,16 @@
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N70" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="M70" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N70" s="6" t="s">
-        <v>83</v>
-      </c>
       <c r="O70" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4601,7 +4592,7 @@
         <v>36</v>
       </c>
       <c r="S70" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="71">
@@ -4618,7 +4609,7 @@
         <v>46195</v>
       </c>
       <c r="E71" s="7">
-        <v>46164</v>
+        <v>46188</v>
       </c>
       <c r="F71" s="8">
         <v>0</v>
@@ -4633,22 +4624,22 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
@@ -4660,12 +4651,12 @@
         <v>28</v>
       </c>
       <c r="S71" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
       <c r="B72" s="7">
         <v>46195</v>
@@ -4677,7 +4668,7 @@
         <v>46195</v>
       </c>
       <c r="E72" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F72" s="8">
         <v>0</v>
@@ -4692,34 +4683,34 @@
         <v>23</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="Q72" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="S72" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="73">
@@ -4736,7 +4727,7 @@
         <v>46195</v>
       </c>
       <c r="E73" s="7">
-        <v>46170</v>
+        <v>46148</v>
       </c>
       <c r="F73" s="8">
         <v>0</v>
@@ -4751,22 +4742,22 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4775,10 +4766,10 @@
         <v>35</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="S73" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="74">
@@ -4795,7 +4786,7 @@
         <v>46195</v>
       </c>
       <c r="E74" s="7">
-        <v>46188</v>
+        <v>46148</v>
       </c>
       <c r="F74" s="8">
         <v>0</v>
@@ -4810,22 +4801,22 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4834,10 +4825,10 @@
         <v>35</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="S74" s="9">
-        <v>700</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="75">
@@ -4854,7 +4845,7 @@
         <v>46195</v>
       </c>
       <c r="E75" s="7">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="F75" s="8">
         <v>0</v>
@@ -4869,42 +4860,42 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="Q75" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="S75" s="9">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="B76" s="7">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C76" s="7">
         <v>46195</v>
@@ -4912,14 +4903,14 @@
       <c r="D76" s="7">
         <v>46195</v>
       </c>
-      <c r="E76" s="7">
-        <v>46182</v>
+      <c r="E76" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F76" s="8">
         <v>0</v>
       </c>
       <c r="G76" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -4928,34 +4919,34 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q76" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R76" s="6" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="S76" s="9">
-        <v>800</v>
+        <v>80.46</v>
       </c>
     </row>
     <row r="77">
@@ -4963,22 +4954,22 @@
         <v>22</v>
       </c>
       <c r="B77" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="C77" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D77" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="E77" s="7">
-        <v>46160</v>
+        <v>46185</v>
       </c>
       <c r="F77" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G77" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -4987,34 +4978,34 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c r="Q77" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R77" s="6" t="s">
-        <v>129</v>
+        <v>36</v>
       </c>
       <c r="S77" s="9">
-        <v>1200</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="78">
@@ -5022,22 +5013,22 @@
         <v>22</v>
       </c>
       <c r="B78" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C78" s="7">
-        <v>46195</v>
+        <v>46174</v>
       </c>
       <c r="D78" s="7">
-        <v>46195</v>
+        <v>46218</v>
       </c>
       <c r="E78" s="7">
-        <v>46148</v>
+        <v>46190</v>
       </c>
       <c r="F78" s="8">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G78" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -5046,34 +5037,34 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>131</v>
+        <v>56</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q78" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R78" s="6" t="s">
-        <v>129</v>
+        <v>36</v>
       </c>
       <c r="S78" s="9">
-        <v>1200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79">
@@ -5081,22 +5072,22 @@
         <v>22</v>
       </c>
       <c r="B79" s="7">
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="C79" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D79" s="7">
-        <v>46195</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>23</v>
+        <v>46202</v>
+      </c>
+      <c r="E79" s="7">
+        <v>46153</v>
       </c>
       <c r="F79" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G79" s="8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>23</v>
@@ -5105,34 +5096,34 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>133</v>
+        <v>46</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="Q79" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S79" s="9">
-        <v>80.46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80">
@@ -5140,58 +5131,58 @@
         <v>22</v>
       </c>
       <c r="B80" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="C80" s="7">
         <v>46143</v>
       </c>
       <c r="D80" s="7">
-        <v>46197</v>
+        <v>46188</v>
       </c>
       <c r="E80" s="7">
-        <v>46185</v>
+        <v>46167</v>
       </c>
       <c r="F80" s="8">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="G80" s="8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q80" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S80" s="9">
-        <v>4400</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81">
@@ -5202,16 +5193,16 @@
         <v>46202</v>
       </c>
       <c r="C81" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D81" s="7">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="E81" s="7">
-        <v>46190</v>
+        <v>46167</v>
       </c>
       <c r="F81" s="8">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G81" s="8">
         <v>7</v>
@@ -5223,22 +5214,22 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>23</v>
@@ -5250,7 +5241,7 @@
         <v>36</v>
       </c>
       <c r="S81" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82">
@@ -5261,13 +5252,13 @@
         <v>46202</v>
       </c>
       <c r="C82" s="7">
-        <v>46143</v>
+        <v>46188</v>
       </c>
       <c r="D82" s="7">
         <v>46202</v>
       </c>
       <c r="E82" s="7">
-        <v>46153</v>
+        <v>46188</v>
       </c>
       <c r="F82" s="8">
         <v>7</v>
@@ -5282,34 +5273,34 @@
         <v>23</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="Q82" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R82" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S82" s="9">
-        <v>50</v>
+        <v>116.66</v>
       </c>
     </row>
     <row r="83">
@@ -5320,43 +5311,43 @@
         <v>46202</v>
       </c>
       <c r="C83" s="7">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="D83" s="7">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="E83" s="7">
-        <v>46167</v>
+        <v>46097</v>
       </c>
       <c r="F83" s="8">
-        <v>-7</v>
+        <v>7</v>
       </c>
       <c r="G83" s="8">
         <v>7</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>79</v>
+        <v>26</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>23</v>
@@ -5365,10 +5356,10 @@
         <v>29</v>
       </c>
       <c r="R83" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S83" s="9">
-        <v>100</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="84">
@@ -5379,13 +5370,13 @@
         <v>46202</v>
       </c>
       <c r="C84" s="7">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D84" s="7">
         <v>46202</v>
       </c>
       <c r="E84" s="7">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="F84" s="8">
         <v>7</v>
@@ -5400,34 +5391,34 @@
         <v>23</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q84" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S84" s="9">
-        <v>100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="85">
@@ -5438,13 +5429,13 @@
         <v>46202</v>
       </c>
       <c r="C85" s="7">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="D85" s="7">
         <v>46202</v>
       </c>
       <c r="E85" s="7">
-        <v>46188</v>
+        <v>46169</v>
       </c>
       <c r="F85" s="8">
         <v>7</v>
@@ -5459,22 +5450,22 @@
         <v>23</v>
       </c>
       <c r="J85" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="K85" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="K85" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L85" s="6" t="s">
-        <v>121</v>
-      </c>
       <c r="M85" s="6" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P85" s="6" t="s">
         <v>23</v>
@@ -5483,10 +5474,10 @@
         <v>35</v>
       </c>
       <c r="R85" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S85" s="9">
-        <v>116.66</v>
+        <v>600</v>
       </c>
     </row>
     <row r="86">
@@ -5497,13 +5488,13 @@
         <v>46202</v>
       </c>
       <c r="C86" s="7">
-        <v>46082</v>
+        <v>46202</v>
       </c>
       <c r="D86" s="7">
         <v>46202</v>
       </c>
       <c r="E86" s="7">
-        <v>46097</v>
+        <v>46164</v>
       </c>
       <c r="F86" s="8">
         <v>7</v>
@@ -5518,34 +5509,34 @@
         <v>23</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q86" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R86" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S86" s="9">
-        <v>146.55</v>
+        <v>630</v>
       </c>
     </row>
     <row r="87">
@@ -5577,22 +5568,22 @@
         <v>23</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="N87" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P87" s="6" t="s">
         <v>23</v>
@@ -5604,7 +5595,7 @@
         <v>36</v>
       </c>
       <c r="S87" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="88">
@@ -5636,22 +5627,22 @@
         <v>23</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K88" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>23</v>
@@ -5663,7 +5654,7 @@
         <v>36</v>
       </c>
       <c r="S88" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="89">
@@ -5680,7 +5671,7 @@
         <v>46202</v>
       </c>
       <c r="E89" s="7">
-        <v>46163</v>
+        <v>46169</v>
       </c>
       <c r="F89" s="8">
         <v>7</v>
@@ -5695,22 +5686,22 @@
         <v>23</v>
       </c>
       <c r="J89" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="M89" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N89" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O89" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P89" s="6" t="s">
         <v>23</v>
@@ -5739,7 +5730,7 @@
         <v>46202</v>
       </c>
       <c r="E90" s="7">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="F90" s="8">
         <v>7</v>
@@ -5754,22 +5745,22 @@
         <v>23</v>
       </c>
       <c r="J90" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="M90" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>23</v>
@@ -5798,7 +5789,7 @@
         <v>46202</v>
       </c>
       <c r="E91" s="7">
-        <v>46169</v>
+        <v>46188</v>
       </c>
       <c r="F91" s="8">
         <v>7</v>
@@ -5813,22 +5804,22 @@
         <v>23</v>
       </c>
       <c r="J91" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N91" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O91" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P91" s="6" t="s">
         <v>23</v>
@@ -5837,10 +5828,10 @@
         <v>35</v>
       </c>
       <c r="R91" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S91" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="92">
@@ -5857,7 +5848,7 @@
         <v>46202</v>
       </c>
       <c r="E92" s="7">
-        <v>46169</v>
+        <v>46127</v>
       </c>
       <c r="F92" s="8">
         <v>7</v>
@@ -5878,16 +5869,16 @@
         <v>23</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>58</v>
+        <v>103</v>
       </c>
       <c r="M92" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P92" s="6" t="s">
         <v>23</v>
@@ -5899,7 +5890,7 @@
         <v>36</v>
       </c>
       <c r="S92" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="93">
@@ -5916,7 +5907,7 @@
         <v>46202</v>
       </c>
       <c r="E93" s="7">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="F93" s="8">
         <v>7</v>
@@ -5937,16 +5928,16 @@
         <v>23</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="M93" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N93" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O93" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P93" s="6" t="s">
         <v>23</v>
@@ -5958,7 +5949,7 @@
         <v>36</v>
       </c>
       <c r="S93" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="94">
@@ -5975,7 +5966,7 @@
         <v>46202</v>
       </c>
       <c r="E94" s="7">
-        <v>46188</v>
+        <v>46153</v>
       </c>
       <c r="F94" s="8">
         <v>7</v>
@@ -5990,22 +5981,22 @@
         <v>23</v>
       </c>
       <c r="J94" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K94" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="M94" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>23</v>
@@ -6014,7 +6005,7 @@
         <v>35</v>
       </c>
       <c r="R94" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S94" s="9">
         <v>650</v>
@@ -6034,7 +6025,7 @@
         <v>46202</v>
       </c>
       <c r="E95" s="7">
-        <v>46127</v>
+        <v>46167</v>
       </c>
       <c r="F95" s="8">
         <v>7</v>
@@ -6049,22 +6040,22 @@
         <v>23</v>
       </c>
       <c r="J95" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="M95" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N95" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O95" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P95" s="6" t="s">
         <v>23</v>
@@ -6076,7 +6067,7 @@
         <v>36</v>
       </c>
       <c r="S95" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="96">
@@ -6093,7 +6084,7 @@
         <v>46202</v>
       </c>
       <c r="E96" s="7">
-        <v>46153</v>
+        <v>46182</v>
       </c>
       <c r="F96" s="8">
         <v>7</v>
@@ -6108,22 +6099,22 @@
         <v>23</v>
       </c>
       <c r="J96" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="M96" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>23</v>
@@ -6135,7 +6126,7 @@
         <v>36</v>
       </c>
       <c r="S96" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="97">
@@ -6152,7 +6143,7 @@
         <v>46202</v>
       </c>
       <c r="E97" s="7">
-        <v>46160</v>
+        <v>46182</v>
       </c>
       <c r="F97" s="8">
         <v>7</v>
@@ -6167,22 +6158,22 @@
         <v>23</v>
       </c>
       <c r="J97" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="M97" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N97" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O97" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P97" s="6" t="s">
         <v>23</v>
@@ -6194,7 +6185,7 @@
         <v>36</v>
       </c>
       <c r="S97" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="98">
@@ -6211,7 +6202,7 @@
         <v>46202</v>
       </c>
       <c r="E98" s="7">
-        <v>46167</v>
+        <v>46182</v>
       </c>
       <c r="F98" s="8">
         <v>7</v>
@@ -6232,16 +6223,16 @@
         <v>23</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="M98" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>23</v>
@@ -6270,7 +6261,7 @@
         <v>46202</v>
       </c>
       <c r="E99" s="7">
-        <v>46182</v>
+        <v>46164</v>
       </c>
       <c r="F99" s="8">
         <v>7</v>
@@ -6291,16 +6282,16 @@
         <v>23</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="M99" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N99" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O99" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P99" s="6" t="s">
         <v>23</v>
@@ -6309,7 +6300,7 @@
         <v>35</v>
       </c>
       <c r="R99" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S99" s="9">
         <v>680</v>
@@ -6329,7 +6320,7 @@
         <v>46202</v>
       </c>
       <c r="E100" s="7">
-        <v>46182</v>
+        <v>46170</v>
       </c>
       <c r="F100" s="8">
         <v>7</v>
@@ -6350,16 +6341,16 @@
         <v>23</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="M100" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>23</v>
@@ -6371,7 +6362,7 @@
         <v>36</v>
       </c>
       <c r="S100" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="101">
@@ -6388,7 +6379,7 @@
         <v>46202</v>
       </c>
       <c r="E101" s="7">
-        <v>46164</v>
+        <v>46188</v>
       </c>
       <c r="F101" s="8">
         <v>7</v>
@@ -6409,16 +6400,16 @@
         <v>23</v>
       </c>
       <c r="L101" s="6" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="M101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N101" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O101" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P101" s="6" t="s">
         <v>23</v>
@@ -6430,7 +6421,7 @@
         <v>28</v>
       </c>
       <c r="S101" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="102">
@@ -6447,7 +6438,7 @@
         <v>46202</v>
       </c>
       <c r="E102" s="7">
-        <v>46182</v>
+        <v>46148</v>
       </c>
       <c r="F102" s="8">
         <v>7</v>
@@ -6474,10 +6465,10 @@
         <v>23</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>23</v>
@@ -6486,15 +6477,15 @@
         <v>35</v>
       </c>
       <c r="R102" s="6" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="S102" s="9">
-        <v>680</v>
+        <v>800</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="s">
-        <v>22</v>
+        <v>119</v>
       </c>
       <c r="B103" s="7">
         <v>46202</v>
@@ -6506,7 +6497,7 @@
         <v>46202</v>
       </c>
       <c r="E103" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F103" s="8">
         <v>7</v>
@@ -6527,16 +6518,16 @@
         <v>23</v>
       </c>
       <c r="L103" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M103" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N103" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O103" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P103" s="6" t="s">
         <v>23</v>
@@ -6545,10 +6536,10 @@
         <v>35</v>
       </c>
       <c r="R103" s="6" t="s">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="S103" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="104">
@@ -6565,7 +6556,7 @@
         <v>46202</v>
       </c>
       <c r="E104" s="7">
-        <v>46188</v>
+        <v>46148</v>
       </c>
       <c r="F104" s="8">
         <v>7</v>
@@ -6586,16 +6577,16 @@
         <v>23</v>
       </c>
       <c r="L104" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="M104" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>23</v>
@@ -6604,15 +6595,15 @@
         <v>35</v>
       </c>
       <c r="R104" s="6" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="S104" s="9">
-        <v>700</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="B105" s="7">
         <v>46202</v>
@@ -6624,7 +6615,7 @@
         <v>46202</v>
       </c>
       <c r="E105" s="7">
-        <v>46182</v>
+        <v>46160</v>
       </c>
       <c r="F105" s="8">
         <v>7</v>
@@ -6645,28 +6636,28 @@
         <v>23</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="M105" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N105" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O105" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P105" s="6" t="s">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="Q105" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R105" s="6" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="S105" s="9">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="106">
@@ -6683,7 +6674,7 @@
         <v>46202</v>
       </c>
       <c r="E106" s="7">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="F106" s="8">
         <v>7</v>
@@ -6698,234 +6689,57 @@
         <v>23</v>
       </c>
       <c r="J106" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K106" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="M106" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>23</v>
+        <v>128</v>
       </c>
       <c r="Q106" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R106" s="6" t="s">
-        <v>73</v>
+        <v>125</v>
       </c>
       <c r="S106" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B107" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C107" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D107" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E107" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F107" s="8">
-        <v>7</v>
-      </c>
-      <c r="G107" s="8">
-        <v>7</v>
-      </c>
-      <c r="H107" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I107" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J107" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="K107" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L107" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="M107" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N107" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="O107" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="P107" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q107" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R107" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="S107" s="9">
         <v>1200</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B108" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C108" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D108" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E108" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F108" s="8">
-        <v>7</v>
-      </c>
-      <c r="G108" s="8">
-        <v>7</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I108" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J108" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="K108" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L108" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="M108" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N108" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="O108" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q108" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R108" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="S108" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B109" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C109" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D109" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E109" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F109" s="8">
-        <v>7</v>
-      </c>
-      <c r="G109" s="8">
-        <v>7</v>
-      </c>
-      <c r="H109" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I109" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J109" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="K109" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L109" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="M109" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N109" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="O109" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="P109" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q109" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R109" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="S109" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="110" ht="23" customHeight="1">
-      <c r="A110" s="10"/>
-      <c r="B110" s="11"/>
-      <c r="C110" s="11"/>
-      <c r="D110" s="11"/>
-      <c r="E110" s="11"/>
-      <c r="F110" s="12"/>
-      <c r="G110" s="12"/>
-      <c r="H110" s="10"/>
-      <c r="I110" s="10"/>
-      <c r="J110" s="10"/>
-      <c r="K110" s="10"/>
-      <c r="L110" s="10"/>
-      <c r="M110" s="10"/>
-      <c r="N110" s="10"/>
-      <c r="O110" s="10"/>
-      <c r="P110" s="10"/>
-      <c r="Q110" s="10"/>
-      <c r="R110" s="10"/>
-      <c r="S110" s="13">
-        <f>SUM(S6:S109)</f>
+    <row r="107" ht="23" customHeight="1">
+      <c r="A107" s="10"/>
+      <c r="B107" s="11"/>
+      <c r="C107" s="11"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="11"/>
+      <c r="F107" s="12"/>
+      <c r="G107" s="12"/>
+      <c r="H107" s="10"/>
+      <c r="I107" s="10"/>
+      <c r="J107" s="10"/>
+      <c r="K107" s="10"/>
+      <c r="L107" s="10"/>
+      <c r="M107" s="10"/>
+      <c r="N107" s="10"/>
+      <c r="O107" s="10"/>
+      <c r="P107" s="10"/>
+      <c r="Q107" s="10"/>
+      <c r="R107" s="10"/>
+      <c r="S107" s="13">
+        <f>SUM(S6:S106)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$107</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$88</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em segunda-feira, 22 de junho de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em quarta-feira, 24 de junho de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -148,9 +148,6 @@
     <t>FA-11559</t>
   </si>
   <si>
-    <t>FA-11553</t>
-  </si>
-  <si>
     <t>VENCIDO ATÉ 30 DIAS</t>
   </si>
   <si>
@@ -163,6 +160,15 @@
     <t>FA-11565</t>
   </si>
   <si>
+    <t>SÓCIOS</t>
+  </si>
+  <si>
+    <t>QGQ-2837/1</t>
+  </si>
+  <si>
+    <t>AAA TESTE PROPOSTA</t>
+  </si>
+  <si>
     <t>FA-11568</t>
   </si>
   <si>
@@ -178,346 +184,286 @@
     <t>PRIVADO</t>
   </si>
   <si>
-    <t>FA-11806</t>
+    <t>FA-11571</t>
+  </si>
+  <si>
+    <t>FA-11724</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11572</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>FA-11776</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11679</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11818</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11756</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11785</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>ND-11870</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-11775</t>
+  </si>
+  <si>
+    <t>FA-11787</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11693</t>
+  </si>
+  <si>
+    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
+  </si>
+  <si>
+    <t>FA-11791</t>
+  </si>
+  <si>
+    <t>FA-11800</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11728</t>
+  </si>
+  <si>
+    <t>FA-11850</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>FA-11799</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11695</t>
+  </si>
+  <si>
+    <t>FA-11822</t>
+  </si>
+  <si>
+    <t>FA-11680</t>
+  </si>
+  <si>
+    <t>FA-11789</t>
+  </si>
+  <si>
+    <t>FA-11851</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-11605</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>FA-11824</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>FA-11807</t>
   </si>
   <si>
     <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
   </si>
   <si>
-    <t>FA-11571</t>
-  </si>
-  <si>
-    <t>FA-11797</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11724</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11572</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
     <t>FA-11798</t>
   </si>
   <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11776</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
     <t>FA-11848</t>
   </si>
   <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>FA-11679</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11818</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>ND-11844</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11756</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11785</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11772</t>
+    <t>FA-11823</t>
   </si>
   <si>
     <t>OLIZIEL DA SILVA CARDOSO</t>
   </si>
   <si>
-    <t>FA-11842</t>
-  </si>
-  <si>
-    <t>M&amp;S DO TRABALHO</t>
+    <t>FA-11672</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>FA-11843</t>
+  </si>
+  <si>
+    <t>SEGCOMP</t>
+  </si>
+  <si>
+    <t>SEGCOMP TECNOLOGIA LTDA</t>
   </si>
   <si>
     <t>ND-11700</t>
   </si>
   <si>
-    <t>HOJE</t>
-  </si>
-  <si>
-    <t>ND-11870</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>FA-11775</t>
-  </si>
-  <si>
-    <t>FA-11787</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11693</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11791</t>
-  </si>
-  <si>
-    <t>FA-11730</t>
+    <t>FA-11849</t>
+  </si>
+  <si>
+    <t>FA-11750</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11735</t>
   </si>
   <si>
     <t>JOZILDO TARQUINO DE BRITO</t>
   </si>
   <si>
-    <t>FA-11807</t>
-  </si>
-  <si>
-    <t>FA-11672</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11731</t>
+    <t>FA-11737</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11732</t>
+  </si>
+  <si>
+    <t>FA-11734</t>
   </si>
   <si>
     <t>ANA FLORIPES CARVALHO DA CUNHA</t>
   </si>
   <si>
-    <t>FA-11728</t>
-  </si>
-  <si>
-    <t>FA-11790</t>
-  </si>
-  <si>
-    <t>FA-11800</t>
-  </si>
-  <si>
-    <t>FA-11687</t>
+    <t>FA-11673</t>
+  </si>
+  <si>
+    <t>FA-11688</t>
   </si>
   <si>
     <t>GILVAN RODRIGUES MACHADO</t>
   </si>
   <si>
-    <t>FA-11850</t>
-  </si>
-  <si>
-    <t>FA-11799</t>
-  </si>
-  <si>
-    <t>FA-11508</t>
+    <t>FA-11852</t>
+  </si>
+  <si>
+    <t>FA-11509</t>
   </si>
   <si>
     <t>WESCLY JEAN DE MEDEIROS</t>
   </si>
   <si>
-    <t>FA-11625</t>
+    <t>FA-11626</t>
   </si>
   <si>
     <t>DANILO DE ALMEIDA TORRES</t>
   </si>
   <si>
-    <t>FA-11438</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11695</t>
-  </si>
-  <si>
-    <t>FA-11811</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11823</t>
-  </si>
-  <si>
-    <t>FA-11822</t>
-  </si>
-  <si>
-    <t>FA-11680</t>
-  </si>
-  <si>
-    <t>FA-11789</t>
-  </si>
-  <si>
-    <t>FA-11765</t>
+    <t>FA-11661</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>FA-11696</t>
+  </si>
+  <si>
+    <t>FA-11827</t>
+  </si>
+  <si>
+    <t>FA-11825</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11826</t>
+  </si>
+  <si>
+    <t>FA-11681</t>
+  </si>
+  <si>
+    <t>FA-11766</t>
   </si>
   <si>
     <t>ANNY KATARINA ACIOLE DA SILVA</t>
   </si>
   <si>
-    <t>FA-11851</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>FA-11824</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t>FA-11605</t>
-  </si>
-  <si>
-    <t>FA-11595</t>
+    <t>FA-11853</t>
+  </si>
+  <si>
+    <t>FA-11606</t>
+  </si>
+  <si>
+    <t>FA-11828</t>
+  </si>
+  <si>
+    <t>FA-11637</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11596</t>
   </si>
   <si>
     <t>JACKSON CASSIANO VERISSIMO</t>
   </si>
   <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11636</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-11821</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11843</t>
-  </si>
-  <si>
-    <t>SEGCOMP</t>
-  </si>
-  <si>
-    <t>SEGCOMP TECNOLOGIA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11849</t>
-  </si>
-  <si>
-    <t>FA-11735</t>
-  </si>
-  <si>
-    <t>FA-11750</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11688</t>
-  </si>
-  <si>
-    <t>FA-11737</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11732</t>
-  </si>
-  <si>
-    <t>FA-11734</t>
-  </si>
-  <si>
-    <t>FA-11673</t>
-  </si>
-  <si>
-    <t>FA-11852</t>
-  </si>
-  <si>
-    <t>FA-11509</t>
-  </si>
-  <si>
-    <t>FA-11661</t>
-  </si>
-  <si>
-    <t>LUCA ZOLI</t>
-  </si>
-  <si>
-    <t>FA-11626</t>
-  </si>
-  <si>
-    <t>FA-11696</t>
-  </si>
-  <si>
-    <t>FA-11825</t>
-  </si>
-  <si>
-    <t>FA-11826</t>
-  </si>
-  <si>
-    <t>FA-11827</t>
-  </si>
-  <si>
-    <t>FA-11681</t>
-  </si>
-  <si>
-    <t>FA-11766</t>
-  </si>
-  <si>
-    <t>FA-11853</t>
-  </si>
-  <si>
-    <t>FA-11606</t>
-  </si>
-  <si>
-    <t>FA-11828</t>
-  </si>
-  <si>
-    <t>FA-11596</t>
-  </si>
-  <si>
     <t>FA-11649</t>
   </si>
   <si>
     <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11637</t>
   </si>
 </sst>
 </file>
@@ -660,7 +606,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S107"/>
+  <dimension ref="A1:S88"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -777,10 +723,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-70</v>
+        <v>-72</v>
       </c>
       <c r="G6" s="8">
-        <v>-61</v>
+        <v>-63</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -836,10 +782,10 @@
         <v>46097</v>
       </c>
       <c r="F7" s="8">
-        <v>-56</v>
+        <v>-58</v>
       </c>
       <c r="G7" s="8">
-        <v>-56</v>
+        <v>-58</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>24</v>
@@ -895,10 +841,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-63</v>
+        <v>-65</v>
       </c>
       <c r="G8" s="8">
-        <v>-55</v>
+        <v>-57</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -954,10 +900,10 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-84</v>
+        <v>-86</v>
       </c>
       <c r="G9" s="8">
-        <v>-55</v>
+        <v>-57</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>24</v>
@@ -1013,10 +959,10 @@
         <v>23</v>
       </c>
       <c r="F10" s="8">
-        <v>-70</v>
+        <v>-72</v>
       </c>
       <c r="G10" s="8">
-        <v>-55</v>
+        <v>-57</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>24</v>
@@ -1072,10 +1018,10 @@
         <v>46097</v>
       </c>
       <c r="F11" s="8">
-        <v>-49</v>
+        <v>-51</v>
       </c>
       <c r="G11" s="8">
-        <v>-49</v>
+        <v>-51</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>24</v>
@@ -1131,10 +1077,10 @@
         <v>46097</v>
       </c>
       <c r="F12" s="8">
-        <v>-42</v>
+        <v>-44</v>
       </c>
       <c r="G12" s="8">
-        <v>-42</v>
+        <v>-44</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>24</v>
@@ -1190,10 +1136,10 @@
         <v>46141</v>
       </c>
       <c r="F13" s="8">
-        <v>-42</v>
+        <v>-44</v>
       </c>
       <c r="G13" s="8">
-        <v>-42</v>
+        <v>-44</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>24</v>
@@ -1249,10 +1195,10 @@
         <v>46097</v>
       </c>
       <c r="F14" s="8">
-        <v>-35</v>
+        <v>-37</v>
       </c>
       <c r="G14" s="8">
-        <v>-35</v>
+        <v>-37</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>24</v>
@@ -1308,10 +1254,10 @@
         <v>46141</v>
       </c>
       <c r="F15" s="8">
-        <v>-35</v>
+        <v>-37</v>
       </c>
       <c r="G15" s="8">
-        <v>-35</v>
+        <v>-37</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>24</v>
@@ -1355,37 +1301,37 @@
         <v>22</v>
       </c>
       <c r="B16" s="7">
-        <v>46164</v>
+        <v>46167</v>
       </c>
       <c r="C16" s="7">
-        <v>46146</v>
+        <v>46082</v>
       </c>
       <c r="D16" s="7">
-        <v>46146</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>23</v>
+        <v>46167</v>
+      </c>
+      <c r="E16" s="7">
+        <v>46097</v>
       </c>
       <c r="F16" s="8">
-        <v>-49</v>
+        <v>-30</v>
       </c>
       <c r="G16" s="8">
-        <v>-31</v>
+        <v>-30</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>23</v>
@@ -1400,13 +1346,13 @@
         <v>23</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S16" s="9">
-        <v>210</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="17">
@@ -1417,34 +1363,34 @@
         <v>46167</v>
       </c>
       <c r="C17" s="7">
-        <v>46082</v>
+        <v>46167</v>
       </c>
       <c r="D17" s="7">
         <v>46167</v>
       </c>
       <c r="E17" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F17" s="8">
-        <v>-28</v>
+        <v>-30</v>
       </c>
       <c r="G17" s="8">
-        <v>-28</v>
+        <v>-30</v>
       </c>
       <c r="H17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>25</v>
-      </c>
       <c r="K17" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>23</v>
@@ -1459,13 +1405,13 @@
         <v>23</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S17" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="18">
@@ -1473,38 +1419,38 @@
         <v>22</v>
       </c>
       <c r="B18" s="7">
-        <v>46167</v>
+        <v>46172</v>
       </c>
       <c r="C18" s="7">
-        <v>46167</v>
+        <v>45930</v>
       </c>
       <c r="D18" s="7">
-        <v>46167</v>
-      </c>
-      <c r="E18" s="7">
-        <v>46141</v>
+        <v>46172</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F18" s="8">
-        <v>-28</v>
+        <v>-25</v>
       </c>
       <c r="G18" s="8">
-        <v>-28</v>
+        <v>-25</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K18" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>34</v>
-      </c>
       <c r="M18" s="6" t="s">
         <v>23</v>
       </c>
@@ -1518,13 +1464,13 @@
         <v>23</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="S18" s="9">
-        <v>310</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="19">
@@ -1532,16 +1478,16 @@
         <v>22</v>
       </c>
       <c r="B19" s="7">
-        <v>46172</v>
+        <v>46174</v>
       </c>
       <c r="C19" s="7">
-        <v>45930</v>
+        <v>46082</v>
       </c>
       <c r="D19" s="7">
-        <v>46172</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>23</v>
+        <v>46174</v>
+      </c>
+      <c r="E19" s="7">
+        <v>46097</v>
       </c>
       <c r="F19" s="8">
         <v>-23</v>
@@ -1550,19 +1496,19 @@
         <v>-23</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K19" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>23</v>
@@ -1577,13 +1523,13 @@
         <v>23</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="S19" s="9">
-        <v>185.5</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="20">
@@ -1594,34 +1540,34 @@
         <v>46174</v>
       </c>
       <c r="C20" s="7">
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="D20" s="7">
         <v>46174</v>
       </c>
       <c r="E20" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F20" s="8">
-        <v>-21</v>
+        <v>-23</v>
       </c>
       <c r="G20" s="8">
-        <v>-21</v>
+        <v>-23</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="K20" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>23</v>
@@ -1636,18 +1582,18 @@
         <v>23</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S20" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B21" s="7">
         <v>46174</v>
@@ -1658,29 +1604,29 @@
       <c r="D21" s="7">
         <v>46174</v>
       </c>
-      <c r="E21" s="7">
-        <v>46141</v>
+      <c r="E21" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F21" s="8">
-        <v>-21</v>
+        <v>-23</v>
       </c>
       <c r="G21" s="8">
-        <v>-21</v>
+        <v>-23</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>23</v>
@@ -1695,13 +1641,13 @@
         <v>23</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S21" s="9">
-        <v>310</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="22">
@@ -1721,16 +1667,16 @@
         <v>46097</v>
       </c>
       <c r="F22" s="8">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="G22" s="8">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>25</v>
@@ -1780,19 +1726,19 @@
         <v>46141</v>
       </c>
       <c r="F23" s="8">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="G23" s="8">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>23</v>
@@ -1839,19 +1785,19 @@
         <v>46170</v>
       </c>
       <c r="F24" s="8">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="G24" s="8">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>23</v>
@@ -1898,25 +1844,25 @@
         <v>46153</v>
       </c>
       <c r="F25" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="G25" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>23</v>
@@ -1928,7 +1874,7 @@
         <v>27</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="Q25" s="6" t="s">
         <v>29</v>
@@ -1948,37 +1894,37 @@
         <v>46188</v>
       </c>
       <c r="C26" s="7">
-        <v>46188</v>
+        <v>46082</v>
       </c>
       <c r="D26" s="7">
         <v>46188</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>23</v>
+      <c r="E26" s="7">
+        <v>46097</v>
       </c>
       <c r="F26" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="G26" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>27</v>
@@ -1990,13 +1936,13 @@
         <v>23</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="S26" s="9">
-        <v>70.07</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="27">
@@ -2007,34 +1953,34 @@
         <v>46188</v>
       </c>
       <c r="C27" s="7">
-        <v>46082</v>
+        <v>46188</v>
       </c>
       <c r="D27" s="7">
         <v>46188</v>
       </c>
       <c r="E27" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F27" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="G27" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -2049,13 +1995,13 @@
         <v>23</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S27" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="28">
@@ -2072,28 +2018,28 @@
         <v>46188</v>
       </c>
       <c r="E28" s="7">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="F28" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="G28" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>23</v>
@@ -2114,7 +2060,7 @@
         <v>36</v>
       </c>
       <c r="S28" s="9">
-        <v>310</v>
+        <v>540</v>
       </c>
     </row>
     <row r="29">
@@ -2130,32 +2076,32 @@
       <c r="D29" s="7">
         <v>46188</v>
       </c>
-      <c r="E29" s="7" t="s">
-        <v>23</v>
+      <c r="E29" s="7">
+        <v>46141</v>
       </c>
       <c r="F29" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="G29" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K29" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>27</v>
@@ -2167,13 +2113,13 @@
         <v>23</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S29" s="9">
-        <v>330</v>
+        <v>620</v>
       </c>
     </row>
     <row r="30">
@@ -2190,31 +2136,31 @@
         <v>46188</v>
       </c>
       <c r="E30" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F30" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="G30" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K30" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -2232,7 +2178,7 @@
         <v>36</v>
       </c>
       <c r="S30" s="9">
-        <v>540</v>
+        <v>650</v>
       </c>
     </row>
     <row r="31">
@@ -2249,31 +2195,31 @@
         <v>46188</v>
       </c>
       <c r="E31" s="7">
-        <v>46141</v>
+        <v>46164</v>
       </c>
       <c r="F31" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="G31" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K31" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>27</v>
@@ -2288,10 +2234,10 @@
         <v>35</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S31" s="9">
-        <v>620</v>
+        <v>680</v>
       </c>
     </row>
     <row r="32">
@@ -2308,28 +2254,28 @@
         <v>46188</v>
       </c>
       <c r="E32" s="7">
-        <v>46170</v>
+        <v>46182</v>
       </c>
       <c r="F32" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="G32" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K32" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>23</v>
@@ -2350,7 +2296,7 @@
         <v>36</v>
       </c>
       <c r="S32" s="9">
-        <v>630</v>
+        <v>680</v>
       </c>
     </row>
     <row r="33">
@@ -2358,7 +2304,7 @@
         <v>22</v>
       </c>
       <c r="B33" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C33" s="7">
         <v>46188</v>
@@ -2366,32 +2312,32 @@
       <c r="D33" s="7">
         <v>46188</v>
       </c>
-      <c r="E33" s="7">
-        <v>46170</v>
+      <c r="E33" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F33" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="G33" s="8">
         <v>-7</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K33" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="N33" s="6" t="s">
         <v>27</v>
@@ -2403,13 +2349,13 @@
         <v>23</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S33" s="9">
-        <v>650</v>
+        <v>134.74</v>
       </c>
     </row>
     <row r="34">
@@ -2417,7 +2363,7 @@
         <v>22</v>
       </c>
       <c r="B34" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C34" s="7">
         <v>46188</v>
@@ -2425,29 +2371,29 @@
       <c r="D34" s="7">
         <v>46188</v>
       </c>
-      <c r="E34" s="7">
-        <v>46188</v>
+      <c r="E34" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F34" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="G34" s="8">
         <v>-7</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>23</v>
@@ -2459,16 +2405,16 @@
         <v>27</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S34" s="9">
-        <v>650</v>
+        <v>190</v>
       </c>
     </row>
     <row r="35">
@@ -2476,37 +2422,37 @@
         <v>22</v>
       </c>
       <c r="B35" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C35" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D35" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E35" s="7">
-        <v>46164</v>
+        <v>46153</v>
       </c>
       <c r="F35" s="8">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="G35" s="8">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>23</v>
@@ -2518,16 +2464,16 @@
         <v>27</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S35" s="9">
-        <v>680</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36">
@@ -2535,28 +2481,28 @@
         <v>22</v>
       </c>
       <c r="B36" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="C36" s="7">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="D36" s="7">
-        <v>46188</v>
+        <v>46211</v>
       </c>
       <c r="E36" s="7">
-        <v>46182</v>
+        <v>46190</v>
       </c>
       <c r="F36" s="8">
-        <v>-7</v>
+        <v>14</v>
       </c>
       <c r="G36" s="8">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>65</v>
@@ -2565,13 +2511,13 @@
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>27</v>
@@ -2580,13 +2526,13 @@
         <v>23</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S36" s="9">
-        <v>680</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
@@ -2594,37 +2540,37 @@
         <v>22</v>
       </c>
       <c r="B37" s="7">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="C37" s="7">
-        <v>46174</v>
+        <v>46082</v>
       </c>
       <c r="D37" s="7">
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="E37" s="7">
-        <v>46185</v>
+        <v>46097</v>
       </c>
       <c r="F37" s="8">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="G37" s="8">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>23</v>
@@ -2642,10 +2588,10 @@
         <v>29</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="S37" s="9">
-        <v>170.96</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="38">
@@ -2653,40 +2599,40 @@
         <v>22</v>
       </c>
       <c r="B38" s="7">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="C38" s="7">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="D38" s="7">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-7</v>
+        <v>-16</v>
       </c>
       <c r="G38" s="8">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>27</v>
@@ -2704,7 +2650,7 @@
         <v>36</v>
       </c>
       <c r="S38" s="9">
-        <v>134.74</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39">
@@ -2712,7 +2658,7 @@
         <v>22</v>
       </c>
       <c r="B39" s="7">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="C39" s="7">
         <v>46188</v>
@@ -2724,28 +2670,28 @@
         <v>23</v>
       </c>
       <c r="F39" s="8">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="G39" s="8">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="K39" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>27</v>
@@ -2754,7 +2700,7 @@
         <v>27</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="Q39" s="6" t="s">
         <v>23</v>
@@ -2763,7 +2709,7 @@
         <v>36</v>
       </c>
       <c r="S39" s="9">
-        <v>190</v>
+        <v>500</v>
       </c>
     </row>
     <row r="40">
@@ -2771,37 +2717,37 @@
         <v>22</v>
       </c>
       <c r="B40" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C40" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="D40" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F40" s="8">
-        <v>-21</v>
+        <v>-16</v>
       </c>
       <c r="G40" s="8">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>23</v>
@@ -2822,7 +2768,7 @@
         <v>36</v>
       </c>
       <c r="S40" s="9">
-        <v>160.54</v>
+        <v>540</v>
       </c>
     </row>
     <row r="41">
@@ -2830,40 +2776,40 @@
         <v>22</v>
       </c>
       <c r="B41" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="C41" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D41" s="7">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="E41" s="7">
-        <v>46185</v>
+        <v>46170</v>
       </c>
       <c r="F41" s="8">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="G41" s="8">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>27</v>
@@ -2881,7 +2827,7 @@
         <v>36</v>
       </c>
       <c r="S41" s="9">
-        <v>2100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="42">
@@ -2892,34 +2838,34 @@
         <v>46195</v>
       </c>
       <c r="C42" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D42" s="7">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="E42" s="7">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="F42" s="8">
-        <v>-14</v>
+        <v>-2</v>
       </c>
       <c r="G42" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -2928,19 +2874,19 @@
         <v>27</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S42" s="9">
-        <v>50</v>
+        <v>630</v>
       </c>
     </row>
     <row r="43">
@@ -2951,55 +2897,55 @@
         <v>46195</v>
       </c>
       <c r="C43" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D43" s="7">
         <v>46195</v>
       </c>
       <c r="E43" s="7">
-        <v>46153</v>
+        <v>46169</v>
       </c>
       <c r="F43" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G43" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="P43" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="Q43" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S43" s="9">
-        <v>50</v>
+        <v>630</v>
       </c>
     </row>
     <row r="44">
@@ -3010,55 +2956,55 @@
         <v>46195</v>
       </c>
       <c r="C44" s="7">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="D44" s="7">
-        <v>46211</v>
+        <v>46195</v>
       </c>
       <c r="E44" s="7">
-        <v>46190</v>
+        <v>46188</v>
       </c>
       <c r="F44" s="8">
-        <v>16</v>
+        <v>-2</v>
       </c>
       <c r="G44" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S44" s="9">
-        <v>50</v>
+        <v>650</v>
       </c>
     </row>
     <row r="45">
@@ -3069,25 +3015,25 @@
         <v>46195</v>
       </c>
       <c r="C45" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="D45" s="7">
         <v>46195</v>
       </c>
       <c r="E45" s="7">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="F45" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G45" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J45" s="6" t="s">
         <v>78</v>
@@ -3096,28 +3042,28 @@
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N45" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S45" s="9">
-        <v>100</v>
+        <v>650</v>
       </c>
     </row>
     <row r="46">
@@ -3128,55 +3074,55 @@
         <v>46195</v>
       </c>
       <c r="C46" s="7">
-        <v>46082</v>
+        <v>46195</v>
       </c>
       <c r="D46" s="7">
         <v>46195</v>
       </c>
       <c r="E46" s="7">
-        <v>46097</v>
+        <v>46167</v>
       </c>
       <c r="F46" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G46" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q46" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S46" s="9">
-        <v>146.55</v>
+        <v>680</v>
       </c>
     </row>
     <row r="47">
@@ -3187,28 +3133,28 @@
         <v>46195</v>
       </c>
       <c r="C47" s="7">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="D47" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>23</v>
+        <v>46195</v>
+      </c>
+      <c r="E47" s="7">
+        <v>46182</v>
       </c>
       <c r="F47" s="8">
-        <v>-14</v>
+        <v>-2</v>
       </c>
       <c r="G47" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
@@ -3217,25 +3163,25 @@
         <v>60</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="N47" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q47" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S47" s="9">
-        <v>500</v>
+        <v>680</v>
       </c>
     </row>
     <row r="48">
@@ -3246,55 +3192,55 @@
         <v>46195</v>
       </c>
       <c r="C48" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="D48" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>23</v>
+        <v>46195</v>
+      </c>
+      <c r="E48" s="7">
+        <v>46164</v>
       </c>
       <c r="F48" s="8">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="G48" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="N48" s="6" t="s">
         <v>27</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q48" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S48" s="9">
-        <v>500</v>
+        <v>680</v>
       </c>
     </row>
     <row r="49">
@@ -3305,34 +3251,34 @@
         <v>46195</v>
       </c>
       <c r="C49" s="7">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="D49" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>23</v>
+        <v>46195</v>
+      </c>
+      <c r="E49" s="7">
+        <v>46170</v>
       </c>
       <c r="F49" s="8">
-        <v>-14</v>
+        <v>-2</v>
       </c>
       <c r="G49" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>23</v>
@@ -3341,19 +3287,19 @@
         <v>27</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="Q49" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S49" s="9">
-        <v>540</v>
+        <v>700</v>
       </c>
     </row>
     <row r="50">
@@ -3370,37 +3316,37 @@
         <v>46195</v>
       </c>
       <c r="E50" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F50" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G50" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J50" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K50" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>23</v>
@@ -3409,10 +3355,10 @@
         <v>35</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S50" s="9">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="51">
@@ -3429,37 +3375,37 @@
         <v>46195</v>
       </c>
       <c r="E51" s="7">
-        <v>46169</v>
+        <v>46148</v>
       </c>
       <c r="F51" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G51" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I51" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="N51" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>23</v>
@@ -3468,15 +3414,15 @@
         <v>35</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="S51" s="9">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="B52" s="7">
         <v>46195</v>
@@ -3488,19 +3434,19 @@
         <v>46195</v>
       </c>
       <c r="E52" s="7">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="F52" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G52" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I52" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J52" s="6" t="s">
         <v>90</v>
@@ -3509,16 +3455,16 @@
         <v>23</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>23</v>
@@ -3527,18 +3473,18 @@
         <v>35</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="S52" s="9">
-        <v>620</v>
+        <v>800</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B53" s="7">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C53" s="7">
         <v>46195</v>
@@ -3546,50 +3492,50 @@
       <c r="D53" s="7">
         <v>46195</v>
       </c>
-      <c r="E53" s="7">
-        <v>46163</v>
+      <c r="E53" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F53" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G53" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I53" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="N53" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q53" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S53" s="9">
-        <v>630</v>
+        <v>26.85</v>
       </c>
     </row>
     <row r="54">
@@ -3597,58 +3543,58 @@
         <v>22</v>
       </c>
       <c r="B54" s="7">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C54" s="7">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="D54" s="7">
-        <v>46195</v>
-      </c>
-      <c r="E54" s="7">
-        <v>46169</v>
+        <v>46188</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F54" s="8">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="G54" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q54" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S54" s="9">
-        <v>630</v>
+        <v>430</v>
       </c>
     </row>
     <row r="55">
@@ -3656,28 +3602,28 @@
         <v>22</v>
       </c>
       <c r="B55" s="7">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C55" s="7">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="D55" s="7">
-        <v>46195</v>
-      </c>
-      <c r="E55" s="7">
-        <v>46169</v>
+        <v>46188</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F55" s="8">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="G55" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J55" s="6" t="s">
         <v>95</v>
@@ -3686,28 +3632,28 @@
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N55" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q55" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S55" s="9">
-        <v>630</v>
+        <v>550</v>
       </c>
     </row>
     <row r="56">
@@ -3715,7 +3661,7 @@
         <v>22</v>
       </c>
       <c r="B56" s="7">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C56" s="7">
         <v>46195</v>
@@ -3723,20 +3669,20 @@
       <c r="D56" s="7">
         <v>46195</v>
       </c>
-      <c r="E56" s="7">
-        <v>46170</v>
+      <c r="E56" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F56" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G56" s="8">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="J56" s="6" t="s">
         <v>96</v>
@@ -3745,28 +3691,28 @@
         <v>23</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="Q56" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S56" s="9">
-        <v>630</v>
+        <v>572.77</v>
       </c>
     </row>
     <row r="57">
@@ -3774,7 +3720,7 @@
         <v>22</v>
       </c>
       <c r="B57" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="C57" s="7">
         <v>46195</v>
@@ -3782,50 +3728,50 @@
       <c r="D57" s="7">
         <v>46195</v>
       </c>
-      <c r="E57" s="7">
-        <v>46170</v>
+      <c r="E57" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F57" s="8">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G57" s="8">
         <v>0</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J57" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S57" s="9">
-        <v>630</v>
+        <v>90</v>
       </c>
     </row>
     <row r="58">
@@ -3833,16 +3779,16 @@
         <v>22</v>
       </c>
       <c r="B58" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="C58" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D58" s="7">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="E58" s="7">
-        <v>46164</v>
+        <v>46185</v>
       </c>
       <c r="F58" s="8">
         <v>0</v>
@@ -3857,22 +3803,22 @@
         <v>23</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>23</v>
@@ -3884,7 +3830,7 @@
         <v>36</v>
       </c>
       <c r="S58" s="9">
-        <v>630</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="59">
@@ -3892,22 +3838,22 @@
         <v>22</v>
       </c>
       <c r="B59" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C59" s="7">
-        <v>46195</v>
+        <v>46174</v>
       </c>
       <c r="D59" s="7">
-        <v>46195</v>
+        <v>46218</v>
       </c>
       <c r="E59" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="F59" s="8">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G59" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>23</v>
@@ -3916,34 +3862,34 @@
         <v>23</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q59" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S59" s="9">
-        <v>650</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60">
@@ -3951,22 +3897,22 @@
         <v>22</v>
       </c>
       <c r="B60" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C60" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D60" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E60" s="7">
-        <v>46170</v>
+        <v>46153</v>
       </c>
       <c r="F60" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G60" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H60" s="6" t="s">
         <v>23</v>
@@ -3975,34 +3921,34 @@
         <v>23</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="Q60" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S60" s="9">
-        <v>650</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61">
@@ -4010,58 +3956,58 @@
         <v>22</v>
       </c>
       <c r="B61" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C61" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D61" s="7">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="E61" s="7">
-        <v>46127</v>
+        <v>46167</v>
       </c>
       <c r="F61" s="8">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="G61" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q61" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S61" s="9">
-        <v>650</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62">
@@ -4069,22 +4015,22 @@
         <v>22</v>
       </c>
       <c r="B62" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C62" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D62" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E62" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="F62" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G62" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>23</v>
@@ -4099,28 +4045,28 @@
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S62" s="9">
-        <v>650</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63">
@@ -4128,22 +4074,22 @@
         <v>22</v>
       </c>
       <c r="B63" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C63" s="7">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="D63" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E63" s="7">
-        <v>46119</v>
+        <v>46188</v>
       </c>
       <c r="F63" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G63" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>23</v>
@@ -4152,22 +4098,22 @@
         <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
@@ -4176,10 +4122,10 @@
         <v>35</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S63" s="9">
-        <v>670</v>
+        <v>116.66</v>
       </c>
     </row>
     <row r="64">
@@ -4187,22 +4133,22 @@
         <v>22</v>
       </c>
       <c r="B64" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C64" s="7">
-        <v>46195</v>
+        <v>46082</v>
       </c>
       <c r="D64" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E64" s="7">
-        <v>46167</v>
+        <v>46097</v>
       </c>
       <c r="F64" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G64" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>23</v>
@@ -4211,34 +4157,34 @@
         <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q64" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S64" s="9">
-        <v>680</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="65">
@@ -4246,22 +4192,22 @@
         <v>22</v>
       </c>
       <c r="B65" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C65" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D65" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E65" s="7">
-        <v>46176</v>
+        <v>46169</v>
       </c>
       <c r="F65" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G65" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H65" s="6" t="s">
         <v>23</v>
@@ -4270,22 +4216,22 @@
         <v>23</v>
       </c>
       <c r="J65" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="K65" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
@@ -4297,7 +4243,7 @@
         <v>36</v>
       </c>
       <c r="S65" s="9">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="66">
@@ -4305,22 +4251,22 @@
         <v>22</v>
       </c>
       <c r="B66" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C66" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D66" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E66" s="7">
-        <v>46182</v>
+        <v>46169</v>
       </c>
       <c r="F66" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G66" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>23</v>
@@ -4329,22 +4275,22 @@
         <v>23</v>
       </c>
       <c r="J66" s="6" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
@@ -4356,7 +4302,7 @@
         <v>36</v>
       </c>
       <c r="S66" s="9">
-        <v>680</v>
+        <v>600</v>
       </c>
     </row>
     <row r="67">
@@ -4364,22 +4310,22 @@
         <v>22</v>
       </c>
       <c r="B67" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C67" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D67" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E67" s="7">
-        <v>46182</v>
+        <v>46169</v>
       </c>
       <c r="F67" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G67" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>23</v>
@@ -4388,22 +4334,22 @@
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="M67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>23</v>
@@ -4415,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="S67" s="9">
-        <v>680</v>
+        <v>630</v>
       </c>
     </row>
     <row r="68">
@@ -4423,22 +4369,22 @@
         <v>22</v>
       </c>
       <c r="B68" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C68" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D68" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E68" s="7">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="F68" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G68" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>23</v>
@@ -4447,22 +4393,22 @@
         <v>23</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="M68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
@@ -4471,10 +4417,10 @@
         <v>35</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S68" s="9">
-        <v>680</v>
+        <v>630</v>
       </c>
     </row>
     <row r="69">
@@ -4482,22 +4428,22 @@
         <v>22</v>
       </c>
       <c r="B69" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C69" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D69" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E69" s="7">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="F69" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G69" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>23</v>
@@ -4506,25 +4452,25 @@
         <v>23</v>
       </c>
       <c r="J69" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="K69" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="K69" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L69" s="6" t="s">
-        <v>73</v>
-      </c>
       <c r="M69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="Q69" s="6" t="s">
         <v>35</v>
@@ -4533,7 +4479,7 @@
         <v>36</v>
       </c>
       <c r="S69" s="9">
-        <v>700</v>
+        <v>630</v>
       </c>
     </row>
     <row r="70">
@@ -4541,22 +4487,22 @@
         <v>22</v>
       </c>
       <c r="B70" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C70" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D70" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E70" s="7">
-        <v>46170</v>
+        <v>46163</v>
       </c>
       <c r="F70" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G70" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>23</v>
@@ -4571,16 +4517,16 @@
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4592,7 +4538,7 @@
         <v>36</v>
       </c>
       <c r="S70" s="9">
-        <v>700</v>
+        <v>630</v>
       </c>
     </row>
     <row r="71">
@@ -4600,22 +4546,22 @@
         <v>22</v>
       </c>
       <c r="B71" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C71" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D71" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E71" s="7">
-        <v>46188</v>
+        <v>46164</v>
       </c>
       <c r="F71" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G71" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>23</v>
@@ -4624,22 +4570,22 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="K71" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="K71" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L71" s="6" t="s">
-        <v>118</v>
-      </c>
       <c r="M71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
@@ -4648,33 +4594,33 @@
         <v>35</v>
       </c>
       <c r="R71" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S71" s="9">
-        <v>700</v>
+        <v>630</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
-        <v>119</v>
+        <v>22</v>
       </c>
       <c r="B72" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C72" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D72" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E72" s="7">
-        <v>46182</v>
+        <v>46188</v>
       </c>
       <c r="F72" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G72" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>23</v>
@@ -4683,22 +4629,22 @@
         <v>23</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>23</v>
@@ -4707,10 +4653,10 @@
         <v>35</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="S72" s="9">
-        <v>800</v>
+        <v>650</v>
       </c>
     </row>
     <row r="73">
@@ -4718,22 +4664,22 @@
         <v>22</v>
       </c>
       <c r="B73" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C73" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D73" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E73" s="7">
-        <v>46148</v>
+        <v>46127</v>
       </c>
       <c r="F73" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G73" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>23</v>
@@ -4742,22 +4688,22 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4766,10 +4712,10 @@
         <v>35</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="S73" s="9">
-        <v>800</v>
+        <v>650</v>
       </c>
     </row>
     <row r="74">
@@ -4777,22 +4723,22 @@
         <v>22</v>
       </c>
       <c r="B74" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C74" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D74" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E74" s="7">
-        <v>46148</v>
+        <v>46153</v>
       </c>
       <c r="F74" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G74" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>23</v>
@@ -4801,22 +4747,22 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4825,10 +4771,10 @@
         <v>35</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>125</v>
+        <v>36</v>
       </c>
       <c r="S74" s="9">
-        <v>1200</v>
+        <v>650</v>
       </c>
     </row>
     <row r="75">
@@ -4836,22 +4782,22 @@
         <v>22</v>
       </c>
       <c r="B75" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="C75" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D75" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E75" s="7">
         <v>46160</v>
       </c>
       <c r="F75" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G75" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>23</v>
@@ -4860,34 +4806,34 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>128</v>
+        <v>23</v>
       </c>
       <c r="Q75" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>125</v>
+        <v>36</v>
       </c>
       <c r="S75" s="9">
-        <v>1200</v>
+        <v>650</v>
       </c>
     </row>
     <row r="76">
@@ -4895,22 +4841,22 @@
         <v>22</v>
       </c>
       <c r="B76" s="7">
-        <v>46196</v>
+        <v>46202</v>
       </c>
       <c r="C76" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="D76" s="7">
-        <v>46195</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>23</v>
+        <v>46202</v>
+      </c>
+      <c r="E76" s="7">
+        <v>46167</v>
       </c>
       <c r="F76" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G76" s="8">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>23</v>
@@ -4919,34 +4865,34 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>130</v>
+        <v>71</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q76" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S76" s="9">
-        <v>80.46</v>
+        <v>680</v>
       </c>
     </row>
     <row r="77">
@@ -4954,22 +4900,22 @@
         <v>22</v>
       </c>
       <c r="B77" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="C77" s="7">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D77" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="E77" s="7">
-        <v>46185</v>
+        <v>46182</v>
       </c>
       <c r="F77" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G77" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>23</v>
@@ -4978,22 +4924,22 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>133</v>
+        <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -5005,7 +4951,7 @@
         <v>36</v>
       </c>
       <c r="S77" s="9">
-        <v>4400</v>
+        <v>680</v>
       </c>
     </row>
     <row r="78">
@@ -5016,19 +4962,19 @@
         <v>46202</v>
       </c>
       <c r="C78" s="7">
-        <v>46174</v>
+        <v>46202</v>
       </c>
       <c r="D78" s="7">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="E78" s="7">
-        <v>46190</v>
+        <v>46182</v>
       </c>
       <c r="F78" s="8">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="G78" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>23</v>
@@ -5037,34 +4983,34 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q78" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S78" s="9">
-        <v>50</v>
+        <v>680</v>
       </c>
     </row>
     <row r="79">
@@ -5075,19 +5021,19 @@
         <v>46202</v>
       </c>
       <c r="C79" s="7">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D79" s="7">
         <v>46202</v>
       </c>
       <c r="E79" s="7">
-        <v>46153</v>
+        <v>46182</v>
       </c>
       <c r="F79" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G79" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>23</v>
@@ -5096,34 +5042,34 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>45</v>
+        <v>129</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="Q79" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S79" s="9">
-        <v>50</v>
+        <v>680</v>
       </c>
     </row>
     <row r="80">
@@ -5134,55 +5080,55 @@
         <v>46202</v>
       </c>
       <c r="C80" s="7">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D80" s="7">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="E80" s="7">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="F80" s="8">
-        <v>-7</v>
+        <v>5</v>
       </c>
       <c r="G80" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>78</v>
+        <v>130</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q80" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S80" s="9">
-        <v>100</v>
+        <v>680</v>
       </c>
     </row>
     <row r="81">
@@ -5193,19 +5139,19 @@
         <v>46202</v>
       </c>
       <c r="C81" s="7">
-        <v>46143</v>
+        <v>46202</v>
       </c>
       <c r="D81" s="7">
         <v>46202</v>
       </c>
       <c r="E81" s="7">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="F81" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G81" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>23</v>
@@ -5214,34 +5160,34 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q81" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S81" s="9">
-        <v>100</v>
+        <v>700</v>
       </c>
     </row>
     <row r="82">
@@ -5252,7 +5198,7 @@
         <v>46202</v>
       </c>
       <c r="C82" s="7">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="D82" s="7">
         <v>46202</v>
@@ -5261,10 +5207,10 @@
         <v>46188</v>
       </c>
       <c r="F82" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G82" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>23</v>
@@ -5273,22 +5219,22 @@
         <v>23</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>23</v>
@@ -5300,7 +5246,7 @@
         <v>28</v>
       </c>
       <c r="S82" s="9">
-        <v>116.66</v>
+        <v>700</v>
       </c>
     </row>
     <row r="83">
@@ -5311,19 +5257,19 @@
         <v>46202</v>
       </c>
       <c r="C83" s="7">
-        <v>46082</v>
+        <v>46202</v>
       </c>
       <c r="D83" s="7">
         <v>46202</v>
       </c>
       <c r="E83" s="7">
-        <v>46097</v>
+        <v>46148</v>
       </c>
       <c r="F83" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G83" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>23</v>
@@ -5332,39 +5278,39 @@
         <v>23</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>26</v>
+        <v>87</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q83" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R83" s="6" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="S83" s="9">
-        <v>146.55</v>
+        <v>800</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="B84" s="7">
         <v>46202</v>
@@ -5376,13 +5322,13 @@
         <v>46202</v>
       </c>
       <c r="E84" s="7">
-        <v>46169</v>
+        <v>46182</v>
       </c>
       <c r="F84" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G84" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>23</v>
@@ -5397,16 +5343,16 @@
         <v>23</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>89</v>
+        <v>23</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>23</v>
@@ -5415,10 +5361,10 @@
         <v>35</v>
       </c>
       <c r="R84" s="6" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="S84" s="9">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="85">
@@ -5435,13 +5381,13 @@
         <v>46202</v>
       </c>
       <c r="E85" s="7">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="F85" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G85" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>23</v>
@@ -5459,25 +5405,25 @@
         <v>137</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>137</v>
+        <v>23</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="Q85" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R85" s="6" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="S85" s="9">
-        <v>600</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="86">
@@ -5494,13 +5440,13 @@
         <v>46202</v>
       </c>
       <c r="E86" s="7">
-        <v>46164</v>
+        <v>46148</v>
       </c>
       <c r="F86" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G86" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>23</v>
@@ -5509,22 +5455,22 @@
         <v>23</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="K86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>99</v>
+        <v>141</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>23</v>
@@ -5533,10 +5479,10 @@
         <v>35</v>
       </c>
       <c r="R86" s="6" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="S86" s="9">
-        <v>630</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="87">
@@ -5553,13 +5499,13 @@
         <v>46202</v>
       </c>
       <c r="E87" s="7">
-        <v>46169</v>
+        <v>46160</v>
       </c>
       <c r="F87" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G87" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H87" s="6" t="s">
         <v>23</v>
@@ -5568,1178 +5514,57 @@
         <v>23</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="M87" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N87" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="Q87" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R87" s="6" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="S87" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B88" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C88" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D88" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E88" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F88" s="8">
-        <v>7</v>
-      </c>
-      <c r="G88" s="8">
-        <v>7</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J88" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="K88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N88" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q88" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R88" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S88" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B89" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C89" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D89" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E89" s="7">
-        <v>46169</v>
-      </c>
-      <c r="F89" s="8">
-        <v>7</v>
-      </c>
-      <c r="G89" s="8">
-        <v>7</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J89" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="K89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L89" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="M89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N89" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O89" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P89" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q89" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R89" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S89" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B90" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C90" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D90" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E90" s="7">
-        <v>46163</v>
-      </c>
-      <c r="F90" s="8">
-        <v>7</v>
-      </c>
-      <c r="G90" s="8">
-        <v>7</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J90" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="K90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L90" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="M90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N90" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O90" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P90" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q90" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R90" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S90" s="9">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B91" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C91" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D91" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E91" s="7">
-        <v>46188</v>
-      </c>
-      <c r="F91" s="8">
-        <v>7</v>
-      </c>
-      <c r="G91" s="8">
-        <v>7</v>
-      </c>
-      <c r="H91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J91" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="K91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L91" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="M91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N91" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O91" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P91" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q91" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R91" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S91" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B92" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C92" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D92" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E92" s="7">
-        <v>46127</v>
-      </c>
-      <c r="F92" s="8">
-        <v>7</v>
-      </c>
-      <c r="G92" s="8">
-        <v>7</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J92" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="K92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L92" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="M92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N92" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O92" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P92" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q92" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R92" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S92" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B93" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C93" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D93" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E93" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F93" s="8">
-        <v>7</v>
-      </c>
-      <c r="G93" s="8">
-        <v>7</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J93" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="K93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L93" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="M93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N93" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O93" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P93" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q93" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R93" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S93" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B94" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C94" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D94" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E94" s="7">
-        <v>46153</v>
-      </c>
-      <c r="F94" s="8">
-        <v>7</v>
-      </c>
-      <c r="G94" s="8">
-        <v>7</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J94" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="K94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L94" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="M94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N94" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q94" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R94" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S94" s="9">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B95" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C95" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D95" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E95" s="7">
-        <v>46167</v>
-      </c>
-      <c r="F95" s="8">
-        <v>7</v>
-      </c>
-      <c r="G95" s="8">
-        <v>7</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J95" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="K95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L95" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="M95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N95" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O95" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P95" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q95" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R95" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S95" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B96" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C96" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D96" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E96" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F96" s="8">
-        <v>7</v>
-      </c>
-      <c r="G96" s="8">
-        <v>7</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J96" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="K96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L96" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="M96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N96" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O96" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q96" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R96" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S96" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B97" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C97" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D97" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E97" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F97" s="8">
-        <v>7</v>
-      </c>
-      <c r="G97" s="8">
-        <v>7</v>
-      </c>
-      <c r="H97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J97" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="K97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L97" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="M97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N97" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O97" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P97" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q97" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R97" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S97" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B98" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C98" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D98" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E98" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F98" s="8">
-        <v>7</v>
-      </c>
-      <c r="G98" s="8">
-        <v>7</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J98" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="K98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L98" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="M98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N98" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O98" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P98" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q98" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R98" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S98" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B99" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C99" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D99" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E99" s="7">
-        <v>46164</v>
-      </c>
-      <c r="F99" s="8">
-        <v>7</v>
-      </c>
-      <c r="G99" s="8">
-        <v>7</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J99" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="K99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L99" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="M99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N99" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O99" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P99" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q99" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R99" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S99" s="9">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B100" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C100" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D100" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E100" s="7">
-        <v>46170</v>
-      </c>
-      <c r="F100" s="8">
-        <v>7</v>
-      </c>
-      <c r="G100" s="8">
-        <v>7</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J100" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="K100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L100" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="M100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N100" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O100" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q100" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R100" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S100" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B101" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C101" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D101" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E101" s="7">
-        <v>46188</v>
-      </c>
-      <c r="F101" s="8">
-        <v>7</v>
-      </c>
-      <c r="G101" s="8">
-        <v>7</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J101" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="K101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L101" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="M101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N101" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O101" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q101" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R101" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="S101" s="9">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B102" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C102" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D102" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E102" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F102" s="8">
-        <v>7</v>
-      </c>
-      <c r="G102" s="8">
-        <v>7</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J102" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="K102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L102" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="M102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N102" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O102" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P102" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q102" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R102" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="S102" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B103" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C103" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D103" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E103" s="7">
-        <v>46182</v>
-      </c>
-      <c r="F103" s="8">
-        <v>7</v>
-      </c>
-      <c r="G103" s="8">
-        <v>7</v>
-      </c>
-      <c r="H103" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I103" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J103" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="K103" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L103" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="M103" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N103" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O103" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P103" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q103" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R103" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="S103" s="9">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B104" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C104" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D104" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E104" s="7">
-        <v>46148</v>
-      </c>
-      <c r="F104" s="8">
-        <v>7</v>
-      </c>
-      <c r="G104" s="8">
-        <v>7</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J104" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="K104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L104" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="M104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N104" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O104" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P104" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q104" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R104" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="S104" s="9">
         <v>1200</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B105" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C105" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D105" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E105" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F105" s="8">
-        <v>7</v>
-      </c>
-      <c r="G105" s="8">
-        <v>7</v>
-      </c>
-      <c r="H105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J105" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="K105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L105" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="M105" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N105" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O105" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P105" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q105" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R105" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="S105" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B106" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C106" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D106" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E106" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F106" s="8">
-        <v>7</v>
-      </c>
-      <c r="G106" s="8">
-        <v>7</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I106" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J106" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="K106" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L106" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="M106" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N106" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="O106" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="P106" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q106" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R106" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="S106" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="107" ht="23" customHeight="1">
-      <c r="A107" s="10"/>
-      <c r="B107" s="11"/>
-      <c r="C107" s="11"/>
-      <c r="D107" s="11"/>
-      <c r="E107" s="11"/>
-      <c r="F107" s="12"/>
-      <c r="G107" s="12"/>
-      <c r="H107" s="10"/>
-      <c r="I107" s="10"/>
-      <c r="J107" s="10"/>
-      <c r="K107" s="10"/>
-      <c r="L107" s="10"/>
-      <c r="M107" s="10"/>
-      <c r="N107" s="10"/>
-      <c r="O107" s="10"/>
-      <c r="P107" s="10"/>
-      <c r="Q107" s="10"/>
-      <c r="R107" s="10"/>
-      <c r="S107" s="13">
-        <f>SUM(S6:S106)</f>
+    <row r="88" ht="23" customHeight="1">
+      <c r="A88" s="10"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="11"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="12"/>
+      <c r="H88" s="10"/>
+      <c r="I88" s="10"/>
+      <c r="J88" s="10"/>
+      <c r="K88" s="10"/>
+      <c r="L88" s="10"/>
+      <c r="M88" s="10"/>
+      <c r="N88" s="10"/>
+      <c r="O88" s="10"/>
+      <c r="P88" s="10"/>
+      <c r="Q88" s="10"/>
+      <c r="R88" s="10"/>
+      <c r="S88" s="13">
+        <f>SUM(S6:S87)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$88</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$87</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -160,15 +160,6 @@
     <t>FA-11565</t>
   </si>
   <si>
-    <t>SÓCIOS</t>
-  </si>
-  <si>
-    <t>QGQ-2837/1</t>
-  </si>
-  <si>
-    <t>AAA TESTE PROPOSTA</t>
-  </si>
-  <si>
     <t>FA-11568</t>
   </si>
   <si>
@@ -292,24 +283,24 @@
     <t>MAICON LOPES SILVA</t>
   </si>
   <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>FA-11824</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
     <t>FA-11605</t>
   </si>
   <si>
     <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
   </si>
   <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>FA-11824</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
     <t>FA-11807</t>
   </si>
   <si>
@@ -409,21 +400,21 @@
     <t>LUCA ZOLI</t>
   </si>
   <si>
+    <t>FA-11827</t>
+  </si>
+  <si>
+    <t>FA-11825</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11826</t>
+  </si>
+  <si>
     <t>FA-11696</t>
   </si>
   <si>
-    <t>FA-11827</t>
-  </si>
-  <si>
-    <t>FA-11825</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11826</t>
-  </si>
-  <si>
     <t>FA-11681</t>
   </si>
   <si>
@@ -436,34 +427,34 @@
     <t>FA-11853</t>
   </si>
   <si>
+    <t>FA-11828</t>
+  </si>
+  <si>
     <t>FA-11606</t>
   </si>
   <si>
-    <t>FA-11828</t>
+    <t>FA-11596</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11649</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
   </si>
   <si>
     <t>FA-11637</t>
   </si>
   <si>
     <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11596</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>FA-11649</t>
-  </si>
-  <si>
-    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
   </si>
 </sst>
 </file>
@@ -606,7 +597,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S88"/>
+  <dimension ref="A1:S87"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -1593,25 +1584,25 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B21" s="7">
-        <v>46174</v>
+        <v>46181</v>
       </c>
       <c r="C21" s="7">
-        <v>46174</v>
+        <v>46082</v>
       </c>
       <c r="D21" s="7">
-        <v>46174</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>23</v>
+        <v>46181</v>
+      </c>
+      <c r="E21" s="7">
+        <v>46097</v>
       </c>
       <c r="F21" s="8">
-        <v>-23</v>
+        <v>-16</v>
       </c>
       <c r="G21" s="8">
-        <v>-23</v>
+        <v>-16</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>38</v>
@@ -1620,13 +1611,13 @@
         <v>38</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>23</v>
@@ -1641,13 +1632,13 @@
         <v>23</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S21" s="9">
-        <v>40000</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="22">
@@ -1658,13 +1649,13 @@
         <v>46181</v>
       </c>
       <c r="C22" s="7">
-        <v>46082</v>
+        <v>46181</v>
       </c>
       <c r="D22" s="7">
         <v>46181</v>
       </c>
       <c r="E22" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F22" s="8">
         <v>-16</v>
@@ -1679,13 +1670,13 @@
         <v>38</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>23</v>
@@ -1700,13 +1691,13 @@
         <v>23</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S22" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="23">
@@ -1717,13 +1708,13 @@
         <v>46181</v>
       </c>
       <c r="C23" s="7">
-        <v>46181</v>
+        <v>46143</v>
       </c>
       <c r="D23" s="7">
         <v>46181</v>
       </c>
       <c r="E23" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="F23" s="8">
         <v>-16</v>
@@ -1738,13 +1729,13 @@
         <v>38</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>23</v>
@@ -1759,13 +1750,13 @@
         <v>23</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S23" s="9">
-        <v>310</v>
+        <v>2969.17</v>
       </c>
     </row>
     <row r="24">
@@ -1773,22 +1764,22 @@
         <v>22</v>
       </c>
       <c r="B24" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="C24" s="7">
         <v>46143</v>
       </c>
       <c r="D24" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="E24" s="7">
-        <v>46170</v>
+        <v>46153</v>
       </c>
       <c r="F24" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="G24" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>38</v>
@@ -1797,34 +1788,34 @@
         <v>38</v>
       </c>
       <c r="J24" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N24" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="P24" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N24" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O24" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="P24" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="Q24" s="6" t="s">
         <v>29</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S24" s="9">
-        <v>2969.17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25">
@@ -1835,13 +1826,13 @@
         <v>46188</v>
       </c>
       <c r="C25" s="7">
-        <v>46143</v>
+        <v>46082</v>
       </c>
       <c r="D25" s="7">
         <v>46188</v>
       </c>
       <c r="E25" s="7">
-        <v>46153</v>
+        <v>46097</v>
       </c>
       <c r="F25" s="8">
         <v>-9</v>
@@ -1856,13 +1847,13 @@
         <v>38</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="K25" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>23</v>
@@ -1874,16 +1865,16 @@
         <v>27</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="Q25" s="6" t="s">
         <v>29</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S25" s="9">
-        <v>50</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="26">
@@ -1894,13 +1885,13 @@
         <v>46188</v>
       </c>
       <c r="C26" s="7">
-        <v>46082</v>
+        <v>46188</v>
       </c>
       <c r="D26" s="7">
         <v>46188</v>
       </c>
       <c r="E26" s="7">
-        <v>46097</v>
+        <v>46141</v>
       </c>
       <c r="F26" s="8">
         <v>-9</v>
@@ -1915,13 +1906,13 @@
         <v>38</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="K26" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>23</v>
@@ -1936,13 +1927,13 @@
         <v>23</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S26" s="9">
-        <v>146.55</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27">
@@ -1959,7 +1950,7 @@
         <v>46188</v>
       </c>
       <c r="E27" s="7">
-        <v>46141</v>
+        <v>46169</v>
       </c>
       <c r="F27" s="8">
         <v>-9</v>
@@ -1974,13 +1965,13 @@
         <v>38</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="K27" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>23</v>
@@ -2001,7 +1992,7 @@
         <v>36</v>
       </c>
       <c r="S27" s="9">
-        <v>310</v>
+        <v>540</v>
       </c>
     </row>
     <row r="28">
@@ -2018,7 +2009,7 @@
         <v>46188</v>
       </c>
       <c r="E28" s="7">
-        <v>46169</v>
+        <v>46141</v>
       </c>
       <c r="F28" s="8">
         <v>-9</v>
@@ -2033,16 +2024,16 @@
         <v>38</v>
       </c>
       <c r="J28" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="K28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>52</v>
-      </c>
       <c r="M28" s="6" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>27</v>
@@ -2060,7 +2051,7 @@
         <v>36</v>
       </c>
       <c r="S28" s="9">
-        <v>540</v>
+        <v>620</v>
       </c>
     </row>
     <row r="29">
@@ -2077,7 +2068,7 @@
         <v>46188</v>
       </c>
       <c r="E29" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="F29" s="8">
         <v>-9</v>
@@ -2092,16 +2083,16 @@
         <v>38</v>
       </c>
       <c r="J29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="K29" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="M29" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N29" s="6" t="s">
         <v>27</v>
@@ -2119,7 +2110,7 @@
         <v>36</v>
       </c>
       <c r="S29" s="9">
-        <v>620</v>
+        <v>650</v>
       </c>
     </row>
     <row r="30">
@@ -2136,7 +2127,7 @@
         <v>46188</v>
       </c>
       <c r="E30" s="7">
-        <v>46170</v>
+        <v>46164</v>
       </c>
       <c r="F30" s="8">
         <v>-9</v>
@@ -2151,16 +2142,16 @@
         <v>38</v>
       </c>
       <c r="J30" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="K30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>56</v>
-      </c>
       <c r="M30" s="6" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="N30" s="6" t="s">
         <v>27</v>
@@ -2175,10 +2166,10 @@
         <v>35</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S30" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="31">
@@ -2195,7 +2186,7 @@
         <v>46188</v>
       </c>
       <c r="E31" s="7">
-        <v>46164</v>
+        <v>46182</v>
       </c>
       <c r="F31" s="8">
         <v>-9</v>
@@ -2210,13 +2201,13 @@
         <v>38</v>
       </c>
       <c r="J31" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="K31" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>23</v>
@@ -2234,7 +2225,7 @@
         <v>35</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S31" s="9">
         <v>680</v>
@@ -2245,7 +2236,7 @@
         <v>22</v>
       </c>
       <c r="B32" s="7">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="C32" s="7">
         <v>46188</v>
@@ -2253,14 +2244,14 @@
       <c r="D32" s="7">
         <v>46188</v>
       </c>
-      <c r="E32" s="7">
-        <v>46182</v>
+      <c r="E32" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F32" s="8">
         <v>-9</v>
       </c>
       <c r="G32" s="8">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>38</v>
@@ -2269,14 +2260,14 @@
         <v>38</v>
       </c>
       <c r="J32" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K32" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="M32" s="6" t="s">
         <v>23</v>
       </c>
@@ -2290,13 +2281,13 @@
         <v>23</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S32" s="9">
-        <v>680</v>
+        <v>134.74</v>
       </c>
     </row>
     <row r="33">
@@ -2328,14 +2319,14 @@
         <v>38</v>
       </c>
       <c r="J33" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="K33" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>62</v>
-      </c>
       <c r="M33" s="6" t="s">
         <v>23</v>
       </c>
@@ -2346,7 +2337,7 @@
         <v>27</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="Q33" s="6" t="s">
         <v>23</v>
@@ -2355,7 +2346,7 @@
         <v>36</v>
       </c>
       <c r="S33" s="9">
-        <v>134.74</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34">
@@ -2363,22 +2354,22 @@
         <v>22</v>
       </c>
       <c r="B34" s="7">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="C34" s="7">
-        <v>46188</v>
+        <v>46143</v>
       </c>
       <c r="D34" s="7">
-        <v>46188</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>23</v>
+        <v>46195</v>
+      </c>
+      <c r="E34" s="7">
+        <v>46153</v>
       </c>
       <c r="F34" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G34" s="8">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>38</v>
@@ -2387,13 +2378,13 @@
         <v>38</v>
       </c>
       <c r="J34" s="6" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>23</v>
@@ -2405,16 +2396,16 @@
         <v>27</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S34" s="9">
-        <v>190</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
@@ -2425,46 +2416,46 @@
         <v>46195</v>
       </c>
       <c r="C35" s="7">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="D35" s="7">
-        <v>46195</v>
+        <v>46211</v>
       </c>
       <c r="E35" s="7">
-        <v>46153</v>
+        <v>46190</v>
       </c>
       <c r="F35" s="8">
-        <v>-2</v>
+        <v>14</v>
       </c>
       <c r="G35" s="8">
         <v>-2</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>38</v>
       </c>
       <c r="J35" s="6" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="K35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>27</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="Q35" s="6" t="s">
         <v>29</v>
@@ -2484,40 +2475,40 @@
         <v>46195</v>
       </c>
       <c r="C36" s="7">
-        <v>46174</v>
+        <v>46082</v>
       </c>
       <c r="D36" s="7">
-        <v>46211</v>
+        <v>46195</v>
       </c>
       <c r="E36" s="7">
-        <v>46190</v>
+        <v>46097</v>
       </c>
       <c r="F36" s="8">
-        <v>14</v>
+        <v>-2</v>
       </c>
       <c r="G36" s="8">
         <v>-2</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I36" s="6" t="s">
         <v>38</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="K36" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>27</v>
@@ -2529,10 +2520,10 @@
         <v>29</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S36" s="9">
-        <v>50</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="37">
@@ -2543,16 +2534,16 @@
         <v>46195</v>
       </c>
       <c r="C37" s="7">
-        <v>46082</v>
+        <v>46181</v>
       </c>
       <c r="D37" s="7">
-        <v>46195</v>
-      </c>
-      <c r="E37" s="7">
-        <v>46097</v>
+        <v>46181</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F37" s="8">
-        <v>-2</v>
+        <v>-16</v>
       </c>
       <c r="G37" s="8">
         <v>-2</v>
@@ -2564,16 +2555,16 @@
         <v>38</v>
       </c>
       <c r="J37" s="6" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="K37" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>27</v>
@@ -2585,13 +2576,13 @@
         <v>23</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S37" s="9">
-        <v>146.55</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38">
@@ -2602,16 +2593,16 @@
         <v>46195</v>
       </c>
       <c r="C38" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="D38" s="7">
-        <v>46181</v>
+        <v>46188</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-16</v>
+        <v>-9</v>
       </c>
       <c r="G38" s="8">
         <v>-2</v>
@@ -2623,16 +2614,16 @@
         <v>38</v>
       </c>
       <c r="J38" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>27</v>
@@ -2650,7 +2641,7 @@
         <v>36</v>
       </c>
       <c r="S38" s="9">
-        <v>190</v>
+        <v>500</v>
       </c>
     </row>
     <row r="39">
@@ -2661,16 +2652,16 @@
         <v>46195</v>
       </c>
       <c r="C39" s="7">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="D39" s="7">
-        <v>46188</v>
+        <v>46181</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F39" s="8">
-        <v>-9</v>
+        <v>-16</v>
       </c>
       <c r="G39" s="8">
         <v>-2</v>
@@ -2682,16 +2673,16 @@
         <v>38</v>
       </c>
       <c r="J39" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="K39" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L39" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="M39" s="6" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>27</v>
@@ -2709,7 +2700,7 @@
         <v>36</v>
       </c>
       <c r="S39" s="9">
-        <v>500</v>
+        <v>540</v>
       </c>
     </row>
     <row r="40">
@@ -2720,16 +2711,16 @@
         <v>46195</v>
       </c>
       <c r="C40" s="7">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="D40" s="7">
-        <v>46181</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>23</v>
+        <v>46195</v>
+      </c>
+      <c r="E40" s="7">
+        <v>46170</v>
       </c>
       <c r="F40" s="8">
-        <v>-16</v>
+        <v>-2</v>
       </c>
       <c r="G40" s="8">
         <v>-2</v>
@@ -2741,16 +2732,16 @@
         <v>38</v>
       </c>
       <c r="J40" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>27</v>
@@ -2762,13 +2753,13 @@
         <v>23</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S40" s="9">
-        <v>540</v>
+        <v>600</v>
       </c>
     </row>
     <row r="41">
@@ -2800,16 +2791,16 @@
         <v>38</v>
       </c>
       <c r="J41" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K41" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>27</v>
@@ -2827,7 +2818,7 @@
         <v>36</v>
       </c>
       <c r="S41" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="42">
@@ -2844,7 +2835,7 @@
         <v>46195</v>
       </c>
       <c r="E42" s="7">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="F42" s="8">
         <v>-2</v>
@@ -2859,13 +2850,13 @@
         <v>38</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K42" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -2903,7 +2894,7 @@
         <v>46195</v>
       </c>
       <c r="E43" s="7">
-        <v>46169</v>
+        <v>46188</v>
       </c>
       <c r="F43" s="8">
         <v>-2</v>
@@ -2918,13 +2909,13 @@
         <v>38</v>
       </c>
       <c r="J43" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K43" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>23</v>
@@ -2942,10 +2933,10 @@
         <v>35</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S43" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="44">
@@ -2962,7 +2953,7 @@
         <v>46195</v>
       </c>
       <c r="E44" s="7">
-        <v>46188</v>
+        <v>46170</v>
       </c>
       <c r="F44" s="8">
         <v>-2</v>
@@ -2977,13 +2968,13 @@
         <v>38</v>
       </c>
       <c r="J44" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="K44" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L44" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>23</v>
@@ -3001,7 +2992,7 @@
         <v>35</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S44" s="9">
         <v>650</v>
@@ -3021,7 +3012,7 @@
         <v>46195</v>
       </c>
       <c r="E45" s="7">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="F45" s="8">
         <v>-2</v>
@@ -3036,13 +3027,13 @@
         <v>38</v>
       </c>
       <c r="J45" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K45" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>23</v>
@@ -3063,7 +3054,7 @@
         <v>36</v>
       </c>
       <c r="S45" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="46">
@@ -3080,7 +3071,7 @@
         <v>46195</v>
       </c>
       <c r="E46" s="7">
-        <v>46167</v>
+        <v>46182</v>
       </c>
       <c r="F46" s="8">
         <v>-2</v>
@@ -3095,13 +3086,13 @@
         <v>38</v>
       </c>
       <c r="J46" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>23</v>
@@ -3139,7 +3130,7 @@
         <v>46195</v>
       </c>
       <c r="E47" s="7">
-        <v>46182</v>
+        <v>46164</v>
       </c>
       <c r="F47" s="8">
         <v>-2</v>
@@ -3154,13 +3145,13 @@
         <v>38</v>
       </c>
       <c r="J47" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>23</v>
@@ -3178,7 +3169,7 @@
         <v>35</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S47" s="9">
         <v>680</v>
@@ -3198,7 +3189,7 @@
         <v>46195</v>
       </c>
       <c r="E48" s="7">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="F48" s="8">
         <v>-2</v>
@@ -3213,13 +3204,13 @@
         <v>38</v>
       </c>
       <c r="J48" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>23</v>
@@ -3231,16 +3222,16 @@
         <v>27</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="Q48" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S48" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="49">
@@ -3257,7 +3248,7 @@
         <v>46195</v>
       </c>
       <c r="E49" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F49" s="8">
         <v>-2</v>
@@ -3272,13 +3263,13 @@
         <v>38</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K49" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>23</v>
@@ -3290,13 +3281,13 @@
         <v>27</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="Q49" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S49" s="9">
         <v>700</v>
@@ -3304,7 +3295,7 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="B50" s="7">
         <v>46195</v>
@@ -3316,7 +3307,7 @@
         <v>46195</v>
       </c>
       <c r="E50" s="7">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="F50" s="8">
         <v>-2</v>
@@ -3355,10 +3346,10 @@
         <v>35</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="S50" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="51">
@@ -3390,13 +3381,13 @@
         <v>38</v>
       </c>
       <c r="J51" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K51" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>23</v>
@@ -3414,7 +3405,7 @@
         <v>35</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S51" s="9">
         <v>800</v>
@@ -3422,10 +3413,10 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="B52" s="7">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="C52" s="7">
         <v>46195</v>
@@ -3433,14 +3424,14 @@
       <c r="D52" s="7">
         <v>46195</v>
       </c>
-      <c r="E52" s="7">
-        <v>46182</v>
+      <c r="E52" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="F52" s="8">
         <v>-2</v>
       </c>
       <c r="G52" s="8">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>38</v>
@@ -3449,16 +3440,16 @@
         <v>38</v>
       </c>
       <c r="J52" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="K52" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>91</v>
-      </c>
       <c r="M52" s="6" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="N52" s="6" t="s">
         <v>27</v>
@@ -3470,33 +3461,33 @@
         <v>23</v>
       </c>
       <c r="Q52" s="6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="S52" s="9">
-        <v>800</v>
+        <v>26.85</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B53" s="7">
         <v>46196</v>
       </c>
       <c r="C53" s="7">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="D53" s="7">
-        <v>46195</v>
+        <v>46188</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F53" s="8">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="G53" s="8">
         <v>-1</v>
@@ -3508,16 +3499,16 @@
         <v>38</v>
       </c>
       <c r="J53" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K53" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="N53" s="6" t="s">
         <v>27</v>
@@ -3532,10 +3523,10 @@
         <v>23</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S53" s="9">
-        <v>26.85</v>
+        <v>430</v>
       </c>
     </row>
     <row r="54">
@@ -3567,7 +3558,7 @@
         <v>38</v>
       </c>
       <c r="J54" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K54" s="6" t="s">
         <v>23</v>
@@ -3591,10 +3582,10 @@
         <v>23</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S54" s="9">
-        <v>430</v>
+        <v>550</v>
       </c>
     </row>
     <row r="55">
@@ -3605,16 +3596,16 @@
         <v>46196</v>
       </c>
       <c r="C55" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="D55" s="7">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F55" s="8">
-        <v>-9</v>
+        <v>-2</v>
       </c>
       <c r="G55" s="8">
         <v>-1</v>
@@ -3626,13 +3617,13 @@
         <v>38</v>
       </c>
       <c r="J55" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K55" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>23</v>
@@ -3650,10 +3641,10 @@
         <v>23</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S55" s="9">
-        <v>550</v>
+        <v>572.77</v>
       </c>
     </row>
     <row r="56">
@@ -3661,7 +3652,7 @@
         <v>22</v>
       </c>
       <c r="B56" s="7">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C56" s="7">
         <v>46195</v>
@@ -3676,31 +3667,31 @@
         <v>-2</v>
       </c>
       <c r="G56" s="8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>38</v>
       </c>
       <c r="I56" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="J56" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="K56" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L56" s="6" t="s">
+      <c r="M56" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="O56" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="M56" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N56" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O56" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>23</v>
@@ -3712,7 +3703,7 @@
         <v>36</v>
       </c>
       <c r="S56" s="9">
-        <v>572.77</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57">
@@ -3723,22 +3714,22 @@
         <v>46197</v>
       </c>
       <c r="C57" s="7">
-        <v>46195</v>
+        <v>46143</v>
       </c>
       <c r="D57" s="7">
-        <v>46195</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>23</v>
+        <v>46197</v>
+      </c>
+      <c r="E57" s="7">
+        <v>46185</v>
       </c>
       <c r="F57" s="8">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G57" s="8">
         <v>0</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="I57" s="6" t="s">
         <v>23</v>
@@ -3753,25 +3744,25 @@
         <v>99</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="N57" s="6" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q57" s="6" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S57" s="9">
-        <v>90</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="58">
@@ -3779,22 +3770,22 @@
         <v>22</v>
       </c>
       <c r="B58" s="7">
-        <v>46197</v>
+        <v>46202</v>
       </c>
       <c r="C58" s="7">
-        <v>46143</v>
+        <v>46174</v>
       </c>
       <c r="D58" s="7">
-        <v>46197</v>
+        <v>46218</v>
       </c>
       <c r="E58" s="7">
-        <v>46185</v>
+        <v>46190</v>
       </c>
       <c r="F58" s="8">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G58" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>23</v>
@@ -3803,34 +3794,34 @@
         <v>23</v>
       </c>
       <c r="J58" s="6" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="K58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>100</v>
+        <v>63</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q58" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R58" s="6" t="s">
         <v>36</v>
       </c>
       <c r="S58" s="9">
-        <v>4400</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
@@ -3841,16 +3832,16 @@
         <v>46202</v>
       </c>
       <c r="C59" s="7">
-        <v>46174</v>
+        <v>46143</v>
       </c>
       <c r="D59" s="7">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="E59" s="7">
-        <v>46190</v>
+        <v>46153</v>
       </c>
       <c r="F59" s="8">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="G59" s="8">
         <v>5</v>
@@ -3862,25 +3853,25 @@
         <v>23</v>
       </c>
       <c r="J59" s="6" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="K59" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="N59" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="Q59" s="6" t="s">
         <v>29</v>
@@ -3903,43 +3894,43 @@
         <v>46143</v>
       </c>
       <c r="D60" s="7">
-        <v>46202</v>
+        <v>46188</v>
       </c>
       <c r="E60" s="7">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="F60" s="8">
-        <v>5</v>
+        <v>-9</v>
       </c>
       <c r="G60" s="8">
         <v>5</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="I60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="Q60" s="6" t="s">
         <v>29</v>
@@ -3948,7 +3939,7 @@
         <v>36</v>
       </c>
       <c r="S60" s="9">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61">
@@ -3962,40 +3953,40 @@
         <v>46143</v>
       </c>
       <c r="D61" s="7">
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="E61" s="7">
         <v>46167</v>
       </c>
       <c r="F61" s="8">
-        <v>-9</v>
+        <v>5</v>
       </c>
       <c r="G61" s="8">
         <v>5</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="I61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="J61" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N61" s="6" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>23</v>
@@ -4018,13 +4009,13 @@
         <v>46202</v>
       </c>
       <c r="C62" s="7">
-        <v>46143</v>
+        <v>46188</v>
       </c>
       <c r="D62" s="7">
         <v>46202</v>
       </c>
       <c r="E62" s="7">
-        <v>46167</v>
+        <v>46188</v>
       </c>
       <c r="F62" s="8">
         <v>5</v>
@@ -4039,34 +4030,34 @@
         <v>23</v>
       </c>
       <c r="J62" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q62" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S62" s="9">
-        <v>100</v>
+        <v>116.66</v>
       </c>
     </row>
     <row r="63">
@@ -4077,13 +4068,13 @@
         <v>46202</v>
       </c>
       <c r="C63" s="7">
-        <v>46188</v>
+        <v>46082</v>
       </c>
       <c r="D63" s="7">
         <v>46202</v>
       </c>
       <c r="E63" s="7">
-        <v>46188</v>
+        <v>46097</v>
       </c>
       <c r="F63" s="8">
         <v>5</v>
@@ -4098,34 +4089,34 @@
         <v>23</v>
       </c>
       <c r="J63" s="6" t="s">
-        <v>105</v>
+        <v>25</v>
       </c>
       <c r="K63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N63" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q63" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="S63" s="9">
-        <v>116.66</v>
+        <v>146.55</v>
       </c>
     </row>
     <row r="64">
@@ -4136,13 +4127,13 @@
         <v>46202</v>
       </c>
       <c r="C64" s="7">
-        <v>46082</v>
+        <v>46202</v>
       </c>
       <c r="D64" s="7">
         <v>46202</v>
       </c>
       <c r="E64" s="7">
-        <v>46097</v>
+        <v>46169</v>
       </c>
       <c r="F64" s="8">
         <v>5</v>
@@ -4157,34 +4148,34 @@
         <v>23</v>
       </c>
       <c r="J64" s="6" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>23</v>
+        <v>104</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>23</v>
       </c>
       <c r="Q64" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S64" s="9">
-        <v>146.55</v>
+        <v>600</v>
       </c>
     </row>
     <row r="65">
@@ -4216,22 +4207,22 @@
         <v>23</v>
       </c>
       <c r="J65" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="K65" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L65" s="6" t="s">
-        <v>107</v>
-      </c>
       <c r="M65" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N65" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>23</v>
@@ -4275,22 +4266,22 @@
         <v>23</v>
       </c>
       <c r="J66" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="K66" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L66" s="6" t="s">
-        <v>109</v>
-      </c>
       <c r="M66" s="6" t="s">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>23</v>
@@ -4302,7 +4293,7 @@
         <v>36</v>
       </c>
       <c r="S66" s="9">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="67">
@@ -4334,22 +4325,22 @@
         <v>23</v>
       </c>
       <c r="J67" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="M67" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N67" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>23</v>
@@ -4393,22 +4384,22 @@
         <v>23</v>
       </c>
       <c r="J68" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="M68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>23</v>
@@ -4437,7 +4428,7 @@
         <v>46202</v>
       </c>
       <c r="E69" s="7">
-        <v>46169</v>
+        <v>46163</v>
       </c>
       <c r="F69" s="8">
         <v>5</v>
@@ -4452,22 +4443,22 @@
         <v>23</v>
       </c>
       <c r="J69" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="M69" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N69" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>23</v>
@@ -4496,7 +4487,7 @@
         <v>46202</v>
       </c>
       <c r="E70" s="7">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F70" s="8">
         <v>5</v>
@@ -4511,22 +4502,22 @@
         <v>23</v>
       </c>
       <c r="J70" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="M70" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>23</v>
@@ -4555,7 +4546,7 @@
         <v>46202</v>
       </c>
       <c r="E71" s="7">
-        <v>46164</v>
+        <v>46188</v>
       </c>
       <c r="F71" s="8">
         <v>5</v>
@@ -4570,22 +4561,22 @@
         <v>23</v>
       </c>
       <c r="J71" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="M71" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N71" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>23</v>
@@ -4594,10 +4585,10 @@
         <v>35</v>
       </c>
       <c r="R71" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S71" s="9">
-        <v>630</v>
+        <v>650</v>
       </c>
     </row>
     <row r="72">
@@ -4614,7 +4605,7 @@
         <v>46202</v>
       </c>
       <c r="E72" s="7">
-        <v>46188</v>
+        <v>46127</v>
       </c>
       <c r="F72" s="8">
         <v>5</v>
@@ -4629,22 +4620,22 @@
         <v>23</v>
       </c>
       <c r="J72" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="M72" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P72" s="6" t="s">
         <v>23</v>
@@ -4653,7 +4644,7 @@
         <v>35</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S72" s="9">
         <v>650</v>
@@ -4673,7 +4664,7 @@
         <v>46202</v>
       </c>
       <c r="E73" s="7">
-        <v>46127</v>
+        <v>46153</v>
       </c>
       <c r="F73" s="8">
         <v>5</v>
@@ -4688,22 +4679,22 @@
         <v>23</v>
       </c>
       <c r="J73" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="K73" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="K73" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L73" s="6" t="s">
-        <v>120</v>
-      </c>
       <c r="M73" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N73" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P73" s="6" t="s">
         <v>23</v>
@@ -4732,7 +4723,7 @@
         <v>46202</v>
       </c>
       <c r="E74" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="F74" s="8">
         <v>5</v>
@@ -4747,22 +4738,22 @@
         <v>23</v>
       </c>
       <c r="J74" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="K74" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L74" s="6" t="s">
-        <v>122</v>
-      </c>
       <c r="M74" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>23</v>
@@ -4791,7 +4782,7 @@
         <v>46202</v>
       </c>
       <c r="E75" s="7">
-        <v>46160</v>
+        <v>46182</v>
       </c>
       <c r="F75" s="8">
         <v>5</v>
@@ -4806,22 +4797,22 @@
         <v>23</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N75" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>23</v>
@@ -4833,7 +4824,7 @@
         <v>36</v>
       </c>
       <c r="S75" s="9">
-        <v>650</v>
+        <v>680</v>
       </c>
     </row>
     <row r="76">
@@ -4850,7 +4841,7 @@
         <v>46202</v>
       </c>
       <c r="E76" s="7">
-        <v>46167</v>
+        <v>46182</v>
       </c>
       <c r="F76" s="8">
         <v>5</v>
@@ -4865,22 +4856,22 @@
         <v>23</v>
       </c>
       <c r="J76" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>23</v>
@@ -4924,22 +4915,22 @@
         <v>23</v>
       </c>
       <c r="J77" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N77" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P77" s="6" t="s">
         <v>23</v>
@@ -4968,7 +4959,7 @@
         <v>46202</v>
       </c>
       <c r="E78" s="7">
-        <v>46182</v>
+        <v>46167</v>
       </c>
       <c r="F78" s="8">
         <v>5</v>
@@ -4983,22 +4974,22 @@
         <v>23</v>
       </c>
       <c r="J78" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="M78" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>23</v>
@@ -5027,7 +5018,7 @@
         <v>46202</v>
       </c>
       <c r="E79" s="7">
-        <v>46182</v>
+        <v>46164</v>
       </c>
       <c r="F79" s="8">
         <v>5</v>
@@ -5042,22 +5033,22 @@
         <v>23</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M79" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N79" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>23</v>
@@ -5066,7 +5057,7 @@
         <v>35</v>
       </c>
       <c r="R79" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S79" s="9">
         <v>680</v>
@@ -5086,7 +5077,7 @@
         <v>46202</v>
       </c>
       <c r="E80" s="7">
-        <v>46164</v>
+        <v>46170</v>
       </c>
       <c r="F80" s="8">
         <v>5</v>
@@ -5101,22 +5092,22 @@
         <v>23</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>23</v>
@@ -5125,10 +5116,10 @@
         <v>35</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S80" s="9">
-        <v>680</v>
+        <v>700</v>
       </c>
     </row>
     <row r="81">
@@ -5145,7 +5136,7 @@
         <v>46202</v>
       </c>
       <c r="E81" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F81" s="8">
         <v>5</v>
@@ -5160,22 +5151,22 @@
         <v>23</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N81" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P81" s="6" t="s">
         <v>23</v>
@@ -5184,7 +5175,7 @@
         <v>35</v>
       </c>
       <c r="R81" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S81" s="9">
         <v>700</v>
@@ -5192,7 +5183,7 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="B82" s="7">
         <v>46202</v>
@@ -5204,7 +5195,7 @@
         <v>46202</v>
       </c>
       <c r="E82" s="7">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="F82" s="8">
         <v>5</v>
@@ -5219,7 +5210,7 @@
         <v>23</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>23</v>
@@ -5231,10 +5222,10 @@
         <v>23</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>23</v>
@@ -5243,10 +5234,10 @@
         <v>35</v>
       </c>
       <c r="R82" s="6" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="S82" s="9">
-        <v>700</v>
+        <v>800</v>
       </c>
     </row>
     <row r="83">
@@ -5278,22 +5269,22 @@
         <v>23</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N83" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P83" s="6" t="s">
         <v>23</v>
@@ -5302,7 +5293,7 @@
         <v>35</v>
       </c>
       <c r="R83" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S83" s="9">
         <v>800</v>
@@ -5310,7 +5301,7 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="s">
-        <v>89</v>
+        <v>22</v>
       </c>
       <c r="B84" s="7">
         <v>46202</v>
@@ -5322,7 +5313,7 @@
         <v>46202</v>
       </c>
       <c r="E84" s="7">
-        <v>46182</v>
+        <v>46148</v>
       </c>
       <c r="F84" s="8">
         <v>5</v>
@@ -5337,22 +5328,22 @@
         <v>23</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="M84" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>23</v>
@@ -5361,10 +5352,10 @@
         <v>35</v>
       </c>
       <c r="R84" s="6" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="S84" s="9">
-        <v>800</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="85">
@@ -5408,10 +5399,10 @@
         <v>23</v>
       </c>
       <c r="N85" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P85" s="6" t="s">
         <v>138</v>
@@ -5420,7 +5411,7 @@
         <v>35</v>
       </c>
       <c r="R85" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="S85" s="9">
         <v>1200</v>
@@ -5440,7 +5431,7 @@
         <v>46202</v>
       </c>
       <c r="E86" s="7">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="F86" s="8">
         <v>5</v>
@@ -5455,116 +5446,57 @@
         <v>23</v>
       </c>
       <c r="J86" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="K86" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="K86" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L86" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="M86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>23</v>
+        <v>138</v>
       </c>
       <c r="Q86" s="6" t="s">
         <v>35</v>
       </c>
       <c r="R86" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="S86" s="9">
         <v>1200</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B87" s="7">
-        <v>46202</v>
-      </c>
-      <c r="C87" s="7">
-        <v>46202</v>
-      </c>
-      <c r="D87" s="7">
-        <v>46202</v>
-      </c>
-      <c r="E87" s="7">
-        <v>46160</v>
-      </c>
-      <c r="F87" s="8">
-        <v>5</v>
-      </c>
-      <c r="G87" s="8">
-        <v>5</v>
-      </c>
-      <c r="H87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="J87" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="K87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L87" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="M87" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N87" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="O87" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="P87" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q87" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="R87" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="S87" s="9">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="88" ht="23" customHeight="1">
-      <c r="A88" s="10"/>
-      <c r="B88" s="11"/>
-      <c r="C88" s="11"/>
-      <c r="D88" s="11"/>
-      <c r="E88" s="11"/>
-      <c r="F88" s="12"/>
-      <c r="G88" s="12"/>
-      <c r="H88" s="10"/>
-      <c r="I88" s="10"/>
-      <c r="J88" s="10"/>
-      <c r="K88" s="10"/>
-      <c r="L88" s="10"/>
-      <c r="M88" s="10"/>
-      <c r="N88" s="10"/>
-      <c r="O88" s="10"/>
-      <c r="P88" s="10"/>
-      <c r="Q88" s="10"/>
-      <c r="R88" s="10"/>
-      <c r="S88" s="13">
-        <f>SUM(S6:S87)</f>
+    <row r="87" ht="23" customHeight="1">
+      <c r="A87" s="10"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="11"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="12"/>
+      <c r="H87" s="10"/>
+      <c r="I87" s="10"/>
+      <c r="J87" s="10"/>
+      <c r="K87" s="10"/>
+      <c r="L87" s="10"/>
+      <c r="M87" s="10"/>
+      <c r="N87" s="10"/>
+      <c r="O87" s="10"/>
+      <c r="P87" s="10"/>
+      <c r="Q87" s="10"/>
+      <c r="R87" s="10"/>
+      <c r="S87" s="13">
+        <f>SUM(S6:S86)</f>
       </c>
     </row>
   </sheetData>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$87</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$86</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quarta-feira, 24 de junho de 2026 por KAROL MEDEIROS</t>
+    <t>Relatório exportado em quinta-feira, 25 de junho de 2026 por KAROL MEDEIROS</t>
   </si>
   <si>
     <t>Conta de Recebimento</t>
@@ -148,12 +148,12 @@
     <t>FA-11559</t>
   </si>
   <si>
+    <t>FA-11562</t>
+  </si>
+  <si>
     <t>VENCIDO ATÉ 30 DIAS</t>
   </si>
   <si>
-    <t>FA-11562</t>
-  </si>
-  <si>
     <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
   </si>
   <si>
@@ -244,13 +244,19 @@
     <t>FA-11791</t>
   </si>
   <si>
+    <t>FA-11728</t>
+  </si>
+  <si>
     <t>FA-11800</t>
   </si>
   <si>
     <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
   </si>
   <si>
-    <t>FA-11728</t>
+    <t>FA-11799</t>
+  </si>
+  <si>
+    <t>FELIPE DA SILVA</t>
   </si>
   <si>
     <t>FA-11850</t>
@@ -259,12 +265,6 @@
     <t>ANDRE CAVALCANTI DA FE</t>
   </si>
   <si>
-    <t>FA-11799</t>
-  </si>
-  <si>
-    <t>FELIPE DA SILVA</t>
-  </si>
-  <si>
     <t>FA-11695</t>
   </si>
   <si>
@@ -283,6 +283,15 @@
     <t>MAICON LOPES SILVA</t>
   </si>
   <si>
+    <t>FA-11605</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
     <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
   </si>
   <si>
@@ -292,15 +301,6 @@
     <t>ELIONILSON CORDEIRO BARBOSA</t>
   </si>
   <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11605</t>
-  </si>
-  <si>
-    <t>PEDRO GABRIEL FASANARO DE OLIVEIRA</t>
-  </si>
-  <si>
     <t>FA-11807</t>
   </si>
   <si>
@@ -319,60 +319,54 @@
     <t>OLIZIEL DA SILVA CARDOSO</t>
   </si>
   <si>
-    <t>FA-11672</t>
+    <t>FA-11843</t>
+  </si>
+  <si>
+    <t>SEGCOMP</t>
+  </si>
+  <si>
+    <t>SEGCOMP TECNOLOGIA LTDA</t>
+  </si>
+  <si>
+    <t>ND-11700</t>
+  </si>
+  <si>
+    <t>FA-11849</t>
+  </si>
+  <si>
+    <t>FA-11750</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11735</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11737</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11732</t>
+  </si>
+  <si>
+    <t>FA-11734</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11673</t>
   </si>
   <si>
     <t>RICARDO ARAUJO DE MIRANDA</t>
   </si>
   <si>
-    <t>HOJE</t>
-  </si>
-  <si>
-    <t>FA-11843</t>
-  </si>
-  <si>
-    <t>SEGCOMP</t>
-  </si>
-  <si>
-    <t>SEGCOMP TECNOLOGIA LTDA</t>
-  </si>
-  <si>
-    <t>ND-11700</t>
-  </si>
-  <si>
-    <t>FA-11849</t>
-  </si>
-  <si>
-    <t>FA-11750</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11735</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-11737</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11732</t>
-  </si>
-  <si>
-    <t>FA-11734</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11673</t>
-  </si>
-  <si>
     <t>FA-11688</t>
   </si>
   <si>
@@ -400,6 +394,9 @@
     <t>LUCA ZOLI</t>
   </si>
   <si>
+    <t>FA-11696</t>
+  </si>
+  <si>
     <t>FA-11827</t>
   </si>
   <si>
@@ -409,13 +406,13 @@
     <t>ANDERSON QUEIROZ PINHEIRO</t>
   </si>
   <si>
+    <t>FA-11681</t>
+  </si>
+  <si>
     <t>FA-11826</t>
   </si>
   <si>
-    <t>FA-11696</t>
-  </si>
-  <si>
-    <t>FA-11681</t>
+    <t>FA-11853</t>
   </si>
   <si>
     <t>FA-11766</t>
@@ -424,37 +421,34 @@
     <t>ANNY KATARINA ACIOLE DA SILVA</t>
   </si>
   <si>
-    <t>FA-11853</t>
-  </si>
-  <si>
     <t>FA-11828</t>
   </si>
   <si>
     <t>FA-11606</t>
   </si>
   <si>
+    <t>FA-11649</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11637</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
     <t>FA-11596</t>
   </si>
   <si>
     <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11649</t>
-  </si>
-  <si>
-    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-11637</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
   </si>
 </sst>
 </file>
@@ -597,7 +591,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S87"/>
+  <dimension ref="A1:S86"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1" style="1"/>
@@ -714,10 +708,10 @@
         <v>23</v>
       </c>
       <c r="F6" s="8">
-        <v>-72</v>
+        <v>-73</v>
       </c>
       <c r="G6" s="8">
-        <v>-63</v>
+        <v>-64</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>24</v>
@@ -773,10 +767,10 @@
         <v>46097</v>
       </c>
       <c r="F7" s="8">
-        <v>-58</v>
+        <v>-59</v>
       </c>
       <c r="G7" s="8">
-        <v>-58</v>
+        <v>-59</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>24</v>
@@ -832,10 +826,10 @@
         <v>23</v>
       </c>
       <c r="F8" s="8">
-        <v>-65</v>
+        <v>-66</v>
       </c>
       <c r="G8" s="8">
-        <v>-57</v>
+        <v>-58</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>24</v>
@@ -891,10 +885,10 @@
         <v>23</v>
       </c>
       <c r="F9" s="8">
-        <v>-86</v>
+        <v>-87</v>
       </c>
       <c r="G9" s="8">
-        <v>-57</v>
+        <v>-58</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>24</v>
@@ -950,10 +944,10 @@
         <v>23</v>
       </c>
       <c r="F10" s="8">
-        <v>-72</v>
+        <v>-73</v>
       </c>
       <c r="G10" s="8">
-        <v>-57</v>
+        <v>-58</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>24</v>
@@ -1009,10 +1003,10 @@
         <v>46097</v>
       </c>
       <c r="F11" s="8">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="G11" s="8">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>24</v>
@@ -1068,10 +1062,10 @@
         <v>46097</v>
       </c>
       <c r="F12" s="8">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="G12" s="8">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>24</v>
@@ -1127,10 +1121,10 @@
         <v>46141</v>
       </c>
       <c r="F13" s="8">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="G13" s="8">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>24</v>
@@ -1186,10 +1180,10 @@
         <v>46097</v>
       </c>
       <c r="F14" s="8">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="G14" s="8">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>24</v>
@@ -1245,10 +1239,10 @@
         <v>46141</v>
       </c>
       <c r="F15" s="8">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="G15" s="8">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>24</v>
@@ -1304,16 +1298,16 @@
         <v>46097</v>
       </c>
       <c r="F16" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="G16" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>25</v>
@@ -1363,19 +1357,19 @@
         <v>46141</v>
       </c>
       <c r="F17" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="G17" s="8">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="H17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="J17" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="K17" s="6" t="s">
         <v>23</v>
@@ -1422,16 +1416,16 @@
         <v>23</v>
       </c>
       <c r="F18" s="8">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="G18" s="8">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>23</v>
@@ -1481,16 +1475,16 @@
         <v>46097</v>
       </c>
       <c r="F19" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G19" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>25</v>
@@ -1540,16 +1534,16 @@
         <v>46141</v>
       </c>
       <c r="F20" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="G20" s="8">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>41</v>
@@ -1599,16 +1593,16 @@
         <v>46097</v>
       </c>
       <c r="F21" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G21" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>25</v>
@@ -1658,16 +1652,16 @@
         <v>46141</v>
       </c>
       <c r="F22" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G22" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>42</v>
@@ -1717,16 +1711,16 @@
         <v>46170</v>
       </c>
       <c r="F23" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G23" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>43</v>
@@ -1776,16 +1770,16 @@
         <v>46153</v>
       </c>
       <c r="F24" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G24" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>44</v>
@@ -1835,16 +1829,16 @@
         <v>46097</v>
       </c>
       <c r="F25" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G25" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J25" s="6" t="s">
         <v>25</v>
@@ -1894,16 +1888,16 @@
         <v>46141</v>
       </c>
       <c r="F26" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G26" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>47</v>
@@ -1953,16 +1947,16 @@
         <v>46169</v>
       </c>
       <c r="F27" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G27" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J27" s="6" t="s">
         <v>48</v>
@@ -2012,16 +2006,16 @@
         <v>46141</v>
       </c>
       <c r="F28" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G28" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>50</v>
@@ -2071,16 +2065,16 @@
         <v>46170</v>
       </c>
       <c r="F29" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G29" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J29" s="6" t="s">
         <v>52</v>
@@ -2130,16 +2124,16 @@
         <v>46164</v>
       </c>
       <c r="F30" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G30" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J30" s="6" t="s">
         <v>54</v>
@@ -2189,16 +2183,16 @@
         <v>46182</v>
       </c>
       <c r="F31" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G31" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>56</v>
@@ -2248,16 +2242,16 @@
         <v>23</v>
       </c>
       <c r="F32" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G32" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>58</v>
@@ -2307,16 +2301,16 @@
         <v>23</v>
       </c>
       <c r="F33" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G33" s="8">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J33" s="6" t="s">
         <v>60</v>
@@ -2366,16 +2360,16 @@
         <v>46153</v>
       </c>
       <c r="F34" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G34" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>44</v>
@@ -2425,16 +2419,16 @@
         <v>46190</v>
       </c>
       <c r="F35" s="8">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G35" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>23</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J35" s="6" t="s">
         <v>62</v>
@@ -2484,16 +2478,16 @@
         <v>46097</v>
       </c>
       <c r="F36" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G36" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>25</v>
@@ -2543,16 +2537,16 @@
         <v>23</v>
       </c>
       <c r="F37" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G37" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>64</v>
@@ -2602,16 +2596,16 @@
         <v>23</v>
       </c>
       <c r="F38" s="8">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="G38" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J38" s="6" t="s">
         <v>65</v>
@@ -2661,16 +2655,16 @@
         <v>23</v>
       </c>
       <c r="F39" s="8">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="G39" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J39" s="6" t="s">
         <v>67</v>
@@ -2720,16 +2714,16 @@
         <v>46170</v>
       </c>
       <c r="F40" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G40" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J40" s="6" t="s">
         <v>69</v>
@@ -2776,19 +2770,19 @@
         <v>46195</v>
       </c>
       <c r="E41" s="7">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="F41" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G41" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I41" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J41" s="6" t="s">
         <v>70</v>
@@ -2797,7 +2791,7 @@
         <v>23</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>23</v>
@@ -2835,28 +2829,28 @@
         <v>46195</v>
       </c>
       <c r="E42" s="7">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="F42" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G42" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J42" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>23</v>
@@ -2894,19 +2888,19 @@
         <v>46195</v>
       </c>
       <c r="E43" s="7">
-        <v>46188</v>
+        <v>46170</v>
       </c>
       <c r="F43" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G43" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I43" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J43" s="6" t="s">
         <v>73</v>
@@ -2933,7 +2927,7 @@
         <v>35</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S43" s="9">
         <v>650</v>
@@ -2953,19 +2947,19 @@
         <v>46195</v>
       </c>
       <c r="E44" s="7">
-        <v>46170</v>
+        <v>46188</v>
       </c>
       <c r="F44" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G44" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J44" s="6" t="s">
         <v>75</v>
@@ -2992,7 +2986,7 @@
         <v>35</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="S44" s="9">
         <v>650</v>
@@ -3015,16 +3009,16 @@
         <v>46167</v>
       </c>
       <c r="F45" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G45" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I45" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J45" s="6" t="s">
         <v>77</v>
@@ -3074,16 +3068,16 @@
         <v>46182</v>
       </c>
       <c r="F46" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G46" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>78</v>
@@ -3133,16 +3127,16 @@
         <v>46164</v>
       </c>
       <c r="F47" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G47" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I47" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J47" s="6" t="s">
         <v>79</v>
@@ -3192,16 +3186,16 @@
         <v>46170</v>
       </c>
       <c r="F48" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G48" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>80</v>
@@ -3251,16 +3245,16 @@
         <v>46188</v>
       </c>
       <c r="F49" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G49" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I49" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J49" s="6" t="s">
         <v>81</v>
@@ -3295,7 +3289,7 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
-        <v>83</v>
+        <v>22</v>
       </c>
       <c r="B50" s="7">
         <v>46195</v>
@@ -3307,28 +3301,28 @@
         <v>46195</v>
       </c>
       <c r="E50" s="7">
-        <v>46182</v>
+        <v>46148</v>
       </c>
       <c r="F50" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="G50" s="8">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J50" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="K50" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5